--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud2\Boulot 2026\Test site orientation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud2\Boulot 2026\Site orientation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F10C877-2398-4022-A31D-F1B5A07E2B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E101A4CE-1C60-4F2B-8BF3-9DB230FE87AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="781">
   <si>
     <t>Initiale NOM</t>
   </si>
@@ -2005,9 +2005,6 @@
     <t>Roman</t>
   </si>
   <si>
-    <t>Matteo</t>
-  </si>
-  <si>
     <t>Louis</t>
   </si>
   <si>
@@ -2215,27 +2212,178 @@
     <t>fonctionnaire</t>
   </si>
   <si>
-    <t>https://youtu.be/z25K_8EWzlU</t>
-  </si>
-  <si>
     <t>Lien_Video</t>
   </si>
   <si>
-    <t>https://github.com/eekez/chesnoy-orientation/blob/main/fiches/Cours_1_Suitesrevisions_Eleve.pdf</t>
-  </si>
-  <si>
     <t>Lien_Fiche_Poste</t>
+  </si>
+  <si>
+    <t>BOUTY</t>
+  </si>
+  <si>
+    <t>Aurore</t>
+  </si>
+  <si>
+    <t>CARTERON</t>
+  </si>
+  <si>
+    <t>DI PIPPO</t>
+  </si>
+  <si>
+    <t>HENRIET</t>
+  </si>
+  <si>
+    <t>HERING</t>
+  </si>
+  <si>
+    <t>NONET</t>
+  </si>
+  <si>
+    <t>PETIT</t>
+  </si>
+  <si>
+    <t>PREGERMAIN</t>
+  </si>
+  <si>
+    <t>DEVAUX</t>
+  </si>
+  <si>
+    <t>SILVERT</t>
+  </si>
+  <si>
+    <t>TRICHARD</t>
+  </si>
+  <si>
+    <t>RENOUX</t>
+  </si>
+  <si>
+    <t>LE PANS</t>
+  </si>
+  <si>
+    <t>BARBEAU</t>
+  </si>
+  <si>
+    <t>FOUSSEREAU</t>
+  </si>
+  <si>
+    <t>BOURGEOIS</t>
+  </si>
+  <si>
+    <t>SAILLAIRD</t>
+  </si>
+  <si>
+    <t>NICOLLEAU</t>
+  </si>
+  <si>
+    <t>JOLY</t>
+  </si>
+  <si>
+    <t>GODOT</t>
+  </si>
+  <si>
+    <t>AMARY</t>
+  </si>
+  <si>
+    <t>DOS SANTOS</t>
+  </si>
+  <si>
+    <t>ROUSTAN</t>
+  </si>
+  <si>
+    <t>VUILE</t>
+  </si>
+  <si>
+    <t>BABO</t>
+  </si>
+  <si>
+    <t>Mattéo</t>
+  </si>
+  <si>
+    <t>MATHELIN</t>
+  </si>
+  <si>
+    <t>AUCLER</t>
+  </si>
+  <si>
+    <t>COMBE</t>
+  </si>
+  <si>
+    <t>GARDES</t>
+  </si>
+  <si>
+    <t>RICHER</t>
+  </si>
+  <si>
+    <t>DUTILLEUL</t>
+  </si>
+  <si>
+    <t>BOUILLY</t>
+  </si>
+  <si>
+    <t>COURALET</t>
+  </si>
+  <si>
+    <t>HENRI</t>
+  </si>
+  <si>
+    <t>JACOB</t>
+  </si>
+  <si>
+    <t>KASPEREK</t>
+  </si>
+  <si>
+    <t>MANSART</t>
+  </si>
+  <si>
+    <t>MATIVET</t>
+  </si>
+  <si>
+    <t>THEBAULT</t>
+  </si>
+  <si>
+    <t>TREMBLAIS</t>
+  </si>
+  <si>
+    <t>LESIEUR</t>
+  </si>
+  <si>
+    <t>BATTAIT</t>
+  </si>
+  <si>
+    <t>MALARD</t>
+  </si>
+  <si>
+    <t>PHILIPPE</t>
+  </si>
+  <si>
+    <t>VERMET</t>
+  </si>
+  <si>
+    <t>AGOGUE</t>
+  </si>
+  <si>
+    <t>Arnaud</t>
+  </si>
+  <si>
+    <t>https://youtu.be/VHcNJpiErws</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2372,10 +2520,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2389,64 +2537,64 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2455,34 +2603,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2714,7 +2865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.42578125" customWidth="1"/>
@@ -2723,6 +2874,7 @@
     <col min="4" max="4" width="8.5703125" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
     <col min="6" max="6" width="44.85546875" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2745,18 +2897,18 @@
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -2774,10 +2926,13 @@
         <v>8</v>
       </c>
       <c r="G2" s="1"/>
+      <c r="H2" t="s">
+        <v>780</v>
+      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -2798,7 +2953,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>11</v>
@@ -2819,7 +2974,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>14</v>
@@ -2840,7 +2995,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>17</v>
@@ -2861,7 +3016,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>17</v>
@@ -2882,7 +3037,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>22</v>
@@ -2903,7 +3058,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>22</v>
@@ -2945,7 +3100,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="37" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>29</v>
@@ -2966,7 +3121,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="37" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>31</v>
@@ -2987,7 +3142,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="37" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>34</v>
@@ -3008,7 +3163,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="37" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>34</v>
@@ -3029,7 +3184,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="37" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>34</v>
@@ -3050,7 +3205,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="37" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>41</v>
@@ -3071,7 +3226,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>44</v>
@@ -3092,7 +3247,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="37" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>47</v>
@@ -3113,7 +3268,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="37" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>49</v>
@@ -3134,7 +3289,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="37" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>51</v>
@@ -3154,7 +3309,9 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
+      <c r="A21" s="39" t="s">
+        <v>745</v>
+      </c>
       <c r="B21" s="1" t="s">
         <v>11</v>
       </c>
@@ -3173,7 +3330,9 @@
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
+      <c r="A22" s="39" t="s">
+        <v>747</v>
+      </c>
       <c r="B22" s="1" t="s">
         <v>11</v>
       </c>
@@ -3192,7 +3351,9 @@
       <c r="G22" s="1"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
+      <c r="A23" s="39" t="s">
+        <v>733</v>
+      </c>
       <c r="B23" s="1" t="s">
         <v>14</v>
       </c>
@@ -3211,7 +3372,9 @@
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
+      <c r="A24" s="39" t="s">
+        <v>740</v>
+      </c>
       <c r="B24" s="1" t="s">
         <v>17</v>
       </c>
@@ -3230,7 +3393,9 @@
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
+      <c r="A25" s="39" t="s">
+        <v>734</v>
+      </c>
       <c r="B25" s="1" t="s">
         <v>17</v>
       </c>
@@ -3249,7 +3414,9 @@
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
+      <c r="A26" s="39" t="s">
+        <v>746</v>
+      </c>
       <c r="B26" s="1" t="s">
         <v>22</v>
       </c>
@@ -3268,7 +3435,9 @@
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
+      <c r="A27" s="39" t="s">
+        <v>735</v>
+      </c>
       <c r="B27" s="1" t="s">
         <v>29</v>
       </c>
@@ -3287,7 +3456,9 @@
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
+      <c r="A28" s="39" t="s">
+        <v>736</v>
+      </c>
       <c r="B28" s="1" t="s">
         <v>29</v>
       </c>
@@ -3323,7 +3494,9 @@
       <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
+      <c r="A30" s="39" t="s">
+        <v>750</v>
+      </c>
       <c r="B30" s="1" t="s">
         <v>31</v>
       </c>
@@ -3342,7 +3515,9 @@
       <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
+      <c r="A31" s="39" t="s">
+        <v>744</v>
+      </c>
       <c r="B31" s="1" t="s">
         <v>34</v>
       </c>
@@ -3361,7 +3536,9 @@
       <c r="G31" s="1"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
+      <c r="A32" s="39" t="s">
+        <v>749</v>
+      </c>
       <c r="B32" s="1" t="s">
         <v>67</v>
       </c>
@@ -3380,7 +3557,9 @@
       <c r="G32" s="1"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
+      <c r="A33" s="39" t="s">
+        <v>737</v>
+      </c>
       <c r="B33" s="1" t="s">
         <v>67</v>
       </c>
@@ -3418,7 +3597,9 @@
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
+      <c r="A35" s="39" t="s">
+        <v>738</v>
+      </c>
       <c r="B35" s="1" t="s">
         <v>44</v>
       </c>
@@ -3437,7 +3618,9 @@
       <c r="G35" s="1"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
+      <c r="A36" s="39" t="s">
+        <v>739</v>
+      </c>
       <c r="B36" s="1" t="s">
         <v>44</v>
       </c>
@@ -3456,7 +3639,9 @@
       <c r="G36" s="1"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
+      <c r="A37" s="39" t="s">
+        <v>743</v>
+      </c>
       <c r="B37" s="1" t="s">
         <v>73</v>
       </c>
@@ -3475,7 +3660,9 @@
       <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
+      <c r="A38" s="39" t="s">
+        <v>748</v>
+      </c>
       <c r="B38" s="1" t="s">
         <v>47</v>
       </c>
@@ -3494,7 +3681,9 @@
       <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
+      <c r="A39" s="39" t="s">
+        <v>741</v>
+      </c>
       <c r="B39" s="1" t="s">
         <v>47</v>
       </c>
@@ -3513,7 +3702,9 @@
       <c r="G39" s="1"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
+      <c r="A40" s="39" t="s">
+        <v>742</v>
+      </c>
       <c r="B40" s="1" t="s">
         <v>76</v>
       </c>
@@ -3532,7 +3723,9 @@
       <c r="G40" s="1"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="1"/>
+      <c r="A41" s="39" t="s">
+        <v>774</v>
+      </c>
       <c r="B41" s="29" t="s">
         <v>11</v>
       </c>
@@ -3551,7 +3744,9 @@
       <c r="G41" s="35"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="1"/>
+      <c r="A42" s="39" t="s">
+        <v>764</v>
+      </c>
       <c r="B42" s="29" t="s">
         <v>11</v>
       </c>
@@ -3570,12 +3765,14 @@
       <c r="G42" s="35"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
+      <c r="A43" s="39" t="s">
+        <v>765</v>
+      </c>
       <c r="B43" s="29" t="s">
         <v>14</v>
       </c>
       <c r="C43" s="34" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D43" s="29">
         <v>2023</v>
@@ -3587,7 +3784,7 @@
         <v>25</v>
       </c>
       <c r="G43" s="35" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -3596,7 +3793,7 @@
         <v>17</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D44" s="29">
         <v>2023</v>
@@ -3608,7 +3805,7 @@
         <v>25</v>
       </c>
       <c r="G44" s="35" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3617,7 +3814,7 @@
         <v>26</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D45" s="29">
         <v>2023</v>
@@ -3629,7 +3826,7 @@
         <v>25</v>
       </c>
       <c r="G45" s="35" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3638,7 +3835,7 @@
         <v>26</v>
       </c>
       <c r="C46" s="34" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D46" s="29">
         <v>2023</v>
@@ -3652,12 +3849,14 @@
       <c r="G46" s="35"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="1"/>
+      <c r="A47" s="39" t="s">
+        <v>766</v>
+      </c>
       <c r="B47" s="29" t="s">
         <v>29</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D47" s="29">
         <v>2023</v>
@@ -3666,12 +3865,14 @@
         <v>7</v>
       </c>
       <c r="F47" s="35" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="G47" s="35"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="1"/>
+      <c r="A48" s="39" t="s">
+        <v>767</v>
+      </c>
       <c r="B48" s="29" t="s">
         <v>31</v>
       </c>
@@ -3690,9 +3891,11 @@
       <c r="G48" s="35"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="1"/>
+      <c r="A49" s="39" t="s">
+        <v>768</v>
+      </c>
       <c r="B49" s="29" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C49" s="34" t="s">
         <v>477</v>
@@ -3709,12 +3912,14 @@
       <c r="G49" s="35"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
+      <c r="A50" s="39" t="s">
+        <v>773</v>
+      </c>
       <c r="B50" s="29" t="s">
         <v>34</v>
       </c>
       <c r="C50" s="34" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D50" s="29">
         <v>2023</v>
@@ -3728,12 +3933,14 @@
       <c r="G50" s="35"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="1"/>
+      <c r="A51" s="39" t="s">
+        <v>775</v>
+      </c>
       <c r="B51" s="29" t="s">
         <v>41</v>
       </c>
       <c r="C51" s="34" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D51" s="29">
         <v>2023</v>
@@ -3742,17 +3949,19 @@
         <v>7</v>
       </c>
       <c r="F51" s="35" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="G51" s="35"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="1"/>
+      <c r="A52" s="39" t="s">
+        <v>769</v>
+      </c>
       <c r="B52" s="29" t="s">
         <v>41</v>
       </c>
       <c r="C52" s="34" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D52" s="29">
         <v>2023</v>
@@ -3766,12 +3975,14 @@
       <c r="G52" s="35"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="1"/>
+      <c r="A53" s="39" t="s">
+        <v>770</v>
+      </c>
       <c r="B53" s="29" t="s">
         <v>41</v>
       </c>
       <c r="C53" s="34" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D53" s="29">
         <v>2023</v>
@@ -3785,12 +3996,14 @@
       <c r="G53" s="35"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="1"/>
+      <c r="A54" s="39" t="s">
+        <v>776</v>
+      </c>
       <c r="B54" s="29" t="s">
         <v>44</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D54" s="29">
         <v>2023</v>
@@ -3804,7 +4017,9 @@
       <c r="G54" s="35"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="1"/>
+      <c r="A55" s="39" t="s">
+        <v>771</v>
+      </c>
       <c r="B55" s="29" t="s">
         <v>76</v>
       </c>
@@ -3823,7 +4038,9 @@
       <c r="G55" s="35"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="1"/>
+      <c r="A56" s="39" t="s">
+        <v>772</v>
+      </c>
       <c r="B56" s="29" t="s">
         <v>76</v>
       </c>
@@ -3842,7 +4059,9 @@
       <c r="G56" s="35"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="1"/>
+      <c r="A57" s="39" t="s">
+        <v>777</v>
+      </c>
       <c r="B57" s="29" t="s">
         <v>49</v>
       </c>
@@ -3861,7 +4080,9 @@
       <c r="G57" s="35"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="1"/>
+      <c r="A58" s="39" t="s">
+        <v>752</v>
+      </c>
       <c r="B58" s="35" t="s">
         <v>5</v>
       </c>
@@ -3880,7 +4101,9 @@
       <c r="G58" s="35"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="1"/>
+      <c r="A59" s="39" t="s">
+        <v>759</v>
+      </c>
       <c r="B59" s="35" t="s">
         <v>5</v>
       </c>
@@ -3894,12 +4117,14 @@
         <v>7</v>
       </c>
       <c r="F59" s="35" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="G59" s="35"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="1"/>
+      <c r="A60" s="39" t="s">
+        <v>756</v>
+      </c>
       <c r="B60" s="35" t="s">
         <v>11</v>
       </c>
@@ -3918,7 +4143,9 @@
       <c r="G60" s="35"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="1"/>
+      <c r="A61" s="39" t="s">
+        <v>760</v>
+      </c>
       <c r="B61" s="35" t="s">
         <v>14</v>
       </c>
@@ -3937,7 +4164,9 @@
       <c r="G61" s="35"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="1"/>
+      <c r="A62" s="39" t="s">
+        <v>753</v>
+      </c>
       <c r="B62" s="35" t="s">
         <v>656</v>
       </c>
@@ -3956,7 +4185,9 @@
       <c r="G62" s="35"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="1"/>
+      <c r="A63" s="39" t="s">
+        <v>763</v>
+      </c>
       <c r="B63" s="35" t="s">
         <v>17</v>
       </c>
@@ -3975,7 +4206,9 @@
       <c r="G63" s="35"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="1"/>
+      <c r="A64" s="39" t="s">
+        <v>761</v>
+      </c>
       <c r="B64" s="35" t="s">
         <v>26</v>
       </c>
@@ -3992,11 +4225,13 @@
         <v>25</v>
       </c>
       <c r="G64" s="35" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="1"/>
+      <c r="A65" s="39" t="s">
+        <v>751</v>
+      </c>
       <c r="B65" s="35" t="s">
         <v>26</v>
       </c>
@@ -4015,12 +4250,14 @@
       <c r="G65" s="29"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="1"/>
+      <c r="A66" s="39" t="s">
+        <v>758</v>
+      </c>
       <c r="B66" s="35" t="s">
         <v>41</v>
       </c>
       <c r="C66" s="35" t="s">
-        <v>660</v>
+        <v>757</v>
       </c>
       <c r="D66" s="29">
         <v>2022</v>
@@ -4032,11 +4269,13 @@
         <v>25</v>
       </c>
       <c r="G66" s="35" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="1"/>
+      <c r="A67" s="39" t="s">
+        <v>762</v>
+      </c>
       <c r="B67" s="35" t="s">
         <v>73</v>
       </c>
@@ -4055,12 +4294,14 @@
       <c r="G67" s="35"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="1"/>
+      <c r="A68" s="39" t="s">
+        <v>754</v>
+      </c>
       <c r="B68" s="35" t="s">
         <v>73</v>
       </c>
       <c r="C68" s="35" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D68" s="29">
         <v>2022</v>
@@ -4074,7 +4315,9 @@
       <c r="G68" s="35"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="1"/>
+      <c r="A69" s="39" t="s">
+        <v>755</v>
+      </c>
       <c r="B69" s="35" t="s">
         <v>49</v>
       </c>
@@ -4094,14 +4337,14 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="35" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B70" s="1" t="str">
         <f>LEFT(A70)</f>
         <v>A</v>
       </c>
       <c r="C70" s="35" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D70" s="29">
         <v>2021</v>
@@ -4116,14 +4359,14 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="35" t="s">
+        <v>663</v>
+      </c>
+      <c r="B71" s="1" t="str">
+        <f t="shared" ref="B71:B100" si="0">LEFT(A71)</f>
+        <v>B</v>
+      </c>
+      <c r="C71" s="35" t="s">
         <v>664</v>
-      </c>
-      <c r="B71" s="1" t="str">
-        <f t="shared" ref="B71:B86" si="0">LEFT(A71)</f>
-        <v>B</v>
-      </c>
-      <c r="C71" s="35" t="s">
-        <v>665</v>
       </c>
       <c r="D71" s="29">
         <v>2021</v>
@@ -4132,20 +4375,20 @@
         <v>7</v>
       </c>
       <c r="F71" s="35" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="G71" s="1"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="35" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B72" s="1" t="str">
         <f t="shared" si="0"/>
         <v>B</v>
       </c>
       <c r="C72" s="35" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D72" s="29">
         <v>2021</v>
@@ -4154,20 +4397,20 @@
         <v>7</v>
       </c>
       <c r="F72" s="35" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G72" s="1"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="35" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B73" s="1" t="str">
         <f t="shared" si="0"/>
         <v>C</v>
       </c>
       <c r="C73" s="35" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D73" s="29">
         <v>2021</v>
@@ -4182,7 +4425,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="35" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B74" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4204,14 +4447,14 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="35" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B75" s="1" t="str">
         <f t="shared" si="0"/>
         <v>C</v>
       </c>
       <c r="C75" s="35" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D75" s="29">
         <v>2021</v>
@@ -4226,14 +4469,14 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="35" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B76" s="1" t="str">
         <f t="shared" si="0"/>
         <v>C</v>
       </c>
       <c r="C76" s="35" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D76" s="29">
         <v>2021</v>
@@ -4248,14 +4491,14 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="35" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B77" s="1" t="str">
         <f t="shared" si="0"/>
         <v>E</v>
       </c>
       <c r="C77" s="35" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D77" s="29">
         <v>2021</v>
@@ -4270,7 +4513,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="35" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B78" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4292,7 +4535,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="35" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B79" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4314,14 +4557,14 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="35" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B80" s="1" t="str">
         <f t="shared" si="0"/>
         <v>L</v>
       </c>
       <c r="C80" s="35" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D80" s="29">
         <v>2021</v>
@@ -4336,14 +4579,14 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="35" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B81" s="1" t="str">
         <f t="shared" si="0"/>
         <v>M</v>
       </c>
       <c r="C81" s="35" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D81" s="29">
         <v>2021</v>
@@ -4358,7 +4601,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="35" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B82" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4380,14 +4623,14 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="35" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B83" s="1" t="str">
         <f t="shared" si="0"/>
         <v>N</v>
       </c>
       <c r="C83" s="35" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D83" s="29">
         <v>2021</v>
@@ -4402,14 +4645,14 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="35" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B84" s="1" t="str">
         <f t="shared" si="0"/>
         <v>P</v>
       </c>
       <c r="C84" s="35" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D84" s="29">
         <v>2021</v>
@@ -4424,7 +4667,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="35" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B85" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4446,14 +4689,14 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="35" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B86" s="1" t="str">
         <f t="shared" si="0"/>
         <v>R</v>
       </c>
       <c r="C86" s="35" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D86" s="29">
         <v>2021</v>
@@ -4466,9 +4709,166 @@
       </c>
       <c r="G86" s="1"/>
     </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="35" t="s">
+        <v>731</v>
+      </c>
+      <c r="B87" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
+      <c r="C87" s="35" t="s">
+        <v>732</v>
+      </c>
+      <c r="D87" s="29">
+        <v>2020</v>
+      </c>
+      <c r="E87" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F87" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="35" t="s">
+        <v>778</v>
+      </c>
+      <c r="B88" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>A</v>
+      </c>
+      <c r="C88" s="35" t="s">
+        <v>779</v>
+      </c>
+      <c r="D88" s="29">
+        <v>2020</v>
+      </c>
+      <c r="E88" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F88" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="35"/>
+      <c r="B89" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E89" s="29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="35"/>
+      <c r="B90" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E90" s="29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="35"/>
+      <c r="B91" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E91" s="29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="35"/>
+      <c r="B92" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E92" s="29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="35"/>
+      <c r="B93" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E93" s="29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="35"/>
+      <c r="B94" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E94" s="29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="35"/>
+      <c r="B95" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E95" s="29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="35"/>
+      <c r="B96" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E96" s="29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="35"/>
+      <c r="B97" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E97" s="29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="35"/>
+      <c r="B98" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E98" s="29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B99" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E99" s="29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B100" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="12">
@@ -4582,10 +4982,10 @@
         <v>4</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="I1" s="38" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -4606,13 +5006,7 @@
         <v>197</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>707</v>
-      </c>
-      <c r="H2" t="s">
-        <v>730</v>
-      </c>
-      <c r="I2" t="s">
-        <v>732</v>
+        <v>706</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -4633,7 +5027,7 @@
         <v>197</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -4675,7 +5069,7 @@
         <v>197</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -5284,7 +5678,7 @@
         <v>197</v>
       </c>
       <c r="F34" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -5326,7 +5720,7 @@
         <v>197</v>
       </c>
       <c r="F36" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -5431,7 +5825,7 @@
         <v>197</v>
       </c>
       <c r="F41" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -5452,7 +5846,7 @@
         <v>197</v>
       </c>
       <c r="F42" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -5851,7 +6245,7 @@
         <v>197</v>
       </c>
       <c r="F61" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -5977,7 +6371,7 @@
         <v>197</v>
       </c>
       <c r="F67" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -6019,7 +6413,7 @@
         <v>197</v>
       </c>
       <c r="F69" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -6418,7 +6812,7 @@
         <v>197</v>
       </c>
       <c r="F88" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -6460,7 +6854,7 @@
         <v>197</v>
       </c>
       <c r="F90" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -6963,7 +7357,7 @@
         <v>197</v>
       </c>
       <c r="F114" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -6984,7 +7378,7 @@
         <v>197</v>
       </c>
       <c r="F115" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -7240,7 +7634,7 @@
     </row>
     <row r="7" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>84</v>
@@ -9309,7 +9703,7 @@
     </row>
     <row r="69" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A69" s="31" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>147</v>
@@ -9333,18 +9727,18 @@
         <v>91</v>
       </c>
       <c r="I69" s="14" t="s">
+        <v>702</v>
+      </c>
+      <c r="J69" s="32" t="s">
         <v>703</v>
       </c>
-      <c r="J69" s="32" t="s">
+      <c r="K69" s="3" t="s">
         <v>704</v>
-      </c>
-      <c r="K69" s="3" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A70" s="31" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>84</v>
@@ -9371,10 +9765,10 @@
         <v>108</v>
       </c>
       <c r="J70" s="33" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
   </sheetData>

--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud2\Boulot 2026\Site orientation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E101A4CE-1C60-4F2B-8BF3-9DB230FE87AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECFB3C63-19A8-4639-8B0F-3A307F578077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2926,9 +2926,6 @@
         <v>8</v>
       </c>
       <c r="G2" s="1"/>
-      <c r="H2" t="s">
-        <v>780</v>
-      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -3224,7 +3221,7 @@
       </c>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
         <v>724</v>
       </c>
@@ -3245,7 +3242,7 @@
       </c>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="37" t="s">
         <v>725</v>
       </c>
@@ -3266,7 +3263,7 @@
       </c>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="37" t="s">
         <v>726</v>
       </c>
@@ -3287,7 +3284,7 @@
       </c>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="37" t="s">
         <v>727</v>
       </c>
@@ -3308,7 +3305,7 @@
       </c>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="39" t="s">
         <v>745</v>
       </c>
@@ -3329,7 +3326,7 @@
       </c>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="39" t="s">
         <v>747</v>
       </c>
@@ -3350,7 +3347,7 @@
       </c>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="39" t="s">
         <v>733</v>
       </c>
@@ -3371,7 +3368,7 @@
       </c>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="39" t="s">
         <v>740</v>
       </c>
@@ -3392,7 +3389,7 @@
       </c>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="39" t="s">
         <v>734</v>
       </c>
@@ -3413,7 +3410,7 @@
       </c>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="39" t="s">
         <v>746</v>
       </c>
@@ -3434,7 +3431,7 @@
       </c>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="39" t="s">
         <v>735</v>
       </c>
@@ -3455,7 +3452,7 @@
       </c>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="39" t="s">
         <v>736</v>
       </c>
@@ -3476,7 +3473,7 @@
       </c>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
         <v>29</v>
@@ -3493,7 +3490,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="39" t="s">
         <v>750</v>
       </c>
@@ -3514,7 +3511,7 @@
       </c>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="39" t="s">
         <v>744</v>
       </c>
@@ -3535,7 +3532,7 @@
       </c>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="39" t="s">
         <v>749</v>
       </c>
@@ -3555,6 +3552,9 @@
         <v>36</v>
       </c>
       <c r="G32" s="1"/>
+      <c r="H32" t="s">
+        <v>780</v>
+      </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="39" t="s">
@@ -4942,7 +4942,7 @@
           <x14:formula1>
             <xm:f>Ecoles!$A$2:$A124</xm:f>
           </x14:formula1>
-          <xm:sqref>F19:F22 F24:F25 F27:F34 F36:F40 F87:F387</xm:sqref>
+          <xm:sqref>F19:F22 F87:F387 F36:F40 F27:F34 F24:F25</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud2\Boulot 2026\Site orientation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECFB3C63-19A8-4639-8B0F-3A307F578077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375340CB-B739-48A3-A591-F448C92A9160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud2\Boulot 2026\Site orientation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud4\Boulot 2026\Site orientation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375340CB-B739-48A3-A591-F448C92A9160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCAA2C1-B451-4272-82FA-17F4E4328B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elèves_BCPST" sheetId="1" r:id="rId1"/>
@@ -19,11 +19,22 @@
     <sheet name="Listes validation" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="781">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="782">
   <si>
     <t>Initiale NOM</t>
   </si>
@@ -2366,13 +2377,16 @@
   </si>
   <si>
     <t>https://youtu.be/VHcNJpiErws</t>
+  </si>
+  <si>
+    <t>https://youtu.be/kYzrs1HNg9k</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2866,18 +2880,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I100"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="27.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="44.85546875" customWidth="1"/>
+    <col min="6" max="6" width="44.88671875" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="36" t="s">
         <v>77</v>
       </c>
@@ -2906,7 +2920,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>710</v>
       </c>
@@ -2927,7 +2941,7 @@
       </c>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>711</v>
       </c>
@@ -2948,7 +2962,7 @@
       </c>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>712</v>
       </c>
@@ -2969,7 +2983,7 @@
       </c>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>713</v>
       </c>
@@ -2990,7 +3004,7 @@
       </c>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>714</v>
       </c>
@@ -3011,7 +3025,7 @@
       </c>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>715</v>
       </c>
@@ -3032,7 +3046,7 @@
       </c>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9">
       <c r="A8" s="37" t="s">
         <v>716</v>
       </c>
@@ -3053,7 +3067,7 @@
       </c>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9">
       <c r="A9" s="37" t="s">
         <v>717</v>
       </c>
@@ -3074,7 +3088,7 @@
       </c>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" s="37" t="s">
         <v>252</v>
       </c>
@@ -3095,7 +3109,7 @@
       </c>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="A11" s="37" t="s">
         <v>718</v>
       </c>
@@ -3116,7 +3130,7 @@
       </c>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="A12" s="37" t="s">
         <v>719</v>
       </c>
@@ -3137,7 +3151,7 @@
       </c>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="A13" s="37" t="s">
         <v>720</v>
       </c>
@@ -3157,8 +3171,11 @@
         <v>36</v>
       </c>
       <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H13" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="37" t="s">
         <v>721</v>
       </c>
@@ -3179,7 +3196,7 @@
       </c>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15" s="37" t="s">
         <v>722</v>
       </c>
@@ -3200,7 +3217,7 @@
       </c>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9">
       <c r="A16" s="37" t="s">
         <v>723</v>
       </c>
@@ -3221,7 +3238,7 @@
       </c>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8">
       <c r="A17" s="37" t="s">
         <v>724</v>
       </c>
@@ -3242,7 +3259,7 @@
       </c>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8">
       <c r="A18" s="37" t="s">
         <v>725</v>
       </c>
@@ -3263,7 +3280,7 @@
       </c>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="A19" s="37" t="s">
         <v>726</v>
       </c>
@@ -3284,7 +3301,7 @@
       </c>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="37" t="s">
         <v>727</v>
       </c>
@@ -3305,7 +3322,7 @@
       </c>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="39" t="s">
         <v>745</v>
       </c>
@@ -3326,7 +3343,7 @@
       </c>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" s="39" t="s">
         <v>747</v>
       </c>
@@ -3347,7 +3364,7 @@
       </c>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" s="39" t="s">
         <v>733</v>
       </c>
@@ -3368,7 +3385,7 @@
       </c>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8">
       <c r="A24" s="39" t="s">
         <v>740</v>
       </c>
@@ -3389,7 +3406,7 @@
       </c>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" s="39" t="s">
         <v>734</v>
       </c>
@@ -3410,7 +3427,7 @@
       </c>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" s="39" t="s">
         <v>746</v>
       </c>
@@ -3431,7 +3448,7 @@
       </c>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" s="39" t="s">
         <v>735</v>
       </c>
@@ -3452,7 +3469,7 @@
       </c>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" s="39" t="s">
         <v>736</v>
       </c>
@@ -3473,7 +3490,7 @@
       </c>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
         <v>29</v>
@@ -3490,7 +3507,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8">
       <c r="A30" s="39" t="s">
         <v>750</v>
       </c>
@@ -3511,7 +3528,7 @@
       </c>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8">
       <c r="A31" s="39" t="s">
         <v>744</v>
       </c>
@@ -3532,7 +3549,7 @@
       </c>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8">
       <c r="A32" s="39" t="s">
         <v>749</v>
       </c>
@@ -3556,7 +3573,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7">
       <c r="A33" s="39" t="s">
         <v>737</v>
       </c>
@@ -3577,7 +3594,7 @@
       </c>
       <c r="G33" s="1"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
         <v>67</v>
@@ -3596,7 +3613,7 @@
       </c>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7">
       <c r="A35" s="39" t="s">
         <v>738</v>
       </c>
@@ -3617,7 +3634,7 @@
       </c>
       <c r="G35" s="1"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7">
       <c r="A36" s="39" t="s">
         <v>739</v>
       </c>
@@ -3638,7 +3655,7 @@
       </c>
       <c r="G36" s="1"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7">
       <c r="A37" s="39" t="s">
         <v>743</v>
       </c>
@@ -3659,7 +3676,7 @@
       </c>
       <c r="G37" s="1"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7">
       <c r="A38" s="39" t="s">
         <v>748</v>
       </c>
@@ -3680,7 +3697,7 @@
       </c>
       <c r="G38" s="1"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7">
       <c r="A39" s="39" t="s">
         <v>741</v>
       </c>
@@ -3701,7 +3718,7 @@
       </c>
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7">
       <c r="A40" s="39" t="s">
         <v>742</v>
       </c>
@@ -3722,7 +3739,7 @@
       </c>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7">
       <c r="A41" s="39" t="s">
         <v>774</v>
       </c>
@@ -3743,7 +3760,7 @@
       </c>
       <c r="G41" s="35"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7">
       <c r="A42" s="39" t="s">
         <v>764</v>
       </c>
@@ -3764,7 +3781,7 @@
       </c>
       <c r="G42" s="35"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7">
       <c r="A43" s="39" t="s">
         <v>765</v>
       </c>
@@ -3787,7 +3804,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7">
       <c r="A44" s="1"/>
       <c r="B44" s="29" t="s">
         <v>17</v>
@@ -3808,7 +3825,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7">
       <c r="A45" s="1"/>
       <c r="B45" s="29" t="s">
         <v>26</v>
@@ -3829,7 +3846,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7">
       <c r="A46" s="1"/>
       <c r="B46" s="29" t="s">
         <v>26</v>
@@ -3848,7 +3865,7 @@
       </c>
       <c r="G46" s="35"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7">
       <c r="A47" s="39" t="s">
         <v>766</v>
       </c>
@@ -3869,7 +3886,7 @@
       </c>
       <c r="G47" s="35"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7">
       <c r="A48" s="39" t="s">
         <v>767</v>
       </c>
@@ -3890,7 +3907,7 @@
       </c>
       <c r="G48" s="35"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7">
       <c r="A49" s="39" t="s">
         <v>768</v>
       </c>
@@ -3911,7 +3928,7 @@
       </c>
       <c r="G49" s="35"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7">
       <c r="A50" s="39" t="s">
         <v>773</v>
       </c>
@@ -3932,7 +3949,7 @@
       </c>
       <c r="G50" s="35"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7">
       <c r="A51" s="39" t="s">
         <v>775</v>
       </c>
@@ -3953,7 +3970,7 @@
       </c>
       <c r="G51" s="35"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7">
       <c r="A52" s="39" t="s">
         <v>769</v>
       </c>
@@ -3974,7 +3991,7 @@
       </c>
       <c r="G52" s="35"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7">
       <c r="A53" s="39" t="s">
         <v>770</v>
       </c>
@@ -3995,7 +4012,7 @@
       </c>
       <c r="G53" s="35"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7">
       <c r="A54" s="39" t="s">
         <v>776</v>
       </c>
@@ -4016,7 +4033,7 @@
       </c>
       <c r="G54" s="35"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7">
       <c r="A55" s="39" t="s">
         <v>771</v>
       </c>
@@ -4037,7 +4054,7 @@
       </c>
       <c r="G55" s="35"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7">
       <c r="A56" s="39" t="s">
         <v>772</v>
       </c>
@@ -4058,7 +4075,7 @@
       </c>
       <c r="G56" s="35"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7">
       <c r="A57" s="39" t="s">
         <v>777</v>
       </c>
@@ -4079,7 +4096,7 @@
       </c>
       <c r="G57" s="35"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7">
       <c r="A58" s="39" t="s">
         <v>752</v>
       </c>
@@ -4100,7 +4117,7 @@
       </c>
       <c r="G58" s="35"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7">
       <c r="A59" s="39" t="s">
         <v>759</v>
       </c>
@@ -4121,7 +4138,7 @@
       </c>
       <c r="G59" s="35"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7">
       <c r="A60" s="39" t="s">
         <v>756</v>
       </c>
@@ -4142,7 +4159,7 @@
       </c>
       <c r="G60" s="35"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7">
       <c r="A61" s="39" t="s">
         <v>760</v>
       </c>
@@ -4163,7 +4180,7 @@
       </c>
       <c r="G61" s="35"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7">
       <c r="A62" s="39" t="s">
         <v>753</v>
       </c>
@@ -4184,7 +4201,7 @@
       </c>
       <c r="G62" s="35"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7">
       <c r="A63" s="39" t="s">
         <v>763</v>
       </c>
@@ -4205,7 +4222,7 @@
       </c>
       <c r="G63" s="35"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7">
       <c r="A64" s="39" t="s">
         <v>761</v>
       </c>
@@ -4228,7 +4245,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7">
       <c r="A65" s="39" t="s">
         <v>751</v>
       </c>
@@ -4249,7 +4266,7 @@
       </c>
       <c r="G65" s="29"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7">
       <c r="A66" s="39" t="s">
         <v>758</v>
       </c>
@@ -4272,7 +4289,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7">
       <c r="A67" s="39" t="s">
         <v>762</v>
       </c>
@@ -4293,7 +4310,7 @@
       </c>
       <c r="G67" s="35"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7">
       <c r="A68" s="39" t="s">
         <v>754</v>
       </c>
@@ -4314,7 +4331,7 @@
       </c>
       <c r="G68" s="35"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7">
       <c r="A69" s="39" t="s">
         <v>755</v>
       </c>
@@ -4335,7 +4352,7 @@
       </c>
       <c r="G69" s="35"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7">
       <c r="A70" s="35" t="s">
         <v>661</v>
       </c>
@@ -4357,7 +4374,7 @@
       </c>
       <c r="G70" s="1"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7">
       <c r="A71" s="35" t="s">
         <v>663</v>
       </c>
@@ -4379,7 +4396,7 @@
       </c>
       <c r="G71" s="1"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7">
       <c r="A72" s="35" t="s">
         <v>665</v>
       </c>
@@ -4401,7 +4418,7 @@
       </c>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7">
       <c r="A73" s="35" t="s">
         <v>668</v>
       </c>
@@ -4423,7 +4440,7 @@
       </c>
       <c r="G73" s="1"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7">
       <c r="A74" s="35" t="s">
         <v>670</v>
       </c>
@@ -4445,7 +4462,7 @@
       </c>
       <c r="G74" s="1"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7">
       <c r="A75" s="35" t="s">
         <v>671</v>
       </c>
@@ -4467,7 +4484,7 @@
       </c>
       <c r="G75" s="1"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7">
       <c r="A76" s="35" t="s">
         <v>673</v>
       </c>
@@ -4489,7 +4506,7 @@
       </c>
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7">
       <c r="A77" s="35" t="s">
         <v>675</v>
       </c>
@@ -4511,7 +4528,7 @@
       </c>
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7">
       <c r="A78" s="35" t="s">
         <v>677</v>
       </c>
@@ -4533,7 +4550,7 @@
       </c>
       <c r="G78" s="1"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7">
       <c r="A79" s="35" t="s">
         <v>678</v>
       </c>
@@ -4555,7 +4572,7 @@
       </c>
       <c r="G79" s="1"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7">
       <c r="A80" s="35" t="s">
         <v>679</v>
       </c>
@@ -4577,7 +4594,7 @@
       </c>
       <c r="G80" s="1"/>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7">
       <c r="A81" s="35" t="s">
         <v>681</v>
       </c>
@@ -4599,7 +4616,7 @@
       </c>
       <c r="G81" s="1"/>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7">
       <c r="A82" s="35" t="s">
         <v>683</v>
       </c>
@@ -4621,7 +4638,7 @@
       </c>
       <c r="G82" s="1"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7">
       <c r="A83" s="35" t="s">
         <v>684</v>
       </c>
@@ -4643,7 +4660,7 @@
       </c>
       <c r="G83" s="1"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7">
       <c r="A84" s="35" t="s">
         <v>686</v>
       </c>
@@ -4665,7 +4682,7 @@
       </c>
       <c r="G84" s="1"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7">
       <c r="A85" s="35" t="s">
         <v>688</v>
       </c>
@@ -4687,7 +4704,7 @@
       </c>
       <c r="G85" s="1"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7">
       <c r="A86" s="35" t="s">
         <v>689</v>
       </c>
@@ -4709,7 +4726,7 @@
       </c>
       <c r="G86" s="1"/>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7">
       <c r="A87" s="35" t="s">
         <v>731</v>
       </c>
@@ -4730,7 +4747,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7">
       <c r="A88" s="35" t="s">
         <v>778</v>
       </c>
@@ -4751,7 +4768,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7">
       <c r="A89" s="35"/>
       <c r="B89" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4761,7 +4778,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7">
       <c r="A90" s="35"/>
       <c r="B90" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4771,7 +4788,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7">
       <c r="A91" s="35"/>
       <c r="B91" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4781,7 +4798,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7">
       <c r="A92" s="35"/>
       <c r="B92" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4791,7 +4808,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7">
       <c r="A93" s="35"/>
       <c r="B93" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4801,7 +4818,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7">
       <c r="A94" s="35"/>
       <c r="B94" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4811,7 +4828,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7">
       <c r="A95" s="35"/>
       <c r="B95" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4821,7 +4838,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7">
       <c r="A96" s="35"/>
       <c r="B96" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4831,7 +4848,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5">
       <c r="A97" s="35"/>
       <c r="B97" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4841,7 +4858,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5">
       <c r="A98" s="35"/>
       <c r="B98" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4851,7 +4868,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5">
       <c r="B99" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4860,7 +4877,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5">
       <c r="B100" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4953,16 +4970,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7423C6-280D-4FEC-B3EE-2664E2210568}">
   <dimension ref="A1:I116"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" customWidth="1"/>
-    <col min="6" max="6" width="42.28515625" customWidth="1"/>
-    <col min="8" max="8" width="32.28515625" customWidth="1"/>
-    <col min="9" max="9" width="96.7109375" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" customWidth="1"/>
+    <col min="6" max="6" width="42.33203125" customWidth="1"/>
+    <col min="8" max="8" width="32.33203125" customWidth="1"/>
+    <col min="9" max="9" width="96.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>230</v>
       </c>
@@ -4988,7 +5005,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>231</v>
       </c>
@@ -5009,7 +5026,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>232</v>
       </c>
@@ -5030,7 +5047,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>233</v>
       </c>
@@ -5051,7 +5068,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>234</v>
       </c>
@@ -5072,7 +5089,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>235</v>
       </c>
@@ -5093,7 +5110,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>236</v>
       </c>
@@ -5114,7 +5131,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>237</v>
       </c>
@@ -5135,7 +5152,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>250</v>
       </c>
@@ -5156,7 +5173,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>252</v>
       </c>
@@ -5177,7 +5194,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>254</v>
       </c>
@@ -5198,7 +5215,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
         <v>238</v>
       </c>
@@ -5219,7 +5236,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
         <v>240</v>
       </c>
@@ -5240,7 +5257,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
         <v>242</v>
       </c>
@@ -5261,7 +5278,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
         <v>244</v>
       </c>
@@ -5282,7 +5299,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
         <v>246</v>
       </c>
@@ -5303,7 +5320,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
         <v>248</v>
       </c>
@@ -5324,7 +5341,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
         <v>264</v>
       </c>
@@ -5345,7 +5362,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>272</v>
       </c>
@@ -5366,7 +5383,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20" s="7" t="s">
         <v>282</v>
       </c>
@@ -5387,7 +5404,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
         <v>259</v>
       </c>
@@ -5408,7 +5425,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
         <v>261</v>
       </c>
@@ -5429,7 +5446,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>263</v>
       </c>
@@ -5450,7 +5467,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
         <v>265</v>
       </c>
@@ -5471,7 +5488,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>274</v>
       </c>
@@ -5492,7 +5509,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26" s="7" t="s">
         <v>283</v>
       </c>
@@ -5513,7 +5530,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27" s="7" t="s">
         <v>285</v>
       </c>
@@ -5534,7 +5551,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28" s="7" t="s">
         <v>289</v>
       </c>
@@ -5555,7 +5572,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29" s="7" t="s">
         <v>295</v>
       </c>
@@ -5576,7 +5593,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30" s="7" t="s">
         <v>287</v>
       </c>
@@ -5597,7 +5614,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31" s="7" t="s">
         <v>291</v>
       </c>
@@ -5618,7 +5635,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32" s="7" t="s">
         <v>293</v>
       </c>
@@ -5639,7 +5656,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6">
       <c r="A33" s="7" t="s">
         <v>297</v>
       </c>
@@ -5660,7 +5677,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6">
       <c r="A34" s="7" t="s">
         <v>304</v>
       </c>
@@ -5681,7 +5698,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6">
       <c r="A35" s="7" t="s">
         <v>306</v>
       </c>
@@ -5702,7 +5719,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6">
       <c r="A36" s="7" t="s">
         <v>308</v>
       </c>
@@ -5723,7 +5740,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6">
       <c r="A37" s="7" t="s">
         <v>310</v>
       </c>
@@ -5744,7 +5761,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6">
       <c r="A38" s="7" t="s">
         <v>312</v>
       </c>
@@ -5765,7 +5782,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>318</v>
       </c>
@@ -5786,7 +5803,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6">
       <c r="A40" s="7" t="s">
         <v>325</v>
       </c>
@@ -5807,7 +5824,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6">
       <c r="A41" s="7" t="s">
         <v>330</v>
       </c>
@@ -5828,7 +5845,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6">
       <c r="A42" s="7" t="s">
         <v>331</v>
       </c>
@@ -5849,7 +5866,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6">
       <c r="A43" s="7" t="s">
         <v>327</v>
       </c>
@@ -5870,7 +5887,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6">
       <c r="A44" s="7" t="s">
         <v>328</v>
       </c>
@@ -5891,7 +5908,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6">
       <c r="A45" s="7" t="s">
         <v>333</v>
       </c>
@@ -5912,7 +5929,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6">
       <c r="A46" s="7" t="s">
         <v>335</v>
       </c>
@@ -5933,7 +5950,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6">
       <c r="A47" s="7" t="s">
         <v>235</v>
       </c>
@@ -5954,7 +5971,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6">
       <c r="A48" s="7" t="s">
         <v>337</v>
       </c>
@@ -5975,7 +5992,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6">
       <c r="A49" s="7" t="s">
         <v>341</v>
       </c>
@@ -5996,7 +6013,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6">
       <c r="A50" s="7" t="s">
         <v>344</v>
       </c>
@@ -6017,7 +6034,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6">
       <c r="A51" s="7" t="s">
         <v>346</v>
       </c>
@@ -6038,7 +6055,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6">
       <c r="A52" s="7" t="s">
         <v>348</v>
       </c>
@@ -6059,7 +6076,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6">
       <c r="A53" s="7" t="s">
         <v>352</v>
       </c>
@@ -6080,7 +6097,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>378</v>
       </c>
@@ -6101,7 +6118,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6">
       <c r="A55" s="7" t="s">
         <v>339</v>
       </c>
@@ -6122,7 +6139,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6">
       <c r="A56" s="7" t="s">
         <v>343</v>
       </c>
@@ -6143,7 +6160,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6">
       <c r="A57" s="7" t="s">
         <v>350</v>
       </c>
@@ -6164,7 +6181,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>354</v>
       </c>
@@ -6185,7 +6202,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>356</v>
       </c>
@@ -6206,7 +6223,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>358</v>
       </c>
@@ -6227,7 +6244,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>360</v>
       </c>
@@ -6248,7 +6265,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>362</v>
       </c>
@@ -6269,7 +6286,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>363</v>
       </c>
@@ -6290,7 +6307,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>370</v>
       </c>
@@ -6311,7 +6328,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>372</v>
       </c>
@@ -6332,7 +6349,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>374</v>
       </c>
@@ -6353,7 +6370,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>375</v>
       </c>
@@ -6374,7 +6391,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>377</v>
       </c>
@@ -6395,7 +6412,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>380</v>
       </c>
@@ -6416,7 +6433,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>387</v>
       </c>
@@ -6437,7 +6454,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>389</v>
       </c>
@@ -6458,7 +6475,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
         <v>390</v>
       </c>
@@ -6479,7 +6496,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
         <v>391</v>
       </c>
@@ -6500,7 +6517,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>393</v>
       </c>
@@ -6521,7 +6538,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>395</v>
       </c>
@@ -6542,7 +6559,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>396</v>
       </c>
@@ -6563,7 +6580,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>398</v>
       </c>
@@ -6584,7 +6601,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>399</v>
       </c>
@@ -6605,7 +6622,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>401</v>
       </c>
@@ -6626,7 +6643,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
         <v>403</v>
       </c>
@@ -6647,7 +6664,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>405</v>
       </c>
@@ -6668,7 +6685,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>406</v>
       </c>
@@ -6689,7 +6706,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>408</v>
       </c>
@@ -6710,7 +6727,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>415</v>
       </c>
@@ -6731,7 +6748,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>417</v>
       </c>
@@ -6752,7 +6769,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
         <v>419</v>
       </c>
@@ -6773,7 +6790,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>421</v>
       </c>
@@ -6794,7 +6811,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
         <v>422</v>
       </c>
@@ -6815,7 +6832,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>423</v>
       </c>
@@ -6836,7 +6853,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>425</v>
       </c>
@@ -6857,7 +6874,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>427</v>
       </c>
@@ -6878,7 +6895,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>428</v>
       </c>
@@ -6899,7 +6916,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>430</v>
       </c>
@@ -6920,7 +6937,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
         <v>451</v>
       </c>
@@ -6941,7 +6958,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
         <v>453</v>
       </c>
@@ -6962,7 +6979,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>454</v>
       </c>
@@ -6983,7 +7000,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6">
       <c r="A97" s="9" t="s">
         <v>466</v>
       </c>
@@ -7003,7 +7020,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6">
       <c r="A98" s="9" t="s">
         <v>468</v>
       </c>
@@ -7024,7 +7041,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6">
       <c r="A99" s="9" t="s">
         <v>470</v>
       </c>
@@ -7045,7 +7062,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6">
       <c r="A100" s="9" t="s">
         <v>472</v>
       </c>
@@ -7066,7 +7083,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6">
       <c r="A101" s="9" t="s">
         <v>474</v>
       </c>
@@ -7087,7 +7104,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6">
       <c r="A102" s="9" t="s">
         <v>476</v>
       </c>
@@ -7108,7 +7125,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6">
       <c r="A103" s="9" t="s">
         <v>478</v>
       </c>
@@ -7129,7 +7146,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6">
       <c r="A104" s="9" t="s">
         <v>480</v>
       </c>
@@ -7150,7 +7167,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6">
       <c r="A105" s="9" t="s">
         <v>482</v>
       </c>
@@ -7171,7 +7188,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6">
       <c r="A106" s="9" t="s">
         <v>484</v>
       </c>
@@ -7192,7 +7209,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6">
       <c r="A107" s="9" t="s">
         <v>486</v>
       </c>
@@ -7213,7 +7230,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6">
       <c r="A108" s="9" t="s">
         <v>488</v>
       </c>
@@ -7234,7 +7251,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6">
       <c r="A109" s="9" t="s">
         <v>494</v>
       </c>
@@ -7255,7 +7272,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6">
       <c r="A110" s="9" t="s">
         <v>495</v>
       </c>
@@ -7276,7 +7293,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6">
       <c r="A111" s="9" t="s">
         <v>497</v>
       </c>
@@ -7297,7 +7314,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6">
       <c r="A112" s="9" t="s">
         <v>499</v>
       </c>
@@ -7318,7 +7335,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6">
       <c r="A113" s="9" t="s">
         <v>500</v>
       </c>
@@ -7339,7 +7356,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>501</v>
       </c>
@@ -7360,7 +7377,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6">
       <c r="A115" s="9" t="s">
         <v>502</v>
       </c>
@@ -7381,7 +7398,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6">
       <c r="B116" s="1" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -7410,19 +7427,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K70"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" style="3" customWidth="1"/>
-    <col min="2" max="6" width="11.42578125" style="3"/>
-    <col min="7" max="7" width="69.140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" style="3"/>
-    <col min="9" max="9" width="21.42578125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="42.42578125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="72.28515625" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="22.33203125" style="3" customWidth="1"/>
+    <col min="2" max="6" width="11.44140625" style="3"/>
+    <col min="7" max="7" width="69.109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" style="3"/>
+    <col min="9" max="9" width="21.44140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="42.44140625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="72.33203125" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="11.44140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="39.9" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>77</v>
       </c>
@@ -7457,7 +7474,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="39.9" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>43</v>
       </c>
@@ -7492,7 +7509,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="39.9" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -7527,7 +7544,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="39.9" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
@@ -7562,7 +7579,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="39.9" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>40</v>
       </c>
@@ -7597,7 +7614,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="39.9" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>25</v>
       </c>
@@ -7632,7 +7649,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="39.9" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>708</v>
       </c>
@@ -7667,7 +7684,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="39.9" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>33</v>
       </c>
@@ -7702,7 +7719,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="39.9" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>53</v>
       </c>
@@ -7737,7 +7754,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="39.9" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -7772,7 +7789,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="39.9" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>122</v>
       </c>
@@ -7807,7 +7824,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="39.9" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>128</v>
       </c>
@@ -7842,7 +7859,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="39.9" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>57</v>
       </c>
@@ -7877,7 +7894,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="39.9" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>136</v>
       </c>
@@ -7912,7 +7929,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="39.9" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>138</v>
       </c>
@@ -7944,7 +7961,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="39.9" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>10</v>
       </c>
@@ -7973,7 +7990,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="39.9" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>72</v>
       </c>
@@ -8008,7 +8025,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="39.9" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>13</v>
       </c>
@@ -8043,7 +8060,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="39.9" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>155</v>
       </c>
@@ -8078,7 +8095,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="39.9" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>59</v>
       </c>
@@ -8113,7 +8130,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="39.9" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>8</v>
       </c>
@@ -8148,7 +8165,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="39.9" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
@@ -8183,7 +8200,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="39.9" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>171</v>
       </c>
@@ -8218,7 +8235,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="39.9" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>176</v>
       </c>
@@ -8253,7 +8270,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="39.9" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>180</v>
       </c>
@@ -8288,7 +8305,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="39.9" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -8323,7 +8340,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="39.9" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>16</v>
       </c>
@@ -8358,7 +8375,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="39.9" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>46</v>
       </c>
@@ -8393,7 +8410,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="39.9" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>268</v>
       </c>
@@ -8428,7 +8445,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="39.9" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>276</v>
       </c>
@@ -8463,7 +8480,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="39.9" customHeight="1">
       <c r="A31" s="6" t="s">
         <v>298</v>
       </c>
@@ -8498,7 +8515,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="39.9" customHeight="1">
       <c r="A32" s="6" t="s">
         <v>313</v>
       </c>
@@ -8533,7 +8550,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" ht="39.9" customHeight="1">
       <c r="A33" s="6" t="s">
         <v>320</v>
       </c>
@@ -8568,7 +8585,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" ht="39.9" customHeight="1">
       <c r="A34" s="3" t="s">
         <v>365</v>
       </c>
@@ -8603,7 +8620,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" ht="39.9" customHeight="1">
       <c r="A35" s="3" t="s">
         <v>382</v>
       </c>
@@ -8638,7 +8655,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" ht="44.25" customHeight="1">
       <c r="A36" s="3" t="s">
         <v>410</v>
       </c>
@@ -8673,7 +8690,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" ht="72">
       <c r="A37" s="3" t="s">
         <v>432</v>
       </c>
@@ -8708,7 +8725,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" ht="29.25" customHeight="1">
       <c r="A38" s="3" t="s">
         <v>437</v>
       </c>
@@ -8743,7 +8760,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" ht="34.5" customHeight="1">
       <c r="A39" s="3" t="s">
         <v>438</v>
       </c>
@@ -8778,7 +8795,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" ht="47.25" customHeight="1">
       <c r="A40" s="3" t="s">
         <v>439</v>
       </c>
@@ -8813,7 +8830,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" ht="49.5" customHeight="1">
       <c r="A41" s="3" t="s">
         <v>456</v>
       </c>
@@ -8848,7 +8865,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" ht="72">
       <c r="A42" s="11" t="s">
         <v>461</v>
       </c>
@@ -8883,7 +8900,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" ht="72">
       <c r="A43" s="11" t="s">
         <v>489</v>
       </c>
@@ -8918,7 +8935,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" ht="72">
       <c r="A44" s="11" t="s">
         <v>503</v>
       </c>
@@ -8953,7 +8970,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" ht="72">
       <c r="A45" s="15" t="s">
         <v>603</v>
       </c>
@@ -8984,7 +9001,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" ht="72">
       <c r="A46" s="13" t="s">
         <v>512</v>
       </c>
@@ -9019,7 +9036,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" ht="72">
       <c r="A47" s="13" t="s">
         <v>518</v>
       </c>
@@ -9050,7 +9067,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" ht="72">
       <c r="A48" s="13" t="s">
         <v>523</v>
       </c>
@@ -9081,7 +9098,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" ht="72">
       <c r="A49" s="13" t="s">
         <v>530</v>
       </c>
@@ -9112,7 +9129,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" ht="51" customHeight="1">
       <c r="A50" s="13" t="s">
         <v>536</v>
       </c>
@@ -9147,7 +9164,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" ht="72">
       <c r="A51" s="13" t="s">
         <v>542</v>
       </c>
@@ -9182,7 +9199,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" ht="72">
       <c r="A52" s="13" t="s">
         <v>547</v>
       </c>
@@ -9217,7 +9234,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" ht="57.6">
       <c r="A53" s="13" t="s">
         <v>552</v>
       </c>
@@ -9248,7 +9265,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" ht="57.6">
       <c r="A54" s="13" t="s">
         <v>557</v>
       </c>
@@ -9279,7 +9296,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" ht="72">
       <c r="A55" s="13" t="s">
         <v>562</v>
       </c>
@@ -9310,7 +9327,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" ht="72">
       <c r="A56" s="13" t="s">
         <v>567</v>
       </c>
@@ -9341,7 +9358,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" ht="72">
       <c r="A57" s="13" t="s">
         <v>572</v>
       </c>
@@ -9372,7 +9389,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" ht="86.4">
       <c r="A58" s="13" t="s">
         <v>578</v>
       </c>
@@ -9403,7 +9420,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" ht="72">
       <c r="A59" s="13" t="s">
         <v>581</v>
       </c>
@@ -9434,7 +9451,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" ht="72">
       <c r="A60" s="13" t="s">
         <v>585</v>
       </c>
@@ -9465,7 +9482,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" ht="72">
       <c r="A61" s="3" t="s">
         <v>594</v>
       </c>
@@ -9496,7 +9513,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" ht="72">
       <c r="A62" s="11" t="s">
         <v>597</v>
       </c>
@@ -9527,7 +9544,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" ht="48" customHeight="1">
       <c r="A63" s="18" t="s">
         <v>615</v>
       </c>
@@ -9556,7 +9573,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" ht="42" customHeight="1">
       <c r="A64" s="19" t="s">
         <v>617</v>
       </c>
@@ -9585,7 +9602,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" ht="45" customHeight="1">
       <c r="A65" s="19" t="s">
         <v>618</v>
       </c>
@@ -9614,7 +9631,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" ht="72">
       <c r="A66" s="19" t="s">
         <v>619</v>
       </c>
@@ -9643,7 +9660,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" ht="72">
       <c r="A67" s="19" t="s">
         <v>620</v>
       </c>
@@ -9672,7 +9689,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" ht="72">
       <c r="A68" s="19" t="s">
         <v>623</v>
       </c>
@@ -9701,7 +9718,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" ht="409.6">
       <c r="A69" s="31" t="s">
         <v>701</v>
       </c>
@@ -9736,7 +9753,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" ht="409.6">
       <c r="A70" s="31" t="s">
         <v>706</v>
       </c>
@@ -9847,13 +9864,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="5" max="5" width="23.7109375" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="23" t="s">
         <v>608</v>
       </c>
@@ -9870,7 +9887,7 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="20" t="s">
         <v>84</v>
       </c>
@@ -9887,7 +9904,7 @@
       </c>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="20" t="s">
         <v>139</v>
       </c>
@@ -9904,7 +9921,7 @@
       </c>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="20" t="s">
         <v>147</v>
       </c>
@@ -9921,7 +9938,7 @@
       </c>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="20" t="s">
         <v>167</v>
       </c>
@@ -9936,7 +9953,7 @@
       </c>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="20" t="s">
         <v>188</v>
       </c>
@@ -9951,7 +9968,7 @@
       </c>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="20" t="s">
         <v>123</v>
       </c>
@@ -9962,7 +9979,7 @@
       <c r="F7" s="20"/>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="21" t="s">
         <v>321</v>
       </c>
@@ -9973,7 +9990,7 @@
       <c r="F8" s="20"/>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="22" t="s">
         <v>610</v>
       </c>
@@ -9984,7 +10001,7 @@
       <c r="F9" s="20"/>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="20" t="s">
         <v>612</v>
       </c>
@@ -9995,7 +10012,7 @@
       <c r="F10" s="20"/>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="22" t="s">
         <v>616</v>
       </c>
@@ -10006,7 +10023,7 @@
       <c r="F11" s="20"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="20" t="s">
         <v>647</v>
       </c>
@@ -10017,7 +10034,7 @@
       <c r="F12" s="20"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="20" t="s">
         <v>648</v>
       </c>
@@ -10028,7 +10045,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="28.8">
       <c r="A14" s="27" t="s">
         <v>649</v>
       </c>
@@ -10039,7 +10056,7 @@
       <c r="F14" s="20"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="20"/>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -10048,7 +10065,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="20"/>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
@@ -10057,7 +10074,7 @@
       <c r="F16" s="20"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="20"/>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
@@ -10066,7 +10083,7 @@
       <c r="F17" s="20"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>

--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud4\Boulot 2026\Site orientation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCAA2C1-B451-4272-82FA-17F4E4328B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{802EE769-E51B-4C4E-A935-F69C09D81C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elèves_BCPST" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="784">
   <si>
     <t>Initiale NOM</t>
   </si>
@@ -2380,6 +2380,12 @@
   </si>
   <si>
     <t>https://youtu.be/kYzrs1HNg9k</t>
+  </si>
+  <si>
+    <t>https://github.com/eekez/chesnoy-orientation/blob/216e7669804b7fea651a1fa01f4fd98afa5c26af/fiches/fiche%20de%20poste%20REMOND%20A.pdf</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/-Ft-YouRkKg</t>
   </si>
 </sst>
 </file>
@@ -2537,7 +2543,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2650,6 +2656,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -5656,7 +5663,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:9">
       <c r="A33" s="7" t="s">
         <v>297</v>
       </c>
@@ -5677,7 +5684,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:9">
       <c r="A34" s="7" t="s">
         <v>304</v>
       </c>
@@ -5698,7 +5705,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:9">
       <c r="A35" s="7" t="s">
         <v>306</v>
       </c>
@@ -5719,7 +5726,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:9">
       <c r="A36" s="7" t="s">
         <v>308</v>
       </c>
@@ -5740,7 +5747,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:9">
       <c r="A37" s="7" t="s">
         <v>310</v>
       </c>
@@ -5761,7 +5768,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:9">
       <c r="A38" s="7" t="s">
         <v>312</v>
       </c>
@@ -5782,7 +5789,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:9">
       <c r="A39" t="s">
         <v>318</v>
       </c>
@@ -5803,7 +5810,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:9">
       <c r="A40" s="7" t="s">
         <v>325</v>
       </c>
@@ -5824,7 +5831,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:9">
       <c r="A41" s="7" t="s">
         <v>330</v>
       </c>
@@ -5845,7 +5852,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:9">
       <c r="A42" s="7" t="s">
         <v>331</v>
       </c>
@@ -5866,7 +5873,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:9">
       <c r="A43" s="7" t="s">
         <v>327</v>
       </c>
@@ -5887,7 +5894,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:9">
       <c r="A44" s="7" t="s">
         <v>328</v>
       </c>
@@ -5908,7 +5915,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:9">
       <c r="A45" s="7" t="s">
         <v>333</v>
       </c>
@@ -5928,8 +5935,14 @@
       <c r="F45" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="46" spans="1:6">
+      <c r="H45" s="40" t="s">
+        <v>783</v>
+      </c>
+      <c r="I45" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" s="7" t="s">
         <v>335</v>
       </c>
@@ -5950,7 +5963,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:9">
       <c r="A47" s="7" t="s">
         <v>235</v>
       </c>
@@ -5971,7 +5984,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:9">
       <c r="A48" s="7" t="s">
         <v>337</v>
       </c>
@@ -7408,6 +7421,9 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F69">
     <sortCondition descending="1" ref="D2:D69"/>
   </sortState>
+  <hyperlinks>
+    <hyperlink ref="H45" r:id="rId1" xr:uid="{D3D23827-3ABF-46BA-A7B9-D1DEB1598B58}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">

--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud4\Boulot 2026\Site orientation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{802EE769-E51B-4C4E-A935-F69C09D81C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCC3EFE-69BD-4736-AFB4-6DADFDDE8CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1669" uniqueCount="787">
   <si>
     <t>Initiale NOM</t>
   </si>
@@ -2382,10 +2382,19 @@
     <t>https://youtu.be/kYzrs1HNg9k</t>
   </si>
   <si>
-    <t>https://github.com/eekez/chesnoy-orientation/blob/216e7669804b7fea651a1fa01f4fd98afa5c26af/fiches/fiche%20de%20poste%20REMOND%20A.pdf</t>
-  </si>
-  <si>
     <t>https://youtube.com/shorts/-Ft-YouRkKg</t>
+  </si>
+  <si>
+    <t>https://eekez.github.io/chesnoy-orientation/fiches/ficheAntoineR.pdf</t>
+  </si>
+  <si>
+    <t>GUÉRINI</t>
+  </si>
+  <si>
+    <t>RAFFAULT</t>
+  </si>
+  <si>
+    <t>Éva</t>
   </si>
 </sst>
 </file>
@@ -4976,7 +4985,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7423C6-280D-4FEC-B3EE-2664E2210568}">
-  <dimension ref="A1:I116"/>
+  <dimension ref="A1:I118"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="19.33203125" customWidth="1"/>
@@ -5014,56 +5023,60 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>231</v>
+        <v>784</v>
       </c>
       <c r="B2" s="1" t="str">
-        <f t="shared" ref="B2:B33" si="0">LEFT(A2)</f>
-        <v>B</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D2" s="1">
-        <v>2025</v>
-      </c>
-      <c r="E2" s="1" t="s">
+        <f t="shared" ref="B2:B35" si="0">LEFT(A2)</f>
+        <v>G</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>197</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>706</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>232</v>
+        <v>785</v>
       </c>
       <c r="B3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>C</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D3" s="1">
-        <v>2025</v>
-      </c>
-      <c r="E3" s="1" t="s">
+        <v>R</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>197</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>708</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="38"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>D</v>
+        <v>B</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D4" s="1">
         <v>2025</v>
@@ -5072,523 +5085,523 @@
         <v>197</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>138</v>
+        <v>706</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B5" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>C</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D5" s="1">
+        <v>2025</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>D</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2025</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B5" s="4" t="str">
+      <c r="B7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>F</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D7" s="1">
         <v>2025</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="E7" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="1" t="s">
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B6" s="4" t="str">
+      <c r="B8" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D8" s="1">
         <v>2025</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="E8" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="1" t="s">
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B7" s="4" t="str">
+      <c r="B9" s="4" t="str">
         <f t="shared" si="0"/>
         <v>U</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D9" s="1">
         <v>2025</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="E9" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="1" t="s">
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B8" s="4" t="str">
+      <c r="B10" s="4" t="str">
         <f t="shared" si="0"/>
         <v>W</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D10" s="1">
         <v>2025</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="E10" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="1" t="s">
+    <row r="11" spans="1:9">
+      <c r="A11" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B9" s="4" t="str">
+      <c r="B11" s="4" t="str">
         <f t="shared" si="0"/>
         <v>T</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D11" s="1">
         <v>2025</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F9" s="1" t="s">
+      <c r="E11" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="1" t="s">
+    <row r="12" spans="1:9">
+      <c r="A12" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B10" s="4" t="str">
+      <c r="B12" s="4" t="str">
         <f t="shared" si="0"/>
         <v>G</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D12" s="1">
         <v>2025</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F10" s="1" t="s">
+      <c r="E12" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="1" t="s">
+    <row r="13" spans="1:9">
+      <c r="A13" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B11" s="4" t="str">
+      <c r="B13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D13" s="1">
         <v>2025</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F11" s="1" t="s">
+      <c r="E13" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="1" t="s">
+    <row r="14" spans="1:9">
+      <c r="A14" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B12" s="4" t="str">
+      <c r="B14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>B</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D14" s="1">
         <v>2024</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="E14" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="1" t="s">
+    <row r="15" spans="1:9">
+      <c r="A15" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B13" s="4" t="str">
+      <c r="B15" s="4" t="str">
         <f t="shared" si="0"/>
         <v>E</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D15" s="1">
         <v>2024</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F13" s="1" t="s">
+      <c r="E15" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="1" t="s">
+    <row r="16" spans="1:9">
+      <c r="A16" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B14" s="4" t="str">
+      <c r="B16" s="4" t="str">
         <f t="shared" si="0"/>
         <v>G</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D16" s="1">
         <v>2024</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F14" s="1" t="s">
+      <c r="E16" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="1" t="s">
+    <row r="17" spans="1:6">
+      <c r="A17" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B15" s="4" t="str">
+      <c r="B17" s="4" t="str">
         <f t="shared" si="0"/>
         <v>H</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D17" s="1">
         <v>2024</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F15" s="1" t="s">
+      <c r="E17" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="1" t="s">
+    <row r="18" spans="1:6">
+      <c r="A18" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B16" s="4" t="str">
+      <c r="B18" s="4" t="str">
         <f t="shared" si="0"/>
         <v>P</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D18" s="1">
         <v>2024</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F16" s="1" t="s">
+      <c r="E18" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="1" t="s">
+    <row r="19" spans="1:6">
+      <c r="A19" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B17" s="4" t="str">
+      <c r="B19" s="4" t="str">
         <f t="shared" si="0"/>
         <v>R</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D19" s="1">
         <v>2024</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F17" s="1" t="s">
+      <c r="E19" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="1" t="s">
+    <row r="20" spans="1:6">
+      <c r="A20" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B18" s="4" t="str">
+      <c r="B20" s="4" t="str">
         <f t="shared" si="0"/>
         <v>L</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D20" s="1">
         <v>2024</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F18" s="1" t="s">
+      <c r="E20" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
         <v>272</v>
       </c>
-      <c r="B19" s="4" t="str">
+      <c r="B21" s="4" t="str">
         <f t="shared" si="0"/>
         <v>M</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C21" t="s">
         <v>273</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D21" s="1">
         <v>2024</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F19" s="1" t="s">
+      <c r="E21" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="7" t="s">
+    <row r="22" spans="1:6">
+      <c r="A22" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="B20" s="4" t="str">
+      <c r="B22" s="4" t="str">
         <f t="shared" si="0"/>
         <v>R</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C22" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D22" s="1">
         <v>2024</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F20" s="1" t="s">
+      <c r="E22" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="1" t="s">
+    <row r="23" spans="1:6">
+      <c r="A23" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B21" s="4" t="str">
+      <c r="B23" s="4" t="str">
         <f t="shared" si="0"/>
         <v>F</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C23" t="s">
         <v>260</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D23" s="1">
         <v>2023</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F21" s="1" t="s">
+      <c r="E23" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="1" t="s">
+    <row r="24" spans="1:6">
+      <c r="A24" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B22" s="4" t="str">
+      <c r="B24" s="4" t="str">
         <f t="shared" si="0"/>
         <v>G</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C24" t="s">
         <v>262</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D24" s="1">
         <v>2023</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F22" s="1" t="s">
+      <c r="E24" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="A23" t="s">
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
         <v>263</v>
       </c>
-      <c r="B23" s="4" t="str">
+      <c r="B25" s="4" t="str">
         <f t="shared" si="0"/>
         <v>J</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D25" s="1">
         <v>2023</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F23" s="1" t="s">
+      <c r="E25" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="1" t="s">
+    <row r="26" spans="1:6">
+      <c r="A26" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B24" s="4" t="str">
+      <c r="B26" s="4" t="str">
         <f t="shared" si="0"/>
         <v>L</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C26" t="s">
         <v>266</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D26" s="1">
         <v>2023</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F24" s="1" t="s">
+      <c r="E26" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
         <v>274</v>
       </c>
-      <c r="B25" s="4" t="str">
+      <c r="B27" s="4" t="str">
         <f t="shared" si="0"/>
         <v>P</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C27" t="s">
         <v>275</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D27" s="1">
         <v>2023</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F25" s="1" t="s">
+      <c r="E27" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="7" t="s">
+    <row r="28" spans="1:6">
+      <c r="A28" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="B26" s="4" t="str">
+      <c r="B28" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C28" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D28" s="1">
         <v>2023</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="E28" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="7" t="s">
+    <row r="29" spans="1:6">
+      <c r="A29" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="B27" s="4" t="str">
+      <c r="B29" s="4" t="str">
         <f t="shared" si="0"/>
         <v>V</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C29" s="7" t="s">
         <v>286</v>
-      </c>
-      <c r="D27" s="1">
-        <v>2023</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F27" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="B28" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>B</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="D28" s="1">
-        <v>2023</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F28" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="B29" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>D</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>296</v>
       </c>
       <c r="D29" s="1">
         <v>2023</v>
@@ -5597,61 +5610,61 @@
         <v>197</v>
       </c>
       <c r="F29" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B30" s="4" t="str">
         <f t="shared" si="0"/>
         <v>B</v>
       </c>
-      <c r="C30" t="s">
-        <v>288</v>
+      <c r="C30" s="7" t="s">
+        <v>290</v>
       </c>
       <c r="D30" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>197</v>
       </c>
       <c r="F30" t="s">
-        <v>176</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="7" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B31" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>C</v>
+        <v>D</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D31" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>197</v>
       </c>
       <c r="F31" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="7" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B32" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>C</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>294</v>
+        <v>B</v>
+      </c>
+      <c r="C32" t="s">
+        <v>288</v>
       </c>
       <c r="D32" s="1">
         <v>2022</v>
@@ -5660,19 +5673,19 @@
         <v>197</v>
       </c>
       <c r="F32" t="s">
-        <v>33</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B33" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>C</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>23</v>
+        <v>292</v>
       </c>
       <c r="D33" s="1">
         <v>2022</v>
@@ -5681,19 +5694,19 @@
         <v>197</v>
       </c>
       <c r="F33" t="s">
-        <v>298</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="7" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="B34" s="4" t="str">
-        <f t="shared" ref="B34:B65" si="1">LEFT(A34)</f>
-        <v>G</v>
+        <f t="shared" si="0"/>
+        <v>C</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="D34" s="1">
         <v>2022</v>
@@ -5702,1180 +5715,1180 @@
         <v>197</v>
       </c>
       <c r="F34" t="s">
-        <v>706</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="B35" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>F</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2022</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F35" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="B36" s="4" t="str">
+        <f t="shared" ref="B36:B67" si="1">LEFT(A36)</f>
+        <v>G</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D36" s="1">
+        <v>2022</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F36" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="B35" s="1" t="str">
+      <c r="B37" s="1" t="str">
         <f t="shared" si="1"/>
         <v>J</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C37" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D37" s="1">
         <v>2022</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="E37" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F37" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="7" t="s">
+    <row r="38" spans="1:9">
+      <c r="A38" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="B36" s="1" t="str">
+      <c r="B38" s="1" t="str">
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C38" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D38" s="1">
         <v>2022</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="E38" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F38" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="7" t="s">
+    <row r="39" spans="1:9">
+      <c r="A39" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="B37" s="1" t="str">
+      <c r="B39" s="1" t="str">
         <f t="shared" si="1"/>
         <v>R</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C39" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D39" s="1">
         <v>2022</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="E39" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F39" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="7" t="s">
+    <row r="40" spans="1:9">
+      <c r="A40" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="B38" s="1" t="str">
+      <c r="B40" s="1" t="str">
         <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C40" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D40" s="1">
         <v>2022</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="E40" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F40" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
-      <c r="A39" t="s">
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
         <v>318</v>
       </c>
-      <c r="B39" s="1" t="str">
+      <c r="B41" s="1" t="str">
         <f t="shared" si="1"/>
         <v>W</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C41" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D41" s="1">
         <v>2022</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="E41" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F41" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="7" t="s">
+    <row r="42" spans="1:9">
+      <c r="A42" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="B40" s="1" t="str">
+      <c r="B42" s="1" t="str">
         <f t="shared" si="1"/>
         <v>B</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C42" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D42" s="1">
         <v>2022</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="E42" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F42" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="7" t="s">
+    <row r="43" spans="1:9">
+      <c r="A43" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="B41" s="1" t="str">
+      <c r="B43" s="1" t="str">
         <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C43" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D43" s="1">
         <v>2022</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="E43" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F43" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="7" t="s">
+    <row r="44" spans="1:9">
+      <c r="A44" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="B42" s="1" t="str">
+      <c r="B44" s="1" t="str">
         <f t="shared" si="1"/>
         <v>P</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C44" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D44" s="1">
         <v>2022</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="E44" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F44" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="7" t="s">
+    <row r="45" spans="1:9">
+      <c r="A45" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="B43" s="1" t="str">
+      <c r="B45" s="1" t="str">
         <f t="shared" si="1"/>
         <v>B</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C45" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D45" s="1">
         <v>2021</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="E45" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F45" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
-      <c r="A44" s="7" t="s">
+    <row r="46" spans="1:9">
+      <c r="A46" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="B44" s="1" t="str">
+      <c r="B46" s="1" t="str">
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C46" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D46" s="1">
         <v>2021</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="E46" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F46" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="7" t="s">
+    <row r="47" spans="1:9">
+      <c r="A47" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="B45" s="1" t="str">
+      <c r="B47" s="1" t="str">
         <f t="shared" si="1"/>
         <v>R</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C47" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D47" s="1">
         <v>2021</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F45" t="s">
+      <c r="E47" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F47" t="s">
         <v>59</v>
       </c>
-      <c r="H45" s="40" t="s">
+      <c r="H47" s="40" t="s">
+        <v>782</v>
+      </c>
+      <c r="I47" s="40" t="s">
         <v>783</v>
       </c>
-      <c r="I45" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46" s="7" t="s">
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="B46" s="1" t="str">
+      <c r="B48" s="1" t="str">
         <f t="shared" si="1"/>
         <v>R</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C48" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D48" s="1">
         <v>2021</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="E48" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F48" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
-      <c r="A47" s="7" t="s">
+    <row r="49" spans="1:6">
+      <c r="A49" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="B47" s="1" t="str">
+      <c r="B49" s="1" t="str">
         <f t="shared" si="1"/>
         <v>S</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C49" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D49" s="1">
         <v>2021</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F47" t="s">
+      <c r="E49" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F49" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="7" t="s">
+    <row r="50" spans="1:6">
+      <c r="A50" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B48" s="1" t="str">
+      <c r="B50" s="1" t="str">
         <f t="shared" si="1"/>
         <v>A</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C50" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D50" s="1">
         <v>2021</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="E50" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F50" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="7" t="s">
+    <row r="51" spans="1:6">
+      <c r="A51" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="B49" s="1" t="str">
+      <c r="B51" s="1" t="str">
         <f t="shared" si="1"/>
         <v>B</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C51" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D51" s="1">
         <v>2021</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="E51" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F51" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="7" t="s">
+    <row r="52" spans="1:6">
+      <c r="A52" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="B50" s="1" t="str">
+      <c r="B52" s="1" t="str">
         <f t="shared" si="1"/>
         <v>K</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C52" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D52" s="1">
         <v>2021</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="E52" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F52" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="7" t="s">
+    <row r="53" spans="1:6">
+      <c r="A53" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="B51" s="1" t="str">
+      <c r="B53" s="1" t="str">
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C53" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="D51" s="1">
+      <c r="D53" s="1">
         <v>2021</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="E53" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F53" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="7" t="s">
+    <row r="54" spans="1:6">
+      <c r="A54" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="B52" s="1" t="str">
+      <c r="B54" s="1" t="str">
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C54" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="D52" s="1">
+      <c r="D54" s="1">
         <v>2021</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="E54" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F54" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="7" t="s">
+    <row r="55" spans="1:6">
+      <c r="A55" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="B53" s="1" t="str">
+      <c r="B55" s="1" t="str">
         <f t="shared" si="1"/>
         <v>P</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C55" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D55" s="1">
         <v>2021</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="E55" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F55" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
-      <c r="A54" t="s">
+    <row r="56" spans="1:6">
+      <c r="A56" t="s">
         <v>378</v>
       </c>
-      <c r="B54" s="1" t="str">
+      <c r="B56" s="1" t="str">
         <f t="shared" si="1"/>
         <v>P</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C56" t="s">
         <v>379</v>
       </c>
-      <c r="D54" s="1">
+      <c r="D56" s="1">
         <v>2021</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F54" t="s">
+      <c r="E56" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F56" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="7" t="s">
+    <row r="57" spans="1:6">
+      <c r="A57" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="B55" s="1" t="str">
+      <c r="B57" s="1" t="str">
         <f t="shared" si="1"/>
         <v>A</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C57" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="D55" s="1">
+      <c r="D57" s="1">
         <v>2020</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="E57" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F57" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
-      <c r="A56" s="7" t="s">
+    <row r="58" spans="1:6">
+      <c r="A58" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="B56" s="1" t="str">
+      <c r="B58" s="1" t="str">
         <f t="shared" si="1"/>
         <v>C</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C58" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D56" s="1">
+      <c r="D58" s="1">
         <v>2020</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F56" t="s">
+      <c r="E58" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F58" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="7" t="s">
+    <row r="59" spans="1:6">
+      <c r="A59" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="B57" s="1" t="str">
+      <c r="B59" s="1" t="str">
         <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C59" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="D57" s="1">
+      <c r="D59" s="1">
         <v>2020</v>
       </c>
-      <c r="E57" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F57" t="s">
+      <c r="E59" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F59" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
-      <c r="A58" t="s">
+    <row r="60" spans="1:6">
+      <c r="A60" t="s">
         <v>354</v>
       </c>
-      <c r="B58" s="1" t="str">
+      <c r="B60" s="1" t="str">
         <f t="shared" si="1"/>
         <v>A</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="C60" s="9" t="s">
         <v>355</v>
       </c>
-      <c r="D58" s="1">
+      <c r="D60" s="1">
         <v>2020</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F58" t="s">
+      <c r="E60" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F60" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
-      <c r="A59" t="s">
+    <row r="61" spans="1:6">
+      <c r="A61" t="s">
         <v>356</v>
       </c>
-      <c r="B59" s="1" t="str">
+      <c r="B61" s="1" t="str">
         <f t="shared" si="1"/>
         <v>D</v>
       </c>
-      <c r="C59" s="9" t="s">
+      <c r="C61" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="D59" s="1">
+      <c r="D61" s="1">
         <v>2020</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F59" t="s">
+      <c r="E61" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F61" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
-      <c r="A60" t="s">
+    <row r="62" spans="1:6">
+      <c r="A62" t="s">
         <v>358</v>
       </c>
-      <c r="B60" s="1" t="str">
+      <c r="B62" s="1" t="str">
         <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="C62" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="D60" s="1">
+      <c r="D62" s="1">
         <v>2020</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F60" t="s">
+      <c r="E62" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F62" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
-      <c r="A61" t="s">
+    <row r="63" spans="1:6">
+      <c r="A63" t="s">
         <v>360</v>
       </c>
-      <c r="B61" s="1" t="str">
+      <c r="B63" s="1" t="str">
         <f t="shared" si="1"/>
         <v>P</v>
       </c>
-      <c r="C61" s="9" t="s">
+      <c r="C63" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="D61" s="1">
+      <c r="D63" s="1">
         <v>2020</v>
       </c>
-      <c r="E61" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F61" t="s">
+      <c r="E63" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F63" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
-      <c r="A62" t="s">
+    <row r="64" spans="1:6">
+      <c r="A64" t="s">
         <v>362</v>
       </c>
-      <c r="B62" s="1" t="str">
+      <c r="B64" s="1" t="str">
         <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="C62" s="9" t="s">
+      <c r="C64" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D62" s="1">
+      <c r="D64" s="1">
         <v>2020</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F62" t="s">
+      <c r="E64" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F64" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
-      <c r="A63" t="s">
+    <row r="65" spans="1:6">
+      <c r="A65" t="s">
         <v>363</v>
       </c>
-      <c r="B63" s="1" t="str">
+      <c r="B65" s="1" t="str">
         <f t="shared" si="1"/>
         <v>C</v>
       </c>
-      <c r="C63" s="9" t="s">
+      <c r="C65" s="9" t="s">
         <v>364</v>
       </c>
-      <c r="D63" s="1">
+      <c r="D65" s="1">
         <v>2019</v>
       </c>
-      <c r="E63" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F63" t="s">
+      <c r="E65" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F65" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
-      <c r="A64" t="s">
+    <row r="66" spans="1:6">
+      <c r="A66" t="s">
         <v>370</v>
       </c>
-      <c r="B64" s="1" t="str">
+      <c r="B66" s="1" t="str">
         <f t="shared" si="1"/>
         <v>C</v>
       </c>
-      <c r="C64" s="9" t="s">
+      <c r="C66" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="D64" s="1">
+      <c r="D66" s="1">
         <v>2019</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F64" t="s">
+      <c r="E66" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F66" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
-      <c r="A65" t="s">
+    <row r="67" spans="1:6">
+      <c r="A67" t="s">
         <v>372</v>
       </c>
-      <c r="B65" s="1" t="str">
+      <c r="B67" s="1" t="str">
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C67" t="s">
         <v>373</v>
       </c>
-      <c r="D65" s="1">
+      <c r="D67" s="1">
         <v>2019</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F65" t="s">
+      <c r="E67" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F67" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
-      <c r="A66" t="s">
+    <row r="68" spans="1:6">
+      <c r="A68" t="s">
         <v>374</v>
       </c>
-      <c r="B66" s="1" t="str">
-        <f t="shared" ref="B66:B69" si="2">LEFT(A66)</f>
+      <c r="B68" s="1" t="str">
+        <f t="shared" ref="B68:B71" si="2">LEFT(A68)</f>
         <v>R</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C68" t="s">
         <v>68</v>
       </c>
-      <c r="D66" s="1">
+      <c r="D68" s="1">
         <v>2019</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F66" t="s">
+      <c r="E68" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F68" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
-      <c r="A67" t="s">
+    <row r="69" spans="1:6">
+      <c r="A69" t="s">
         <v>375</v>
       </c>
-      <c r="B67" s="1" t="str">
+      <c r="B69" s="1" t="str">
         <f t="shared" si="2"/>
         <v>R</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C69" t="s">
         <v>376</v>
       </c>
-      <c r="D67" s="1">
+      <c r="D69" s="1">
         <v>2019</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F67" t="s">
+      <c r="E69" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F69" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
-      <c r="A68" t="s">
+    <row r="70" spans="1:6">
+      <c r="A70" t="s">
         <v>377</v>
       </c>
-      <c r="B68" s="1" t="str">
+      <c r="B70" s="1" t="str">
         <f t="shared" si="2"/>
         <v>V</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C70" t="s">
         <v>275</v>
       </c>
-      <c r="D68" s="1">
+      <c r="D70" s="1">
         <v>2019</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F68" t="s">
+      <c r="E70" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F70" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
-      <c r="A69" t="s">
+    <row r="71" spans="1:6">
+      <c r="A71" t="s">
         <v>380</v>
       </c>
-      <c r="B69" s="1" t="str">
+      <c r="B71" s="1" t="str">
         <f t="shared" si="2"/>
         <v>H</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C71" t="s">
         <v>381</v>
       </c>
-      <c r="D69" s="1">
+      <c r="D71" s="1">
         <v>2019</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F69" t="s">
+      <c r="E71" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F71" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
-      <c r="A70" t="s">
+    <row r="72" spans="1:6">
+      <c r="A72" t="s">
         <v>387</v>
       </c>
-      <c r="B70" s="1" t="str">
-        <f t="shared" ref="B70:B88" si="3">LEFT(A70)</f>
+      <c r="B72" s="1" t="str">
+        <f t="shared" ref="B72:B90" si="3">LEFT(A72)</f>
         <v>M</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C72" t="s">
         <v>388</v>
       </c>
-      <c r="D70" s="1">
+      <c r="D72" s="1">
         <v>2018</v>
       </c>
-      <c r="E70" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F70" t="s">
+      <c r="E72" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F72" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
-      <c r="A71" t="s">
+    <row r="73" spans="1:6">
+      <c r="A73" t="s">
         <v>389</v>
       </c>
-      <c r="B71" s="1" t="str">
+      <c r="B73" s="1" t="str">
         <f t="shared" si="3"/>
         <v>R</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C73" t="s">
         <v>309</v>
       </c>
-      <c r="D71" s="1">
+      <c r="D73" s="1">
         <v>2018</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F71" t="s">
+      <c r="E73" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F73" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
-      <c r="A72" t="s">
+    <row r="74" spans="1:6">
+      <c r="A74" t="s">
         <v>390</v>
       </c>
-      <c r="B72" s="1" t="str">
+      <c r="B74" s="1" t="str">
         <f t="shared" si="3"/>
         <v>T</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C74" t="s">
         <v>255</v>
       </c>
-      <c r="D72" s="1">
+      <c r="D74" s="1">
         <v>2018</v>
       </c>
-      <c r="E72" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F72" t="s">
+      <c r="E74" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F74" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
-      <c r="A73" t="s">
+    <row r="75" spans="1:6">
+      <c r="A75" t="s">
         <v>391</v>
       </c>
-      <c r="B73" s="1" t="str">
+      <c r="B75" s="1" t="str">
         <f t="shared" si="3"/>
         <v>V</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C75" t="s">
         <v>392</v>
       </c>
-      <c r="D73" s="1">
+      <c r="D75" s="1">
         <v>2018</v>
       </c>
-      <c r="E73" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F73" t="s">
+      <c r="E75" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F75" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
-      <c r="A74" t="s">
+    <row r="76" spans="1:6">
+      <c r="A76" t="s">
         <v>393</v>
       </c>
-      <c r="B74" s="1" t="str">
+      <c r="B76" s="1" t="str">
         <f t="shared" si="3"/>
         <v>B</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C76" t="s">
         <v>394</v>
       </c>
-      <c r="D74" s="1">
+      <c r="D76" s="1">
         <v>2018</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F74" t="s">
+      <c r="E76" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F76" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
-      <c r="A75" t="s">
+    <row r="77" spans="1:6">
+      <c r="A77" t="s">
         <v>395</v>
       </c>
-      <c r="B75" s="1" t="str">
+      <c r="B77" s="1" t="str">
         <f t="shared" si="3"/>
         <v>B</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C77" t="s">
         <v>334</v>
       </c>
-      <c r="D75" s="1">
+      <c r="D77" s="1">
         <v>2018</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F75" t="s">
+      <c r="E77" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F77" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
-      <c r="A76" t="s">
+    <row r="78" spans="1:6">
+      <c r="A78" t="s">
         <v>396</v>
       </c>
-      <c r="B76" s="1" t="str">
+      <c r="B78" s="1" t="str">
         <f t="shared" si="3"/>
         <v>D</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C78" t="s">
         <v>397</v>
       </c>
-      <c r="D76" s="1">
+      <c r="D78" s="1">
         <v>2018</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F76" t="s">
+      <c r="E78" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F78" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
-      <c r="A77" t="s">
+    <row r="79" spans="1:6">
+      <c r="A79" t="s">
         <v>398</v>
       </c>
-      <c r="B77" s="1" t="str">
+      <c r="B79" s="1" t="str">
         <f t="shared" si="3"/>
         <v>G</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C79" t="s">
         <v>275</v>
       </c>
-      <c r="D77" s="1">
+      <c r="D79" s="1">
         <v>2018</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F77" t="s">
+      <c r="E79" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F79" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
-      <c r="A78" t="s">
+    <row r="80" spans="1:6">
+      <c r="A80" t="s">
         <v>399</v>
       </c>
-      <c r="B78" s="1" t="str">
+      <c r="B80" s="1" t="str">
         <f t="shared" si="3"/>
         <v>P</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C80" t="s">
         <v>400</v>
       </c>
-      <c r="D78" s="1">
+      <c r="D80" s="1">
         <v>2018</v>
       </c>
-      <c r="E78" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F78" t="s">
+      <c r="E80" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F80" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
-      <c r="A79" t="s">
+    <row r="81" spans="1:6">
+      <c r="A81" t="s">
         <v>401</v>
       </c>
-      <c r="B79" s="1" t="str">
+      <c r="B81" s="1" t="str">
         <f t="shared" si="3"/>
         <v>B</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C81" t="s">
         <v>402</v>
       </c>
-      <c r="D79" s="1">
+      <c r="D81" s="1">
         <v>2017</v>
       </c>
-      <c r="E79" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F79" t="s">
+      <c r="E81" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F81" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
-      <c r="A80" t="s">
+    <row r="82" spans="1:6">
+      <c r="A82" t="s">
         <v>403</v>
       </c>
-      <c r="B80" s="1" t="str">
+      <c r="B82" s="1" t="str">
         <f t="shared" si="3"/>
         <v>D</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C82" t="s">
         <v>404</v>
       </c>
-      <c r="D80" s="1">
+      <c r="D82" s="1">
         <v>2017</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F80" t="s">
+      <c r="E82" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F82" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
-      <c r="A81" t="s">
+    <row r="83" spans="1:6">
+      <c r="A83" t="s">
         <v>405</v>
       </c>
-      <c r="B81" s="1" t="str">
+      <c r="B83" s="1" t="str">
         <f t="shared" si="3"/>
         <v>F</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C83" t="s">
         <v>376</v>
       </c>
-      <c r="D81" s="1">
+      <c r="D83" s="1">
         <v>2017</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F81" s="1" t="s">
+      <c r="E83" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
-      <c r="A82" t="s">
+    <row r="84" spans="1:6">
+      <c r="A84" t="s">
         <v>406</v>
       </c>
-      <c r="B82" s="1" t="str">
+      <c r="B84" s="1" t="str">
         <f t="shared" si="3"/>
         <v>F</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C84" t="s">
         <v>407</v>
       </c>
-      <c r="D82" s="1">
+      <c r="D84" s="1">
         <v>2017</v>
       </c>
-      <c r="E82" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F82" t="s">
+      <c r="E84" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F84" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
-      <c r="A83" t="s">
+    <row r="85" spans="1:6">
+      <c r="A85" t="s">
         <v>408</v>
       </c>
-      <c r="B83" s="1" t="str">
+      <c r="B85" s="1" t="str">
         <f t="shared" si="3"/>
         <v>H</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C85" t="s">
         <v>409</v>
       </c>
-      <c r="D83" s="1">
+      <c r="D85" s="1">
         <v>2017</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F83" t="s">
+      <c r="E85" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F85" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
-      <c r="A84" t="s">
+    <row r="86" spans="1:6">
+      <c r="A86" t="s">
         <v>415</v>
       </c>
-      <c r="B84" s="1" t="str">
+      <c r="B86" s="1" t="str">
         <f t="shared" si="3"/>
         <v>L</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C86" t="s">
         <v>416</v>
       </c>
-      <c r="D84" s="1">
+      <c r="D86" s="1">
         <v>2017</v>
       </c>
-      <c r="E84" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F84" t="s">
+      <c r="E86" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F86" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
-      <c r="A85" t="s">
+    <row r="87" spans="1:6">
+      <c r="A87" t="s">
         <v>417</v>
       </c>
-      <c r="B85" s="1" t="str">
+      <c r="B87" s="1" t="str">
         <f t="shared" si="3"/>
         <v>V</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C87" t="s">
         <v>418</v>
       </c>
-      <c r="D85" s="1">
+      <c r="D87" s="1">
         <v>2017</v>
       </c>
-      <c r="E85" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F85" t="s">
+      <c r="E87" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F87" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
-      <c r="A86" t="s">
+    <row r="88" spans="1:6">
+      <c r="A88" t="s">
         <v>419</v>
       </c>
-      <c r="B86" s="1" t="str">
+      <c r="B88" s="1" t="str">
         <f t="shared" si="3"/>
         <v>G</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C88" t="s">
         <v>420</v>
       </c>
-      <c r="D86" s="1">
+      <c r="D88" s="1">
         <v>2017</v>
       </c>
-      <c r="E86" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F86" t="s">
+      <c r="E88" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F88" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
-      <c r="A87" t="s">
+    <row r="89" spans="1:6">
+      <c r="A89" t="s">
         <v>421</v>
       </c>
-      <c r="B87" s="1" t="str">
+      <c r="B89" s="1" t="str">
         <f t="shared" si="3"/>
         <v>B</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C89" t="s">
         <v>45</v>
       </c>
-      <c r="D87" s="1">
+      <c r="D89" s="1">
         <v>2016</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F87" t="s">
+      <c r="E89" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F89" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
-      <c r="A88" t="s">
+    <row r="90" spans="1:6">
+      <c r="A90" t="s">
         <v>422</v>
       </c>
-      <c r="B88" s="1" t="str">
+      <c r="B90" s="1" t="str">
         <f t="shared" si="3"/>
         <v>C</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C90" t="s">
         <v>334</v>
-      </c>
-      <c r="D88" s="1">
-        <v>2016</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F88" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89" t="s">
-        <v>423</v>
-      </c>
-      <c r="B89" s="1" t="str">
-        <f t="shared" ref="B89:B98" si="4">LEFT(A89)</f>
-        <v>F</v>
-      </c>
-      <c r="C89" t="s">
-        <v>424</v>
-      </c>
-      <c r="D89" s="1">
-        <v>2016</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F89" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90" t="s">
-        <v>425</v>
-      </c>
-      <c r="B90" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>P</v>
-      </c>
-      <c r="C90" t="s">
-        <v>426</v>
       </c>
       <c r="D90" s="1">
         <v>2016</v>
@@ -6884,19 +6897,19 @@
         <v>197</v>
       </c>
       <c r="F90" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B91" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>R</v>
+        <f t="shared" ref="B91:B100" si="4">LEFT(A91)</f>
+        <v>F</v>
       </c>
       <c r="C91" t="s">
-        <v>62</v>
+        <v>424</v>
       </c>
       <c r="D91" s="1">
         <v>2016</v>
@@ -6905,19 +6918,19 @@
         <v>197</v>
       </c>
       <c r="F91" t="s">
-        <v>40</v>
+        <v>138</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B92" s="1" t="str">
         <f t="shared" si="4"/>
         <v>P</v>
       </c>
       <c r="C92" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D92" s="1">
         <v>2016</v>
@@ -6926,19 +6939,19 @@
         <v>197</v>
       </c>
       <c r="F92" t="s">
-        <v>16</v>
+        <v>708</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B93" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>M</v>
+        <v>R</v>
       </c>
       <c r="C93" t="s">
-        <v>431</v>
+        <v>62</v>
       </c>
       <c r="D93" s="1">
         <v>2016</v>
@@ -6947,19 +6960,19 @@
         <v>197</v>
       </c>
       <c r="F93" t="s">
-        <v>432</v>
+        <v>40</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>451</v>
+        <v>428</v>
       </c>
       <c r="B94" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>M</v>
+        <v>P</v>
       </c>
       <c r="C94" t="s">
-        <v>452</v>
+        <v>429</v>
       </c>
       <c r="D94" s="1">
         <v>2016</v>
@@ -6968,19 +6981,19 @@
         <v>197</v>
       </c>
       <c r="F94" t="s">
-        <v>437</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="B95" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>O</v>
+        <v>M</v>
       </c>
       <c r="C95" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="D95" s="1">
         <v>2016</v>
@@ -6989,19 +7002,19 @@
         <v>197</v>
       </c>
       <c r="F95" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B96" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>W</v>
+        <v>M</v>
       </c>
       <c r="C96" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D96" s="1">
         <v>2016</v>
@@ -7010,18 +7023,19 @@
         <v>197</v>
       </c>
       <c r="F96" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="97" spans="1:6">
-      <c r="A97" s="9" t="s">
-        <v>466</v>
-      </c>
-      <c r="B97" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C97" s="9" t="s">
-        <v>467</v>
+      <c r="A97" t="s">
+        <v>453</v>
+      </c>
+      <c r="B97" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>O</v>
+      </c>
+      <c r="C97" t="s">
+        <v>416</v>
       </c>
       <c r="D97" s="1">
         <v>2016</v>
@@ -7030,19 +7044,19 @@
         <v>197</v>
       </c>
       <c r="F97" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
     </row>
     <row r="98" spans="1:6">
-      <c r="A98" s="9" t="s">
-        <v>468</v>
+      <c r="A98" t="s">
+        <v>454</v>
       </c>
       <c r="B98" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>D</v>
-      </c>
-      <c r="C98" s="9" t="s">
-        <v>469</v>
+        <v>W</v>
+      </c>
+      <c r="C98" t="s">
+        <v>455</v>
       </c>
       <c r="D98" s="1">
         <v>2016</v>
@@ -7051,19 +7065,18 @@
         <v>197</v>
       </c>
       <c r="F98" t="s">
-        <v>138</v>
+        <v>439</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="B99" s="1" t="str">
-        <f t="shared" ref="B99:B116" si="5">LEFT(A99)</f>
-        <v>F</v>
+        <v>466</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="D99" s="1">
         <v>2016</v>
@@ -7072,357 +7085,400 @@
         <v>197</v>
       </c>
       <c r="F99" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="B100" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>D</v>
+      </c>
+      <c r="C100" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="D100" s="1">
+        <v>2016</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F100" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="B101" s="1" t="str">
+        <f t="shared" ref="B101:B118" si="5">LEFT(A101)</f>
+        <v>F</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="D101" s="1">
+        <v>2016</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F101" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" s="9" t="s">
         <v>472</v>
       </c>
-      <c r="B100" s="1" t="str">
+      <c r="B102" s="1" t="str">
         <f t="shared" si="5"/>
         <v>G</v>
       </c>
-      <c r="C100" s="9" t="s">
+      <c r="C102" s="9" t="s">
         <v>473</v>
       </c>
-      <c r="D100" s="1">
+      <c r="D102" s="1">
         <v>2016</v>
       </c>
-      <c r="E100" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F100" t="s">
+      <c r="E102" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F102" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
-      <c r="A101" s="9" t="s">
+    <row r="103" spans="1:6">
+      <c r="A103" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B101" s="1" t="str">
+      <c r="B103" s="1" t="str">
         <f t="shared" si="5"/>
         <v>M</v>
       </c>
-      <c r="C101" s="9" t="s">
+      <c r="C103" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="D101" s="1">
+      <c r="D103" s="1">
         <v>2016</v>
       </c>
-      <c r="E101" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F101" t="s">
+      <c r="E103" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F103" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
-      <c r="A102" s="9" t="s">
+    <row r="104" spans="1:6">
+      <c r="A104" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="B102" s="1" t="str">
+      <c r="B104" s="1" t="str">
         <f t="shared" si="5"/>
         <v>M</v>
       </c>
-      <c r="C102" s="9" t="s">
+      <c r="C104" s="9" t="s">
         <v>477</v>
       </c>
-      <c r="D102" s="1">
+      <c r="D104" s="1">
         <v>2016</v>
       </c>
-      <c r="E102" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F102" t="s">
+      <c r="E104" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F104" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
-      <c r="A103" s="9" t="s">
+    <row r="105" spans="1:6">
+      <c r="A105" s="9" t="s">
         <v>478</v>
       </c>
-      <c r="B103" s="1" t="str">
+      <c r="B105" s="1" t="str">
         <f t="shared" si="5"/>
         <v>P</v>
       </c>
-      <c r="C103" s="9" t="s">
+      <c r="C105" s="9" t="s">
         <v>479</v>
       </c>
-      <c r="D103" s="1">
+      <c r="D105" s="1">
         <v>2016</v>
       </c>
-      <c r="E103" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F103" t="s">
+      <c r="E105" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F105" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
-      <c r="A104" s="9" t="s">
+    <row r="106" spans="1:6">
+      <c r="A106" s="9" t="s">
         <v>480</v>
       </c>
-      <c r="B104" s="1" t="str">
+      <c r="B106" s="1" t="str">
         <f t="shared" si="5"/>
         <v>B</v>
       </c>
-      <c r="C104" s="9" t="s">
+      <c r="C106" s="9" t="s">
         <v>481</v>
       </c>
-      <c r="D104" s="1">
+      <c r="D106" s="1">
         <v>2015</v>
       </c>
-      <c r="E104" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F104" t="s">
+      <c r="E106" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F106" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
-      <c r="A105" s="9" t="s">
+    <row r="107" spans="1:6">
+      <c r="A107" s="9" t="s">
         <v>482</v>
       </c>
-      <c r="B105" s="1" t="str">
+      <c r="B107" s="1" t="str">
         <f t="shared" si="5"/>
         <v>C</v>
       </c>
-      <c r="C105" s="9" t="s">
+      <c r="C107" s="9" t="s">
         <v>483</v>
       </c>
-      <c r="D105" s="1">
+      <c r="D107" s="1">
         <v>2015</v>
       </c>
-      <c r="E105" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F105" t="s">
+      <c r="E107" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F107" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
-      <c r="A106" s="9" t="s">
+    <row r="108" spans="1:6">
+      <c r="A108" s="9" t="s">
         <v>484</v>
       </c>
-      <c r="B106" s="1" t="str">
+      <c r="B108" s="1" t="str">
         <f t="shared" si="5"/>
         <v>M</v>
       </c>
-      <c r="C106" s="9" t="s">
+      <c r="C108" s="9" t="s">
         <v>485</v>
       </c>
-      <c r="D106" s="1">
+      <c r="D108" s="1">
         <v>2015</v>
       </c>
-      <c r="E106" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F106" t="s">
+      <c r="E108" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F108" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
-      <c r="A107" s="9" t="s">
+    <row r="109" spans="1:6">
+      <c r="A109" s="9" t="s">
         <v>486</v>
       </c>
-      <c r="B107" s="1" t="str">
+      <c r="B109" s="1" t="str">
         <f t="shared" si="5"/>
         <v>S</v>
       </c>
-      <c r="C107" s="9" t="s">
+      <c r="C109" s="9" t="s">
         <v>487</v>
       </c>
-      <c r="D107" s="1">
+      <c r="D109" s="1">
         <v>2015</v>
       </c>
-      <c r="E107" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="F107" t="s">
+      <c r="E109" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="F109" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
-      <c r="A108" s="9" t="s">
+    <row r="110" spans="1:6">
+      <c r="A110" s="9" t="s">
         <v>488</v>
       </c>
-      <c r="B108" s="1" t="str">
+      <c r="B110" s="1" t="str">
         <f t="shared" si="5"/>
         <v>V</v>
       </c>
-      <c r="C108" s="9" t="s">
+      <c r="C110" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="D108" s="1">
+      <c r="D110" s="1">
         <v>2015</v>
       </c>
-      <c r="E108" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="F108" t="s">
+      <c r="E110" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="F110" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
-      <c r="A109" s="9" t="s">
+    <row r="111" spans="1:6">
+      <c r="A111" s="9" t="s">
         <v>494</v>
       </c>
-      <c r="B109" s="1" t="str">
+      <c r="B111" s="1" t="str">
         <f t="shared" si="5"/>
         <v>P</v>
       </c>
-      <c r="C109" s="9" t="s">
+      <c r="C111" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="D109" s="1">
+      <c r="D111" s="1">
         <v>2015</v>
       </c>
-      <c r="E109" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="F109" t="s">
+      <c r="E111" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="F111" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
-      <c r="A110" s="9" t="s">
+    <row r="112" spans="1:6">
+      <c r="A112" s="9" t="s">
         <v>495</v>
       </c>
-      <c r="B110" s="1" t="str">
+      <c r="B112" s="1" t="str">
         <f t="shared" si="5"/>
         <v>P</v>
       </c>
-      <c r="C110" s="9" t="s">
+      <c r="C112" s="9" t="s">
         <v>496</v>
       </c>
-      <c r="D110" s="1">
+      <c r="D112" s="1">
         <v>2015</v>
       </c>
-      <c r="E110" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="F110" t="s">
+      <c r="E112" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="F112" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
-      <c r="A111" s="9" t="s">
+    <row r="113" spans="1:6">
+      <c r="A113" s="9" t="s">
         <v>497</v>
       </c>
-      <c r="B111" s="1" t="str">
+      <c r="B113" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Z</v>
       </c>
-      <c r="C111" s="9" t="s">
+      <c r="C113" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="D111" s="1">
+      <c r="D113" s="1">
         <v>2015</v>
       </c>
-      <c r="E111" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="F111" t="s">
+      <c r="E113" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="F113" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
-      <c r="A112" s="9" t="s">
+    <row r="114" spans="1:6">
+      <c r="A114" s="9" t="s">
         <v>499</v>
       </c>
-      <c r="B112" s="1" t="str">
+      <c r="B114" s="1" t="str">
         <f t="shared" si="5"/>
         <v>B</v>
       </c>
-      <c r="C112" s="12" t="s">
+      <c r="C114" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="D112" s="1">
+      <c r="D114" s="1">
         <v>2014</v>
       </c>
-      <c r="E112" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="F112" t="s">
+      <c r="E114" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="F114" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
-      <c r="A113" s="9" t="s">
+    <row r="115" spans="1:6">
+      <c r="A115" s="9" t="s">
         <v>500</v>
       </c>
-      <c r="B113" s="1" t="str">
+      <c r="B115" s="1" t="str">
         <f t="shared" si="5"/>
         <v>B</v>
       </c>
-      <c r="C113" s="9" t="s">
+      <c r="C115" s="9" t="s">
         <v>455</v>
       </c>
-      <c r="D113" s="1">
+      <c r="D115" s="1">
         <v>2014</v>
       </c>
-      <c r="E113" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="F113" t="s">
+      <c r="E115" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="F115" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
-      <c r="A114" t="s">
+    <row r="116" spans="1:6">
+      <c r="A116" t="s">
         <v>501</v>
       </c>
-      <c r="B114" s="1" t="str">
+      <c r="B116" s="1" t="str">
         <f t="shared" si="5"/>
         <v>D</v>
       </c>
-      <c r="C114" s="9" t="s">
+      <c r="C116" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D114" s="1">
+      <c r="D116" s="1">
         <v>2014</v>
       </c>
-      <c r="E114" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="F114" t="s">
+      <c r="E116" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="F116" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
-      <c r="A115" s="9" t="s">
+    <row r="117" spans="1:6">
+      <c r="A117" s="9" t="s">
         <v>502</v>
       </c>
-      <c r="B115" s="1" t="str">
+      <c r="B117" s="1" t="str">
         <f t="shared" si="5"/>
         <v>M</v>
       </c>
-      <c r="C115" s="9" t="s">
+      <c r="C117" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="D115" s="1">
+      <c r="D117" s="1">
         <v>2014</v>
       </c>
-      <c r="E115" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="F115" t="s">
+      <c r="E117" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="F117" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
-      <c r="B116" s="1" t="str">
+    <row r="118" spans="1:6">
+      <c r="B118" s="1" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F69">
-    <sortCondition descending="1" ref="D2:D69"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:F71">
+    <sortCondition descending="1" ref="D4:D71"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="H45" r:id="rId1" xr:uid="{D3D23827-3ABF-46BA-A7B9-D1DEB1598B58}"/>
+    <hyperlink ref="H47" r:id="rId1" xr:uid="{D3D23827-3ABF-46BA-A7B9-D1DEB1598B58}"/>
+    <hyperlink ref="I47" r:id="rId2" xr:uid="{FF773514-CF47-40AC-8D35-8E57F04049F3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -7432,7 +7488,7 @@
           <x14:formula1>
             <xm:f>Ecoles!$A$2:$A$1060</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F530</xm:sqref>
+          <xm:sqref>F2:F532</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes validation" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stats_BCPST" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stats_TB" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rangs_Officiels" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stats" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -163,8 +163,13 @@
     <font>
       <sz val="9"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00AA4400"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -212,6 +217,16 @@
         <fgColor rgb="00EDE0F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE4C4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -256,7 +271,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -424,6 +439,18 @@
     <xf numFmtId="0" fontId="21" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -19110,24 +19137,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="52" t="inlineStr">
         <is>
-          <t>Rangs officiels (rapports jury) — à mettre à jour chaque année en juin</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
+          <t>Statistiques de sélectivité — à mettre à jour chaque année en juin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
       <c r="A2" s="53" t="inlineStr">
         <is>
           <t>Nom_Excel</t>
@@ -19145,39 +19174,65 @@
       </c>
       <c r="D2" s="53" t="inlineStr">
         <is>
+          <t>Rg_median</t>
+        </is>
+      </c>
+      <c r="E2" s="53" t="inlineStr">
+        <is>
           <t>Dernier</t>
         </is>
       </c>
-      <c r="E2" s="53" t="inlineStr">
+      <c r="F2" s="53" t="inlineStr">
         <is>
           <t>N_integres</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="14" customHeight="1">
-      <c r="A3" s="54" t="inlineStr">
-        <is>
-          <t>Nom de l'école (identique à l'onglet Ecoles)</t>
-        </is>
-      </c>
-      <c r="B3" s="54" t="inlineStr">
-        <is>
-          <t>BCPST, TB ou G2E</t>
-        </is>
-      </c>
-      <c r="C3" s="54" t="inlineStr">
-        <is>
-          <t>Laisser vide si pas de spécialité distincte</t>
-        </is>
-      </c>
-      <c r="D3" s="54" t="inlineStr">
-        <is>
-          <t>Rang du dernier intégré (rapport jury officiel)</t>
-        </is>
-      </c>
-      <c r="E3" s="54" t="inlineStr">
-        <is>
-          <t>Nombre d'intégrés</t>
+      <c r="G2" s="53" t="inlineStr">
+        <is>
+          <t>Concours</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="61" t="inlineStr">
+        <is>
+          <t>Nom de l'école
+(identique à l'onglet Ecoles)</t>
+        </is>
+      </c>
+      <c r="B3" s="61" t="inlineStr">
+        <is>
+          <t>Filière
+(BCPST, TB ou G2E)</t>
+        </is>
+      </c>
+      <c r="C3" s="61" t="inlineStr">
+        <is>
+          <t>Spécialité
+(vide si pas de spécialité distincte)</t>
+        </is>
+      </c>
+      <c r="D3" s="61" t="inlineStr">
+        <is>
+          <t>Rang médian
+(source : scei-concours.fr)</t>
+        </is>
+      </c>
+      <c r="E3" s="61" t="inlineStr">
+        <is>
+          <t>Rang dernier intégré
+(source : rapport jury PDF)</t>
+        </is>
+      </c>
+      <c r="F3" s="61" t="inlineStr">
+        <is>
+          <t>Nb intégrés</t>
+        </is>
+      </c>
+      <c r="G3" s="61" t="inlineStr">
+        <is>
+          <t>Classement de référence
+(BCPST, TB, Polytech Réseau…)</t>
         </is>
       </c>
     </row>
@@ -19194,10 +19249,18 @@
       </c>
       <c r="C4" s="55" t="inlineStr"/>
       <c r="D4" s="56" t="n">
+        <v>457</v>
+      </c>
+      <c r="E4" s="56" t="n">
         <v>721</v>
       </c>
-      <c r="E4" s="56" t="n">
+      <c r="F4" s="56" t="n">
         <v>274</v>
+      </c>
+      <c r="G4" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -19213,10 +19276,18 @@
       </c>
       <c r="C5" s="55" t="inlineStr"/>
       <c r="D5" s="56" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E5" s="56" t="n">
         <v>1796</v>
       </c>
-      <c r="E5" s="56" t="n">
+      <c r="F5" s="56" t="n">
         <v>88</v>
+      </c>
+      <c r="G5" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
@@ -19232,10 +19303,18 @@
       </c>
       <c r="C6" s="55" t="inlineStr"/>
       <c r="D6" s="56" t="n">
+        <v>1773</v>
+      </c>
+      <c r="E6" s="56" t="n">
         <v>2000</v>
       </c>
-      <c r="E6" s="56" t="n">
+      <c r="F6" s="56" t="n">
         <v>89</v>
+      </c>
+      <c r="G6" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
@@ -19251,10 +19330,18 @@
       </c>
       <c r="C7" s="55" t="inlineStr"/>
       <c r="D7" s="56" t="n">
+        <v>1773</v>
+      </c>
+      <c r="E7" s="56" t="n">
         <v>1768</v>
       </c>
-      <c r="E7" s="56" t="n">
+      <c r="F7" s="56" t="n">
         <v>88</v>
+      </c>
+      <c r="G7" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
@@ -19273,7 +19360,15 @@
         <v>1984</v>
       </c>
       <c r="E8" s="56" t="n">
+        <v>1984</v>
+      </c>
+      <c r="F8" s="56" t="n">
         <v>1</v>
+      </c>
+      <c r="G8" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -19293,10 +19388,18 @@
         </is>
       </c>
       <c r="D9" s="56" t="n">
+        <v>1544</v>
+      </c>
+      <c r="E9" s="56" t="n">
         <v>1824</v>
       </c>
-      <c r="E9" s="56" t="n">
+      <c r="F9" s="56" t="n">
         <v>30</v>
+      </c>
+      <c r="G9" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
@@ -19316,10 +19419,18 @@
         </is>
       </c>
       <c r="D10" s="56" t="n">
+        <v>1858</v>
+      </c>
+      <c r="E10" s="56" t="n">
         <v>2161</v>
       </c>
-      <c r="E10" s="56" t="n">
+      <c r="F10" s="56" t="n">
         <v>40</v>
+      </c>
+      <c r="G10" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -19339,10 +19450,18 @@
         </is>
       </c>
       <c r="D11" s="56" t="n">
+        <v>2006</v>
+      </c>
+      <c r="E11" s="56" t="n">
         <v>2212</v>
       </c>
-      <c r="E11" s="56" t="n">
+      <c r="F11" s="56" t="n">
         <v>28</v>
+      </c>
+      <c r="G11" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -19361,11 +19480,17 @@
           <t>Cursus agronome</t>
         </is>
       </c>
-      <c r="D12" s="56" t="n">
+      <c r="D12" s="56" t="inlineStr"/>
+      <c r="E12" s="56" t="n">
         <v>1239</v>
       </c>
-      <c r="E12" s="56" t="n">
+      <c r="F12" s="56" t="n">
         <v>113</v>
+      </c>
+      <c r="G12" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
@@ -19384,11 +19509,17 @@
           <t>Cursus SAADS</t>
         </is>
       </c>
-      <c r="D13" s="56" t="n">
+      <c r="D13" s="56" t="inlineStr"/>
+      <c r="E13" s="56" t="n">
         <v>1240</v>
       </c>
-      <c r="E13" s="56" t="n">
+      <c r="F13" s="56" t="n">
         <v>11</v>
+      </c>
+      <c r="G13" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
@@ -19407,11 +19538,17 @@
           <t>Cursus agronome</t>
         </is>
       </c>
-      <c r="D14" s="56" t="n">
+      <c r="D14" s="56" t="inlineStr"/>
+      <c r="E14" s="56" t="n">
         <v>1474</v>
       </c>
-      <c r="E14" s="56" t="n">
+      <c r="F14" s="56" t="n">
         <v>137</v>
+      </c>
+      <c r="G14" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
@@ -19430,11 +19567,17 @@
           <t>Cursus horticulture et paysage</t>
         </is>
       </c>
-      <c r="D15" s="56" t="n">
+      <c r="D15" s="56" t="inlineStr"/>
+      <c r="E15" s="56" t="n">
         <v>2188</v>
       </c>
-      <c r="E15" s="56" t="n">
+      <c r="F15" s="56" t="n">
         <v>43</v>
+      </c>
+      <c r="G15" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
@@ -19450,10 +19593,18 @@
       </c>
       <c r="C16" s="55" t="inlineStr"/>
       <c r="D16" s="56" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E16" s="56" t="n">
         <v>2210</v>
       </c>
-      <c r="E16" s="56" t="n">
+      <c r="F16" s="56" t="n">
         <v>53</v>
+      </c>
+      <c r="G16" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
@@ -19469,10 +19620,18 @@
       </c>
       <c r="C17" s="55" t="inlineStr"/>
       <c r="D17" s="56" t="n">
+        <v>1998</v>
+      </c>
+      <c r="E17" s="56" t="n">
         <v>2206</v>
       </c>
-      <c r="E17" s="56" t="n">
+      <c r="F17" s="56" t="n">
         <v>23</v>
+      </c>
+      <c r="G17" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
@@ -19488,10 +19647,18 @@
       </c>
       <c r="C18" s="55" t="inlineStr"/>
       <c r="D18" s="56" t="n">
+        <v>126</v>
+      </c>
+      <c r="E18" s="56" t="n">
         <v>282</v>
       </c>
-      <c r="E18" s="56" t="n">
+      <c r="F18" s="56" t="n">
         <v>68</v>
+      </c>
+      <c r="G18" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
@@ -19507,10 +19674,18 @@
       </c>
       <c r="C19" s="55" t="inlineStr"/>
       <c r="D19" s="56" t="n">
+        <v>61</v>
+      </c>
+      <c r="E19" s="56" t="n">
         <v>306</v>
       </c>
-      <c r="E19" s="56" t="n">
+      <c r="F19" s="56" t="n">
         <v>68</v>
+      </c>
+      <c r="G19" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
@@ -19526,10 +19701,18 @@
       </c>
       <c r="C20" s="55" t="inlineStr"/>
       <c r="D20" s="56" t="n">
+        <v>1998</v>
+      </c>
+      <c r="E20" s="56" t="n">
         <v>363</v>
       </c>
-      <c r="E20" s="56" t="n">
+      <c r="F20" s="56" t="n">
         <v>68</v>
+      </c>
+      <c r="G20" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
@@ -19545,10 +19728,18 @@
       </c>
       <c r="C21" s="55" t="inlineStr"/>
       <c r="D21" s="56" t="n">
+        <v>161</v>
+      </c>
+      <c r="E21" s="56" t="n">
         <v>295</v>
       </c>
-      <c r="E21" s="56" t="n">
+      <c r="F21" s="56" t="n">
         <v>68</v>
+      </c>
+      <c r="G21" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -19564,14 +19755,26 @@
       </c>
       <c r="C22" s="55" t="inlineStr"/>
       <c r="D22" s="56" t="n">
+        <v>556</v>
+      </c>
+      <c r="E22" s="56" t="n">
         <v>684</v>
       </c>
-      <c r="E22" s="56" t="n">
+      <c r="F22" s="56" t="n">
         <v>9</v>
       </c>
+      <c r="G22" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="55" t="inlineStr"/>
+      <c r="A23" s="55" t="inlineStr">
+        <is>
+          <t>ENSC Lille</t>
+        </is>
+      </c>
       <c r="B23" s="55" t="inlineStr">
         <is>
           <t>BCPST</t>
@@ -19579,16 +19782,24 @@
       </c>
       <c r="C23" s="55" t="inlineStr"/>
       <c r="D23" s="56" t="n">
-        <v>453</v>
+        <v>410</v>
       </c>
       <c r="E23" s="56" t="n">
-        <v>5</v>
+        <v>423</v>
+      </c>
+      <c r="F23" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="55" t="inlineStr">
         <is>
-          <t>ENSC Lille</t>
+          <t>ENSC Montpellier</t>
         </is>
       </c>
       <c r="B24" s="55" t="inlineStr">
@@ -19598,16 +19809,24 @@
       </c>
       <c r="C24" s="55" t="inlineStr"/>
       <c r="D24" s="56" t="n">
-        <v>423</v>
+        <v>192</v>
       </c>
       <c r="E24" s="56" t="n">
-        <v>3</v>
+        <v>197</v>
+      </c>
+      <c r="F24" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="55" t="inlineStr">
         <is>
-          <t>ENSC Montpellier</t>
+          <t>Chimie ParisTech</t>
         </is>
       </c>
       <c r="B25" s="55" t="inlineStr">
@@ -19617,16 +19836,24 @@
       </c>
       <c r="C25" s="55" t="inlineStr"/>
       <c r="D25" s="56" t="n">
-        <v>197</v>
+        <v>84</v>
       </c>
       <c r="E25" s="56" t="n">
-        <v>2</v>
+        <v>123</v>
+      </c>
+      <c r="F25" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="55" t="inlineStr">
         <is>
-          <t>Chimie ParisTech</t>
+          <t>ESPCI Paris</t>
         </is>
       </c>
       <c r="B26" s="55" t="inlineStr">
@@ -19636,16 +19863,24 @@
       </c>
       <c r="C26" s="55" t="inlineStr"/>
       <c r="D26" s="56" t="n">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="E26" s="56" t="n">
-        <v>4</v>
+        <v>16</v>
+      </c>
+      <c r="F26" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="55" t="inlineStr">
         <is>
-          <t>ESPCI Paris</t>
+          <t>ENSIC</t>
         </is>
       </c>
       <c r="B27" s="55" t="inlineStr">
@@ -19655,35 +19890,51 @@
       </c>
       <c r="C27" s="55" t="inlineStr"/>
       <c r="D27" s="56" t="n">
-        <v>16</v>
+        <v>512</v>
       </c>
       <c r="E27" s="56" t="n">
-        <v>2</v>
+        <v>522</v>
+      </c>
+      <c r="F27" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="55" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="55" t="inlineStr">
-        <is>
-          <t>ENSIC</t>
-        </is>
-      </c>
-      <c r="B28" s="55" t="inlineStr">
-        <is>
-          <t>BCPST</t>
-        </is>
-      </c>
-      <c r="C28" s="55" t="inlineStr"/>
-      <c r="D28" s="56" t="n">
-        <v>522</v>
-      </c>
-      <c r="E28" s="56" t="n">
-        <v>3</v>
+      <c r="A28" s="57" t="inlineStr">
+        <is>
+          <t>AgroParisTech</t>
+        </is>
+      </c>
+      <c r="B28" s="57" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="C28" s="57" t="inlineStr"/>
+      <c r="D28" s="58" t="n">
+        <v>19</v>
+      </c>
+      <c r="E28" s="58" t="n">
+        <v>47</v>
+      </c>
+      <c r="F28" s="58" t="n">
+        <v>12</v>
+      </c>
+      <c r="G28" s="57" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="57" t="inlineStr">
         <is>
-          <t>AgroParisTech</t>
+          <t>Institut Agro Rennes-Angers, campus Rennes</t>
         </is>
       </c>
       <c r="B29" s="57" t="inlineStr">
@@ -19691,18 +19942,28 @@
           <t>TB</t>
         </is>
       </c>
-      <c r="C29" s="57" t="inlineStr"/>
-      <c r="D29" s="58" t="n">
-        <v>47</v>
-      </c>
+      <c r="C29" s="57" t="inlineStr">
+        <is>
+          <t>Cursus agronome</t>
+        </is>
+      </c>
+      <c r="D29" s="58" t="inlineStr"/>
       <c r="E29" s="58" t="n">
-        <v>12</v>
+        <v>30</v>
+      </c>
+      <c r="F29" s="58" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" s="57" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="57" t="inlineStr">
         <is>
-          <t>Institut Agro Rennes-Angers, campus Rennes</t>
+          <t>Institut Agro Rennes-Angers, campus d'Angers</t>
         </is>
       </c>
       <c r="B30" s="57" t="inlineStr">
@@ -19712,20 +19973,26 @@
       </c>
       <c r="C30" s="57" t="inlineStr">
         <is>
-          <t>Cursus agronome</t>
-        </is>
-      </c>
-      <c r="D30" s="58" t="n">
-        <v>30</v>
-      </c>
+          <t>Cursus horticulture et paysage</t>
+        </is>
+      </c>
+      <c r="D30" s="58" t="inlineStr"/>
       <c r="E30" s="58" t="n">
-        <v>4</v>
+        <v>102</v>
+      </c>
+      <c r="F30" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="57" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="57" t="inlineStr">
         <is>
-          <t>Institut Agro Rennes-Angers, campus d'Angers</t>
+          <t>Institut Agro Dijon</t>
         </is>
       </c>
       <c r="B31" s="57" t="inlineStr">
@@ -19735,14 +20002,22 @@
       </c>
       <c r="C31" s="57" t="inlineStr">
         <is>
-          <t>Cursus horticulture et paysage</t>
+          <t>Cursus agroalimentaire</t>
         </is>
       </c>
       <c r="D31" s="58" t="n">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="E31" s="58" t="n">
-        <v>2</v>
+        <v>99</v>
+      </c>
+      <c r="F31" s="58" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" s="57" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -19758,20 +20033,26 @@
       </c>
       <c r="C32" s="57" t="inlineStr">
         <is>
-          <t>Cursus agroalimentaire</t>
-        </is>
-      </c>
-      <c r="D32" s="58" t="n">
-        <v>99</v>
-      </c>
+          <t>Cursus agronome (civil)</t>
+        </is>
+      </c>
+      <c r="D32" s="58" t="inlineStr"/>
       <c r="E32" s="58" t="n">
-        <v>3</v>
+        <v>60</v>
+      </c>
+      <c r="F32" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="57" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="57" t="inlineStr">
         <is>
-          <t>Institut Agro Dijon</t>
+          <t>Bordeaux Sciences Agro</t>
         </is>
       </c>
       <c r="B33" s="57" t="inlineStr">
@@ -19779,22 +20060,26 @@
           <t>TB</t>
         </is>
       </c>
-      <c r="C33" s="57" t="inlineStr">
-        <is>
-          <t>Cursus agronome (civil)</t>
-        </is>
-      </c>
+      <c r="C33" s="57" t="inlineStr"/>
       <c r="D33" s="58" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E33" s="58" t="n">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="F33" s="58" t="n">
+        <v>8</v>
+      </c>
+      <c r="G33" s="57" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="57" t="inlineStr">
         <is>
-          <t>Bordeaux Sciences Agro</t>
+          <t>ENGEES</t>
         </is>
       </c>
       <c r="B34" s="57" t="inlineStr">
@@ -19803,17 +20088,23 @@
         </is>
       </c>
       <c r="C34" s="57" t="inlineStr"/>
-      <c r="D34" s="58" t="n">
-        <v>100</v>
-      </c>
+      <c r="D34" s="58" t="inlineStr"/>
       <c r="E34" s="58" t="n">
-        <v>8</v>
+        <v>103</v>
+      </c>
+      <c r="F34" s="58" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" s="57" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="57" t="inlineStr">
         <is>
-          <t>ENGEES</t>
+          <t>ENSAIA</t>
         </is>
       </c>
       <c r="B35" s="57" t="inlineStr">
@@ -19823,16 +20114,24 @@
       </c>
       <c r="C35" s="57" t="inlineStr"/>
       <c r="D35" s="58" t="n">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="E35" s="58" t="n">
-        <v>3</v>
+        <v>97</v>
+      </c>
+      <c r="F35" s="58" t="n">
+        <v>10</v>
+      </c>
+      <c r="G35" s="57" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="57" t="inlineStr">
         <is>
-          <t>ENSAIA</t>
+          <t>ENSAT</t>
         </is>
       </c>
       <c r="B36" s="57" t="inlineStr">
@@ -19842,16 +20141,24 @@
       </c>
       <c r="C36" s="57" t="inlineStr"/>
       <c r="D36" s="58" t="n">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="E36" s="58" t="n">
-        <v>10</v>
+        <v>55</v>
+      </c>
+      <c r="F36" s="58" t="n">
+        <v>8</v>
+      </c>
+      <c r="G36" s="57" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="57" t="inlineStr">
         <is>
-          <t>ENSAT</t>
+          <t>Institut Agro Montpellier</t>
         </is>
       </c>
       <c r="B37" s="57" t="inlineStr">
@@ -19859,12 +20166,22 @@
           <t>TB</t>
         </is>
       </c>
-      <c r="C37" s="57" t="inlineStr"/>
-      <c r="D37" s="58" t="n">
-        <v>55</v>
-      </c>
+      <c r="C37" s="57" t="inlineStr">
+        <is>
+          <t>Cursus agronome</t>
+        </is>
+      </c>
+      <c r="D37" s="58" t="inlineStr"/>
       <c r="E37" s="58" t="n">
-        <v>8</v>
+        <v>61</v>
+      </c>
+      <c r="F37" s="58" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" s="57" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
@@ -19880,20 +20197,26 @@
       </c>
       <c r="C38" s="57" t="inlineStr">
         <is>
-          <t>Cursus agronome</t>
-        </is>
-      </c>
-      <c r="D38" s="58" t="n">
-        <v>61</v>
-      </c>
+          <t>Cursus SAADS</t>
+        </is>
+      </c>
+      <c r="D38" s="58" t="inlineStr"/>
       <c r="E38" s="58" t="n">
-        <v>4</v>
+        <v>101</v>
+      </c>
+      <c r="F38" s="58" t="n">
+        <v>6</v>
+      </c>
+      <c r="G38" s="57" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="57" t="inlineStr">
         <is>
-          <t>Institut Agro Montpellier</t>
+          <t>ONIRIS Nantes</t>
         </is>
       </c>
       <c r="B39" s="57" t="inlineStr">
@@ -19901,22 +20224,26 @@
           <t>TB</t>
         </is>
       </c>
-      <c r="C39" s="57" t="inlineStr">
-        <is>
-          <t>Cursus SAADS</t>
-        </is>
-      </c>
+      <c r="C39" s="57" t="inlineStr"/>
       <c r="D39" s="58" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E39" s="58" t="n">
-        <v>6</v>
+        <v>105</v>
+      </c>
+      <c r="F39" s="58" t="n">
+        <v>4</v>
+      </c>
+      <c r="G39" s="57" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="57" t="inlineStr">
         <is>
-          <t>ONIRIS Nantes</t>
+          <t>VetAgro Sup (campus Agro Clermont-Ferrand)</t>
         </is>
       </c>
       <c r="B40" s="57" t="inlineStr">
@@ -19926,35 +20253,51 @@
       </c>
       <c r="C40" s="57" t="inlineStr"/>
       <c r="D40" s="58" t="n">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="E40" s="58" t="n">
-        <v>4</v>
+        <v>98</v>
+      </c>
+      <c r="F40" s="58" t="n">
+        <v>5</v>
+      </c>
+      <c r="G40" s="57" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="57" t="inlineStr">
-        <is>
-          <t>VetAgro Sup (campus Agro Clermont-Ferrand)</t>
-        </is>
-      </c>
-      <c r="B41" s="57" t="inlineStr">
+      <c r="A41" s="62" t="inlineStr">
+        <is>
+          <t>École Nationale Vétérinaire d'Alfort (ENVA)</t>
+        </is>
+      </c>
+      <c r="B41" s="62" t="inlineStr">
         <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="C41" s="57" t="inlineStr"/>
-      <c r="D41" s="58" t="n">
-        <v>98</v>
-      </c>
-      <c r="E41" s="58" t="n">
-        <v>5</v>
+      <c r="C41" s="62" t="inlineStr"/>
+      <c r="D41" s="63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" s="63" t="n">
+        <v>12</v>
+      </c>
+      <c r="F41" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" s="62" t="inlineStr">
+        <is>
+          <t>Concours ENSTIB</t>
+        </is>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="57" t="inlineStr">
         <is>
-          <t>École Nationale Vétérinaire d'Alfort (ENVA)</t>
+          <t>VetAgro Sup (campus Véto Lyon)</t>
         </is>
       </c>
       <c r="B42" s="57" t="inlineStr">
@@ -19964,16 +20307,24 @@
       </c>
       <c r="C42" s="57" t="inlineStr"/>
       <c r="D42" s="58" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="E42" s="58" t="n">
+        <v>10</v>
+      </c>
+      <c r="F42" s="58" t="n">
         <v>2</v>
+      </c>
+      <c r="G42" s="57" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="57" t="inlineStr">
         <is>
-          <t>VetAgro Sup (campus Véto Lyon)</t>
+          <t>ONIRIS Nantes Véto</t>
         </is>
       </c>
       <c r="B43" s="57" t="inlineStr">
@@ -19983,54 +20334,78 @@
       </c>
       <c r="C43" s="57" t="inlineStr"/>
       <c r="D43" s="58" t="n">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="E43" s="58" t="n">
+        <v>11</v>
+      </c>
+      <c r="F43" s="58" t="n">
         <v>2</v>
       </c>
+      <c r="G43" s="57" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="57" t="inlineStr">
-        <is>
-          <t>ONIRIS Nantes Véto</t>
-        </is>
-      </c>
-      <c r="B44" s="57" t="inlineStr">
+      <c r="A44" s="62" t="inlineStr">
+        <is>
+          <t>École Nationale Vétérinaire de Toulouse (ENVT)</t>
+        </is>
+      </c>
+      <c r="B44" s="62" t="inlineStr">
         <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="C44" s="57" t="inlineStr"/>
-      <c r="D44" s="58" t="n">
-        <v>11</v>
-      </c>
-      <c r="E44" s="58" t="n">
-        <v>2</v>
+      <c r="C44" s="62" t="inlineStr"/>
+      <c r="D44" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" s="62" t="inlineStr">
+        <is>
+          <t>Concours ENSTIB</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="57" t="inlineStr">
         <is>
-          <t>École Nationale Vétérinaire de Toulouse (ENVT)</t>
+          <t>EIVP Paris</t>
         </is>
       </c>
       <c r="B45" s="57" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>G2E</t>
         </is>
       </c>
       <c r="C45" s="57" t="inlineStr"/>
       <c r="D45" s="58" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E45" s="58" t="n">
-        <v>3</v>
+        <v>643</v>
+      </c>
+      <c r="F45" s="58" t="n">
+        <v>5</v>
+      </c>
+      <c r="G45" s="57" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="59" t="inlineStr">
         <is>
-          <t>EIVP Paris</t>
+          <t>ENGEES</t>
         </is>
       </c>
       <c r="B46" s="59" t="inlineStr">
@@ -20039,96 +20414,152 @@
         </is>
       </c>
       <c r="C46" s="59" t="inlineStr"/>
-      <c r="D46" s="60" t="n">
-        <v>643</v>
-      </c>
+      <c r="D46" s="60" t="inlineStr"/>
       <c r="E46" s="60" t="n">
+        <v>383</v>
+      </c>
+      <c r="F46" s="60" t="n">
+        <v>8</v>
+      </c>
+      <c r="G46" s="59" t="inlineStr">
+        <is>
+          <t>G2E</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="59" t="inlineStr">
+        <is>
+          <t>ENSG Géologie Nancy</t>
+        </is>
+      </c>
+      <c r="B47" s="59" t="inlineStr">
+        <is>
+          <t>G2E</t>
+        </is>
+      </c>
+      <c r="C47" s="59" t="inlineStr"/>
+      <c r="D47" s="60" t="inlineStr"/>
+      <c r="E47" s="60" t="n">
+        <v>499</v>
+      </c>
+      <c r="F47" s="60" t="n">
+        <v>20</v>
+      </c>
+      <c r="G47" s="59" t="inlineStr">
+        <is>
+          <t>G2E</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="62" t="inlineStr">
+        <is>
+          <t>ENTPE Lyon</t>
+        </is>
+      </c>
+      <c r="B48" s="62" t="inlineStr">
+        <is>
+          <t>G2E</t>
+        </is>
+      </c>
+      <c r="C48" s="62" t="inlineStr"/>
+      <c r="D48" s="63" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" s="63" t="n">
+        <v>581</v>
+      </c>
+      <c r="F48" s="63" t="n">
+        <v>20</v>
+      </c>
+      <c r="G48" s="62" t="inlineStr">
+        <is>
+          <t>G2E</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="64" t="inlineStr">
+        <is>
+          <t>EOST Strasbourg</t>
+        </is>
+      </c>
+      <c r="B49" s="64" t="inlineStr">
+        <is>
+          <t>G2E</t>
+        </is>
+      </c>
+      <c r="C49" s="64" t="inlineStr"/>
+      <c r="D49" s="65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="65" t="n">
+        <v>686</v>
+      </c>
+      <c r="F49" s="65" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Réseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="59" t="inlineStr">
+        <is>
+          <t>IMT Mines Albi</t>
+        </is>
+      </c>
+      <c r="B50" s="59" t="inlineStr">
+        <is>
+          <t>G2E</t>
+        </is>
+      </c>
+      <c r="C50" s="59" t="inlineStr"/>
+      <c r="D50" s="60" t="inlineStr"/>
+      <c r="E50" s="60" t="n">
+        <v>198</v>
+      </c>
+      <c r="F50" s="60" t="n">
+        <v>7</v>
+      </c>
+      <c r="G50" s="59" t="inlineStr">
+        <is>
+          <t>G2E</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="59" t="inlineStr">
+        <is>
+          <t>IMT Mines Alès</t>
+        </is>
+      </c>
+      <c r="B51" s="59" t="inlineStr">
+        <is>
+          <t>G2E</t>
+        </is>
+      </c>
+      <c r="C51" s="59" t="inlineStr"/>
+      <c r="D51" s="60" t="inlineStr"/>
+      <c r="E51" s="60" t="n">
+        <v>297</v>
+      </c>
+      <c r="F51" s="60" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="59" t="inlineStr"/>
-      <c r="B47" s="59" t="inlineStr">
+      <c r="G51" s="59" t="inlineStr">
         <is>
           <t>G2E</t>
         </is>
-      </c>
-      <c r="C47" s="59" t="inlineStr"/>
-      <c r="D47" s="60" t="n">
-        <v>676</v>
-      </c>
-      <c r="E47" s="60" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="59" t="inlineStr">
-        <is>
-          <t>ENGEES</t>
-        </is>
-      </c>
-      <c r="B48" s="59" t="inlineStr">
-        <is>
-          <t>G2E</t>
-        </is>
-      </c>
-      <c r="C48" s="59" t="inlineStr"/>
-      <c r="D48" s="60" t="n">
-        <v>383</v>
-      </c>
-      <c r="E48" s="60" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="59" t="inlineStr"/>
-      <c r="B49" s="59" t="inlineStr">
-        <is>
-          <t>G2E</t>
-        </is>
-      </c>
-      <c r="C49" s="59" t="inlineStr"/>
-      <c r="D49" s="60" t="n">
-        <v>441</v>
-      </c>
-      <c r="E49" s="60" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="59" t="inlineStr"/>
-      <c r="B50" s="59" t="inlineStr">
-        <is>
-          <t>G2E</t>
-        </is>
-      </c>
-      <c r="C50" s="59" t="inlineStr"/>
-      <c r="D50" s="60" t="n">
-        <v>473</v>
-      </c>
-      <c r="E50" s="60" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="59" t="inlineStr"/>
-      <c r="B51" s="59" t="inlineStr">
-        <is>
-          <t>G2E</t>
-        </is>
-      </c>
-      <c r="C51" s="59" t="inlineStr"/>
-      <c r="D51" s="60" t="n">
-        <v>46</v>
-      </c>
-      <c r="E51" s="60" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="59" t="inlineStr">
         <is>
-          <t>ENSG Géologie Nancy</t>
+          <t>IMT Nord-Europe (Mines)</t>
         </is>
       </c>
       <c r="B52" s="59" t="inlineStr">
@@ -20137,231 +20568,661 @@
         </is>
       </c>
       <c r="C52" s="59" t="inlineStr"/>
-      <c r="D52" s="60" t="n">
-        <v>499</v>
-      </c>
+      <c r="D52" s="60" t="inlineStr"/>
       <c r="E52" s="60" t="n">
-        <v>20</v>
+        <v>463</v>
+      </c>
+      <c r="F52" s="60" t="n">
+        <v>3</v>
+      </c>
+      <c r="G52" s="59" t="inlineStr">
+        <is>
+          <t>G2E</t>
+        </is>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="59" t="inlineStr"/>
-      <c r="B53" s="59" t="inlineStr">
-        <is>
-          <t>G2E</t>
-        </is>
-      </c>
-      <c r="C53" s="59" t="inlineStr"/>
-      <c r="D53" s="60" t="n">
-        <v>365</v>
-      </c>
-      <c r="E53" s="60" t="n">
-        <v>71</v>
+      <c r="A53" s="62" t="inlineStr">
+        <is>
+          <t>Enstib</t>
+        </is>
+      </c>
+      <c r="B53" s="62" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
+      </c>
+      <c r="C53" s="62" t="inlineStr"/>
+      <c r="D53" s="63" t="n">
+        <v>30</v>
+      </c>
+      <c r="E53" s="63" t="inlineStr"/>
+      <c r="F53" s="63" t="n">
+        <v>11</v>
+      </c>
+      <c r="G53" s="62" t="inlineStr">
+        <is>
+          <t>Concours ENSTIB</t>
+        </is>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="59" t="inlineStr"/>
-      <c r="B54" s="59" t="inlineStr">
-        <is>
-          <t>G2E</t>
-        </is>
-      </c>
-      <c r="C54" s="59" t="inlineStr"/>
-      <c r="D54" s="60" t="n">
-        <v>583</v>
-      </c>
-      <c r="E54" s="60" t="n">
+      <c r="A54" s="62" t="inlineStr">
+        <is>
+          <t>Enstib</t>
+        </is>
+      </c>
+      <c r="B54" s="62" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="C54" s="62" t="inlineStr"/>
+      <c r="D54" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" s="63" t="inlineStr"/>
+      <c r="F54" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="62" t="inlineStr">
+        <is>
+          <t>Concours ENSTIB</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="64" t="inlineStr">
+        <is>
+          <t>ESIAB</t>
+        </is>
+      </c>
+      <c r="B55" s="64" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
+      </c>
+      <c r="C55" s="64" t="inlineStr">
+        <is>
+          <t>Microbiologie et Qualité / Production, Innovation , Biotechnologies en agro-alimentaire</t>
+        </is>
+      </c>
+      <c r="D55" s="65" t="n">
+        <v>904</v>
+      </c>
+      <c r="E55" s="65" t="inlineStr"/>
+      <c r="F55" s="65" t="n">
+        <v>6</v>
+      </c>
+      <c r="G55" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Réseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="64" t="inlineStr">
+        <is>
+          <t>ESIAB</t>
+        </is>
+      </c>
+      <c r="B56" s="64" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="C56" s="64" t="inlineStr">
+        <is>
+          <t>Microbiologie et Qualité / Production, Innovation , Biotechnologies en agro-alimentaire</t>
+        </is>
+      </c>
+      <c r="D56" s="65" t="n">
+        <v>30</v>
+      </c>
+      <c r="E56" s="65" t="inlineStr"/>
+      <c r="F56" s="65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Réseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="64" t="inlineStr">
+        <is>
+          <t>ESIR</t>
+        </is>
+      </c>
+      <c r="B57" s="64" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
+      </c>
+      <c r="C57" s="64" t="inlineStr">
+        <is>
+          <t>Technologies de l'information pour la santé</t>
+        </is>
+      </c>
+      <c r="D57" s="65" t="n">
+        <v>733</v>
+      </c>
+      <c r="E57" s="65" t="inlineStr"/>
+      <c r="F57" s="65" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Réseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="64" t="inlineStr">
+        <is>
+          <t>ISIFC</t>
+        </is>
+      </c>
+      <c r="B58" s="64" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
+      </c>
+      <c r="C58" s="64" t="inlineStr">
+        <is>
+          <t>Génie Biomédical</t>
+        </is>
+      </c>
+      <c r="D58" s="65" t="n">
+        <v>821</v>
+      </c>
+      <c r="E58" s="65" t="inlineStr"/>
+      <c r="F58" s="65" t="n">
+        <v>14</v>
+      </c>
+      <c r="G58" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Réseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="64" t="inlineStr">
+        <is>
+          <t>ISIFC</t>
+        </is>
+      </c>
+      <c r="B59" s="64" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="C59" s="64" t="inlineStr">
+        <is>
+          <t>Génie Biomédical</t>
+        </is>
+      </c>
+      <c r="D59" s="65" t="n">
+        <v>55</v>
+      </c>
+      <c r="E59" s="65" t="inlineStr"/>
+      <c r="F59" s="65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Réseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Angers</t>
+        </is>
+      </c>
+      <c r="B60" s="64" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
+      </c>
+      <c r="C60" s="64" t="inlineStr">
+        <is>
+          <t>Génie Biologique et Santé</t>
+        </is>
+      </c>
+      <c r="D60" s="65" t="n">
+        <v>828</v>
+      </c>
+      <c r="E60" s="65" t="inlineStr"/>
+      <c r="F60" s="65" t="n">
+        <v>3</v>
+      </c>
+      <c r="G60" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Réseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Angers</t>
+        </is>
+      </c>
+      <c r="B61" s="64" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="C61" s="64" t="inlineStr">
+        <is>
+          <t>Génie Biologique et Santé</t>
+        </is>
+      </c>
+      <c r="D61" s="65" t="n">
+        <v>52</v>
+      </c>
+      <c r="E61" s="65" t="inlineStr"/>
+      <c r="F61" s="65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Réseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Clermont</t>
+        </is>
+      </c>
+      <c r="B62" s="64" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
+      </c>
+      <c r="C62" s="64" t="inlineStr">
+        <is>
+          <t>Génie Biologique</t>
+        </is>
+      </c>
+      <c r="D62" s="65" t="n">
+        <v>817</v>
+      </c>
+      <c r="E62" s="65" t="inlineStr"/>
+      <c r="F62" s="65" t="n">
+        <v>8</v>
+      </c>
+      <c r="G62" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Réseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Clermont</t>
+        </is>
+      </c>
+      <c r="B63" s="64" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="C63" s="64" t="inlineStr">
+        <is>
+          <t>Génie Biologique</t>
+        </is>
+      </c>
+      <c r="D63" s="65" t="n">
+        <v>48</v>
+      </c>
+      <c r="E63" s="65" t="inlineStr"/>
+      <c r="F63" s="65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Réseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Tours</t>
+        </is>
+      </c>
+      <c r="B64" s="64" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
+      </c>
+      <c r="C64" s="64" t="inlineStr">
+        <is>
+          <t>Génie de l'aménagement et de l'environnement</t>
+        </is>
+      </c>
+      <c r="D64" s="65" t="n">
+        <v>910</v>
+      </c>
+      <c r="E64" s="65" t="inlineStr"/>
+      <c r="F64" s="65" t="n">
+        <v>6</v>
+      </c>
+      <c r="G64" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Réseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Nice</t>
+        </is>
+      </c>
+      <c r="B65" s="64" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
+      </c>
+      <c r="C65" s="64" t="inlineStr">
+        <is>
+          <t>Génie biologique</t>
+        </is>
+      </c>
+      <c r="D65" s="65" t="n">
+        <v>612</v>
+      </c>
+      <c r="E65" s="65" t="inlineStr"/>
+      <c r="F65" s="65" t="n">
+        <v>9</v>
+      </c>
+      <c r="G65" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Réseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Nice</t>
+        </is>
+      </c>
+      <c r="B66" s="64" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="C66" s="64" t="inlineStr">
+        <is>
+          <t>Génie biologique</t>
+        </is>
+      </c>
+      <c r="D66" s="65" t="n">
+        <v>26</v>
+      </c>
+      <c r="E66" s="65" t="inlineStr"/>
+      <c r="F66" s="65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Réseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Lille</t>
+        </is>
+      </c>
+      <c r="B67" s="64" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
+      </c>
+      <c r="C67" s="64" t="inlineStr">
+        <is>
+          <t>Génie biologique et alimentaire</t>
+        </is>
+      </c>
+      <c r="D67" s="65" t="n">
+        <v>834</v>
+      </c>
+      <c r="E67" s="65" t="inlineStr"/>
+      <c r="F67" s="65" t="n">
+        <v>6</v>
+      </c>
+      <c r="G67" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Réseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Lille</t>
+        </is>
+      </c>
+      <c r="B68" s="64" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="C68" s="64" t="inlineStr">
+        <is>
+          <t>Génie biologique et alimentaire</t>
+        </is>
+      </c>
+      <c r="D68" s="65" t="n">
+        <v>49</v>
+      </c>
+      <c r="E68" s="65" t="inlineStr"/>
+      <c r="F68" s="65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Réseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Grenoble</t>
+        </is>
+      </c>
+      <c r="B69" s="64" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
+      </c>
+      <c r="C69" s="64" t="inlineStr">
+        <is>
+          <t>Géotechnique et génie civil</t>
+        </is>
+      </c>
+      <c r="D69" s="65" t="n">
+        <v>1021</v>
+      </c>
+      <c r="E69" s="65" t="inlineStr"/>
+      <c r="F69" s="65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Réseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Marseille</t>
+        </is>
+      </c>
+      <c r="B70" s="64" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
+      </c>
+      <c r="C70" s="64" t="inlineStr">
+        <is>
+          <t>Génie Biologique, Biotechnologie</t>
+        </is>
+      </c>
+      <c r="D70" s="65" t="n">
+        <v>489</v>
+      </c>
+      <c r="E70" s="65" t="inlineStr"/>
+      <c r="F70" s="65" t="n">
+        <v>5</v>
+      </c>
+      <c r="G70" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Réseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Sorbonne</t>
+        </is>
+      </c>
+      <c r="B71" s="64" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
+      </c>
+      <c r="C71" s="64" t="inlineStr">
+        <is>
+          <t>Agroalimentaire</t>
+        </is>
+      </c>
+      <c r="D71" s="65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E71" s="65" t="inlineStr"/>
+      <c r="F71" s="65" t="n">
+        <v>6</v>
+      </c>
+      <c r="G71" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Réseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Orléans</t>
+        </is>
+      </c>
+      <c r="B72" s="64" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
+      </c>
+      <c r="C72" s="64" t="inlineStr">
+        <is>
+          <t>Génie industriel</t>
+        </is>
+      </c>
+      <c r="D72" s="65" t="n">
+        <v>1025</v>
+      </c>
+      <c r="E72" s="65" t="inlineStr"/>
+      <c r="F72" s="65" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="59" t="inlineStr"/>
-      <c r="B55" s="59" t="inlineStr">
-        <is>
-          <t>G2E</t>
-        </is>
-      </c>
-      <c r="C55" s="59" t="inlineStr"/>
-      <c r="D55" s="60" t="n">
-        <v>691</v>
-      </c>
-      <c r="E55" s="60" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="59" t="inlineStr"/>
-      <c r="B56" s="59" t="inlineStr">
-        <is>
-          <t>G2E</t>
-        </is>
-      </c>
-      <c r="C56" s="59" t="inlineStr"/>
-      <c r="D56" s="60" t="n">
-        <v>678</v>
-      </c>
-      <c r="E56" s="60" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="59" t="inlineStr"/>
-      <c r="B57" s="59" t="inlineStr">
-        <is>
-          <t>G2E</t>
-        </is>
-      </c>
-      <c r="C57" s="59" t="inlineStr"/>
-      <c r="D57" s="60" t="n">
-        <v>664</v>
-      </c>
-      <c r="E57" s="60" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="59" t="inlineStr"/>
-      <c r="B58" s="59" t="inlineStr">
-        <is>
-          <t>G2E</t>
-        </is>
-      </c>
-      <c r="C58" s="59" t="inlineStr"/>
-      <c r="D58" s="60" t="n">
-        <v>568</v>
-      </c>
-      <c r="E58" s="60" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="59" t="inlineStr">
-        <is>
-          <t>ENTPE Lyon</t>
-        </is>
-      </c>
-      <c r="B59" s="59" t="inlineStr">
-        <is>
-          <t>G2E</t>
-        </is>
-      </c>
-      <c r="C59" s="59" t="inlineStr"/>
-      <c r="D59" s="60" t="n">
-        <v>581</v>
-      </c>
-      <c r="E59" s="60" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="59" t="inlineStr"/>
-      <c r="B60" s="59" t="inlineStr">
-        <is>
-          <t>G2E</t>
-        </is>
-      </c>
-      <c r="C60" s="59" t="inlineStr"/>
-      <c r="D60" s="60" t="n">
-        <v>353</v>
-      </c>
-      <c r="E60" s="60" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="59" t="inlineStr">
-        <is>
-          <t>EOST Strasbourg</t>
-        </is>
-      </c>
-      <c r="B61" s="59" t="inlineStr">
-        <is>
-          <t>G2E</t>
-        </is>
-      </c>
-      <c r="C61" s="59" t="inlineStr"/>
-      <c r="D61" s="60" t="n">
-        <v>686</v>
-      </c>
-      <c r="E61" s="60" t="n">
+      <c r="G72" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Réseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Nantes</t>
+        </is>
+      </c>
+      <c r="B73" s="64" t="inlineStr">
+        <is>
+          <t>BCPST</t>
+        </is>
+      </c>
+      <c r="C73" s="64" t="inlineStr">
+        <is>
+          <t>Génie des Procédés et Bioprocédés</t>
+        </is>
+      </c>
+      <c r="D73" s="65" t="n">
+        <v>784</v>
+      </c>
+      <c r="E73" s="65" t="inlineStr"/>
+      <c r="F73" s="65" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="59" t="inlineStr"/>
-      <c r="B62" s="59" t="inlineStr">
-        <is>
-          <t>G2E</t>
-        </is>
-      </c>
-      <c r="C62" s="59" t="inlineStr"/>
-      <c r="D62" s="60" t="n">
-        <v>298</v>
-      </c>
-      <c r="E62" s="60" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="59" t="inlineStr">
-        <is>
-          <t>IMT Mines Albi</t>
-        </is>
-      </c>
-      <c r="B63" s="59" t="inlineStr">
-        <is>
-          <t>G2E</t>
-        </is>
-      </c>
-      <c r="C63" s="59" t="inlineStr"/>
-      <c r="D63" s="60" t="n">
-        <v>198</v>
-      </c>
-      <c r="E63" s="60" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="59" t="inlineStr">
-        <is>
-          <t>IMT Mines Alès</t>
-        </is>
-      </c>
-      <c r="B64" s="59" t="inlineStr">
-        <is>
-          <t>G2E</t>
-        </is>
-      </c>
-      <c r="C64" s="59" t="inlineStr"/>
-      <c r="D64" s="60" t="n">
-        <v>297</v>
-      </c>
-      <c r="E64" s="60" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="59" t="inlineStr">
-        <is>
-          <t>IMT Nord-Europe (Mines)</t>
-        </is>
-      </c>
-      <c r="B65" s="59" t="inlineStr">
-        <is>
-          <t>G2E</t>
-        </is>
-      </c>
-      <c r="C65" s="59" t="inlineStr"/>
-      <c r="D65" s="60" t="n">
-        <v>463</v>
-      </c>
-      <c r="E65" s="60" t="n">
-        <v>3</v>
+      <c r="G73" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Réseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Nantes</t>
+        </is>
+      </c>
+      <c r="B74" s="64" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="C74" s="64" t="inlineStr">
+        <is>
+          <t>Génie des Procédés et Bioprocédés</t>
+        </is>
+      </c>
+      <c r="D74" s="65" t="n">
+        <v>72</v>
+      </c>
+      <c r="E74" s="65" t="inlineStr"/>
+      <c r="F74" s="65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="64" t="inlineStr">
+        <is>
+          <t>Polytech Réseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="75"/>
+    <row r="76">
+      <c r="A76" s="66" t="inlineStr">
+        <is>
+          <t>⚠️  Rg_median et Dernier sont des rangs SUR LE CLASSEMENT INDIQUÉ EN COLONNE 'Concours'. Pour les Polytech Réseau et Concours ENSTIB, ce n'est PAS le classement BCPST général.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud2\Boulot 2026\Site orientation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102F0949-AE42-4ACE-93D4-C444667EA0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D750927-E284-4E88-A041-F2A6F1DFCDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elèves_BCPST" sheetId="1" r:id="rId1"/>
@@ -2952,16 +2952,6 @@
     <t>ENSTBB Bordeaux</t>
   </si>
   <si>
-    <t>L’Ecole Nationale Supérieure de
-Technologie des Biomolécules de
-Bordeaux (ENSTBB) forme, au sein de
-l’Institut Polytechnique de Bordeaux
-(Bordeaux INP), des ingénieurs
-spécialisés dans les secteurs des
-Biotechnologies pour un développement
-durable de la santé.</t>
-  </si>
-  <si>
     <t>[44.8268,-0.5968]</t>
   </si>
   <si>
@@ -2969,17 +2959,27 @@
   </si>
   <si>
     <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkBmhLT8FoCoqmFXNDUyRYg2IfV4c_sWL8Mih903hj2eQPC0nUb65V7P7_KTM6jZ0XxmRHrkW7AMrSIARAOXRycvHrchBP2beeH4BLdHMbqm9GJ9TsBJ386cIGGZWbef8vcGGo=w1333-h1000-k-no</t>
+  </si>
+  <si>
+    <t>L’Ecole Nationale Supérieure de Technologie des Biomolécules de Bordeaux (ENSTBB) forme, au sein de l’Institut Polytechnique de Bordeaux (Bordeaux INP), des ingénieurs spécialisés dans les secteurs des Biotechnologies pour un développement durable de la santé.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3261,10 +3261,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3278,64 +3278,64 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3344,44 +3344,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3393,78 +3393,84 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3825,7 +3831,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="70" t="s">
         <v>74</v>
       </c>
       <c r="B1" s="37" t="s">
@@ -3854,174 +3860,174 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="68" t="s">
         <v>965</v>
       </c>
-      <c r="B2" s="70" t="str">
+      <c r="B2" s="64" t="str">
         <f t="shared" ref="B2" si="0">LEFT(A2)</f>
         <v>B</v>
       </c>
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="64" t="s">
         <v>172</v>
       </c>
-      <c r="D2" s="70">
+      <c r="D2" s="64">
         <v>2026</v>
       </c>
-      <c r="E2" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="70" t="s">
+      <c r="E2" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="64" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="68" t="s">
         <v>963</v>
       </c>
-      <c r="B3" s="70" t="str">
+      <c r="B3" s="64" t="str">
         <f t="shared" ref="B3" si="1">LEFT(A3)</f>
         <v>B</v>
       </c>
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="64" t="s">
         <v>964</v>
       </c>
-      <c r="D3" s="70">
+      <c r="D3" s="64">
         <v>2026</v>
       </c>
-      <c r="E3" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="70" t="s">
+      <c r="E3" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="64" t="s">
         <v>188</v>
       </c>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="74" t="s">
+      <c r="A4" s="68" t="s">
         <v>956</v>
       </c>
-      <c r="B4" s="70" t="str">
+      <c r="B4" s="64" t="str">
         <f t="shared" ref="B4" si="2">LEFT(A4)</f>
         <v>K</v>
       </c>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="64" t="s">
         <v>957</v>
       </c>
-      <c r="D4" s="70">
+      <c r="D4" s="64">
         <v>2026</v>
       </c>
-      <c r="E4" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="70" t="s">
+      <c r="E4" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="64" t="s">
         <v>958</v>
       </c>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="68" t="s">
         <v>954</v>
       </c>
-      <c r="B5" s="70" t="str">
+      <c r="B5" s="64" t="str">
         <f t="shared" ref="B5" si="3">LEFT(A5)</f>
         <v>C</v>
       </c>
-      <c r="C5" s="70" t="s">
+      <c r="C5" s="64" t="s">
         <v>955</v>
       </c>
-      <c r="D5" s="70">
+      <c r="D5" s="64">
         <v>2026</v>
       </c>
-      <c r="E5" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="70" t="s">
+      <c r="E5" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="64" t="s">
         <v>136</v>
       </c>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="74" t="s">
+      <c r="A6" s="68" t="s">
         <v>952</v>
       </c>
-      <c r="B6" s="70" t="str">
+      <c r="B6" s="64" t="str">
         <f t="shared" ref="B6:B70" si="4">LEFT(A6)</f>
         <v>V</v>
       </c>
-      <c r="C6" s="70" t="s">
+      <c r="C6" s="64" t="s">
         <v>953</v>
       </c>
-      <c r="D6" s="70">
+      <c r="D6" s="64">
         <v>2026</v>
       </c>
-      <c r="E6" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="70" t="s">
+      <c r="E6" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="64" t="s">
         <v>104</v>
       </c>
-      <c r="G6" s="71" t="s">
+      <c r="G6" s="65" t="s">
         <v>182</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="75" t="s">
+      <c r="A7" s="69" t="s">
         <v>950</v>
       </c>
-      <c r="B7" s="72" t="str">
+      <c r="B7" s="66" t="str">
         <f t="shared" si="4"/>
         <v>H</v>
       </c>
-      <c r="C7" s="70" t="s">
+      <c r="C7" s="64" t="s">
         <v>951</v>
       </c>
-      <c r="D7" s="70">
+      <c r="D7" s="64">
         <v>2026</v>
       </c>
-      <c r="E7" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="70" t="s">
+      <c r="E7" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="64" t="s">
         <v>459</v>
       </c>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="72" t="s">
+      <c r="A8" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="B8" s="72" t="str">
+      <c r="B8" s="66" t="str">
         <f t="shared" si="4"/>
         <v>A</v>
       </c>
-      <c r="C8" s="72" t="s">
+      <c r="C8" s="66" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="72">
+      <c r="D8" s="66">
         <v>2025</v>
       </c>
-      <c r="E8" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="72" t="s">
+      <c r="E8" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="G8" s="72"/>
-      <c r="H8" s="73"/>
-      <c r="I8" s="73"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -6102,20 +6108,20 @@
         <f t="shared" ref="B2" si="0">LEFT(A2)</f>
         <v>B</v>
       </c>
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="64" t="s">
         <v>967</v>
       </c>
-      <c r="D2" s="70">
+      <c r="D2" s="64">
         <v>2026</v>
       </c>
-      <c r="E2" s="70" t="s">
+      <c r="E2" s="64" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>968</v>
       </c>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -6125,20 +6131,20 @@
         <f t="shared" ref="B3:B34" si="1">LEFT(A3)</f>
         <v>G</v>
       </c>
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="64" t="s">
         <v>277</v>
       </c>
-      <c r="D3" s="70">
+      <c r="D3" s="64">
         <v>2026</v>
       </c>
-      <c r="E3" s="70" t="s">
+      <c r="E3" s="64" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6148,20 +6154,20 @@
         <f t="shared" si="1"/>
         <v>R</v>
       </c>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="64" t="s">
         <v>279</v>
       </c>
-      <c r="D4" s="70">
+      <c r="D4" s="64">
         <v>2026</v>
       </c>
-      <c r="E4" s="70" t="s">
+      <c r="E4" s="64" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -10982,7 +10988,7 @@
       <c r="G71" s="46" t="s">
         <v>960</v>
       </c>
-      <c r="H71" s="69" t="s">
+      <c r="H71" s="63" t="s">
         <v>583</v>
       </c>
       <c r="I71" s="5" t="s">
@@ -10995,7 +11001,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>968</v>
       </c>
@@ -11014,20 +11020,20 @@
       <c r="F72" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="G72" s="46" t="s">
+      <c r="G72" s="77" t="s">
+        <v>972</v>
+      </c>
+      <c r="H72" s="63" t="s">
+        <v>510</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>970</v>
+      </c>
+      <c r="J72" s="33" t="s">
         <v>969</v>
       </c>
-      <c r="H72" s="69" t="s">
-        <v>510</v>
-      </c>
-      <c r="I72" s="5" t="s">
+      <c r="K72" s="78" t="s">
         <v>971</v>
-      </c>
-      <c r="J72" s="33" t="s">
-        <v>970</v>
-      </c>
-      <c r="K72" s="39" t="s">
-        <v>972</v>
       </c>
     </row>
   </sheetData>
@@ -11441,80 +11447,80 @@
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="66" t="s">
+      <c r="A28" s="73" t="s">
         <v>849</v>
       </c>
-      <c r="B28" s="64"/>
-      <c r="C28" s="64"/>
-      <c r="D28" s="64"/>
-      <c r="E28" s="64"/>
-      <c r="F28" s="64"/>
-      <c r="G28" s="64"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="64"/>
-      <c r="J28" s="64"/>
-      <c r="K28" s="64"/>
-      <c r="L28" s="64"/>
-      <c r="M28" s="64"/>
-      <c r="N28" s="64"/>
-      <c r="O28" s="64"/>
-      <c r="P28" s="64"/>
-      <c r="Q28" s="64"/>
+      <c r="B28" s="72"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="72"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="72"/>
+      <c r="I28" s="72"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="72"/>
+      <c r="M28" s="72"/>
+      <c r="N28" s="72"/>
+      <c r="O28" s="72"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="64"/>
-      <c r="B29" s="64"/>
-      <c r="C29" s="64"/>
-      <c r="D29" s="64"/>
-      <c r="E29" s="64"/>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
-      <c r="H29" s="64"/>
-      <c r="I29" s="64"/>
-      <c r="J29" s="64"/>
-      <c r="K29" s="64"/>
-      <c r="L29" s="64"/>
-      <c r="M29" s="64"/>
-      <c r="N29" s="64"/>
-      <c r="O29" s="64"/>
-      <c r="P29" s="64"/>
-      <c r="Q29" s="64"/>
+      <c r="A29" s="72"/>
+      <c r="B29" s="72"/>
+      <c r="C29" s="72"/>
+      <c r="D29" s="72"/>
+      <c r="E29" s="72"/>
+      <c r="F29" s="72"/>
+      <c r="G29" s="72"/>
+      <c r="H29" s="72"/>
+      <c r="I29" s="72"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="72"/>
+      <c r="M29" s="72"/>
+      <c r="N29" s="72"/>
+      <c r="O29" s="72"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
     </row>
     <row r="30" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="65" t="s">
+      <c r="A30" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="63" t="s">
+      <c r="B30" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="64"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="63" t="s">
+      <c r="C30" s="72"/>
+      <c r="D30" s="72"/>
+      <c r="E30" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="64"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="63" t="s">
+      <c r="F30" s="72"/>
+      <c r="G30" s="72"/>
+      <c r="H30" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="I30" s="64"/>
-      <c r="J30" s="64"/>
-      <c r="K30" s="63" t="s">
+      <c r="I30" s="72"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="L30" s="64"/>
-      <c r="M30" s="64"/>
-      <c r="N30" s="64"/>
-      <c r="O30" s="64"/>
-      <c r="P30" s="63" t="s">
+      <c r="L30" s="72"/>
+      <c r="M30" s="72"/>
+      <c r="N30" s="72"/>
+      <c r="O30" s="72"/>
+      <c r="P30" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="Q30" s="63" t="s">
+      <c r="Q30" s="71" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="64"/>
+      <c r="A31" s="72"/>
       <c r="B31" s="43" t="s">
         <v>27</v>
       </c>
@@ -11557,8 +11563,8 @@
       <c r="O31" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P31" s="64"/>
-      <c r="Q31" s="64"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
     </row>
     <row r="32" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="43" t="s">
@@ -11612,80 +11618,80 @@
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="66" t="s">
+      <c r="A33" s="73" t="s">
         <v>650</v>
       </c>
-      <c r="B33" s="64"/>
-      <c r="C33" s="64"/>
-      <c r="D33" s="64"/>
-      <c r="E33" s="64"/>
-      <c r="F33" s="64"/>
-      <c r="G33" s="64"/>
-      <c r="H33" s="64"/>
-      <c r="I33" s="64"/>
-      <c r="J33" s="64"/>
-      <c r="K33" s="64"/>
-      <c r="L33" s="64"/>
-      <c r="M33" s="64"/>
-      <c r="N33" s="64"/>
-      <c r="O33" s="64"/>
-      <c r="P33" s="64"/>
-      <c r="Q33" s="64"/>
+      <c r="B33" s="72"/>
+      <c r="C33" s="72"/>
+      <c r="D33" s="72"/>
+      <c r="E33" s="72"/>
+      <c r="F33" s="72"/>
+      <c r="G33" s="72"/>
+      <c r="H33" s="72"/>
+      <c r="I33" s="72"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="72"/>
+      <c r="M33" s="72"/>
+      <c r="N33" s="72"/>
+      <c r="O33" s="72"/>
+      <c r="P33" s="72"/>
+      <c r="Q33" s="72"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="64"/>
-      <c r="B34" s="64"/>
-      <c r="C34" s="64"/>
-      <c r="D34" s="64"/>
-      <c r="E34" s="64"/>
-      <c r="F34" s="64"/>
-      <c r="G34" s="64"/>
-      <c r="H34" s="64"/>
-      <c r="I34" s="64"/>
-      <c r="J34" s="64"/>
-      <c r="K34" s="64"/>
-      <c r="L34" s="64"/>
-      <c r="M34" s="64"/>
-      <c r="N34" s="64"/>
-      <c r="O34" s="64"/>
-      <c r="P34" s="64"/>
-      <c r="Q34" s="64"/>
+      <c r="A34" s="72"/>
+      <c r="B34" s="72"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="72"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="72"/>
+      <c r="G34" s="72"/>
+      <c r="H34" s="72"/>
+      <c r="I34" s="72"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="72"/>
+      <c r="L34" s="72"/>
+      <c r="M34" s="72"/>
+      <c r="N34" s="72"/>
+      <c r="O34" s="72"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72"/>
     </row>
     <row r="35" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="65" t="s">
+      <c r="A35" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="63" t="s">
+      <c r="B35" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="64"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="63" t="s">
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="F35" s="64"/>
-      <c r="G35" s="64"/>
-      <c r="H35" s="63" t="s">
+      <c r="F35" s="72"/>
+      <c r="G35" s="72"/>
+      <c r="H35" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="I35" s="64"/>
-      <c r="J35" s="64"/>
-      <c r="K35" s="63" t="s">
+      <c r="I35" s="72"/>
+      <c r="J35" s="72"/>
+      <c r="K35" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="64"/>
-      <c r="M35" s="64"/>
-      <c r="N35" s="64"/>
-      <c r="O35" s="64"/>
-      <c r="P35" s="63" t="s">
+      <c r="L35" s="72"/>
+      <c r="M35" s="72"/>
+      <c r="N35" s="72"/>
+      <c r="O35" s="72"/>
+      <c r="P35" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="Q35" s="63" t="s">
+      <c r="Q35" s="71" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="64"/>
+      <c r="A36" s="72"/>
       <c r="B36" s="43" t="s">
         <v>27</v>
       </c>
@@ -11728,8 +11734,8 @@
       <c r="O36" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P36" s="64"/>
-      <c r="Q36" s="64"/>
+      <c r="P36" s="72"/>
+      <c r="Q36" s="72"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="43" t="s">
@@ -12169,80 +12175,80 @@
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="66" t="s">
+      <c r="A48" s="73" t="s">
         <v>857</v>
       </c>
-      <c r="B48" s="64"/>
-      <c r="C48" s="64"/>
-      <c r="D48" s="64"/>
-      <c r="E48" s="64"/>
-      <c r="F48" s="64"/>
-      <c r="G48" s="64"/>
-      <c r="H48" s="64"/>
-      <c r="I48" s="64"/>
-      <c r="J48" s="64"/>
-      <c r="K48" s="64"/>
-      <c r="L48" s="64"/>
-      <c r="M48" s="64"/>
-      <c r="N48" s="64"/>
-      <c r="O48" s="64"/>
-      <c r="P48" s="64"/>
-      <c r="Q48" s="64"/>
+      <c r="B48" s="72"/>
+      <c r="C48" s="72"/>
+      <c r="D48" s="72"/>
+      <c r="E48" s="72"/>
+      <c r="F48" s="72"/>
+      <c r="G48" s="72"/>
+      <c r="H48" s="72"/>
+      <c r="I48" s="72"/>
+      <c r="J48" s="72"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="72"/>
+      <c r="M48" s="72"/>
+      <c r="N48" s="72"/>
+      <c r="O48" s="72"/>
+      <c r="P48" s="72"/>
+      <c r="Q48" s="72"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="64"/>
-      <c r="B49" s="64"/>
-      <c r="C49" s="64"/>
-      <c r="D49" s="64"/>
-      <c r="E49" s="64"/>
-      <c r="F49" s="64"/>
-      <c r="G49" s="64"/>
-      <c r="H49" s="64"/>
-      <c r="I49" s="64"/>
-      <c r="J49" s="64"/>
-      <c r="K49" s="64"/>
-      <c r="L49" s="64"/>
-      <c r="M49" s="64"/>
-      <c r="N49" s="64"/>
-      <c r="O49" s="64"/>
-      <c r="P49" s="64"/>
-      <c r="Q49" s="64"/>
+      <c r="A49" s="72"/>
+      <c r="B49" s="72"/>
+      <c r="C49" s="72"/>
+      <c r="D49" s="72"/>
+      <c r="E49" s="72"/>
+      <c r="F49" s="72"/>
+      <c r="G49" s="72"/>
+      <c r="H49" s="72"/>
+      <c r="I49" s="72"/>
+      <c r="J49" s="72"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="72"/>
+      <c r="M49" s="72"/>
+      <c r="N49" s="72"/>
+      <c r="O49" s="72"/>
+      <c r="P49" s="72"/>
+      <c r="Q49" s="72"/>
     </row>
     <row r="50" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="65" t="s">
+      <c r="A50" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="B50" s="63" t="s">
+      <c r="B50" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C50" s="64"/>
-      <c r="D50" s="64"/>
-      <c r="E50" s="63" t="s">
+      <c r="C50" s="72"/>
+      <c r="D50" s="72"/>
+      <c r="E50" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="F50" s="64"/>
-      <c r="G50" s="64"/>
-      <c r="H50" s="63" t="s">
+      <c r="F50" s="72"/>
+      <c r="G50" s="72"/>
+      <c r="H50" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="I50" s="64"/>
-      <c r="J50" s="64"/>
-      <c r="K50" s="63" t="s">
+      <c r="I50" s="72"/>
+      <c r="J50" s="72"/>
+      <c r="K50" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="64"/>
-      <c r="M50" s="64"/>
-      <c r="N50" s="64"/>
-      <c r="O50" s="64"/>
-      <c r="P50" s="63" t="s">
+      <c r="L50" s="72"/>
+      <c r="M50" s="72"/>
+      <c r="N50" s="72"/>
+      <c r="O50" s="72"/>
+      <c r="P50" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="Q50" s="63" t="s">
+      <c r="Q50" s="71" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51" s="64"/>
+      <c r="A51" s="72"/>
       <c r="B51" s="43" t="s">
         <v>27</v>
       </c>
@@ -12285,8 +12291,8 @@
       <c r="O51" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P51" s="64"/>
-      <c r="Q51" s="64"/>
+      <c r="P51" s="72"/>
+      <c r="Q51" s="72"/>
     </row>
     <row r="52" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="43" t="s">
@@ -12340,80 +12346,80 @@
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53" s="66" t="s">
+      <c r="A53" s="73" t="s">
         <v>859</v>
       </c>
-      <c r="B53" s="64"/>
-      <c r="C53" s="64"/>
-      <c r="D53" s="64"/>
-      <c r="E53" s="64"/>
-      <c r="F53" s="64"/>
-      <c r="G53" s="64"/>
-      <c r="H53" s="64"/>
-      <c r="I53" s="64"/>
-      <c r="J53" s="64"/>
-      <c r="K53" s="64"/>
-      <c r="L53" s="64"/>
-      <c r="M53" s="64"/>
-      <c r="N53" s="64"/>
-      <c r="O53" s="64"/>
-      <c r="P53" s="64"/>
-      <c r="Q53" s="64"/>
+      <c r="B53" s="72"/>
+      <c r="C53" s="72"/>
+      <c r="D53" s="72"/>
+      <c r="E53" s="72"/>
+      <c r="F53" s="72"/>
+      <c r="G53" s="72"/>
+      <c r="H53" s="72"/>
+      <c r="I53" s="72"/>
+      <c r="J53" s="72"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="72"/>
+      <c r="M53" s="72"/>
+      <c r="N53" s="72"/>
+      <c r="O53" s="72"/>
+      <c r="P53" s="72"/>
+      <c r="Q53" s="72"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="64"/>
-      <c r="B54" s="64"/>
-      <c r="C54" s="64"/>
-      <c r="D54" s="64"/>
-      <c r="E54" s="64"/>
-      <c r="F54" s="64"/>
-      <c r="G54" s="64"/>
-      <c r="H54" s="64"/>
-      <c r="I54" s="64"/>
-      <c r="J54" s="64"/>
-      <c r="K54" s="64"/>
-      <c r="L54" s="64"/>
-      <c r="M54" s="64"/>
-      <c r="N54" s="64"/>
-      <c r="O54" s="64"/>
-      <c r="P54" s="64"/>
-      <c r="Q54" s="64"/>
+      <c r="A54" s="72"/>
+      <c r="B54" s="72"/>
+      <c r="C54" s="72"/>
+      <c r="D54" s="72"/>
+      <c r="E54" s="72"/>
+      <c r="F54" s="72"/>
+      <c r="G54" s="72"/>
+      <c r="H54" s="72"/>
+      <c r="I54" s="72"/>
+      <c r="J54" s="72"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="72"/>
+      <c r="M54" s="72"/>
+      <c r="N54" s="72"/>
+      <c r="O54" s="72"/>
+      <c r="P54" s="72"/>
+      <c r="Q54" s="72"/>
     </row>
     <row r="55" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="65" t="s">
+      <c r="A55" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="B55" s="63" t="s">
+      <c r="B55" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C55" s="64"/>
-      <c r="D55" s="64"/>
-      <c r="E55" s="63" t="s">
+      <c r="C55" s="72"/>
+      <c r="D55" s="72"/>
+      <c r="E55" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="F55" s="64"/>
-      <c r="G55" s="64"/>
-      <c r="H55" s="63" t="s">
+      <c r="F55" s="72"/>
+      <c r="G55" s="72"/>
+      <c r="H55" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="I55" s="64"/>
-      <c r="J55" s="64"/>
-      <c r="K55" s="63" t="s">
+      <c r="I55" s="72"/>
+      <c r="J55" s="72"/>
+      <c r="K55" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="L55" s="64"/>
-      <c r="M55" s="64"/>
-      <c r="N55" s="64"/>
-      <c r="O55" s="64"/>
-      <c r="P55" s="63" t="s">
+      <c r="L55" s="72"/>
+      <c r="M55" s="72"/>
+      <c r="N55" s="72"/>
+      <c r="O55" s="72"/>
+      <c r="P55" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="Q55" s="63" t="s">
+      <c r="Q55" s="71" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="64"/>
+      <c r="A56" s="72"/>
       <c r="B56" s="43" t="s">
         <v>27</v>
       </c>
@@ -12456,8 +12462,8 @@
       <c r="O56" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P56" s="64"/>
-      <c r="Q56" s="64"/>
+      <c r="P56" s="72"/>
+      <c r="Q56" s="72"/>
     </row>
     <row r="57" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="43" t="s">
@@ -12965,80 +12971,80 @@
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A72" s="66" t="s">
+      <c r="A72" s="73" t="s">
         <v>862</v>
       </c>
-      <c r="B72" s="64"/>
-      <c r="C72" s="64"/>
-      <c r="D72" s="64"/>
-      <c r="E72" s="64"/>
-      <c r="F72" s="64"/>
-      <c r="G72" s="64"/>
-      <c r="H72" s="64"/>
-      <c r="I72" s="64"/>
-      <c r="J72" s="64"/>
-      <c r="K72" s="64"/>
-      <c r="L72" s="64"/>
-      <c r="M72" s="64"/>
-      <c r="N72" s="64"/>
-      <c r="O72" s="64"/>
-      <c r="P72" s="64"/>
-      <c r="Q72" s="64"/>
+      <c r="B72" s="72"/>
+      <c r="C72" s="72"/>
+      <c r="D72" s="72"/>
+      <c r="E72" s="72"/>
+      <c r="F72" s="72"/>
+      <c r="G72" s="72"/>
+      <c r="H72" s="72"/>
+      <c r="I72" s="72"/>
+      <c r="J72" s="72"/>
+      <c r="K72" s="72"/>
+      <c r="L72" s="72"/>
+      <c r="M72" s="72"/>
+      <c r="N72" s="72"/>
+      <c r="O72" s="72"/>
+      <c r="P72" s="72"/>
+      <c r="Q72" s="72"/>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A73" s="64"/>
-      <c r="B73" s="64"/>
-      <c r="C73" s="64"/>
-      <c r="D73" s="64"/>
-      <c r="E73" s="64"/>
-      <c r="F73" s="64"/>
-      <c r="G73" s="64"/>
-      <c r="H73" s="64"/>
-      <c r="I73" s="64"/>
-      <c r="J73" s="64"/>
-      <c r="K73" s="64"/>
-      <c r="L73" s="64"/>
-      <c r="M73" s="64"/>
-      <c r="N73" s="64"/>
-      <c r="O73" s="64"/>
-      <c r="P73" s="64"/>
-      <c r="Q73" s="64"/>
+      <c r="A73" s="72"/>
+      <c r="B73" s="72"/>
+      <c r="C73" s="72"/>
+      <c r="D73" s="72"/>
+      <c r="E73" s="72"/>
+      <c r="F73" s="72"/>
+      <c r="G73" s="72"/>
+      <c r="H73" s="72"/>
+      <c r="I73" s="72"/>
+      <c r="J73" s="72"/>
+      <c r="K73" s="72"/>
+      <c r="L73" s="72"/>
+      <c r="M73" s="72"/>
+      <c r="N73" s="72"/>
+      <c r="O73" s="72"/>
+      <c r="P73" s="72"/>
+      <c r="Q73" s="72"/>
     </row>
     <row r="74" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="65" t="s">
+      <c r="A74" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="B74" s="63" t="s">
+      <c r="B74" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C74" s="64"/>
-      <c r="D74" s="64"/>
-      <c r="E74" s="63" t="s">
+      <c r="C74" s="72"/>
+      <c r="D74" s="72"/>
+      <c r="E74" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="F74" s="64"/>
-      <c r="G74" s="64"/>
-      <c r="H74" s="63" t="s">
+      <c r="F74" s="72"/>
+      <c r="G74" s="72"/>
+      <c r="H74" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="I74" s="64"/>
-      <c r="J74" s="64"/>
-      <c r="K74" s="63" t="s">
+      <c r="I74" s="72"/>
+      <c r="J74" s="72"/>
+      <c r="K74" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="L74" s="64"/>
-      <c r="M74" s="64"/>
-      <c r="N74" s="64"/>
-      <c r="O74" s="64"/>
-      <c r="P74" s="63" t="s">
+      <c r="L74" s="72"/>
+      <c r="M74" s="72"/>
+      <c r="N74" s="72"/>
+      <c r="O74" s="72"/>
+      <c r="P74" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="Q74" s="63" t="s">
+      <c r="Q74" s="71" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75" s="64"/>
+      <c r="A75" s="72"/>
       <c r="B75" s="43" t="s">
         <v>27</v>
       </c>
@@ -13081,8 +13087,8 @@
       <c r="O75" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P75" s="64"/>
-      <c r="Q75" s="64"/>
+      <c r="P75" s="72"/>
+      <c r="Q75" s="72"/>
     </row>
     <row r="76" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="43" t="s">
@@ -13260,80 +13266,80 @@
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A81" s="66" t="s">
+      <c r="A81" s="73" t="s">
         <v>864</v>
       </c>
-      <c r="B81" s="64"/>
-      <c r="C81" s="64"/>
-      <c r="D81" s="64"/>
-      <c r="E81" s="64"/>
-      <c r="F81" s="64"/>
-      <c r="G81" s="64"/>
-      <c r="H81" s="64"/>
-      <c r="I81" s="64"/>
-      <c r="J81" s="64"/>
-      <c r="K81" s="64"/>
-      <c r="L81" s="64"/>
-      <c r="M81" s="64"/>
-      <c r="N81" s="64"/>
-      <c r="O81" s="64"/>
-      <c r="P81" s="64"/>
-      <c r="Q81" s="64"/>
+      <c r="B81" s="72"/>
+      <c r="C81" s="72"/>
+      <c r="D81" s="72"/>
+      <c r="E81" s="72"/>
+      <c r="F81" s="72"/>
+      <c r="G81" s="72"/>
+      <c r="H81" s="72"/>
+      <c r="I81" s="72"/>
+      <c r="J81" s="72"/>
+      <c r="K81" s="72"/>
+      <c r="L81" s="72"/>
+      <c r="M81" s="72"/>
+      <c r="N81" s="72"/>
+      <c r="O81" s="72"/>
+      <c r="P81" s="72"/>
+      <c r="Q81" s="72"/>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A82" s="64"/>
-      <c r="B82" s="64"/>
-      <c r="C82" s="64"/>
-      <c r="D82" s="64"/>
-      <c r="E82" s="64"/>
-      <c r="F82" s="64"/>
-      <c r="G82" s="64"/>
-      <c r="H82" s="64"/>
-      <c r="I82" s="64"/>
-      <c r="J82" s="64"/>
-      <c r="K82" s="64"/>
-      <c r="L82" s="64"/>
-      <c r="M82" s="64"/>
-      <c r="N82" s="64"/>
-      <c r="O82" s="64"/>
-      <c r="P82" s="64"/>
-      <c r="Q82" s="64"/>
+      <c r="A82" s="72"/>
+      <c r="B82" s="72"/>
+      <c r="C82" s="72"/>
+      <c r="D82" s="72"/>
+      <c r="E82" s="72"/>
+      <c r="F82" s="72"/>
+      <c r="G82" s="72"/>
+      <c r="H82" s="72"/>
+      <c r="I82" s="72"/>
+      <c r="J82" s="72"/>
+      <c r="K82" s="72"/>
+      <c r="L82" s="72"/>
+      <c r="M82" s="72"/>
+      <c r="N82" s="72"/>
+      <c r="O82" s="72"/>
+      <c r="P82" s="72"/>
+      <c r="Q82" s="72"/>
     </row>
     <row r="83" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="65" t="s">
+      <c r="A83" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="B83" s="63" t="s">
+      <c r="B83" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C83" s="64"/>
-      <c r="D83" s="64"/>
-      <c r="E83" s="63" t="s">
+      <c r="C83" s="72"/>
+      <c r="D83" s="72"/>
+      <c r="E83" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="F83" s="64"/>
-      <c r="G83" s="64"/>
-      <c r="H83" s="63" t="s">
+      <c r="F83" s="72"/>
+      <c r="G83" s="72"/>
+      <c r="H83" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="I83" s="64"/>
-      <c r="J83" s="64"/>
-      <c r="K83" s="63" t="s">
+      <c r="I83" s="72"/>
+      <c r="J83" s="72"/>
+      <c r="K83" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="L83" s="64"/>
-      <c r="M83" s="64"/>
-      <c r="N83" s="64"/>
-      <c r="O83" s="64"/>
-      <c r="P83" s="63" t="s">
+      <c r="L83" s="72"/>
+      <c r="M83" s="72"/>
+      <c r="N83" s="72"/>
+      <c r="O83" s="72"/>
+      <c r="P83" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="Q83" s="63" t="s">
+      <c r="Q83" s="71" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A84" s="64"/>
+      <c r="A84" s="72"/>
       <c r="B84" s="43" t="s">
         <v>27</v>
       </c>
@@ -13376,8 +13382,8 @@
       <c r="O84" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P84" s="64"/>
-      <c r="Q84" s="64"/>
+      <c r="P84" s="72"/>
+      <c r="Q84" s="72"/>
     </row>
     <row r="85" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="43" t="s">
@@ -13654,80 +13660,80 @@
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A93" s="66" t="s">
+      <c r="A93" s="73" t="s">
         <v>869</v>
       </c>
-      <c r="B93" s="64"/>
-      <c r="C93" s="64"/>
-      <c r="D93" s="64"/>
-      <c r="E93" s="64"/>
-      <c r="F93" s="64"/>
-      <c r="G93" s="64"/>
-      <c r="H93" s="64"/>
-      <c r="I93" s="64"/>
-      <c r="J93" s="64"/>
-      <c r="K93" s="64"/>
-      <c r="L93" s="64"/>
-      <c r="M93" s="64"/>
-      <c r="N93" s="64"/>
-      <c r="O93" s="64"/>
-      <c r="P93" s="64"/>
-      <c r="Q93" s="64"/>
+      <c r="B93" s="72"/>
+      <c r="C93" s="72"/>
+      <c r="D93" s="72"/>
+      <c r="E93" s="72"/>
+      <c r="F93" s="72"/>
+      <c r="G93" s="72"/>
+      <c r="H93" s="72"/>
+      <c r="I93" s="72"/>
+      <c r="J93" s="72"/>
+      <c r="K93" s="72"/>
+      <c r="L93" s="72"/>
+      <c r="M93" s="72"/>
+      <c r="N93" s="72"/>
+      <c r="O93" s="72"/>
+      <c r="P93" s="72"/>
+      <c r="Q93" s="72"/>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A94" s="64"/>
-      <c r="B94" s="64"/>
-      <c r="C94" s="64"/>
-      <c r="D94" s="64"/>
-      <c r="E94" s="64"/>
-      <c r="F94" s="64"/>
-      <c r="G94" s="64"/>
-      <c r="H94" s="64"/>
-      <c r="I94" s="64"/>
-      <c r="J94" s="64"/>
-      <c r="K94" s="64"/>
-      <c r="L94" s="64"/>
-      <c r="M94" s="64"/>
-      <c r="N94" s="64"/>
-      <c r="O94" s="64"/>
-      <c r="P94" s="64"/>
-      <c r="Q94" s="64"/>
+      <c r="A94" s="72"/>
+      <c r="B94" s="72"/>
+      <c r="C94" s="72"/>
+      <c r="D94" s="72"/>
+      <c r="E94" s="72"/>
+      <c r="F94" s="72"/>
+      <c r="G94" s="72"/>
+      <c r="H94" s="72"/>
+      <c r="I94" s="72"/>
+      <c r="J94" s="72"/>
+      <c r="K94" s="72"/>
+      <c r="L94" s="72"/>
+      <c r="M94" s="72"/>
+      <c r="N94" s="72"/>
+      <c r="O94" s="72"/>
+      <c r="P94" s="72"/>
+      <c r="Q94" s="72"/>
     </row>
     <row r="95" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="65" t="s">
+      <c r="A95" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="B95" s="63" t="s">
+      <c r="B95" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C95" s="64"/>
-      <c r="D95" s="64"/>
-      <c r="E95" s="63" t="s">
+      <c r="C95" s="72"/>
+      <c r="D95" s="72"/>
+      <c r="E95" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="F95" s="64"/>
-      <c r="G95" s="64"/>
-      <c r="H95" s="63" t="s">
+      <c r="F95" s="72"/>
+      <c r="G95" s="72"/>
+      <c r="H95" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="I95" s="64"/>
-      <c r="J95" s="64"/>
-      <c r="K95" s="63" t="s">
+      <c r="I95" s="72"/>
+      <c r="J95" s="72"/>
+      <c r="K95" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="L95" s="64"/>
-      <c r="M95" s="64"/>
-      <c r="N95" s="64"/>
-      <c r="O95" s="64"/>
-      <c r="P95" s="63" t="s">
+      <c r="L95" s="72"/>
+      <c r="M95" s="72"/>
+      <c r="N95" s="72"/>
+      <c r="O95" s="72"/>
+      <c r="P95" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="Q95" s="63" t="s">
+      <c r="Q95" s="71" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A96" s="64"/>
+      <c r="A96" s="72"/>
       <c r="B96" s="43" t="s">
         <v>27</v>
       </c>
@@ -13770,8 +13776,8 @@
       <c r="O96" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P96" s="64"/>
-      <c r="Q96" s="64"/>
+      <c r="P96" s="72"/>
+      <c r="Q96" s="72"/>
     </row>
     <row r="97" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="43" t="s">
@@ -14774,80 +14780,80 @@
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A127" s="66" t="s">
+      <c r="A127" s="73" t="s">
         <v>562</v>
       </c>
-      <c r="B127" s="64"/>
-      <c r="C127" s="64"/>
-      <c r="D127" s="64"/>
-      <c r="E127" s="64"/>
-      <c r="F127" s="64"/>
-      <c r="G127" s="64"/>
-      <c r="H127" s="64"/>
-      <c r="I127" s="64"/>
-      <c r="J127" s="64"/>
-      <c r="K127" s="64"/>
-      <c r="L127" s="64"/>
-      <c r="M127" s="64"/>
-      <c r="N127" s="64"/>
-      <c r="O127" s="64"/>
-      <c r="P127" s="64"/>
-      <c r="Q127" s="64"/>
+      <c r="B127" s="72"/>
+      <c r="C127" s="72"/>
+      <c r="D127" s="72"/>
+      <c r="E127" s="72"/>
+      <c r="F127" s="72"/>
+      <c r="G127" s="72"/>
+      <c r="H127" s="72"/>
+      <c r="I127" s="72"/>
+      <c r="J127" s="72"/>
+      <c r="K127" s="72"/>
+      <c r="L127" s="72"/>
+      <c r="M127" s="72"/>
+      <c r="N127" s="72"/>
+      <c r="O127" s="72"/>
+      <c r="P127" s="72"/>
+      <c r="Q127" s="72"/>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A128" s="64"/>
-      <c r="B128" s="64"/>
-      <c r="C128" s="64"/>
-      <c r="D128" s="64"/>
-      <c r="E128" s="64"/>
-      <c r="F128" s="64"/>
-      <c r="G128" s="64"/>
-      <c r="H128" s="64"/>
-      <c r="I128" s="64"/>
-      <c r="J128" s="64"/>
-      <c r="K128" s="64"/>
-      <c r="L128" s="64"/>
-      <c r="M128" s="64"/>
-      <c r="N128" s="64"/>
-      <c r="O128" s="64"/>
-      <c r="P128" s="64"/>
-      <c r="Q128" s="64"/>
+      <c r="A128" s="72"/>
+      <c r="B128" s="72"/>
+      <c r="C128" s="72"/>
+      <c r="D128" s="72"/>
+      <c r="E128" s="72"/>
+      <c r="F128" s="72"/>
+      <c r="G128" s="72"/>
+      <c r="H128" s="72"/>
+      <c r="I128" s="72"/>
+      <c r="J128" s="72"/>
+      <c r="K128" s="72"/>
+      <c r="L128" s="72"/>
+      <c r="M128" s="72"/>
+      <c r="N128" s="72"/>
+      <c r="O128" s="72"/>
+      <c r="P128" s="72"/>
+      <c r="Q128" s="72"/>
     </row>
     <row r="129" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="65" t="s">
+      <c r="A129" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="B129" s="63" t="s">
+      <c r="B129" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C129" s="64"/>
-      <c r="D129" s="64"/>
-      <c r="E129" s="63" t="s">
+      <c r="C129" s="72"/>
+      <c r="D129" s="72"/>
+      <c r="E129" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="F129" s="64"/>
-      <c r="G129" s="64"/>
-      <c r="H129" s="63" t="s">
+      <c r="F129" s="72"/>
+      <c r="G129" s="72"/>
+      <c r="H129" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="I129" s="64"/>
-      <c r="J129" s="64"/>
-      <c r="K129" s="63" t="s">
+      <c r="I129" s="72"/>
+      <c r="J129" s="72"/>
+      <c r="K129" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="L129" s="64"/>
-      <c r="M129" s="64"/>
-      <c r="N129" s="64"/>
-      <c r="O129" s="64"/>
-      <c r="P129" s="63" t="s">
+      <c r="L129" s="72"/>
+      <c r="M129" s="72"/>
+      <c r="N129" s="72"/>
+      <c r="O129" s="72"/>
+      <c r="P129" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="Q129" s="63" t="s">
+      <c r="Q129" s="71" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A130" s="64"/>
+      <c r="A130" s="72"/>
       <c r="B130" s="43" t="s">
         <v>27</v>
       </c>
@@ -14890,8 +14896,8 @@
       <c r="O130" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P130" s="64"/>
-      <c r="Q130" s="64"/>
+      <c r="P130" s="72"/>
+      <c r="Q130" s="72"/>
     </row>
     <row r="131" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="43" t="s">
@@ -16022,80 +16028,80 @@
       </c>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A159" s="66" t="s">
+      <c r="A159" s="73" t="s">
         <v>46</v>
       </c>
-      <c r="B159" s="64"/>
-      <c r="C159" s="64"/>
-      <c r="D159" s="64"/>
-      <c r="E159" s="64"/>
-      <c r="F159" s="64"/>
-      <c r="G159" s="64"/>
-      <c r="H159" s="64"/>
-      <c r="I159" s="64"/>
-      <c r="J159" s="64"/>
-      <c r="K159" s="64"/>
-      <c r="L159" s="64"/>
-      <c r="M159" s="64"/>
-      <c r="N159" s="64"/>
-      <c r="O159" s="64"/>
-      <c r="P159" s="64"/>
-      <c r="Q159" s="64"/>
+      <c r="B159" s="72"/>
+      <c r="C159" s="72"/>
+      <c r="D159" s="72"/>
+      <c r="E159" s="72"/>
+      <c r="F159" s="72"/>
+      <c r="G159" s="72"/>
+      <c r="H159" s="72"/>
+      <c r="I159" s="72"/>
+      <c r="J159" s="72"/>
+      <c r="K159" s="72"/>
+      <c r="L159" s="72"/>
+      <c r="M159" s="72"/>
+      <c r="N159" s="72"/>
+      <c r="O159" s="72"/>
+      <c r="P159" s="72"/>
+      <c r="Q159" s="72"/>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A160" s="64"/>
-      <c r="B160" s="64"/>
-      <c r="C160" s="64"/>
-      <c r="D160" s="64"/>
-      <c r="E160" s="64"/>
-      <c r="F160" s="64"/>
-      <c r="G160" s="64"/>
-      <c r="H160" s="64"/>
-      <c r="I160" s="64"/>
-      <c r="J160" s="64"/>
-      <c r="K160" s="64"/>
-      <c r="L160" s="64"/>
-      <c r="M160" s="64"/>
-      <c r="N160" s="64"/>
-      <c r="O160" s="64"/>
-      <c r="P160" s="64"/>
-      <c r="Q160" s="64"/>
+      <c r="A160" s="72"/>
+      <c r="B160" s="72"/>
+      <c r="C160" s="72"/>
+      <c r="D160" s="72"/>
+      <c r="E160" s="72"/>
+      <c r="F160" s="72"/>
+      <c r="G160" s="72"/>
+      <c r="H160" s="72"/>
+      <c r="I160" s="72"/>
+      <c r="J160" s="72"/>
+      <c r="K160" s="72"/>
+      <c r="L160" s="72"/>
+      <c r="M160" s="72"/>
+      <c r="N160" s="72"/>
+      <c r="O160" s="72"/>
+      <c r="P160" s="72"/>
+      <c r="Q160" s="72"/>
     </row>
     <row r="161" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="65" t="s">
+      <c r="A161" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="B161" s="63" t="s">
+      <c r="B161" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C161" s="64"/>
-      <c r="D161" s="64"/>
-      <c r="E161" s="63" t="s">
+      <c r="C161" s="72"/>
+      <c r="D161" s="72"/>
+      <c r="E161" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="F161" s="64"/>
-      <c r="G161" s="64"/>
-      <c r="H161" s="63" t="s">
+      <c r="F161" s="72"/>
+      <c r="G161" s="72"/>
+      <c r="H161" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="I161" s="64"/>
-      <c r="J161" s="64"/>
-      <c r="K161" s="63" t="s">
+      <c r="I161" s="72"/>
+      <c r="J161" s="72"/>
+      <c r="K161" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="L161" s="64"/>
-      <c r="M161" s="64"/>
-      <c r="N161" s="64"/>
-      <c r="O161" s="64"/>
-      <c r="P161" s="63" t="s">
+      <c r="L161" s="72"/>
+      <c r="M161" s="72"/>
+      <c r="N161" s="72"/>
+      <c r="O161" s="72"/>
+      <c r="P161" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="Q161" s="63" t="s">
+      <c r="Q161" s="71" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A162" s="64"/>
+      <c r="A162" s="72"/>
       <c r="B162" s="43" t="s">
         <v>27</v>
       </c>
@@ -16138,8 +16144,8 @@
       <c r="O162" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P162" s="64"/>
-      <c r="Q162" s="64"/>
+      <c r="P162" s="72"/>
+      <c r="Q162" s="72"/>
     </row>
     <row r="163" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="43" t="s">
@@ -16193,80 +16199,80 @@
       </c>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A164" s="66" t="s">
+      <c r="A164" s="73" t="s">
         <v>69</v>
       </c>
-      <c r="B164" s="64"/>
-      <c r="C164" s="64"/>
-      <c r="D164" s="64"/>
-      <c r="E164" s="64"/>
-      <c r="F164" s="64"/>
-      <c r="G164" s="64"/>
-      <c r="H164" s="64"/>
-      <c r="I164" s="64"/>
-      <c r="J164" s="64"/>
-      <c r="K164" s="64"/>
-      <c r="L164" s="64"/>
-      <c r="M164" s="64"/>
-      <c r="N164" s="64"/>
-      <c r="O164" s="64"/>
-      <c r="P164" s="64"/>
-      <c r="Q164" s="64"/>
+      <c r="B164" s="72"/>
+      <c r="C164" s="72"/>
+      <c r="D164" s="72"/>
+      <c r="E164" s="72"/>
+      <c r="F164" s="72"/>
+      <c r="G164" s="72"/>
+      <c r="H164" s="72"/>
+      <c r="I164" s="72"/>
+      <c r="J164" s="72"/>
+      <c r="K164" s="72"/>
+      <c r="L164" s="72"/>
+      <c r="M164" s="72"/>
+      <c r="N164" s="72"/>
+      <c r="O164" s="72"/>
+      <c r="P164" s="72"/>
+      <c r="Q164" s="72"/>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A165" s="64"/>
-      <c r="B165" s="64"/>
-      <c r="C165" s="64"/>
-      <c r="D165" s="64"/>
-      <c r="E165" s="64"/>
-      <c r="F165" s="64"/>
-      <c r="G165" s="64"/>
-      <c r="H165" s="64"/>
-      <c r="I165" s="64"/>
-      <c r="J165" s="64"/>
-      <c r="K165" s="64"/>
-      <c r="L165" s="64"/>
-      <c r="M165" s="64"/>
-      <c r="N165" s="64"/>
-      <c r="O165" s="64"/>
-      <c r="P165" s="64"/>
-      <c r="Q165" s="64"/>
+      <c r="A165" s="72"/>
+      <c r="B165" s="72"/>
+      <c r="C165" s="72"/>
+      <c r="D165" s="72"/>
+      <c r="E165" s="72"/>
+      <c r="F165" s="72"/>
+      <c r="G165" s="72"/>
+      <c r="H165" s="72"/>
+      <c r="I165" s="72"/>
+      <c r="J165" s="72"/>
+      <c r="K165" s="72"/>
+      <c r="L165" s="72"/>
+      <c r="M165" s="72"/>
+      <c r="N165" s="72"/>
+      <c r="O165" s="72"/>
+      <c r="P165" s="72"/>
+      <c r="Q165" s="72"/>
     </row>
     <row r="166" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="65" t="s">
+      <c r="A166" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="B166" s="63" t="s">
+      <c r="B166" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C166" s="64"/>
-      <c r="D166" s="64"/>
-      <c r="E166" s="63" t="s">
+      <c r="C166" s="72"/>
+      <c r="D166" s="72"/>
+      <c r="E166" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="F166" s="64"/>
-      <c r="G166" s="64"/>
-      <c r="H166" s="63" t="s">
+      <c r="F166" s="72"/>
+      <c r="G166" s="72"/>
+      <c r="H166" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="I166" s="64"/>
-      <c r="J166" s="64"/>
-      <c r="K166" s="63" t="s">
+      <c r="I166" s="72"/>
+      <c r="J166" s="72"/>
+      <c r="K166" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="L166" s="64"/>
-      <c r="M166" s="64"/>
-      <c r="N166" s="64"/>
-      <c r="O166" s="64"/>
-      <c r="P166" s="63" t="s">
+      <c r="L166" s="72"/>
+      <c r="M166" s="72"/>
+      <c r="N166" s="72"/>
+      <c r="O166" s="72"/>
+      <c r="P166" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="Q166" s="63" t="s">
+      <c r="Q166" s="71" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A167" s="64"/>
+      <c r="A167" s="72"/>
       <c r="B167" s="43" t="s">
         <v>27</v>
       </c>
@@ -16309,8 +16315,8 @@
       <c r="O167" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P167" s="64"/>
-      <c r="Q167" s="64"/>
+      <c r="P167" s="72"/>
+      <c r="Q167" s="72"/>
     </row>
     <row r="168" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="43" t="s">
@@ -16489,6 +16495,70 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="K166:O166"/>
+    <mergeCell ref="H74:J74"/>
+    <mergeCell ref="H83:J83"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="Q50:Q51"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="P74:P75"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="K129:O129"/>
+    <mergeCell ref="P95:P96"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A81:Q82"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B129:D129"/>
+    <mergeCell ref="Q166:Q167"/>
+    <mergeCell ref="Q35:Q36"/>
+    <mergeCell ref="P161:P162"/>
+    <mergeCell ref="A159:Q160"/>
+    <mergeCell ref="A93:Q94"/>
+    <mergeCell ref="Q161:Q162"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="P83:P84"/>
+    <mergeCell ref="Q129:Q130"/>
+    <mergeCell ref="Q95:Q96"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="H55:J55"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="P55:P56"/>
+    <mergeCell ref="B161:D161"/>
+    <mergeCell ref="P129:P130"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="K74:O74"/>
+    <mergeCell ref="K83:O83"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="A129:A130"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="H166:J166"/>
+    <mergeCell ref="E129:G129"/>
+    <mergeCell ref="H161:J161"/>
+    <mergeCell ref="H129:J129"/>
+    <mergeCell ref="E74:G74"/>
+    <mergeCell ref="E166:G166"/>
+    <mergeCell ref="K95:O95"/>
+    <mergeCell ref="A28:Q29"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A48:Q49"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="Q55:Q56"/>
+    <mergeCell ref="P50:P51"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="Q74:Q75"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="Q83:Q84"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="K35:O35"/>
+    <mergeCell ref="Q30:Q31"/>
+    <mergeCell ref="K50:O50"/>
     <mergeCell ref="P35:P36"/>
     <mergeCell ref="E161:G161"/>
     <mergeCell ref="K30:O30"/>
@@ -16505,70 +16575,6 @@
     <mergeCell ref="A127:Q128"/>
     <mergeCell ref="K161:O161"/>
     <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A28:Q29"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A48:Q49"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="Q55:Q56"/>
-    <mergeCell ref="P50:P51"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="Q74:Q75"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="P30:P31"/>
-    <mergeCell ref="Q83:Q84"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="K35:O35"/>
-    <mergeCell ref="Q30:Q31"/>
-    <mergeCell ref="K50:O50"/>
-    <mergeCell ref="B161:D161"/>
-    <mergeCell ref="P129:P130"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="K74:O74"/>
-    <mergeCell ref="K83:O83"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="A129:A130"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="H166:J166"/>
-    <mergeCell ref="E129:G129"/>
-    <mergeCell ref="H161:J161"/>
-    <mergeCell ref="H129:J129"/>
-    <mergeCell ref="E74:G74"/>
-    <mergeCell ref="E166:G166"/>
-    <mergeCell ref="K95:O95"/>
-    <mergeCell ref="Q166:Q167"/>
-    <mergeCell ref="Q35:Q36"/>
-    <mergeCell ref="P161:P162"/>
-    <mergeCell ref="A159:Q160"/>
-    <mergeCell ref="A93:Q94"/>
-    <mergeCell ref="Q161:Q162"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="P83:P84"/>
-    <mergeCell ref="Q129:Q130"/>
-    <mergeCell ref="Q95:Q96"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="H55:J55"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="K166:O166"/>
-    <mergeCell ref="H74:J74"/>
-    <mergeCell ref="H83:J83"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="Q50:Q51"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="P74:P75"/>
-    <mergeCell ref="E55:G55"/>
-    <mergeCell ref="K129:O129"/>
-    <mergeCell ref="P95:P96"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A81:Q82"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B129:D129"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.scei-concours.fr/stat2025/bcpst.html" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -16704,80 +16710,80 @@
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="66" t="s">
+      <c r="A24" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="64"/>
-      <c r="C24" s="64"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64"/>
-      <c r="F24" s="64"/>
-      <c r="G24" s="64"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="64"/>
-      <c r="K24" s="64"/>
-      <c r="L24" s="64"/>
-      <c r="M24" s="64"/>
-      <c r="N24" s="64"/>
-      <c r="O24" s="64"/>
-      <c r="P24" s="64"/>
-      <c r="Q24" s="64"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="72"/>
+      <c r="N24" s="72"/>
+      <c r="O24" s="72"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="64"/>
-      <c r="B25" s="64"/>
-      <c r="C25" s="64"/>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64"/>
-      <c r="F25" s="64"/>
-      <c r="G25" s="64"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="64"/>
-      <c r="J25" s="64"/>
-      <c r="K25" s="64"/>
-      <c r="L25" s="64"/>
-      <c r="M25" s="64"/>
-      <c r="N25" s="64"/>
-      <c r="O25" s="64"/>
-      <c r="P25" s="64"/>
-      <c r="Q25" s="64"/>
+      <c r="A25" s="72"/>
+      <c r="B25" s="72"/>
+      <c r="C25" s="72"/>
+      <c r="D25" s="72"/>
+      <c r="E25" s="72"/>
+      <c r="F25" s="72"/>
+      <c r="G25" s="72"/>
+      <c r="H25" s="72"/>
+      <c r="I25" s="72"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="72"/>
+      <c r="M25" s="72"/>
+      <c r="N25" s="72"/>
+      <c r="O25" s="72"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
     </row>
     <row r="26" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="65" t="s">
+      <c r="A26" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="63" t="s">
+      <c r="B26" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="64"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="63" t="s">
+      <c r="C26" s="72"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="64"/>
-      <c r="G26" s="64"/>
-      <c r="H26" s="63" t="s">
+      <c r="F26" s="72"/>
+      <c r="G26" s="72"/>
+      <c r="H26" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="I26" s="64"/>
-      <c r="J26" s="64"/>
-      <c r="K26" s="63" t="s">
+      <c r="I26" s="72"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="L26" s="64"/>
-      <c r="M26" s="64"/>
-      <c r="N26" s="64"/>
-      <c r="O26" s="64"/>
-      <c r="P26" s="63" t="s">
+      <c r="L26" s="72"/>
+      <c r="M26" s="72"/>
+      <c r="N26" s="72"/>
+      <c r="O26" s="72"/>
+      <c r="P26" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="Q26" s="63" t="s">
+      <c r="Q26" s="71" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="64"/>
+      <c r="A27" s="72"/>
       <c r="B27" s="43" t="s">
         <v>27</v>
       </c>
@@ -16820,8 +16826,8 @@
       <c r="O27" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P27" s="64"/>
-      <c r="Q27" s="64"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
     </row>
     <row r="28" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="43" t="s">
@@ -17329,80 +17335,80 @@
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="66" t="s">
+      <c r="A43" s="73" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="64"/>
-      <c r="C43" s="64"/>
-      <c r="D43" s="64"/>
-      <c r="E43" s="64"/>
-      <c r="F43" s="64"/>
-      <c r="G43" s="64"/>
-      <c r="H43" s="64"/>
-      <c r="I43" s="64"/>
-      <c r="J43" s="64"/>
-      <c r="K43" s="64"/>
-      <c r="L43" s="64"/>
-      <c r="M43" s="64"/>
-      <c r="N43" s="64"/>
-      <c r="O43" s="64"/>
-      <c r="P43" s="64"/>
-      <c r="Q43" s="64"/>
+      <c r="B43" s="72"/>
+      <c r="C43" s="72"/>
+      <c r="D43" s="72"/>
+      <c r="E43" s="72"/>
+      <c r="F43" s="72"/>
+      <c r="G43" s="72"/>
+      <c r="H43" s="72"/>
+      <c r="I43" s="72"/>
+      <c r="J43" s="72"/>
+      <c r="K43" s="72"/>
+      <c r="L43" s="72"/>
+      <c r="M43" s="72"/>
+      <c r="N43" s="72"/>
+      <c r="O43" s="72"/>
+      <c r="P43" s="72"/>
+      <c r="Q43" s="72"/>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="64"/>
-      <c r="B44" s="64"/>
-      <c r="C44" s="64"/>
-      <c r="D44" s="64"/>
-      <c r="E44" s="64"/>
-      <c r="F44" s="64"/>
-      <c r="G44" s="64"/>
-      <c r="H44" s="64"/>
-      <c r="I44" s="64"/>
-      <c r="J44" s="64"/>
-      <c r="K44" s="64"/>
-      <c r="L44" s="64"/>
-      <c r="M44" s="64"/>
-      <c r="N44" s="64"/>
-      <c r="O44" s="64"/>
-      <c r="P44" s="64"/>
-      <c r="Q44" s="64"/>
+      <c r="A44" s="72"/>
+      <c r="B44" s="72"/>
+      <c r="C44" s="72"/>
+      <c r="D44" s="72"/>
+      <c r="E44" s="72"/>
+      <c r="F44" s="72"/>
+      <c r="G44" s="72"/>
+      <c r="H44" s="72"/>
+      <c r="I44" s="72"/>
+      <c r="J44" s="72"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="72"/>
+      <c r="M44" s="72"/>
+      <c r="N44" s="72"/>
+      <c r="O44" s="72"/>
+      <c r="P44" s="72"/>
+      <c r="Q44" s="72"/>
     </row>
     <row r="45" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="65" t="s">
+      <c r="A45" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="63" t="s">
+      <c r="B45" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="64"/>
-      <c r="D45" s="64"/>
-      <c r="E45" s="63" t="s">
+      <c r="C45" s="72"/>
+      <c r="D45" s="72"/>
+      <c r="E45" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="F45" s="64"/>
-      <c r="G45" s="64"/>
-      <c r="H45" s="63" t="s">
+      <c r="F45" s="72"/>
+      <c r="G45" s="72"/>
+      <c r="H45" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="I45" s="64"/>
-      <c r="J45" s="64"/>
-      <c r="K45" s="63" t="s">
+      <c r="I45" s="72"/>
+      <c r="J45" s="72"/>
+      <c r="K45" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="64"/>
-      <c r="M45" s="64"/>
-      <c r="N45" s="64"/>
-      <c r="O45" s="64"/>
-      <c r="P45" s="63" t="s">
+      <c r="L45" s="72"/>
+      <c r="M45" s="72"/>
+      <c r="N45" s="72"/>
+      <c r="O45" s="72"/>
+      <c r="P45" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="Q45" s="63" t="s">
+      <c r="Q45" s="71" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" s="64"/>
+      <c r="A46" s="72"/>
       <c r="B46" s="43" t="s">
         <v>27</v>
       </c>
@@ -17445,8 +17451,8 @@
       <c r="O46" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P46" s="64"/>
-      <c r="Q46" s="64"/>
+      <c r="P46" s="72"/>
+      <c r="Q46" s="72"/>
     </row>
     <row r="47" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="43" t="s">
@@ -17500,80 +17506,80 @@
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="66" t="s">
+      <c r="A48" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="64"/>
-      <c r="C48" s="64"/>
-      <c r="D48" s="64"/>
-      <c r="E48" s="64"/>
-      <c r="F48" s="64"/>
-      <c r="G48" s="64"/>
-      <c r="H48" s="64"/>
-      <c r="I48" s="64"/>
-      <c r="J48" s="64"/>
-      <c r="K48" s="64"/>
-      <c r="L48" s="64"/>
-      <c r="M48" s="64"/>
-      <c r="N48" s="64"/>
-      <c r="O48" s="64"/>
-      <c r="P48" s="64"/>
-      <c r="Q48" s="64"/>
+      <c r="B48" s="72"/>
+      <c r="C48" s="72"/>
+      <c r="D48" s="72"/>
+      <c r="E48" s="72"/>
+      <c r="F48" s="72"/>
+      <c r="G48" s="72"/>
+      <c r="H48" s="72"/>
+      <c r="I48" s="72"/>
+      <c r="J48" s="72"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="72"/>
+      <c r="M48" s="72"/>
+      <c r="N48" s="72"/>
+      <c r="O48" s="72"/>
+      <c r="P48" s="72"/>
+      <c r="Q48" s="72"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="64"/>
-      <c r="B49" s="64"/>
-      <c r="C49" s="64"/>
-      <c r="D49" s="64"/>
-      <c r="E49" s="64"/>
-      <c r="F49" s="64"/>
-      <c r="G49" s="64"/>
-      <c r="H49" s="64"/>
-      <c r="I49" s="64"/>
-      <c r="J49" s="64"/>
-      <c r="K49" s="64"/>
-      <c r="L49" s="64"/>
-      <c r="M49" s="64"/>
-      <c r="N49" s="64"/>
-      <c r="O49" s="64"/>
-      <c r="P49" s="64"/>
-      <c r="Q49" s="64"/>
+      <c r="A49" s="72"/>
+      <c r="B49" s="72"/>
+      <c r="C49" s="72"/>
+      <c r="D49" s="72"/>
+      <c r="E49" s="72"/>
+      <c r="F49" s="72"/>
+      <c r="G49" s="72"/>
+      <c r="H49" s="72"/>
+      <c r="I49" s="72"/>
+      <c r="J49" s="72"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="72"/>
+      <c r="M49" s="72"/>
+      <c r="N49" s="72"/>
+      <c r="O49" s="72"/>
+      <c r="P49" s="72"/>
+      <c r="Q49" s="72"/>
     </row>
     <row r="50" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="65" t="s">
+      <c r="A50" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="B50" s="63" t="s">
+      <c r="B50" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C50" s="64"/>
-      <c r="D50" s="64"/>
-      <c r="E50" s="63" t="s">
+      <c r="C50" s="72"/>
+      <c r="D50" s="72"/>
+      <c r="E50" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="F50" s="64"/>
-      <c r="G50" s="64"/>
-      <c r="H50" s="63" t="s">
+      <c r="F50" s="72"/>
+      <c r="G50" s="72"/>
+      <c r="H50" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="I50" s="64"/>
-      <c r="J50" s="64"/>
-      <c r="K50" s="63" t="s">
+      <c r="I50" s="72"/>
+      <c r="J50" s="72"/>
+      <c r="K50" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="64"/>
-      <c r="M50" s="64"/>
-      <c r="N50" s="64"/>
-      <c r="O50" s="64"/>
-      <c r="P50" s="63" t="s">
+      <c r="L50" s="72"/>
+      <c r="M50" s="72"/>
+      <c r="N50" s="72"/>
+      <c r="O50" s="72"/>
+      <c r="P50" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="Q50" s="63" t="s">
+      <c r="Q50" s="71" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51" s="64"/>
+      <c r="A51" s="72"/>
       <c r="B51" s="43" t="s">
         <v>27</v>
       </c>
@@ -17616,8 +17622,8 @@
       <c r="O51" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P51" s="64"/>
-      <c r="Q51" s="64"/>
+      <c r="P51" s="72"/>
+      <c r="Q51" s="72"/>
     </row>
     <row r="52" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="43" t="s">
@@ -17795,80 +17801,80 @@
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57" s="66" t="s">
+      <c r="A57" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="B57" s="64"/>
-      <c r="C57" s="64"/>
-      <c r="D57" s="64"/>
-      <c r="E57" s="64"/>
-      <c r="F57" s="64"/>
-      <c r="G57" s="64"/>
-      <c r="H57" s="64"/>
-      <c r="I57" s="64"/>
-      <c r="J57" s="64"/>
-      <c r="K57" s="64"/>
-      <c r="L57" s="64"/>
-      <c r="M57" s="64"/>
-      <c r="N57" s="64"/>
-      <c r="O57" s="64"/>
-      <c r="P57" s="64"/>
-      <c r="Q57" s="64"/>
+      <c r="B57" s="72"/>
+      <c r="C57" s="72"/>
+      <c r="D57" s="72"/>
+      <c r="E57" s="72"/>
+      <c r="F57" s="72"/>
+      <c r="G57" s="72"/>
+      <c r="H57" s="72"/>
+      <c r="I57" s="72"/>
+      <c r="J57" s="72"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="72"/>
+      <c r="M57" s="72"/>
+      <c r="N57" s="72"/>
+      <c r="O57" s="72"/>
+      <c r="P57" s="72"/>
+      <c r="Q57" s="72"/>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A58" s="64"/>
-      <c r="B58" s="64"/>
-      <c r="C58" s="64"/>
-      <c r="D58" s="64"/>
-      <c r="E58" s="64"/>
-      <c r="F58" s="64"/>
-      <c r="G58" s="64"/>
-      <c r="H58" s="64"/>
-      <c r="I58" s="64"/>
-      <c r="J58" s="64"/>
-      <c r="K58" s="64"/>
-      <c r="L58" s="64"/>
-      <c r="M58" s="64"/>
-      <c r="N58" s="64"/>
-      <c r="O58" s="64"/>
-      <c r="P58" s="64"/>
-      <c r="Q58" s="64"/>
+      <c r="A58" s="72"/>
+      <c r="B58" s="72"/>
+      <c r="C58" s="72"/>
+      <c r="D58" s="72"/>
+      <c r="E58" s="72"/>
+      <c r="F58" s="72"/>
+      <c r="G58" s="72"/>
+      <c r="H58" s="72"/>
+      <c r="I58" s="72"/>
+      <c r="J58" s="72"/>
+      <c r="K58" s="72"/>
+      <c r="L58" s="72"/>
+      <c r="M58" s="72"/>
+      <c r="N58" s="72"/>
+      <c r="O58" s="72"/>
+      <c r="P58" s="72"/>
+      <c r="Q58" s="72"/>
     </row>
     <row r="59" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="65" t="s">
+      <c r="A59" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="B59" s="63" t="s">
+      <c r="B59" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C59" s="64"/>
-      <c r="D59" s="64"/>
-      <c r="E59" s="63" t="s">
+      <c r="C59" s="72"/>
+      <c r="D59" s="72"/>
+      <c r="E59" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="F59" s="64"/>
-      <c r="G59" s="64"/>
-      <c r="H59" s="63" t="s">
+      <c r="F59" s="72"/>
+      <c r="G59" s="72"/>
+      <c r="H59" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="I59" s="64"/>
-      <c r="J59" s="64"/>
-      <c r="K59" s="63" t="s">
+      <c r="I59" s="72"/>
+      <c r="J59" s="72"/>
+      <c r="K59" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="L59" s="64"/>
-      <c r="M59" s="64"/>
-      <c r="N59" s="64"/>
-      <c r="O59" s="64"/>
-      <c r="P59" s="63" t="s">
+      <c r="L59" s="72"/>
+      <c r="M59" s="72"/>
+      <c r="N59" s="72"/>
+      <c r="O59" s="72"/>
+      <c r="P59" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="Q59" s="63" t="s">
+      <c r="Q59" s="71" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A60" s="64"/>
+      <c r="A60" s="72"/>
       <c r="B60" s="43" t="s">
         <v>27</v>
       </c>
@@ -17911,8 +17917,8 @@
       <c r="O60" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P60" s="64"/>
-      <c r="Q60" s="64"/>
+      <c r="P60" s="72"/>
+      <c r="Q60" s="72"/>
     </row>
     <row r="61" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="43" t="s">
@@ -18387,80 +18393,80 @@
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75" s="66" t="s">
+      <c r="A75" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="B75" s="64"/>
-      <c r="C75" s="64"/>
-      <c r="D75" s="64"/>
-      <c r="E75" s="64"/>
-      <c r="F75" s="64"/>
-      <c r="G75" s="64"/>
-      <c r="H75" s="64"/>
-      <c r="I75" s="64"/>
-      <c r="J75" s="64"/>
-      <c r="K75" s="64"/>
-      <c r="L75" s="64"/>
-      <c r="M75" s="64"/>
-      <c r="N75" s="64"/>
-      <c r="O75" s="64"/>
-      <c r="P75" s="64"/>
-      <c r="Q75" s="64"/>
+      <c r="B75" s="72"/>
+      <c r="C75" s="72"/>
+      <c r="D75" s="72"/>
+      <c r="E75" s="72"/>
+      <c r="F75" s="72"/>
+      <c r="G75" s="72"/>
+      <c r="H75" s="72"/>
+      <c r="I75" s="72"/>
+      <c r="J75" s="72"/>
+      <c r="K75" s="72"/>
+      <c r="L75" s="72"/>
+      <c r="M75" s="72"/>
+      <c r="N75" s="72"/>
+      <c r="O75" s="72"/>
+      <c r="P75" s="72"/>
+      <c r="Q75" s="72"/>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A76" s="64"/>
-      <c r="B76" s="64"/>
-      <c r="C76" s="64"/>
-      <c r="D76" s="64"/>
-      <c r="E76" s="64"/>
-      <c r="F76" s="64"/>
-      <c r="G76" s="64"/>
-      <c r="H76" s="64"/>
-      <c r="I76" s="64"/>
-      <c r="J76" s="64"/>
-      <c r="K76" s="64"/>
-      <c r="L76" s="64"/>
-      <c r="M76" s="64"/>
-      <c r="N76" s="64"/>
-      <c r="O76" s="64"/>
-      <c r="P76" s="64"/>
-      <c r="Q76" s="64"/>
+      <c r="A76" s="72"/>
+      <c r="B76" s="72"/>
+      <c r="C76" s="72"/>
+      <c r="D76" s="72"/>
+      <c r="E76" s="72"/>
+      <c r="F76" s="72"/>
+      <c r="G76" s="72"/>
+      <c r="H76" s="72"/>
+      <c r="I76" s="72"/>
+      <c r="J76" s="72"/>
+      <c r="K76" s="72"/>
+      <c r="L76" s="72"/>
+      <c r="M76" s="72"/>
+      <c r="N76" s="72"/>
+      <c r="O76" s="72"/>
+      <c r="P76" s="72"/>
+      <c r="Q76" s="72"/>
     </row>
     <row r="77" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="65" t="s">
+      <c r="A77" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="B77" s="63" t="s">
+      <c r="B77" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C77" s="64"/>
-      <c r="D77" s="64"/>
-      <c r="E77" s="63" t="s">
+      <c r="C77" s="72"/>
+      <c r="D77" s="72"/>
+      <c r="E77" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="F77" s="64"/>
-      <c r="G77" s="64"/>
-      <c r="H77" s="63" t="s">
+      <c r="F77" s="72"/>
+      <c r="G77" s="72"/>
+      <c r="H77" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="I77" s="64"/>
-      <c r="J77" s="64"/>
-      <c r="K77" s="63" t="s">
+      <c r="I77" s="72"/>
+      <c r="J77" s="72"/>
+      <c r="K77" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="L77" s="64"/>
-      <c r="M77" s="64"/>
-      <c r="N77" s="64"/>
-      <c r="O77" s="64"/>
-      <c r="P77" s="63" t="s">
+      <c r="L77" s="72"/>
+      <c r="M77" s="72"/>
+      <c r="N77" s="72"/>
+      <c r="O77" s="72"/>
+      <c r="P77" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="Q77" s="63" t="s">
+      <c r="Q77" s="71" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A78" s="64"/>
+      <c r="A78" s="72"/>
       <c r="B78" s="43" t="s">
         <v>27</v>
       </c>
@@ -18503,8 +18509,8 @@
       <c r="O78" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P78" s="64"/>
-      <c r="Q78" s="64"/>
+      <c r="P78" s="72"/>
+      <c r="Q78" s="72"/>
     </row>
     <row r="79" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="43" t="s">
@@ -18558,80 +18564,80 @@
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A80" s="66" t="s">
+      <c r="A80" s="73" t="s">
         <v>69</v>
       </c>
-      <c r="B80" s="64"/>
-      <c r="C80" s="64"/>
-      <c r="D80" s="64"/>
-      <c r="E80" s="64"/>
-      <c r="F80" s="64"/>
-      <c r="G80" s="64"/>
-      <c r="H80" s="64"/>
-      <c r="I80" s="64"/>
-      <c r="J80" s="64"/>
-      <c r="K80" s="64"/>
-      <c r="L80" s="64"/>
-      <c r="M80" s="64"/>
-      <c r="N80" s="64"/>
-      <c r="O80" s="64"/>
-      <c r="P80" s="64"/>
-      <c r="Q80" s="64"/>
+      <c r="B80" s="72"/>
+      <c r="C80" s="72"/>
+      <c r="D80" s="72"/>
+      <c r="E80" s="72"/>
+      <c r="F80" s="72"/>
+      <c r="G80" s="72"/>
+      <c r="H80" s="72"/>
+      <c r="I80" s="72"/>
+      <c r="J80" s="72"/>
+      <c r="K80" s="72"/>
+      <c r="L80" s="72"/>
+      <c r="M80" s="72"/>
+      <c r="N80" s="72"/>
+      <c r="O80" s="72"/>
+      <c r="P80" s="72"/>
+      <c r="Q80" s="72"/>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A81" s="64"/>
-      <c r="B81" s="64"/>
-      <c r="C81" s="64"/>
-      <c r="D81" s="64"/>
-      <c r="E81" s="64"/>
-      <c r="F81" s="64"/>
-      <c r="G81" s="64"/>
-      <c r="H81" s="64"/>
-      <c r="I81" s="64"/>
-      <c r="J81" s="64"/>
-      <c r="K81" s="64"/>
-      <c r="L81" s="64"/>
-      <c r="M81" s="64"/>
-      <c r="N81" s="64"/>
-      <c r="O81" s="64"/>
-      <c r="P81" s="64"/>
-      <c r="Q81" s="64"/>
+      <c r="A81" s="72"/>
+      <c r="B81" s="72"/>
+      <c r="C81" s="72"/>
+      <c r="D81" s="72"/>
+      <c r="E81" s="72"/>
+      <c r="F81" s="72"/>
+      <c r="G81" s="72"/>
+      <c r="H81" s="72"/>
+      <c r="I81" s="72"/>
+      <c r="J81" s="72"/>
+      <c r="K81" s="72"/>
+      <c r="L81" s="72"/>
+      <c r="M81" s="72"/>
+      <c r="N81" s="72"/>
+      <c r="O81" s="72"/>
+      <c r="P81" s="72"/>
+      <c r="Q81" s="72"/>
     </row>
     <row r="82" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="65" t="s">
+      <c r="A82" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="B82" s="63" t="s">
+      <c r="B82" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C82" s="64"/>
-      <c r="D82" s="64"/>
-      <c r="E82" s="63" t="s">
+      <c r="C82" s="72"/>
+      <c r="D82" s="72"/>
+      <c r="E82" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="F82" s="64"/>
-      <c r="G82" s="64"/>
-      <c r="H82" s="63" t="s">
+      <c r="F82" s="72"/>
+      <c r="G82" s="72"/>
+      <c r="H82" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="I82" s="64"/>
-      <c r="J82" s="64"/>
-      <c r="K82" s="63" t="s">
+      <c r="I82" s="72"/>
+      <c r="J82" s="72"/>
+      <c r="K82" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="L82" s="64"/>
-      <c r="M82" s="64"/>
-      <c r="N82" s="64"/>
-      <c r="O82" s="64"/>
-      <c r="P82" s="63" t="s">
+      <c r="L82" s="72"/>
+      <c r="M82" s="72"/>
+      <c r="N82" s="72"/>
+      <c r="O82" s="72"/>
+      <c r="P82" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="Q82" s="63" t="s">
+      <c r="Q82" s="71" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A83" s="64"/>
+      <c r="A83" s="72"/>
       <c r="B83" s="43" t="s">
         <v>27</v>
       </c>
@@ -18674,8 +18680,8 @@
       <c r="O83" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P83" s="64"/>
-      <c r="Q83" s="64"/>
+      <c r="P83" s="72"/>
+      <c r="Q83" s="72"/>
     </row>
     <row r="84" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="43" t="s">
@@ -18821,38 +18827,6 @@
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="K50:O50"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="Q50:Q51"/>
-    <mergeCell ref="A43:Q44"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="P50:P51"/>
-    <mergeCell ref="K45:O45"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="K26:O26"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="K77:O77"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="A75:Q76"/>
-    <mergeCell ref="P59:P60"/>
-    <mergeCell ref="P77:P78"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="A57:Q58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="P82:P83"/>
-    <mergeCell ref="Q59:Q60"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="K59:O59"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="Q82:Q83"/>
     <mergeCell ref="A24:Q25"/>
     <mergeCell ref="K82:O82"/>
     <mergeCell ref="H50:J50"/>
@@ -18869,6 +18843,38 @@
     <mergeCell ref="H82:J82"/>
     <mergeCell ref="Q45:Q46"/>
     <mergeCell ref="A48:Q49"/>
+    <mergeCell ref="P82:P83"/>
+    <mergeCell ref="Q59:Q60"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="K59:O59"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="Q82:Q83"/>
+    <mergeCell ref="K77:O77"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="A75:Q76"/>
+    <mergeCell ref="P59:P60"/>
+    <mergeCell ref="P77:P78"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="A57:Q58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="K50:O50"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="Q50:Q51"/>
+    <mergeCell ref="A43:Q44"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="Q26:Q27"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="P50:P51"/>
+    <mergeCell ref="K45:O45"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="K26:O26"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="B45:D45"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.scei-concours.fr/stat2025/tb.html" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
@@ -18907,15 +18913,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="76" t="s">
         <v>912</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
     </row>
     <row r="2" spans="1:7" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="48" t="s">
@@ -20489,15 +20495,15 @@
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="67" t="s">
+      <c r="A78" s="75" t="s">
         <v>948</v>
       </c>
-      <c r="B78" s="64"/>
-      <c r="C78" s="64"/>
-      <c r="D78" s="64"/>
-      <c r="E78" s="64"/>
-      <c r="F78" s="64"/>
-      <c r="G78" s="64"/>
+      <c r="B78" s="72"/>
+      <c r="C78" s="72"/>
+      <c r="D78" s="72"/>
+      <c r="E78" s="72"/>
+      <c r="F78" s="72"/>
+      <c r="G78" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud2\Boulot 2026\Site orientation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D750927-E284-4E88-A041-F2A6F1DFCDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27C26428-42FD-4B4E-9ED2-4923990A402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elèves_BCPST" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="973">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2418" uniqueCount="980">
   <si>
     <t>Statistiques 2025</t>
   </si>
@@ -2963,16 +2963,51 @@
   <si>
     <t>L’Ecole Nationale Supérieure de Technologie des Biomolécules de Bordeaux (ENSTBB) forme, au sein de l’Institut Polytechnique de Bordeaux (Bordeaux INP), des ingénieurs spécialisés dans les secteurs des Biotechnologies pour un développement durable de la santé.</t>
   </si>
+  <si>
+    <t>Joan</t>
+  </si>
+  <si>
+    <t>SAVORGNANO</t>
+  </si>
+  <si>
+    <t>Jimmy</t>
+  </si>
+  <si>
+    <t>GLAZ</t>
+  </si>
+  <si>
+    <t>Marine</t>
+  </si>
+  <si>
+    <t>BOUCAUD--GAILLET</t>
+  </si>
+  <si>
+    <t>MERCIER</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3205,7 +3240,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -3258,13 +3293,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="2"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2"/>
+      </left>
+      <right style="thin">
+        <color theme="2"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3278,64 +3350,64 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3344,44 +3416,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3393,84 +3465,100 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3816,7 +3904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.42578125" customWidth="1"/>
@@ -3860,15 +3948,15 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="68" t="s">
-        <v>965</v>
+      <c r="A2" s="77" t="s">
+        <v>976</v>
       </c>
       <c r="B2" s="64" t="str">
         <f t="shared" ref="B2" si="0">LEFT(A2)</f>
-        <v>B</v>
+        <v>G</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>172</v>
+        <v>977</v>
       </c>
       <c r="D2" s="64">
         <v>2026</v>
@@ -3877,22 +3965,22 @@
         <v>1</v>
       </c>
       <c r="F2" s="64" t="s">
-        <v>112</v>
+        <v>188</v>
       </c>
       <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="68" t="s">
-        <v>963</v>
+      <c r="A3" s="73" t="s">
+        <v>974</v>
       </c>
       <c r="B3" s="64" t="str">
         <f t="shared" ref="B3" si="1">LEFT(A3)</f>
-        <v>B</v>
+        <v>S</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>964</v>
+        <v>975</v>
       </c>
       <c r="D3" s="64">
         <v>2026</v>
@@ -3901,22 +3989,24 @@
         <v>1</v>
       </c>
       <c r="F3" s="64" t="s">
-        <v>188</v>
-      </c>
-      <c r="G3" s="64"/>
+        <v>104</v>
+      </c>
+      <c r="G3" s="65" t="s">
+        <v>182</v>
+      </c>
       <c r="H3" s="64"/>
       <c r="I3" s="64"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="68" t="s">
-        <v>956</v>
+      <c r="A4" s="73" t="s">
+        <v>347</v>
       </c>
       <c r="B4" s="64" t="str">
         <f t="shared" ref="B4" si="2">LEFT(A4)</f>
-        <v>K</v>
+        <v>T</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>957</v>
+        <v>973</v>
       </c>
       <c r="D4" s="64">
         <v>2026</v>
@@ -3924,8 +4014,8 @@
       <c r="E4" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="64" t="s">
-        <v>958</v>
+      <c r="F4" s="74" t="s">
+        <v>253</v>
       </c>
       <c r="G4" s="64"/>
       <c r="H4" s="64"/>
@@ -3933,14 +4023,14 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="68" t="s">
-        <v>954</v>
+        <v>965</v>
       </c>
       <c r="B5" s="64" t="str">
         <f t="shared" ref="B5" si="3">LEFT(A5)</f>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>955</v>
+        <v>172</v>
       </c>
       <c r="D5" s="64">
         <v>2026</v>
@@ -3949,22 +4039,22 @@
         <v>1</v>
       </c>
       <c r="F5" s="64" t="s">
-        <v>136</v>
-      </c>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
+        <v>112</v>
+      </c>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="68" t="s">
-        <v>952</v>
+        <v>963</v>
       </c>
       <c r="B6" s="64" t="str">
-        <f t="shared" ref="B6:B70" si="4">LEFT(A6)</f>
-        <v>V</v>
+        <f t="shared" ref="B6" si="4">LEFT(A6)</f>
+        <v>B</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>953</v>
+        <v>964</v>
       </c>
       <c r="D6" s="64">
         <v>2026</v>
@@ -3973,24 +4063,22 @@
         <v>1</v>
       </c>
       <c r="F6" s="64" t="s">
-        <v>104</v>
-      </c>
-      <c r="G6" s="65" t="s">
-        <v>182</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="G6" s="64"/>
       <c r="H6" s="64"/>
       <c r="I6" s="64"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="69" t="s">
-        <v>950</v>
-      </c>
-      <c r="B7" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>H</v>
+      <c r="A7" s="68" t="s">
+        <v>956</v>
+      </c>
+      <c r="B7" s="64" t="str">
+        <f t="shared" ref="B7" si="5">LEFT(A7)</f>
+        <v>K</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="D7" s="64">
         <v>2026</v>
@@ -3999,112 +4087,120 @@
         <v>1</v>
       </c>
       <c r="F7" s="64" t="s">
-        <v>459</v>
+        <v>958</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="64"/>
       <c r="I7" s="64"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="66" t="s">
+      <c r="A8" s="68" t="s">
+        <v>954</v>
+      </c>
+      <c r="B8" s="64" t="str">
+        <f t="shared" ref="B8" si="6">LEFT(A8)</f>
+        <v>C</v>
+      </c>
+      <c r="C8" s="64" t="s">
+        <v>955</v>
+      </c>
+      <c r="D8" s="64">
+        <v>2026</v>
+      </c>
+      <c r="E8" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="64" t="s">
+        <v>136</v>
+      </c>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="68" t="s">
+        <v>952</v>
+      </c>
+      <c r="B9" s="64" t="str">
+        <f t="shared" ref="B9:B73" si="7">LEFT(A9)</f>
+        <v>V</v>
+      </c>
+      <c r="C9" s="64" t="s">
+        <v>953</v>
+      </c>
+      <c r="D9" s="64">
+        <v>2026</v>
+      </c>
+      <c r="E9" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="64" t="s">
+        <v>104</v>
+      </c>
+      <c r="G9" s="65" t="s">
+        <v>182</v>
+      </c>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="69" t="s">
+        <v>950</v>
+      </c>
+      <c r="B10" s="66" t="str">
+        <f t="shared" si="7"/>
+        <v>H</v>
+      </c>
+      <c r="C10" s="64" t="s">
+        <v>951</v>
+      </c>
+      <c r="D10" s="64">
+        <v>2026</v>
+      </c>
+      <c r="E10" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="64" t="s">
+        <v>459</v>
+      </c>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="B8" s="66" t="str">
-        <f t="shared" si="4"/>
+      <c r="B11" s="66" t="str">
+        <f t="shared" si="7"/>
         <v>A</v>
       </c>
-      <c r="C8" s="66" t="s">
+      <c r="C11" s="66" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="66">
+      <c r="D11" s="66">
         <v>2025</v>
       </c>
-      <c r="E8" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="66" t="s">
+      <c r="E11" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="G8" s="66"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>A</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" s="1">
-        <v>2025</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B10" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>B</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" s="1">
-        <v>2025</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B11" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>C</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D11" s="1">
-        <v>2025</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G11" s="1"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>D</v>
+        <f t="shared" si="7"/>
+        <v>A</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D12" s="1">
         <v>2025</v>
@@ -4113,20 +4209,21 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G12" s="1"/>
+      <c r="H12" s="76"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>D</v>
+        <f t="shared" si="7"/>
+        <v>B</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D13" s="1">
         <v>2025</v>
@@ -4135,20 +4232,20 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="36" t="s">
-        <v>100</v>
+      <c r="A14" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>F</v>
+        <f t="shared" si="7"/>
+        <v>C</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D14" s="1">
         <v>2025</v>
@@ -4157,20 +4254,20 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="36" t="s">
-        <v>102</v>
+      <c r="A15" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>F</v>
+        <f t="shared" si="7"/>
+        <v>D</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D15" s="1">
         <v>2025</v>
@@ -4179,20 +4276,20 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>104</v>
+        <v>37</v>
       </c>
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="36" t="s">
-        <v>105</v>
+      <c r="A16" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>G</v>
+        <f t="shared" si="7"/>
+        <v>D</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D16" s="1">
         <v>2025</v>
@@ -4201,20 +4298,20 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="36" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>H</v>
+        <f t="shared" si="7"/>
+        <v>F</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D17" s="1">
         <v>2025</v>
@@ -4223,20 +4320,20 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="36" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>J</v>
+        <f t="shared" si="7"/>
+        <v>F</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D18" s="1">
         <v>2025</v>
@@ -4245,20 +4342,20 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="36" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B19" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>L</v>
+        <f t="shared" si="7"/>
+        <v>G</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D19" s="1">
         <v>2025</v>
@@ -4267,23 +4364,20 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="G19" s="1"/>
-      <c r="H19" t="s">
-        <v>116</v>
-      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="36" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B20" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>L</v>
+        <f t="shared" si="7"/>
+        <v>H</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D20" s="1">
         <v>2025</v>
@@ -4292,20 +4386,20 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="36" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B21" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>L</v>
+        <f t="shared" si="7"/>
+        <v>J</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D21" s="1">
         <v>2025</v>
@@ -4314,20 +4408,20 @@
         <v>1</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="36" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B22" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>M</v>
+        <f t="shared" si="7"/>
+        <v>L</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D22" s="1">
         <v>2025</v>
@@ -4336,20 +4430,23 @@
         <v>1</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="G22" s="1"/>
+      <c r="H22" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="36" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B23" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>P</v>
+        <f t="shared" si="7"/>
+        <v>L</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D23" s="1">
         <v>2025</v>
@@ -4358,20 +4455,20 @@
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="36" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B24" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>S</v>
+        <f t="shared" si="7"/>
+        <v>L</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D24" s="1">
         <v>2025</v>
@@ -4380,20 +4477,20 @@
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="36" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="B25" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>V</v>
+        <f t="shared" si="7"/>
+        <v>M</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D25" s="1">
         <v>2025</v>
@@ -4402,20 +4499,20 @@
         <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="36" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="B26" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>W</v>
+        <f t="shared" si="7"/>
+        <v>P</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D26" s="1">
         <v>2025</v>
@@ -4424,86 +4521,86 @@
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="B27" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>S</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2025</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="36" t="s">
+        <v>132</v>
+      </c>
+      <c r="B28" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>V</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D28" s="1">
+        <v>2025</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="B29" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>W</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2025</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="G26" s="1"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="B27" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>B</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D27" s="1">
-        <v>2024</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="G27" s="1"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="38" t="s">
-        <v>140</v>
-      </c>
-      <c r="B28" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>B</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="D28" s="1">
-        <v>2024</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G28" s="1"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="B29" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>C</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D29" s="1">
-        <v>2024</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="38" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B30" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>D</v>
+        <f t="shared" si="7"/>
+        <v>B</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D30" s="1">
         <v>2024</v>
@@ -4512,20 +4609,20 @@
         <v>1</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="38" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B31" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>D</v>
+        <f t="shared" si="7"/>
+        <v>B</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D31" s="1">
         <v>2024</v>
@@ -4534,20 +4631,20 @@
         <v>1</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="G31" s="1"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="38" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B32" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>F</v>
+        <f t="shared" si="7"/>
+        <v>C</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="D32" s="1">
         <v>2024</v>
@@ -4556,20 +4653,20 @@
         <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="G32" s="1"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="38" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B33" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>H</v>
+        <f t="shared" si="7"/>
+        <v>D</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D33" s="1">
         <v>2024</v>
@@ -4578,20 +4675,20 @@
         <v>1</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="G33" s="1"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="38" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B34" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>H</v>
+        <f t="shared" si="7"/>
+        <v>D</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D34" s="1">
         <v>2024</v>
@@ -4600,18 +4697,20 @@
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
+      <c r="A35" s="38" t="s">
+        <v>150</v>
+      </c>
       <c r="B35" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f t="shared" si="7"/>
+        <v>F</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="D35" s="1">
         <v>2024</v>
@@ -4619,19 +4718,21 @@
       <c r="E35" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F35" s="1"/>
+      <c r="F35" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="G35" s="1"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="38" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B36" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>J</v>
+        <f t="shared" si="7"/>
+        <v>H</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D36" s="1">
         <v>2024</v>
@@ -4640,20 +4741,20 @@
         <v>1</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>94</v>
+        <v>139</v>
       </c>
       <c r="G36" s="1"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="38" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B37" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>L</v>
+        <f t="shared" si="7"/>
+        <v>H</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D37" s="1">
         <v>2024</v>
@@ -4662,20 +4763,18 @@
         <v>1</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="38" t="s">
-        <v>160</v>
-      </c>
+      <c r="A38" s="1"/>
       <c r="B38" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>N</v>
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="C38" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D38" s="1">
         <v>2024</v>
@@ -4683,24 +4782,19 @@
       <c r="E38" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>115</v>
-      </c>
+      <c r="F38" s="1"/>
       <c r="G38" s="1"/>
-      <c r="H38" t="s">
-        <v>162</v>
-      </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="38" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B39" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>N</v>
+        <f t="shared" si="7"/>
+        <v>J</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D39" s="1">
         <v>2024</v>
@@ -4709,18 +4803,20 @@
         <v>1</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="G39" s="1"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
+      <c r="A40" s="38" t="s">
+        <v>158</v>
+      </c>
       <c r="B40" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f t="shared" si="7"/>
+        <v>L</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D40" s="1">
         <v>2024</v>
@@ -4729,20 +4825,20 @@
         <v>1</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="G40" s="1"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="38" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B41" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>P</v>
+        <f t="shared" si="7"/>
+        <v>N</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D41" s="1">
         <v>2024</v>
@@ -4751,20 +4847,23 @@
         <v>1</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="G41" s="1"/>
+      <c r="H41" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="38" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B42" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>P</v>
+        <f t="shared" si="7"/>
+        <v>N</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D42" s="1">
         <v>2024</v>
@@ -4773,20 +4872,18 @@
         <v>1</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="38" t="s">
-        <v>170</v>
-      </c>
+      <c r="A43" s="1"/>
       <c r="B43" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>R</v>
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="C43" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D43" s="1">
         <v>2024</v>
@@ -4795,20 +4892,20 @@
         <v>1</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="G43" s="1"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="38" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B44" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>S</v>
+        <f t="shared" si="7"/>
+        <v>P</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D44" s="1">
         <v>2024</v>
@@ -4817,20 +4914,20 @@
         <v>1</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="G44" s="1"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="38" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B45" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>S</v>
+        <f t="shared" si="7"/>
+        <v>P</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D45" s="1">
         <v>2024</v>
@@ -4839,20 +4936,20 @@
         <v>1</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="G45" s="1"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="38" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B46" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>T</v>
+        <f t="shared" si="7"/>
+        <v>R</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="D46" s="1">
         <v>2024</v>
@@ -4861,86 +4958,86 @@
         <v>1</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="G46" s="1"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="38" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B47" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>B</v>
-      </c>
-      <c r="C47" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="D47" s="29">
-        <v>2023</v>
-      </c>
-      <c r="E47" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="G47" s="35"/>
+        <f t="shared" si="7"/>
+        <v>S</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D47" s="1">
+        <v>2024</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G47" s="1"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="38" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B48" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>B</v>
-      </c>
-      <c r="C48" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="D48" s="29">
-        <v>2023</v>
-      </c>
-      <c r="E48" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="G48" s="35"/>
+        <f t="shared" si="7"/>
+        <v>S</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D48" s="1">
+        <v>2024</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G48" s="1"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="38" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B49" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>C</v>
-      </c>
-      <c r="C49" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="D49" s="29">
-        <v>2023</v>
-      </c>
-      <c r="E49" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F49" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="G49" s="35" t="s">
-        <v>182</v>
-      </c>
+        <f t="shared" si="7"/>
+        <v>T</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D49" s="1">
+        <v>2024</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G49" s="1"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
+      <c r="A50" s="38" t="s">
+        <v>177</v>
+      </c>
       <c r="B50" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f t="shared" si="7"/>
+        <v>B</v>
       </c>
       <c r="C50" s="34" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D50" s="29">
         <v>2023</v>
@@ -4948,21 +5045,21 @@
       <c r="E50" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F50" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="G50" s="35" t="s">
-        <v>182</v>
-      </c>
+      <c r="F50" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="G50" s="35"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="1"/>
+      <c r="A51" s="38" t="s">
+        <v>179</v>
+      </c>
       <c r="B51" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f t="shared" si="7"/>
+        <v>B</v>
       </c>
       <c r="C51" s="34" t="s">
-        <v>184</v>
+        <v>128</v>
       </c>
       <c r="D51" s="29">
         <v>2023</v>
@@ -4970,21 +5067,21 @@
       <c r="E51" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F51" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="G51" s="35" t="s">
-        <v>182</v>
-      </c>
+      <c r="F51" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="G51" s="35"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="1"/>
+      <c r="A52" s="38" t="s">
+        <v>180</v>
+      </c>
       <c r="B52" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f t="shared" si="7"/>
+        <v>C</v>
       </c>
       <c r="C52" s="34" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D52" s="29">
         <v>2023</v>
@@ -4992,21 +5089,21 @@
       <c r="E52" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F52" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="G52" s="35"/>
+      <c r="F52" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="G52" s="35" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="38" t="s">
-        <v>186</v>
-      </c>
+      <c r="A53" s="1"/>
       <c r="B53" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>H</v>
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="C53" s="34" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D53" s="29">
         <v>2023</v>
@@ -5014,21 +5111,21 @@
       <c r="E53" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F53" s="35" t="s">
-        <v>188</v>
-      </c>
-      <c r="G53" s="35"/>
+      <c r="F53" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="G53" s="35" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="38" t="s">
-        <v>189</v>
-      </c>
+      <c r="A54" s="1"/>
       <c r="B54" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>J</v>
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="C54" s="34" t="s">
-        <v>84</v>
+        <v>184</v>
       </c>
       <c r="D54" s="29">
         <v>2023</v>
@@ -5036,21 +5133,21 @@
       <c r="E54" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F54" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="G54" s="35"/>
+      <c r="F54" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="G54" s="35" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="38" t="s">
-        <v>190</v>
-      </c>
+      <c r="A55" s="1"/>
       <c r="B55" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>K</v>
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="C55" s="34" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D55" s="29">
         <v>2023</v>
@@ -5059,20 +5156,20 @@
         <v>1</v>
       </c>
       <c r="F55" s="35" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="G55" s="35"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="38" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B56" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>L</v>
+        <f t="shared" si="7"/>
+        <v>H</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D56" s="29">
         <v>2023</v>
@@ -5081,20 +5178,20 @@
         <v>1</v>
       </c>
       <c r="F56" s="35" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="G56" s="35"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="38" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B57" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>M</v>
+        <f t="shared" si="7"/>
+        <v>J</v>
       </c>
       <c r="C57" s="34" t="s">
-        <v>196</v>
+        <v>84</v>
       </c>
       <c r="D57" s="29">
         <v>2023</v>
@@ -5103,20 +5200,20 @@
         <v>1</v>
       </c>
       <c r="F57" s="35" t="s">
-        <v>197</v>
+        <v>112</v>
       </c>
       <c r="G57" s="35"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="38" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B58" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>M</v>
+        <f t="shared" si="7"/>
+        <v>K</v>
       </c>
       <c r="C58" s="34" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D58" s="29">
         <v>2023</v>
@@ -5124,21 +5221,21 @@
       <c r="E58" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F58" s="30" t="s">
-        <v>104</v>
+      <c r="F58" s="35" t="s">
+        <v>112</v>
       </c>
       <c r="G58" s="35"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="38" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B59" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>M</v>
+        <f t="shared" si="7"/>
+        <v>L</v>
       </c>
       <c r="C59" s="34" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D59" s="29">
         <v>2023</v>
@@ -5147,20 +5244,20 @@
         <v>1</v>
       </c>
       <c r="F59" s="35" t="s">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="G59" s="35"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="38" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B60" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>P</v>
+        <f t="shared" si="7"/>
+        <v>M</v>
       </c>
       <c r="C60" s="34" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D60" s="29">
         <v>2023</v>
@@ -5168,21 +5265,21 @@
       <c r="E60" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F60" s="30" t="s">
-        <v>104</v>
+      <c r="F60" s="35" t="s">
+        <v>197</v>
       </c>
       <c r="G60" s="35"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="38" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B61" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>T</v>
+        <f t="shared" si="7"/>
+        <v>M</v>
       </c>
       <c r="C61" s="34" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D61" s="29">
         <v>2023</v>
@@ -5190,21 +5287,21 @@
       <c r="E61" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F61" s="35" t="s">
-        <v>169</v>
+      <c r="F61" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G61" s="35"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="38" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B62" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>T</v>
+        <f t="shared" si="7"/>
+        <v>M</v>
       </c>
       <c r="C62" s="34" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D62" s="29">
         <v>2023</v>
@@ -5213,20 +5310,20 @@
         <v>1</v>
       </c>
       <c r="F62" s="35" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="G62" s="35"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="38" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B63" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>V</v>
+        <f t="shared" si="7"/>
+        <v>P</v>
       </c>
       <c r="C63" s="34" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D63" s="29">
         <v>2023</v>
@@ -5241,80 +5338,80 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="38" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B64" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>A</v>
-      </c>
-      <c r="C64" s="35" t="s">
-        <v>211</v>
+        <f t="shared" si="7"/>
+        <v>T</v>
+      </c>
+      <c r="C64" s="34" t="s">
+        <v>205</v>
       </c>
       <c r="D64" s="29">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E64" s="29" t="s">
         <v>1</v>
       </c>
       <c r="F64" s="35" t="s">
-        <v>212</v>
+        <v>169</v>
       </c>
       <c r="G64" s="35"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="38" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B65" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>A</v>
-      </c>
-      <c r="C65" s="35" t="s">
-        <v>214</v>
+        <f t="shared" si="7"/>
+        <v>T</v>
+      </c>
+      <c r="C65" s="34" t="s">
+        <v>207</v>
       </c>
       <c r="D65" s="29">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E65" s="29" t="s">
         <v>1</v>
       </c>
       <c r="F65" s="35" t="s">
-        <v>188</v>
+        <v>85</v>
       </c>
       <c r="G65" s="35"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="38" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B66" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>B</v>
-      </c>
-      <c r="C66" s="35" t="s">
-        <v>216</v>
+        <f t="shared" si="7"/>
+        <v>V</v>
+      </c>
+      <c r="C66" s="34" t="s">
+        <v>209</v>
       </c>
       <c r="D66" s="29">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E66" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F66" s="35" t="s">
-        <v>37</v>
+      <c r="F66" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G66" s="35"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="38" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B67" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>C</v>
+        <f t="shared" si="7"/>
+        <v>A</v>
       </c>
       <c r="C67" s="35" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D67" s="29">
         <v>2022</v>
@@ -5323,20 +5420,20 @@
         <v>1</v>
       </c>
       <c r="F67" s="35" t="s">
-        <v>112</v>
+        <v>212</v>
       </c>
       <c r="G67" s="35"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="38" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B68" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>D</v>
+        <f t="shared" si="7"/>
+        <v>A</v>
       </c>
       <c r="C68" s="35" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D68" s="29">
         <v>2022</v>
@@ -5345,20 +5442,20 @@
         <v>1</v>
       </c>
       <c r="F68" s="35" t="s">
-        <v>122</v>
+        <v>188</v>
       </c>
       <c r="G68" s="35"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="38" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B69" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>D</v>
+        <f t="shared" si="7"/>
+        <v>B</v>
       </c>
       <c r="C69" s="35" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D69" s="29">
         <v>2022</v>
@@ -5367,20 +5464,20 @@
         <v>1</v>
       </c>
       <c r="F69" s="35" t="s">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c r="G69" s="35"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="38" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B70" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>G</v>
+        <f t="shared" si="7"/>
+        <v>C</v>
       </c>
       <c r="C70" s="35" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D70" s="29">
         <v>2022</v>
@@ -5389,22 +5486,20 @@
         <v>1</v>
       </c>
       <c r="F70" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="G70" s="35" t="s">
-        <v>182</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="G70" s="35"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="38" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B71" s="1" t="str">
-        <f t="shared" ref="B71:B89" si="5">LEFT(A71)</f>
-        <v>G</v>
+        <f t="shared" si="7"/>
+        <v>D</v>
       </c>
       <c r="C71" s="35" t="s">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="D71" s="29">
         <v>2022</v>
@@ -5413,20 +5508,20 @@
         <v>1</v>
       </c>
       <c r="F71" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="G71" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="G71" s="35"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="38" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B72" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>M</v>
+        <f t="shared" si="7"/>
+        <v>D</v>
       </c>
       <c r="C72" s="35" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D72" s="29">
         <v>2022</v>
@@ -5435,22 +5530,20 @@
         <v>1</v>
       </c>
       <c r="F72" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="G72" s="35" t="s">
-        <v>182</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="G72" s="35"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="38" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B73" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>R</v>
+        <f t="shared" si="7"/>
+        <v>G</v>
       </c>
       <c r="C73" s="35" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D73" s="29">
         <v>2022</v>
@@ -5459,20 +5552,22 @@
         <v>1</v>
       </c>
       <c r="F73" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="G73" s="35"/>
+        <v>104</v>
+      </c>
+      <c r="G73" s="35" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="38" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B74" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>R</v>
+        <f t="shared" ref="B74:B92" si="8">LEFT(A74)</f>
+        <v>G</v>
       </c>
       <c r="C74" s="35" t="s">
-        <v>231</v>
+        <v>128</v>
       </c>
       <c r="D74" s="29">
         <v>2022</v>
@@ -5481,20 +5576,20 @@
         <v>1</v>
       </c>
       <c r="F74" s="35" t="s">
-        <v>232</v>
-      </c>
-      <c r="G74" s="35"/>
+        <v>37</v>
+      </c>
+      <c r="G74" s="29"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="38" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B75" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>V</v>
+        <f t="shared" si="8"/>
+        <v>M</v>
       </c>
       <c r="C75" s="35" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D75" s="29">
         <v>2022</v>
@@ -5503,86 +5598,88 @@
         <v>1</v>
       </c>
       <c r="F75" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="G75" s="35" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="38" t="s">
+        <v>228</v>
+      </c>
+      <c r="B76" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v>R</v>
+      </c>
+      <c r="C76" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="D76" s="29">
+        <v>2022</v>
+      </c>
+      <c r="E76" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F76" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="G76" s="35"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="B77" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v>R</v>
+      </c>
+      <c r="C77" s="35" t="s">
+        <v>231</v>
+      </c>
+      <c r="D77" s="29">
+        <v>2022</v>
+      </c>
+      <c r="E77" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F77" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="G77" s="35"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="B78" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v>V</v>
+      </c>
+      <c r="C78" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="D78" s="29">
+        <v>2022</v>
+      </c>
+      <c r="E78" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F78" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="G75" s="35"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="35" t="s">
-        <v>235</v>
-      </c>
-      <c r="B76" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>A</v>
-      </c>
-      <c r="C76" s="35" t="s">
-        <v>236</v>
-      </c>
-      <c r="D76" s="29">
-        <v>2021</v>
-      </c>
-      <c r="E76" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F76" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="G76" s="1"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="35" t="s">
-        <v>237</v>
-      </c>
-      <c r="B77" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>B</v>
-      </c>
-      <c r="C77" s="35" t="s">
-        <v>238</v>
-      </c>
-      <c r="D77" s="29">
-        <v>2021</v>
-      </c>
-      <c r="E77" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F77" s="35" t="s">
-        <v>188</v>
-      </c>
-      <c r="G77" s="1"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="35" t="s">
-        <v>239</v>
-      </c>
-      <c r="B78" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>B</v>
-      </c>
-      <c r="C78" s="35" t="s">
-        <v>240</v>
-      </c>
-      <c r="D78" s="29">
-        <v>2021</v>
-      </c>
-      <c r="E78" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F78" s="35" t="s">
-        <v>241</v>
-      </c>
-      <c r="G78" s="1"/>
+      <c r="G78" s="35"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="35" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="B79" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>C</v>
+        <f t="shared" si="8"/>
+        <v>A</v>
       </c>
       <c r="C79" s="35" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D79" s="29">
         <v>2021</v>
@@ -5591,20 +5688,20 @@
         <v>1</v>
       </c>
       <c r="F79" s="35" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G79" s="1"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="35" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B80" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>C</v>
+        <f t="shared" si="8"/>
+        <v>B</v>
       </c>
       <c r="C80" s="35" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D80" s="29">
         <v>2021</v>
@@ -5613,20 +5710,20 @@
         <v>1</v>
       </c>
       <c r="F80" s="35" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="G80" s="1"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="35" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B81" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>C</v>
+        <f t="shared" si="8"/>
+        <v>B</v>
       </c>
       <c r="C81" s="35" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D81" s="29">
         <v>2021</v>
@@ -5635,20 +5732,20 @@
         <v>1</v>
       </c>
       <c r="F81" s="35" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
       <c r="G81" s="1"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="35" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B82" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>C</v>
       </c>
       <c r="C82" s="35" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D82" s="29">
         <v>2021</v>
@@ -5657,20 +5754,20 @@
         <v>1</v>
       </c>
       <c r="F82" s="35" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="G82" s="1"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="35" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B83" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>E</v>
+        <f t="shared" si="8"/>
+        <v>C</v>
       </c>
       <c r="C83" s="35" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D83" s="29">
         <v>2021</v>
@@ -5679,20 +5776,20 @@
         <v>1</v>
       </c>
       <c r="F83" s="35" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="G83" s="1"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="35" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B84" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>G</v>
+        <f t="shared" si="8"/>
+        <v>C</v>
       </c>
       <c r="C84" s="35" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D84" s="29">
         <v>2021</v>
@@ -5701,20 +5798,20 @@
         <v>1</v>
       </c>
       <c r="F84" s="35" t="s">
-        <v>253</v>
+        <v>122</v>
       </c>
       <c r="G84" s="1"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="35" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="B85" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>J</v>
+        <f t="shared" si="8"/>
+        <v>C</v>
       </c>
       <c r="C85" s="35" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D85" s="29">
         <v>2021</v>
@@ -5723,20 +5820,20 @@
         <v>1</v>
       </c>
       <c r="F85" s="35" t="s">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="G85" s="1"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="35" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B86" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>L</v>
+        <f t="shared" si="8"/>
+        <v>E</v>
       </c>
       <c r="C86" s="35" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="D86" s="29">
         <v>2021</v>
@@ -5745,20 +5842,20 @@
         <v>1</v>
       </c>
       <c r="F86" s="35" t="s">
-        <v>258</v>
+        <v>37</v>
       </c>
       <c r="G86" s="1"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="35" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B87" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>M</v>
+        <f t="shared" si="8"/>
+        <v>G</v>
       </c>
       <c r="C87" s="35" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="D87" s="29">
         <v>2021</v>
@@ -5767,20 +5864,20 @@
         <v>1</v>
       </c>
       <c r="F87" s="35" t="s">
-        <v>112</v>
+        <v>253</v>
       </c>
       <c r="G87" s="1"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="35" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B88" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>M</v>
+        <f t="shared" si="8"/>
+        <v>J</v>
       </c>
       <c r="C88" s="35" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="D88" s="29">
         <v>2021</v>
@@ -5788,21 +5885,21 @@
       <c r="E88" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F88" s="29" t="s">
-        <v>126</v>
+      <c r="F88" s="35" t="s">
+        <v>104</v>
       </c>
       <c r="G88" s="1"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="35" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="B89" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>N</v>
+        <f t="shared" si="8"/>
+        <v>L</v>
       </c>
       <c r="C89" s="35" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D89" s="29">
         <v>2021</v>
@@ -5811,20 +5908,20 @@
         <v>1</v>
       </c>
       <c r="F89" s="35" t="s">
-        <v>122</v>
+        <v>258</v>
       </c>
       <c r="G89" s="1"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="35" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B90" s="1" t="str">
-        <f t="shared" ref="B90:B106" si="6">LEFT(A90)</f>
-        <v>P</v>
+        <f t="shared" si="8"/>
+        <v>M</v>
       </c>
       <c r="C90" s="35" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="D90" s="29">
         <v>2021</v>
@@ -5833,20 +5930,20 @@
         <v>1</v>
       </c>
       <c r="F90" s="35" t="s">
-        <v>267</v>
+        <v>112</v>
       </c>
       <c r="G90" s="1"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="35" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="B91" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>R</v>
+        <f t="shared" si="8"/>
+        <v>M</v>
       </c>
       <c r="C91" s="35" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D91" s="29">
         <v>2021</v>
@@ -5854,21 +5951,21 @@
       <c r="E91" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F91" s="35" t="s">
-        <v>212</v>
+      <c r="F91" s="29" t="s">
+        <v>126</v>
       </c>
       <c r="G91" s="1"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="35" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="B92" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>R</v>
+        <f t="shared" si="8"/>
+        <v>N</v>
       </c>
       <c r="C92" s="35" t="s">
-        <v>236</v>
+        <v>264</v>
       </c>
       <c r="D92" s="29">
         <v>2021</v>
@@ -5883,158 +5980,224 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="35" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B93" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>B</v>
+        <f t="shared" ref="B93:B109" si="9">LEFT(A93)</f>
+        <v>P</v>
       </c>
       <c r="C93" s="35" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D93" s="29">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E93" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F93" t="s">
-        <v>188</v>
-      </c>
+      <c r="F93" s="35" t="s">
+        <v>267</v>
+      </c>
+      <c r="G93" s="1"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="35" t="s">
+        <v>268</v>
+      </c>
+      <c r="B94" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>R</v>
+      </c>
+      <c r="C94" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="D94" s="29">
+        <v>2021</v>
+      </c>
+      <c r="E94" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F94" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="G94" s="1"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="35" t="s">
+        <v>270</v>
+      </c>
+      <c r="B95" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>R</v>
+      </c>
+      <c r="C95" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="D95" s="29">
+        <v>2021</v>
+      </c>
+      <c r="E95" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F95" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="G95" s="1"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="35" t="s">
+        <v>271</v>
+      </c>
+      <c r="B96" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>B</v>
+      </c>
+      <c r="C96" s="35" t="s">
+        <v>272</v>
+      </c>
+      <c r="D96" s="29">
+        <v>2020</v>
+      </c>
+      <c r="E96" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F96" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="35" t="s">
         <v>273</v>
       </c>
-      <c r="B94" s="1" t="str">
-        <f t="shared" si="6"/>
+      <c r="B97" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>A</v>
       </c>
-      <c r="C94" s="35" t="s">
+      <c r="C97" s="35" t="s">
         <v>274</v>
       </c>
-      <c r="D94" s="29">
+      <c r="D97" s="29">
         <v>2020</v>
       </c>
-      <c r="E94" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F94" t="s">
+      <c r="E97" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F97" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="35"/>
-      <c r="B95" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E95" s="29" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="35"/>
-      <c r="B96" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E96" s="29" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="35"/>
-      <c r="B97" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E97" s="29" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="E98" s="29" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="E99" s="29" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="E100" s="29" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="E101" s="29" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="E102" s="29" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="E103" s="29" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="E104" s="29" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="35"/>
       <c r="B105" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="E105" s="29" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="35"/>
       <c r="B106" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="E106" s="29" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="35"/>
+      <c r="B107" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="E107" s="29" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B108" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="E108" s="29" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B109" s="1" t="str">
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6048,13 +6211,13 @@
           <x14:formula1>
             <xm:f>Ecoles!$A$2:$A$70</xm:f>
           </x14:formula1>
-          <xm:sqref>F106</xm:sqref>
+          <xm:sqref>F109</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4FACBFD7-136B-4815-BD4C-3FC873C7A761}">
           <x14:formula1>
             <xm:f>Ecoles!$A$2:$A$71</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F105</xm:sqref>
+          <xm:sqref>F2:F108</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6064,7 +6227,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I119"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
@@ -6102,14 +6265,14 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>966</v>
+        <v>979</v>
       </c>
       <c r="B2" s="1" t="str">
         <f t="shared" ref="B2" si="0">LEFT(A2)</f>
-        <v>B</v>
+        <v>M</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>967</v>
+        <v>96</v>
       </c>
       <c r="D2" s="64">
         <v>2026</v>
@@ -6118,21 +6281,21 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>968</v>
+        <v>115</v>
       </c>
       <c r="H2" s="64"/>
       <c r="I2" s="64"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>276</v>
+        <v>978</v>
       </c>
       <c r="B3" s="1" t="str">
-        <f t="shared" ref="B3:B34" si="1">LEFT(A3)</f>
-        <v>G</v>
+        <f t="shared" ref="B3" si="1">LEFT(A3)</f>
+        <v>B</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>277</v>
+        <v>421</v>
       </c>
       <c r="D3" s="64">
         <v>2026</v>
@@ -6141,21 +6304,21 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="H3" s="64"/>
       <c r="I3" s="64"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>278</v>
+        <v>966</v>
       </c>
       <c r="B4" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>R</v>
+        <f t="shared" ref="B4" si="2">LEFT(A4)</f>
+        <v>B</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>279</v>
+        <v>967</v>
       </c>
       <c r="D4" s="64">
         <v>2026</v>
@@ -6164,63 +6327,67 @@
         <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>194</v>
+        <v>968</v>
       </c>
       <c r="H4" s="64"/>
       <c r="I4" s="64"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B5" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D5" s="1">
-        <v>2025</v>
-      </c>
-      <c r="E5" s="1" t="s">
+        <f t="shared" ref="B5:B36" si="3">LEFT(A5)</f>
+        <v>G</v>
+      </c>
+      <c r="C5" s="64" t="s">
+        <v>277</v>
+      </c>
+      <c r="D5" s="64">
+        <v>2026</v>
+      </c>
+      <c r="E5" s="64" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>188</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B6" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>C</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="D6" s="1">
-        <v>2025</v>
-      </c>
-      <c r="E6" s="1" t="s">
+        <f t="shared" si="3"/>
+        <v>R</v>
+      </c>
+      <c r="C6" s="64" t="s">
+        <v>279</v>
+      </c>
+      <c r="D6" s="64">
+        <v>2026</v>
+      </c>
+      <c r="E6" s="64" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>283</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>D</v>
+        <f t="shared" si="3"/>
+        <v>B</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>285</v>
+        <v>207</v>
       </c>
       <c r="D7" s="1">
         <v>2025</v>
@@ -6229,19 +6396,19 @@
         <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>232</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B8" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>F</v>
+        <v>281</v>
+      </c>
+      <c r="B8" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>C</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="D8" s="1">
         <v>2025</v>
@@ -6250,19 +6417,19 @@
         <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>188</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B9" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>S</v>
+        <v>284</v>
+      </c>
+      <c r="B9" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>D</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D9" s="1">
         <v>2025</v>
@@ -6271,19 +6438,19 @@
         <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>104</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B10" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>U</v>
+        <f t="shared" si="3"/>
+        <v>F</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D10" s="1">
         <v>2025</v>
@@ -6292,19 +6459,19 @@
         <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>91</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B11" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>W</v>
+        <f t="shared" si="3"/>
+        <v>S</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D11" s="1">
         <v>2025</v>
@@ -6313,19 +6480,19 @@
         <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B12" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>T</v>
+        <f t="shared" si="3"/>
+        <v>U</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D12" s="1">
         <v>2025</v>
@@ -6334,19 +6501,19 @@
         <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>105</v>
+        <v>292</v>
       </c>
       <c r="B13" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>G</v>
+        <f t="shared" si="3"/>
+        <v>W</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D13" s="1">
         <v>2025</v>
@@ -6355,19 +6522,19 @@
         <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>122</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B14" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>S</v>
+        <f t="shared" si="3"/>
+        <v>T</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D14" s="1">
         <v>2025</v>
@@ -6376,61 +6543,61 @@
         <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>115</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>299</v>
+        <v>105</v>
       </c>
       <c r="B15" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="3"/>
+        <v>G</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D15" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B16" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>E</v>
+        <f t="shared" si="3"/>
+        <v>S</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D16" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B17" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>G</v>
+        <f t="shared" si="3"/>
+        <v>B</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D17" s="1">
         <v>2024</v>
@@ -6444,14 +6611,14 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B18" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>H</v>
+        <f t="shared" si="3"/>
+        <v>E</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D18" s="1">
         <v>2024</v>
@@ -6460,19 +6627,19 @@
         <v>8</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B19" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>P</v>
+        <f t="shared" si="3"/>
+        <v>G</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D19" s="1">
         <v>2024</v>
@@ -6481,19 +6648,19 @@
         <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B20" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>R</v>
+        <f t="shared" si="3"/>
+        <v>H</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D20" s="1">
         <v>2024</v>
@@ -6502,19 +6669,19 @@
         <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B21" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>L</v>
+        <f t="shared" si="3"/>
+        <v>P</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D21" s="1">
         <v>2024</v>
@@ -6527,15 +6694,15 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>313</v>
+      <c r="A22" s="1" t="s">
+        <v>309</v>
       </c>
       <c r="B22" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>M</v>
-      </c>
-      <c r="C22" t="s">
-        <v>314</v>
+        <f t="shared" si="3"/>
+        <v>R</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>310</v>
       </c>
       <c r="D22" s="1">
         <v>2024</v>
@@ -6544,19 +6711,19 @@
         <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>315</v>
+      <c r="A23" s="1" t="s">
+        <v>311</v>
       </c>
       <c r="B23" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>R</v>
-      </c>
-      <c r="C23" t="s">
-        <v>101</v>
+        <f t="shared" si="3"/>
+        <v>L</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>312</v>
       </c>
       <c r="D23" s="1">
         <v>2024</v>
@@ -6565,61 +6732,61 @@
         <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>316</v>
+      <c r="A24" t="s">
+        <v>313</v>
       </c>
       <c r="B24" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>F</v>
+        <f t="shared" si="3"/>
+        <v>M</v>
       </c>
       <c r="C24" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D24" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>318</v>
+      <c r="A25" s="7" t="s">
+        <v>315</v>
       </c>
       <c r="B25" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>G</v>
+        <f t="shared" si="3"/>
+        <v>R</v>
       </c>
       <c r="C25" t="s">
-        <v>319</v>
+        <v>101</v>
       </c>
       <c r="D25" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>320</v>
+      <c r="A26" s="1" t="s">
+        <v>316</v>
       </c>
       <c r="B26" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>J</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>149</v>
+        <f t="shared" si="3"/>
+        <v>F</v>
+      </c>
+      <c r="C26" t="s">
+        <v>317</v>
       </c>
       <c r="D26" s="1">
         <v>2023</v>
@@ -6628,19 +6795,19 @@
         <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>258</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B27" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>L</v>
+        <f t="shared" si="3"/>
+        <v>G</v>
       </c>
       <c r="C27" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
       <c r="D27" s="1">
         <v>2023</v>
@@ -6649,19 +6816,19 @@
         <v>8</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>322</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B28" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>P</v>
-      </c>
-      <c r="C28" t="s">
-        <v>262</v>
+        <f t="shared" si="3"/>
+        <v>J</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="D28" s="1">
         <v>2023</v>
@@ -6670,19 +6837,19 @@
         <v>8</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>324</v>
+        <v>258</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>325</v>
+      <c r="A29" s="1" t="s">
+        <v>321</v>
       </c>
       <c r="B29" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>S</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>326</v>
+        <f t="shared" si="3"/>
+        <v>L</v>
+      </c>
+      <c r="C29" t="s">
+        <v>277</v>
       </c>
       <c r="D29" s="1">
         <v>2023</v>
@@ -6690,20 +6857,20 @@
       <c r="E29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F29" t="s">
-        <v>37</v>
+      <c r="F29" s="1" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>327</v>
+      <c r="A30" t="s">
+        <v>323</v>
       </c>
       <c r="B30" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>V</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>328</v>
+        <f t="shared" si="3"/>
+        <v>P</v>
+      </c>
+      <c r="C30" t="s">
+        <v>262</v>
       </c>
       <c r="D30" s="1">
         <v>2023</v>
@@ -6711,20 +6878,20 @@
       <c r="E30" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F30" t="s">
-        <v>112</v>
+      <c r="F30" s="1" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B31" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>B</v>
+        <f t="shared" si="3"/>
+        <v>S</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D31" s="1">
         <v>2023</v>
@@ -6733,19 +6900,19 @@
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B32" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>D</v>
+        <f t="shared" si="3"/>
+        <v>V</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>229</v>
+        <v>328</v>
       </c>
       <c r="D32" s="1">
         <v>2023</v>
@@ -6754,61 +6921,61 @@
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B33" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>B</v>
       </c>
-      <c r="C33" t="s">
-        <v>333</v>
+      <c r="C33" s="7" t="s">
+        <v>330</v>
       </c>
       <c r="D33" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B34" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>C</v>
+        <f t="shared" si="3"/>
+        <v>D</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>336</v>
+        <v>229</v>
       </c>
       <c r="D34" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B35" s="4" t="str">
-        <f t="shared" ref="B35:B66" si="2">LEFT(A35)</f>
-        <v>C</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>338</v>
+        <f t="shared" si="3"/>
+        <v>B</v>
+      </c>
+      <c r="C35" t="s">
+        <v>333</v>
       </c>
       <c r="D35" s="1">
         <v>2022</v>
@@ -6817,19 +6984,19 @@
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B36" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v>F</v>
+        <f t="shared" si="3"/>
+        <v>C</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>101</v>
+        <v>336</v>
       </c>
       <c r="D36" s="1">
         <v>2022</v>
@@ -6838,19 +7005,19 @@
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B37" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v>G</v>
+        <f t="shared" ref="B37:B68" si="4">LEFT(A37)</f>
+        <v>C</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D37" s="1">
         <v>2022</v>
@@ -6859,19 +7026,19 @@
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="B38" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>J</v>
+        <v>339</v>
+      </c>
+      <c r="B38" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>F</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>344</v>
+        <v>101</v>
       </c>
       <c r="D38" s="1">
         <v>2022</v>
@@ -6880,19 +7047,19 @@
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="B39" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>L</v>
+        <v>341</v>
+      </c>
+      <c r="B39" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>G</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="D39" s="1">
         <v>2022</v>
@@ -6901,19 +7068,19 @@
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B40" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>R</v>
+        <f t="shared" si="4"/>
+        <v>J</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="D40" s="1">
         <v>2022</v>
@@ -6922,19 +7089,19 @@
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B41" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>V</v>
+        <f t="shared" si="4"/>
+        <v>L</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D41" s="1">
         <v>2022</v>
@@ -6943,19 +7110,19 @@
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>351</v>
+        <v>283</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
+        <v>348</v>
       </c>
       <c r="B42" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>W</v>
+        <f t="shared" si="4"/>
+        <v>R</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D42" s="1">
         <v>2022</v>
@@ -6964,19 +7131,19 @@
         <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B43" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>B</v>
+        <f t="shared" si="4"/>
+        <v>V</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="D43" s="1">
         <v>2022</v>
@@ -6985,19 +7152,19 @@
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
-        <v>356</v>
+        <v>267</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>351</v>
       </c>
       <c r="B44" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>M</v>
+        <f t="shared" si="4"/>
+        <v>W</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>133</v>
+        <v>352</v>
       </c>
       <c r="D44" s="1">
         <v>2022</v>
@@ -7006,19 +7173,19 @@
         <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B45" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>P</v>
+        <f t="shared" si="4"/>
+        <v>B</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D45" s="1">
         <v>2022</v>
@@ -7027,61 +7194,61 @@
         <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B46" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>B</v>
+        <f t="shared" si="4"/>
+        <v>M</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="D46" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B47" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>E</v>
+        <f t="shared" si="4"/>
+        <v>P</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D47" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B48" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>R</v>
+        <f t="shared" si="4"/>
+        <v>B</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>269</v>
+        <v>149</v>
       </c>
       <c r="D48" s="1">
         <v>2021</v>
@@ -7090,25 +7257,19 @@
         <v>8</v>
       </c>
       <c r="F48" t="s">
-        <v>145</v>
-      </c>
-      <c r="H48" s="39" t="s">
-        <v>363</v>
-      </c>
-      <c r="I48" s="39" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B49" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>R</v>
+        <f t="shared" si="4"/>
+        <v>E</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>269</v>
+        <v>361</v>
       </c>
       <c r="D49" s="1">
         <v>2021</v>
@@ -7117,19 +7278,19 @@
         <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>288</v>
+        <v>362</v>
       </c>
       <c r="B50" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>S</v>
+        <f t="shared" si="4"/>
+        <v>R</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>366</v>
+        <v>269</v>
       </c>
       <c r="D50" s="1">
         <v>2021</v>
@@ -7138,19 +7299,25 @@
         <v>8</v>
       </c>
       <c r="F50" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+      <c r="H50" s="39" t="s">
+        <v>363</v>
+      </c>
+      <c r="I50" s="39" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B51" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>A</v>
+        <f t="shared" si="4"/>
+        <v>R</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="D51" s="1">
         <v>2021</v>
@@ -7159,19 +7326,19 @@
         <v>8</v>
       </c>
       <c r="F51" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>368</v>
+        <v>288</v>
       </c>
       <c r="B52" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>B</v>
+        <f t="shared" si="4"/>
+        <v>S</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D52" s="1">
         <v>2021</v>
@@ -7180,19 +7347,19 @@
         <v>8</v>
       </c>
       <c r="F52" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B53" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>K</v>
+        <f t="shared" si="4"/>
+        <v>A</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>372</v>
+        <v>255</v>
       </c>
       <c r="D53" s="1">
         <v>2021</v>
@@ -7201,19 +7368,19 @@
         <v>8</v>
       </c>
       <c r="F53" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B54" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>L</v>
+        <f t="shared" si="4"/>
+        <v>B</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="D54" s="1">
         <v>2021</v>
@@ -7222,19 +7389,19 @@
         <v>8</v>
       </c>
       <c r="F54" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B55" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>L</v>
+        <f t="shared" si="4"/>
+        <v>K</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D55" s="1">
         <v>2021</v>
@@ -7243,19 +7410,19 @@
         <v>8</v>
       </c>
       <c r="F55" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B56" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>P</v>
+        <f t="shared" si="4"/>
+        <v>L</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>133</v>
+        <v>374</v>
       </c>
       <c r="D56" s="1">
         <v>2021</v>
@@ -7264,19 +7431,19 @@
         <v>8</v>
       </c>
       <c r="F56" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>378</v>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="7" t="s">
+        <v>375</v>
       </c>
       <c r="B57" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>P</v>
-      </c>
-      <c r="C57" t="s">
-        <v>379</v>
+        <f t="shared" si="4"/>
+        <v>L</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>376</v>
       </c>
       <c r="D57" s="1">
         <v>2021</v>
@@ -7285,43 +7452,43 @@
         <v>8</v>
       </c>
       <c r="F57" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B58" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>A</v>
+        <f t="shared" si="4"/>
+        <v>P</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>381</v>
+        <v>133</v>
       </c>
       <c r="D58" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F58" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
-        <v>382</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>378</v>
       </c>
       <c r="B59" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>C</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>128</v>
+        <f t="shared" si="4"/>
+        <v>P</v>
+      </c>
+      <c r="C59" t="s">
+        <v>379</v>
       </c>
       <c r="D59" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>8</v>
@@ -7330,16 +7497,16 @@
         <v>122</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B60" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>M</v>
+        <f t="shared" si="4"/>
+        <v>A</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D60" s="1">
         <v>2020</v>
@@ -7348,19 +7515,19 @@
         <v>8</v>
       </c>
       <c r="F60" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>385</v>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
+        <v>382</v>
       </c>
       <c r="B61" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>A</v>
-      </c>
-      <c r="C61" s="9" t="s">
-        <v>386</v>
+        <f t="shared" si="4"/>
+        <v>C</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>128</v>
       </c>
       <c r="D61" s="1">
         <v>2020</v>
@@ -7369,19 +7536,19 @@
         <v>8</v>
       </c>
       <c r="F61" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>387</v>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
+        <v>383</v>
       </c>
       <c r="B62" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>D</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>388</v>
+        <f t="shared" si="4"/>
+        <v>M</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>384</v>
       </c>
       <c r="D62" s="1">
         <v>2020</v>
@@ -7390,19 +7557,19 @@
         <v>8</v>
       </c>
       <c r="F62" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B63" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>M</v>
+        <f t="shared" si="4"/>
+        <v>A</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="D63" s="1">
         <v>2020</v>
@@ -7411,19 +7578,19 @@
         <v>8</v>
       </c>
       <c r="F63" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B64" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>P</v>
+        <f t="shared" si="4"/>
+        <v>D</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D64" s="1">
         <v>2020</v>
@@ -7432,19 +7599,19 @@
         <v>8</v>
       </c>
       <c r="F64" t="s">
-        <v>188</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B65" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>V</v>
+        <f t="shared" si="4"/>
+        <v>M</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>138</v>
+        <v>390</v>
       </c>
       <c r="D65" s="1">
         <v>2020</v>
@@ -7453,61 +7620,61 @@
         <v>8</v>
       </c>
       <c r="F65" t="s">
-        <v>258</v>
+        <v>322</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B66" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>C</v>
+        <f t="shared" si="4"/>
+        <v>P</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D66" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F66" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B67" s="1" t="str">
-        <f t="shared" ref="B67:B98" si="3">LEFT(A67)</f>
-        <v>C</v>
+        <f t="shared" si="4"/>
+        <v>V</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>252</v>
+        <v>138</v>
       </c>
       <c r="D67" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F67" t="s">
-        <v>322</v>
+        <v>258</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B68" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>L</v>
-      </c>
-      <c r="C68" t="s">
-        <v>398</v>
+        <f t="shared" si="4"/>
+        <v>C</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>395</v>
       </c>
       <c r="D68" s="1">
         <v>2019</v>
@@ -7516,19 +7683,19 @@
         <v>8</v>
       </c>
       <c r="F68" t="s">
-        <v>334</v>
+        <v>212</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B69" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>R</v>
-      </c>
-      <c r="C69" t="s">
-        <v>161</v>
+        <f t="shared" ref="B69:B100" si="5">LEFT(A69)</f>
+        <v>C</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>252</v>
       </c>
       <c r="D69" s="1">
         <v>2019</v>
@@ -7537,19 +7704,19 @@
         <v>8</v>
       </c>
       <c r="F69" t="s">
-        <v>122</v>
+        <v>322</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B70" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>R</v>
+        <f t="shared" si="5"/>
+        <v>L</v>
       </c>
       <c r="C70" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D70" s="1">
         <v>2019</v>
@@ -7558,19 +7725,19 @@
         <v>8</v>
       </c>
       <c r="F70" t="s">
-        <v>283</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B71" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>V</v>
+        <f t="shared" si="5"/>
+        <v>R</v>
       </c>
       <c r="C71" t="s">
-        <v>262</v>
+        <v>161</v>
       </c>
       <c r="D71" s="1">
         <v>2019</v>
@@ -7579,19 +7746,19 @@
         <v>8</v>
       </c>
       <c r="F71" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B72" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>H</v>
+        <f t="shared" si="5"/>
+        <v>R</v>
       </c>
       <c r="C72" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D72" s="1">
         <v>2019</v>
@@ -7605,56 +7772,56 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B73" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>M</v>
+        <f t="shared" si="5"/>
+        <v>V</v>
       </c>
       <c r="C73" t="s">
-        <v>406</v>
+        <v>262</v>
       </c>
       <c r="D73" s="1">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F73" t="s">
-        <v>407</v>
+        <v>104</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B74" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>R</v>
+        <f t="shared" si="5"/>
+        <v>H</v>
       </c>
       <c r="C74" t="s">
-        <v>347</v>
+        <v>404</v>
       </c>
       <c r="D74" s="1">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F74" t="s">
-        <v>112</v>
+        <v>283</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B75" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>T</v>
+        <f t="shared" si="5"/>
+        <v>M</v>
       </c>
       <c r="C75" t="s">
-        <v>298</v>
+        <v>406</v>
       </c>
       <c r="D75" s="1">
         <v>2018</v>
@@ -7663,19 +7830,19 @@
         <v>8</v>
       </c>
       <c r="F75" t="s">
-        <v>115</v>
+        <v>407</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B76" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>V</v>
+        <f t="shared" si="5"/>
+        <v>R</v>
       </c>
       <c r="C76" t="s">
-        <v>411</v>
+        <v>347</v>
       </c>
       <c r="D76" s="1">
         <v>2018</v>
@@ -7684,19 +7851,19 @@
         <v>8</v>
       </c>
       <c r="F76" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B77" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>B</v>
+        <f t="shared" si="5"/>
+        <v>T</v>
       </c>
       <c r="C77" t="s">
-        <v>413</v>
+        <v>298</v>
       </c>
       <c r="D77" s="1">
         <v>2018</v>
@@ -7705,19 +7872,19 @@
         <v>8</v>
       </c>
       <c r="F77" t="s">
-        <v>232</v>
+        <v>115</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B78" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>B</v>
+        <f t="shared" si="5"/>
+        <v>V</v>
       </c>
       <c r="C78" t="s">
-        <v>269</v>
+        <v>411</v>
       </c>
       <c r="D78" s="1">
         <v>2018</v>
@@ -7726,19 +7893,19 @@
         <v>8</v>
       </c>
       <c r="F78" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B79" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>D</v>
+        <f t="shared" si="5"/>
+        <v>B</v>
       </c>
       <c r="C79" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D79" s="1">
         <v>2018</v>
@@ -7747,19 +7914,19 @@
         <v>8</v>
       </c>
       <c r="F79" t="s">
-        <v>91</v>
+        <v>232</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B80" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>G</v>
+        <f t="shared" si="5"/>
+        <v>B</v>
       </c>
       <c r="C80" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="D80" s="1">
         <v>2018</v>
@@ -7768,19 +7935,19 @@
         <v>8</v>
       </c>
       <c r="F80" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B81" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>P</v>
+        <f t="shared" si="5"/>
+        <v>D</v>
       </c>
       <c r="C81" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D81" s="1">
         <v>2018</v>
@@ -7789,61 +7956,61 @@
         <v>8</v>
       </c>
       <c r="F81" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B82" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>B</v>
+        <f t="shared" si="5"/>
+        <v>G</v>
       </c>
       <c r="C82" t="s">
-        <v>421</v>
+        <v>262</v>
       </c>
       <c r="D82" s="1">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F82" t="s">
-        <v>232</v>
+        <v>104</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="B83" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>D</v>
+        <f t="shared" si="5"/>
+        <v>P</v>
       </c>
       <c r="C83" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="D83" s="1">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F83" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B84" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>F</v>
+        <f t="shared" si="5"/>
+        <v>B</v>
       </c>
       <c r="C84" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="D84" s="1">
         <v>2017</v>
@@ -7851,20 +8018,20 @@
       <c r="E84" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F84" s="1" t="s">
-        <v>136</v>
+      <c r="F84" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B85" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>F</v>
+        <f t="shared" si="5"/>
+        <v>D</v>
       </c>
       <c r="C85" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D85" s="1">
         <v>2017</v>
@@ -7873,19 +8040,19 @@
         <v>8</v>
       </c>
       <c r="F85" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B86" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>H</v>
+        <f t="shared" si="5"/>
+        <v>F</v>
       </c>
       <c r="C86" t="s">
-        <v>428</v>
+        <v>401</v>
       </c>
       <c r="D86" s="1">
         <v>2017</v>
@@ -7893,20 +8060,20 @@
       <c r="E86" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F86" t="s">
-        <v>429</v>
+      <c r="F86" s="1" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B87" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>L</v>
+        <f t="shared" si="5"/>
+        <v>F</v>
       </c>
       <c r="C87" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="D87" s="1">
         <v>2017</v>
@@ -7915,19 +8082,19 @@
         <v>8</v>
       </c>
       <c r="F87" t="s">
-        <v>37</v>
+        <v>115</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B88" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>V</v>
+        <f t="shared" si="5"/>
+        <v>H</v>
       </c>
       <c r="C88" t="s">
-        <v>205</v>
+        <v>428</v>
       </c>
       <c r="D88" s="1">
         <v>2017</v>
@@ -7936,19 +8103,19 @@
         <v>8</v>
       </c>
       <c r="F88" t="s">
-        <v>122</v>
+        <v>429</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B89" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>G</v>
+        <f t="shared" si="5"/>
+        <v>L</v>
       </c>
       <c r="C89" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D89" s="1">
         <v>2017</v>
@@ -7957,61 +8124,61 @@
         <v>8</v>
       </c>
       <c r="F89" t="s">
-        <v>407</v>
+        <v>37</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B90" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>B</v>
+        <f t="shared" si="5"/>
+        <v>V</v>
       </c>
       <c r="C90" t="s">
-        <v>128</v>
+        <v>205</v>
       </c>
       <c r="D90" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F90" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B91" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>C</v>
+        <f t="shared" si="5"/>
+        <v>G</v>
       </c>
       <c r="C91" t="s">
-        <v>269</v>
+        <v>434</v>
       </c>
       <c r="D91" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F91" t="s">
-        <v>188</v>
+        <v>407</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B92" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>F</v>
+        <f t="shared" si="5"/>
+        <v>B</v>
       </c>
       <c r="C92" t="s">
-        <v>209</v>
+        <v>128</v>
       </c>
       <c r="D92" s="1">
         <v>2016</v>
@@ -8020,19 +8187,19 @@
         <v>8</v>
       </c>
       <c r="F92" t="s">
-        <v>232</v>
+        <v>126</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B93" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>P</v>
+        <f t="shared" si="5"/>
+        <v>C</v>
       </c>
       <c r="C93" t="s">
-        <v>439</v>
+        <v>269</v>
       </c>
       <c r="D93" s="1">
         <v>2016</v>
@@ -8041,19 +8208,19 @@
         <v>8</v>
       </c>
       <c r="F93" t="s">
-        <v>283</v>
+        <v>188</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B94" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>R</v>
+        <f t="shared" si="5"/>
+        <v>F</v>
       </c>
       <c r="C94" t="s">
-        <v>152</v>
+        <v>209</v>
       </c>
       <c r="D94" s="1">
         <v>2016</v>
@@ -8062,19 +8229,19 @@
         <v>8</v>
       </c>
       <c r="F94" t="s">
-        <v>122</v>
+        <v>232</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B95" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>P</v>
       </c>
       <c r="C95" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D95" s="1">
         <v>2016</v>
@@ -8083,19 +8250,19 @@
         <v>8</v>
       </c>
       <c r="F95" t="s">
-        <v>94</v>
+        <v>283</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B96" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>M</v>
+        <f t="shared" si="5"/>
+        <v>R</v>
       </c>
       <c r="C96" t="s">
-        <v>444</v>
+        <v>152</v>
       </c>
       <c r="D96" s="1">
         <v>2016</v>
@@ -8104,19 +8271,19 @@
         <v>8</v>
       </c>
       <c r="F96" t="s">
-        <v>445</v>
+        <v>122</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="B97" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>M</v>
+        <f t="shared" si="5"/>
+        <v>P</v>
       </c>
       <c r="C97" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D97" s="1">
         <v>2016</v>
@@ -8125,19 +8292,19 @@
         <v>8</v>
       </c>
       <c r="F97" t="s">
-        <v>448</v>
+        <v>94</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="B98" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>O</v>
+        <f t="shared" si="5"/>
+        <v>M</v>
       </c>
       <c r="C98" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="D98" s="1">
         <v>2016</v>
@@ -8146,19 +8313,19 @@
         <v>8</v>
       </c>
       <c r="F98" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="B99" s="1" t="str">
-        <f t="shared" ref="B99" si="4">LEFT(A99)</f>
-        <v>W</v>
+        <f t="shared" si="5"/>
+        <v>M</v>
       </c>
       <c r="C99" t="s">
-        <v>234</v>
+        <v>447</v>
       </c>
       <c r="D99" s="1">
         <v>2016</v>
@@ -8167,18 +8334,19 @@
         <v>8</v>
       </c>
       <c r="F99" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="B100" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="C100" s="9" t="s">
-        <v>454</v>
+      <c r="A100" t="s">
+        <v>449</v>
+      </c>
+      <c r="B100" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>O</v>
+      </c>
+      <c r="C100" t="s">
+        <v>431</v>
       </c>
       <c r="D100" s="1">
         <v>2016</v>
@@ -8187,19 +8355,19 @@
         <v>8</v>
       </c>
       <c r="F100" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="9" t="s">
-        <v>456</v>
+      <c r="A101" t="s">
+        <v>451</v>
       </c>
       <c r="B101" s="1" t="str">
-        <f t="shared" ref="B101:B119" si="5">LEFT(A101)</f>
-        <v>D</v>
-      </c>
-      <c r="C101" s="9" t="s">
-        <v>178</v>
+        <f t="shared" ref="B101" si="6">LEFT(A101)</f>
+        <v>W</v>
+      </c>
+      <c r="C101" t="s">
+        <v>234</v>
       </c>
       <c r="D101" s="1">
         <v>2016</v>
@@ -8208,19 +8376,18 @@
         <v>8</v>
       </c>
       <c r="F101" t="s">
-        <v>232</v>
+        <v>452</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="B102" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>F</v>
+        <v>453</v>
+      </c>
+      <c r="B102" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="D102" s="1">
         <v>2016</v>
@@ -8229,19 +8396,19 @@
         <v>8</v>
       </c>
       <c r="F102" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="9" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B103" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>G</v>
+        <f t="shared" ref="B103:B121" si="7">LEFT(A103)</f>
+        <v>D</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>461</v>
+        <v>178</v>
       </c>
       <c r="D103" s="1">
         <v>2016</v>
@@ -8250,19 +8417,19 @@
         <v>8</v>
       </c>
       <c r="F103" t="s">
-        <v>429</v>
+        <v>232</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="9" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B104" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>M</v>
+        <f t="shared" si="7"/>
+        <v>F</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="D104" s="1">
         <v>2016</v>
@@ -8271,19 +8438,19 @@
         <v>8</v>
       </c>
       <c r="F104" t="s">
-        <v>91</v>
+        <v>459</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="9" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B105" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>M</v>
+        <f t="shared" si="7"/>
+        <v>G</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>191</v>
+        <v>461</v>
       </c>
       <c r="D105" s="1">
         <v>2016</v>
@@ -8292,19 +8459,19 @@
         <v>8</v>
       </c>
       <c r="F105" t="s">
-        <v>267</v>
+        <v>429</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="9" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B106" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>P</v>
+        <f t="shared" si="7"/>
+        <v>M</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D106" s="1">
         <v>2016</v>
@@ -8313,61 +8480,61 @@
         <v>8</v>
       </c>
       <c r="F106" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="9" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B107" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>B</v>
+        <f t="shared" si="7"/>
+        <v>M</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>468</v>
+        <v>191</v>
       </c>
       <c r="D107" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F107" t="s">
-        <v>136</v>
+        <v>267</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="9" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B108" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>C</v>
+        <f t="shared" si="7"/>
+        <v>P</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="D108" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F108" t="s">
-        <v>142</v>
+        <v>104</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="9" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B109" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>M</v>
+        <f t="shared" si="7"/>
+        <v>B</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="D109" s="1">
         <v>2015</v>
@@ -8376,61 +8543,61 @@
         <v>8</v>
       </c>
       <c r="F109" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="9" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="B110" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>S</v>
+        <f t="shared" si="7"/>
+        <v>C</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="D110" s="1">
         <v>2015</v>
       </c>
-      <c r="E110" s="12" t="s">
+      <c r="E110" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F110" t="s">
-        <v>99</v>
+        <v>142</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="9" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B111" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>V</v>
+        <f t="shared" si="7"/>
+        <v>M</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>401</v>
+        <v>472</v>
       </c>
       <c r="D111" s="1">
         <v>2015</v>
       </c>
-      <c r="E111" s="12" t="s">
+      <c r="E111" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F111" t="s">
-        <v>99</v>
+        <v>142</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="9" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B112" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>P</v>
+        <f t="shared" si="7"/>
+        <v>S</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>310</v>
+        <v>474</v>
       </c>
       <c r="D112" s="1">
         <v>2015</v>
@@ -8439,19 +8606,19 @@
         <v>8</v>
       </c>
       <c r="F112" t="s">
-        <v>477</v>
+        <v>99</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="9" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B113" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>P</v>
+        <f t="shared" si="7"/>
+        <v>V</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>479</v>
+        <v>401</v>
       </c>
       <c r="D113" s="1">
         <v>2015</v>
@@ -8460,19 +8627,19 @@
         <v>8</v>
       </c>
       <c r="F113" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="9" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B114" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>Z</v>
+        <f t="shared" si="7"/>
+        <v>P</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>481</v>
+        <v>310</v>
       </c>
       <c r="D114" s="1">
         <v>2015</v>
@@ -8481,61 +8648,61 @@
         <v>8</v>
       </c>
       <c r="F114" t="s">
-        <v>126</v>
+        <v>477</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="9" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B115" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>B</v>
-      </c>
-      <c r="C115" s="12" t="s">
-        <v>347</v>
+        <f t="shared" si="7"/>
+        <v>P</v>
+      </c>
+      <c r="C115" s="9" t="s">
+        <v>479</v>
       </c>
       <c r="D115" s="1">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="E115" s="12" t="s">
         <v>8</v>
       </c>
       <c r="F115" t="s">
-        <v>459</v>
+        <v>91</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="9" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B116" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>B</v>
+        <f t="shared" si="7"/>
+        <v>Z</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>234</v>
+        <v>481</v>
       </c>
       <c r="D116" s="1">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="E116" s="12" t="s">
         <v>8</v>
       </c>
       <c r="F116" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>484</v>
+      <c r="A117" s="9" t="s">
+        <v>482</v>
       </c>
       <c r="B117" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>D</v>
-      </c>
-      <c r="C117" s="9" t="s">
-        <v>125</v>
+        <f t="shared" si="7"/>
+        <v>B</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>347</v>
       </c>
       <c r="D117" s="1">
         <v>2014</v>
@@ -8544,19 +8711,19 @@
         <v>8</v>
       </c>
       <c r="F117" t="s">
-        <v>283</v>
+        <v>459</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="9" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B118" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>M</v>
+        <f t="shared" si="7"/>
+        <v>B</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>304</v>
+        <v>234</v>
       </c>
       <c r="D118" s="1">
         <v>2014</v>
@@ -8565,19 +8732,61 @@
         <v>8</v>
       </c>
       <c r="F118" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>484</v>
+      </c>
+      <c r="B119" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>D</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="D119" s="1">
+        <v>2014</v>
+      </c>
+      <c r="E119" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F119" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B119" s="1" t="str">
-        <f t="shared" si="5"/>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="B120" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>M</v>
+      </c>
+      <c r="C120" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="D120" s="1">
+        <v>2014</v>
+      </c>
+      <c r="E120" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F120" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B121" s="1" t="str">
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H48" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="I48" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="H50" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="I50" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -8587,13 +8796,13 @@
           <x14:formula1>
             <xm:f>Ecoles!$A$2:$A$71</xm:f>
           </x14:formula1>
-          <xm:sqref>F120:F125</xm:sqref>
+          <xm:sqref>F122:F127</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{986D1C62-C1E8-4BE3-9C02-C464CE3171CD}">
           <x14:formula1>
             <xm:f>Ecoles!$A$2:$A$72</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F119</xm:sqref>
+          <xm:sqref>F2:F121</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -11020,7 +11229,7 @@
       <c r="F72" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="G72" s="77" t="s">
+      <c r="G72" s="71" t="s">
         <v>972</v>
       </c>
       <c r="H72" s="63" t="s">
@@ -11032,7 +11241,7 @@
       <c r="J72" s="33" t="s">
         <v>969</v>
       </c>
-      <c r="K72" s="78" t="s">
+      <c r="K72" s="72" t="s">
         <v>971</v>
       </c>
     </row>
@@ -11447,80 +11656,80 @@
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="73" t="s">
+      <c r="A28" s="82" t="s">
         <v>849</v>
       </c>
-      <c r="B28" s="72"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="72"/>
-      <c r="G28" s="72"/>
-      <c r="H28" s="72"/>
-      <c r="I28" s="72"/>
-      <c r="J28" s="72"/>
-      <c r="K28" s="72"/>
-      <c r="L28" s="72"/>
-      <c r="M28" s="72"/>
-      <c r="N28" s="72"/>
-      <c r="O28" s="72"/>
-      <c r="P28" s="72"/>
-      <c r="Q28" s="72"/>
+      <c r="B28" s="80"/>
+      <c r="C28" s="80"/>
+      <c r="D28" s="80"/>
+      <c r="E28" s="80"/>
+      <c r="F28" s="80"/>
+      <c r="G28" s="80"/>
+      <c r="H28" s="80"/>
+      <c r="I28" s="80"/>
+      <c r="J28" s="80"/>
+      <c r="K28" s="80"/>
+      <c r="L28" s="80"/>
+      <c r="M28" s="80"/>
+      <c r="N28" s="80"/>
+      <c r="O28" s="80"/>
+      <c r="P28" s="80"/>
+      <c r="Q28" s="80"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="72"/>
-      <c r="B29" s="72"/>
-      <c r="C29" s="72"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="72"/>
-      <c r="F29" s="72"/>
-      <c r="G29" s="72"/>
-      <c r="H29" s="72"/>
-      <c r="I29" s="72"/>
-      <c r="J29" s="72"/>
-      <c r="K29" s="72"/>
-      <c r="L29" s="72"/>
-      <c r="M29" s="72"/>
-      <c r="N29" s="72"/>
-      <c r="O29" s="72"/>
-      <c r="P29" s="72"/>
-      <c r="Q29" s="72"/>
+      <c r="A29" s="80"/>
+      <c r="B29" s="80"/>
+      <c r="C29" s="80"/>
+      <c r="D29" s="80"/>
+      <c r="E29" s="80"/>
+      <c r="F29" s="80"/>
+      <c r="G29" s="80"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="80"/>
+      <c r="J29" s="80"/>
+      <c r="K29" s="80"/>
+      <c r="L29" s="80"/>
+      <c r="M29" s="80"/>
+      <c r="N29" s="80"/>
+      <c r="O29" s="80"/>
+      <c r="P29" s="80"/>
+      <c r="Q29" s="80"/>
     </row>
     <row r="30" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="74" t="s">
+      <c r="A30" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="71" t="s">
+      <c r="B30" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="72"/>
-      <c r="D30" s="72"/>
-      <c r="E30" s="71" t="s">
+      <c r="C30" s="80"/>
+      <c r="D30" s="80"/>
+      <c r="E30" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="72"/>
-      <c r="G30" s="72"/>
-      <c r="H30" s="71" t="s">
+      <c r="F30" s="80"/>
+      <c r="G30" s="80"/>
+      <c r="H30" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="I30" s="72"/>
-      <c r="J30" s="72"/>
-      <c r="K30" s="71" t="s">
+      <c r="I30" s="80"/>
+      <c r="J30" s="80"/>
+      <c r="K30" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="L30" s="72"/>
-      <c r="M30" s="72"/>
-      <c r="N30" s="72"/>
-      <c r="O30" s="72"/>
-      <c r="P30" s="71" t="s">
+      <c r="L30" s="80"/>
+      <c r="M30" s="80"/>
+      <c r="N30" s="80"/>
+      <c r="O30" s="80"/>
+      <c r="P30" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="Q30" s="71" t="s">
+      <c r="Q30" s="79" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="72"/>
+      <c r="A31" s="80"/>
       <c r="B31" s="43" t="s">
         <v>27</v>
       </c>
@@ -11563,8 +11772,8 @@
       <c r="O31" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P31" s="72"/>
-      <c r="Q31" s="72"/>
+      <c r="P31" s="80"/>
+      <c r="Q31" s="80"/>
     </row>
     <row r="32" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="43" t="s">
@@ -11618,80 +11827,80 @@
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="73" t="s">
+      <c r="A33" s="82" t="s">
         <v>650</v>
       </c>
-      <c r="B33" s="72"/>
-      <c r="C33" s="72"/>
-      <c r="D33" s="72"/>
-      <c r="E33" s="72"/>
-      <c r="F33" s="72"/>
-      <c r="G33" s="72"/>
-      <c r="H33" s="72"/>
-      <c r="I33" s="72"/>
-      <c r="J33" s="72"/>
-      <c r="K33" s="72"/>
-      <c r="L33" s="72"/>
-      <c r="M33" s="72"/>
-      <c r="N33" s="72"/>
-      <c r="O33" s="72"/>
-      <c r="P33" s="72"/>
-      <c r="Q33" s="72"/>
+      <c r="B33" s="80"/>
+      <c r="C33" s="80"/>
+      <c r="D33" s="80"/>
+      <c r="E33" s="80"/>
+      <c r="F33" s="80"/>
+      <c r="G33" s="80"/>
+      <c r="H33" s="80"/>
+      <c r="I33" s="80"/>
+      <c r="J33" s="80"/>
+      <c r="K33" s="80"/>
+      <c r="L33" s="80"/>
+      <c r="M33" s="80"/>
+      <c r="N33" s="80"/>
+      <c r="O33" s="80"/>
+      <c r="P33" s="80"/>
+      <c r="Q33" s="80"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="72"/>
-      <c r="B34" s="72"/>
-      <c r="C34" s="72"/>
-      <c r="D34" s="72"/>
-      <c r="E34" s="72"/>
-      <c r="F34" s="72"/>
-      <c r="G34" s="72"/>
-      <c r="H34" s="72"/>
-      <c r="I34" s="72"/>
-      <c r="J34" s="72"/>
-      <c r="K34" s="72"/>
-      <c r="L34" s="72"/>
-      <c r="M34" s="72"/>
-      <c r="N34" s="72"/>
-      <c r="O34" s="72"/>
-      <c r="P34" s="72"/>
-      <c r="Q34" s="72"/>
+      <c r="A34" s="80"/>
+      <c r="B34" s="80"/>
+      <c r="C34" s="80"/>
+      <c r="D34" s="80"/>
+      <c r="E34" s="80"/>
+      <c r="F34" s="80"/>
+      <c r="G34" s="80"/>
+      <c r="H34" s="80"/>
+      <c r="I34" s="80"/>
+      <c r="J34" s="80"/>
+      <c r="K34" s="80"/>
+      <c r="L34" s="80"/>
+      <c r="M34" s="80"/>
+      <c r="N34" s="80"/>
+      <c r="O34" s="80"/>
+      <c r="P34" s="80"/>
+      <c r="Q34" s="80"/>
     </row>
     <row r="35" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="74" t="s">
+      <c r="A35" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="71" t="s">
+      <c r="B35" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="71" t="s">
+      <c r="C35" s="80"/>
+      <c r="D35" s="80"/>
+      <c r="E35" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="F35" s="72"/>
-      <c r="G35" s="72"/>
-      <c r="H35" s="71" t="s">
+      <c r="F35" s="80"/>
+      <c r="G35" s="80"/>
+      <c r="H35" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="I35" s="72"/>
-      <c r="J35" s="72"/>
-      <c r="K35" s="71" t="s">
+      <c r="I35" s="80"/>
+      <c r="J35" s="80"/>
+      <c r="K35" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="72"/>
-      <c r="M35" s="72"/>
-      <c r="N35" s="72"/>
-      <c r="O35" s="72"/>
-      <c r="P35" s="71" t="s">
+      <c r="L35" s="80"/>
+      <c r="M35" s="80"/>
+      <c r="N35" s="80"/>
+      <c r="O35" s="80"/>
+      <c r="P35" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="Q35" s="71" t="s">
+      <c r="Q35" s="79" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="72"/>
+      <c r="A36" s="80"/>
       <c r="B36" s="43" t="s">
         <v>27</v>
       </c>
@@ -11734,8 +11943,8 @@
       <c r="O36" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P36" s="72"/>
-      <c r="Q36" s="72"/>
+      <c r="P36" s="80"/>
+      <c r="Q36" s="80"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="43" t="s">
@@ -12175,80 +12384,80 @@
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="73" t="s">
+      <c r="A48" s="82" t="s">
         <v>857</v>
       </c>
-      <c r="B48" s="72"/>
-      <c r="C48" s="72"/>
-      <c r="D48" s="72"/>
-      <c r="E48" s="72"/>
-      <c r="F48" s="72"/>
-      <c r="G48" s="72"/>
-      <c r="H48" s="72"/>
-      <c r="I48" s="72"/>
-      <c r="J48" s="72"/>
-      <c r="K48" s="72"/>
-      <c r="L48" s="72"/>
-      <c r="M48" s="72"/>
-      <c r="N48" s="72"/>
-      <c r="O48" s="72"/>
-      <c r="P48" s="72"/>
-      <c r="Q48" s="72"/>
+      <c r="B48" s="80"/>
+      <c r="C48" s="80"/>
+      <c r="D48" s="80"/>
+      <c r="E48" s="80"/>
+      <c r="F48" s="80"/>
+      <c r="G48" s="80"/>
+      <c r="H48" s="80"/>
+      <c r="I48" s="80"/>
+      <c r="J48" s="80"/>
+      <c r="K48" s="80"/>
+      <c r="L48" s="80"/>
+      <c r="M48" s="80"/>
+      <c r="N48" s="80"/>
+      <c r="O48" s="80"/>
+      <c r="P48" s="80"/>
+      <c r="Q48" s="80"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="72"/>
-      <c r="B49" s="72"/>
-      <c r="C49" s="72"/>
-      <c r="D49" s="72"/>
-      <c r="E49" s="72"/>
-      <c r="F49" s="72"/>
-      <c r="G49" s="72"/>
-      <c r="H49" s="72"/>
-      <c r="I49" s="72"/>
-      <c r="J49" s="72"/>
-      <c r="K49" s="72"/>
-      <c r="L49" s="72"/>
-      <c r="M49" s="72"/>
-      <c r="N49" s="72"/>
-      <c r="O49" s="72"/>
-      <c r="P49" s="72"/>
-      <c r="Q49" s="72"/>
+      <c r="A49" s="80"/>
+      <c r="B49" s="80"/>
+      <c r="C49" s="80"/>
+      <c r="D49" s="80"/>
+      <c r="E49" s="80"/>
+      <c r="F49" s="80"/>
+      <c r="G49" s="80"/>
+      <c r="H49" s="80"/>
+      <c r="I49" s="80"/>
+      <c r="J49" s="80"/>
+      <c r="K49" s="80"/>
+      <c r="L49" s="80"/>
+      <c r="M49" s="80"/>
+      <c r="N49" s="80"/>
+      <c r="O49" s="80"/>
+      <c r="P49" s="80"/>
+      <c r="Q49" s="80"/>
     </row>
     <row r="50" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="74" t="s">
+      <c r="A50" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B50" s="71" t="s">
+      <c r="B50" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C50" s="72"/>
-      <c r="D50" s="72"/>
-      <c r="E50" s="71" t="s">
+      <c r="C50" s="80"/>
+      <c r="D50" s="80"/>
+      <c r="E50" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="F50" s="72"/>
-      <c r="G50" s="72"/>
-      <c r="H50" s="71" t="s">
+      <c r="F50" s="80"/>
+      <c r="G50" s="80"/>
+      <c r="H50" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="I50" s="72"/>
-      <c r="J50" s="72"/>
-      <c r="K50" s="71" t="s">
+      <c r="I50" s="80"/>
+      <c r="J50" s="80"/>
+      <c r="K50" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="72"/>
-      <c r="M50" s="72"/>
-      <c r="N50" s="72"/>
-      <c r="O50" s="72"/>
-      <c r="P50" s="71" t="s">
+      <c r="L50" s="80"/>
+      <c r="M50" s="80"/>
+      <c r="N50" s="80"/>
+      <c r="O50" s="80"/>
+      <c r="P50" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="Q50" s="71" t="s">
+      <c r="Q50" s="79" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51" s="72"/>
+      <c r="A51" s="80"/>
       <c r="B51" s="43" t="s">
         <v>27</v>
       </c>
@@ -12291,8 +12500,8 @@
       <c r="O51" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P51" s="72"/>
-      <c r="Q51" s="72"/>
+      <c r="P51" s="80"/>
+      <c r="Q51" s="80"/>
     </row>
     <row r="52" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="43" t="s">
@@ -12346,80 +12555,80 @@
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53" s="73" t="s">
+      <c r="A53" s="82" t="s">
         <v>859</v>
       </c>
-      <c r="B53" s="72"/>
-      <c r="C53" s="72"/>
-      <c r="D53" s="72"/>
-      <c r="E53" s="72"/>
-      <c r="F53" s="72"/>
-      <c r="G53" s="72"/>
-      <c r="H53" s="72"/>
-      <c r="I53" s="72"/>
-      <c r="J53" s="72"/>
-      <c r="K53" s="72"/>
-      <c r="L53" s="72"/>
-      <c r="M53" s="72"/>
-      <c r="N53" s="72"/>
-      <c r="O53" s="72"/>
-      <c r="P53" s="72"/>
-      <c r="Q53" s="72"/>
+      <c r="B53" s="80"/>
+      <c r="C53" s="80"/>
+      <c r="D53" s="80"/>
+      <c r="E53" s="80"/>
+      <c r="F53" s="80"/>
+      <c r="G53" s="80"/>
+      <c r="H53" s="80"/>
+      <c r="I53" s="80"/>
+      <c r="J53" s="80"/>
+      <c r="K53" s="80"/>
+      <c r="L53" s="80"/>
+      <c r="M53" s="80"/>
+      <c r="N53" s="80"/>
+      <c r="O53" s="80"/>
+      <c r="P53" s="80"/>
+      <c r="Q53" s="80"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="72"/>
-      <c r="B54" s="72"/>
-      <c r="C54" s="72"/>
-      <c r="D54" s="72"/>
-      <c r="E54" s="72"/>
-      <c r="F54" s="72"/>
-      <c r="G54" s="72"/>
-      <c r="H54" s="72"/>
-      <c r="I54" s="72"/>
-      <c r="J54" s="72"/>
-      <c r="K54" s="72"/>
-      <c r="L54" s="72"/>
-      <c r="M54" s="72"/>
-      <c r="N54" s="72"/>
-      <c r="O54" s="72"/>
-      <c r="P54" s="72"/>
-      <c r="Q54" s="72"/>
+      <c r="A54" s="80"/>
+      <c r="B54" s="80"/>
+      <c r="C54" s="80"/>
+      <c r="D54" s="80"/>
+      <c r="E54" s="80"/>
+      <c r="F54" s="80"/>
+      <c r="G54" s="80"/>
+      <c r="H54" s="80"/>
+      <c r="I54" s="80"/>
+      <c r="J54" s="80"/>
+      <c r="K54" s="80"/>
+      <c r="L54" s="80"/>
+      <c r="M54" s="80"/>
+      <c r="N54" s="80"/>
+      <c r="O54" s="80"/>
+      <c r="P54" s="80"/>
+      <c r="Q54" s="80"/>
     </row>
     <row r="55" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="74" t="s">
+      <c r="A55" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B55" s="71" t="s">
+      <c r="B55" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C55" s="72"/>
-      <c r="D55" s="72"/>
-      <c r="E55" s="71" t="s">
+      <c r="C55" s="80"/>
+      <c r="D55" s="80"/>
+      <c r="E55" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="F55" s="72"/>
-      <c r="G55" s="72"/>
-      <c r="H55" s="71" t="s">
+      <c r="F55" s="80"/>
+      <c r="G55" s="80"/>
+      <c r="H55" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="I55" s="72"/>
-      <c r="J55" s="72"/>
-      <c r="K55" s="71" t="s">
+      <c r="I55" s="80"/>
+      <c r="J55" s="80"/>
+      <c r="K55" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="L55" s="72"/>
-      <c r="M55" s="72"/>
-      <c r="N55" s="72"/>
-      <c r="O55" s="72"/>
-      <c r="P55" s="71" t="s">
+      <c r="L55" s="80"/>
+      <c r="M55" s="80"/>
+      <c r="N55" s="80"/>
+      <c r="O55" s="80"/>
+      <c r="P55" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="Q55" s="71" t="s">
+      <c r="Q55" s="79" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="72"/>
+      <c r="A56" s="80"/>
       <c r="B56" s="43" t="s">
         <v>27</v>
       </c>
@@ -12462,8 +12671,8 @@
       <c r="O56" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P56" s="72"/>
-      <c r="Q56" s="72"/>
+      <c r="P56" s="80"/>
+      <c r="Q56" s="80"/>
     </row>
     <row r="57" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="43" t="s">
@@ -12971,80 +13180,80 @@
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A72" s="73" t="s">
+      <c r="A72" s="82" t="s">
         <v>862</v>
       </c>
-      <c r="B72" s="72"/>
-      <c r="C72" s="72"/>
-      <c r="D72" s="72"/>
-      <c r="E72" s="72"/>
-      <c r="F72" s="72"/>
-      <c r="G72" s="72"/>
-      <c r="H72" s="72"/>
-      <c r="I72" s="72"/>
-      <c r="J72" s="72"/>
-      <c r="K72" s="72"/>
-      <c r="L72" s="72"/>
-      <c r="M72" s="72"/>
-      <c r="N72" s="72"/>
-      <c r="O72" s="72"/>
-      <c r="P72" s="72"/>
-      <c r="Q72" s="72"/>
+      <c r="B72" s="80"/>
+      <c r="C72" s="80"/>
+      <c r="D72" s="80"/>
+      <c r="E72" s="80"/>
+      <c r="F72" s="80"/>
+      <c r="G72" s="80"/>
+      <c r="H72" s="80"/>
+      <c r="I72" s="80"/>
+      <c r="J72" s="80"/>
+      <c r="K72" s="80"/>
+      <c r="L72" s="80"/>
+      <c r="M72" s="80"/>
+      <c r="N72" s="80"/>
+      <c r="O72" s="80"/>
+      <c r="P72" s="80"/>
+      <c r="Q72" s="80"/>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A73" s="72"/>
-      <c r="B73" s="72"/>
-      <c r="C73" s="72"/>
-      <c r="D73" s="72"/>
-      <c r="E73" s="72"/>
-      <c r="F73" s="72"/>
-      <c r="G73" s="72"/>
-      <c r="H73" s="72"/>
-      <c r="I73" s="72"/>
-      <c r="J73" s="72"/>
-      <c r="K73" s="72"/>
-      <c r="L73" s="72"/>
-      <c r="M73" s="72"/>
-      <c r="N73" s="72"/>
-      <c r="O73" s="72"/>
-      <c r="P73" s="72"/>
-      <c r="Q73" s="72"/>
+      <c r="A73" s="80"/>
+      <c r="B73" s="80"/>
+      <c r="C73" s="80"/>
+      <c r="D73" s="80"/>
+      <c r="E73" s="80"/>
+      <c r="F73" s="80"/>
+      <c r="G73" s="80"/>
+      <c r="H73" s="80"/>
+      <c r="I73" s="80"/>
+      <c r="J73" s="80"/>
+      <c r="K73" s="80"/>
+      <c r="L73" s="80"/>
+      <c r="M73" s="80"/>
+      <c r="N73" s="80"/>
+      <c r="O73" s="80"/>
+      <c r="P73" s="80"/>
+      <c r="Q73" s="80"/>
     </row>
     <row r="74" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="74" t="s">
+      <c r="A74" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B74" s="71" t="s">
+      <c r="B74" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C74" s="72"/>
-      <c r="D74" s="72"/>
-      <c r="E74" s="71" t="s">
+      <c r="C74" s="80"/>
+      <c r="D74" s="80"/>
+      <c r="E74" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="F74" s="72"/>
-      <c r="G74" s="72"/>
-      <c r="H74" s="71" t="s">
+      <c r="F74" s="80"/>
+      <c r="G74" s="80"/>
+      <c r="H74" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="I74" s="72"/>
-      <c r="J74" s="72"/>
-      <c r="K74" s="71" t="s">
+      <c r="I74" s="80"/>
+      <c r="J74" s="80"/>
+      <c r="K74" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="L74" s="72"/>
-      <c r="M74" s="72"/>
-      <c r="N74" s="72"/>
-      <c r="O74" s="72"/>
-      <c r="P74" s="71" t="s">
+      <c r="L74" s="80"/>
+      <c r="M74" s="80"/>
+      <c r="N74" s="80"/>
+      <c r="O74" s="80"/>
+      <c r="P74" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="Q74" s="71" t="s">
+      <c r="Q74" s="79" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75" s="72"/>
+      <c r="A75" s="80"/>
       <c r="B75" s="43" t="s">
         <v>27</v>
       </c>
@@ -13087,8 +13296,8 @@
       <c r="O75" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P75" s="72"/>
-      <c r="Q75" s="72"/>
+      <c r="P75" s="80"/>
+      <c r="Q75" s="80"/>
     </row>
     <row r="76" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="43" t="s">
@@ -13266,80 +13475,80 @@
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A81" s="73" t="s">
+      <c r="A81" s="82" t="s">
         <v>864</v>
       </c>
-      <c r="B81" s="72"/>
-      <c r="C81" s="72"/>
-      <c r="D81" s="72"/>
-      <c r="E81" s="72"/>
-      <c r="F81" s="72"/>
-      <c r="G81" s="72"/>
-      <c r="H81" s="72"/>
-      <c r="I81" s="72"/>
-      <c r="J81" s="72"/>
-      <c r="K81" s="72"/>
-      <c r="L81" s="72"/>
-      <c r="M81" s="72"/>
-      <c r="N81" s="72"/>
-      <c r="O81" s="72"/>
-      <c r="P81" s="72"/>
-      <c r="Q81" s="72"/>
+      <c r="B81" s="80"/>
+      <c r="C81" s="80"/>
+      <c r="D81" s="80"/>
+      <c r="E81" s="80"/>
+      <c r="F81" s="80"/>
+      <c r="G81" s="80"/>
+      <c r="H81" s="80"/>
+      <c r="I81" s="80"/>
+      <c r="J81" s="80"/>
+      <c r="K81" s="80"/>
+      <c r="L81" s="80"/>
+      <c r="M81" s="80"/>
+      <c r="N81" s="80"/>
+      <c r="O81" s="80"/>
+      <c r="P81" s="80"/>
+      <c r="Q81" s="80"/>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A82" s="72"/>
-      <c r="B82" s="72"/>
-      <c r="C82" s="72"/>
-      <c r="D82" s="72"/>
-      <c r="E82" s="72"/>
-      <c r="F82" s="72"/>
-      <c r="G82" s="72"/>
-      <c r="H82" s="72"/>
-      <c r="I82" s="72"/>
-      <c r="J82" s="72"/>
-      <c r="K82" s="72"/>
-      <c r="L82" s="72"/>
-      <c r="M82" s="72"/>
-      <c r="N82" s="72"/>
-      <c r="O82" s="72"/>
-      <c r="P82" s="72"/>
-      <c r="Q82" s="72"/>
+      <c r="A82" s="80"/>
+      <c r="B82" s="80"/>
+      <c r="C82" s="80"/>
+      <c r="D82" s="80"/>
+      <c r="E82" s="80"/>
+      <c r="F82" s="80"/>
+      <c r="G82" s="80"/>
+      <c r="H82" s="80"/>
+      <c r="I82" s="80"/>
+      <c r="J82" s="80"/>
+      <c r="K82" s="80"/>
+      <c r="L82" s="80"/>
+      <c r="M82" s="80"/>
+      <c r="N82" s="80"/>
+      <c r="O82" s="80"/>
+      <c r="P82" s="80"/>
+      <c r="Q82" s="80"/>
     </row>
     <row r="83" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="74" t="s">
+      <c r="A83" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B83" s="71" t="s">
+      <c r="B83" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C83" s="72"/>
-      <c r="D83" s="72"/>
-      <c r="E83" s="71" t="s">
+      <c r="C83" s="80"/>
+      <c r="D83" s="80"/>
+      <c r="E83" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="F83" s="72"/>
-      <c r="G83" s="72"/>
-      <c r="H83" s="71" t="s">
+      <c r="F83" s="80"/>
+      <c r="G83" s="80"/>
+      <c r="H83" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="I83" s="72"/>
-      <c r="J83" s="72"/>
-      <c r="K83" s="71" t="s">
+      <c r="I83" s="80"/>
+      <c r="J83" s="80"/>
+      <c r="K83" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="L83" s="72"/>
-      <c r="M83" s="72"/>
-      <c r="N83" s="72"/>
-      <c r="O83" s="72"/>
-      <c r="P83" s="71" t="s">
+      <c r="L83" s="80"/>
+      <c r="M83" s="80"/>
+      <c r="N83" s="80"/>
+      <c r="O83" s="80"/>
+      <c r="P83" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="Q83" s="71" t="s">
+      <c r="Q83" s="79" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A84" s="72"/>
+      <c r="A84" s="80"/>
       <c r="B84" s="43" t="s">
         <v>27</v>
       </c>
@@ -13382,8 +13591,8 @@
       <c r="O84" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P84" s="72"/>
-      <c r="Q84" s="72"/>
+      <c r="P84" s="80"/>
+      <c r="Q84" s="80"/>
     </row>
     <row r="85" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="43" t="s">
@@ -13660,80 +13869,80 @@
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A93" s="73" t="s">
+      <c r="A93" s="82" t="s">
         <v>869</v>
       </c>
-      <c r="B93" s="72"/>
-      <c r="C93" s="72"/>
-      <c r="D93" s="72"/>
-      <c r="E93" s="72"/>
-      <c r="F93" s="72"/>
-      <c r="G93" s="72"/>
-      <c r="H93" s="72"/>
-      <c r="I93" s="72"/>
-      <c r="J93" s="72"/>
-      <c r="K93" s="72"/>
-      <c r="L93" s="72"/>
-      <c r="M93" s="72"/>
-      <c r="N93" s="72"/>
-      <c r="O93" s="72"/>
-      <c r="P93" s="72"/>
-      <c r="Q93" s="72"/>
+      <c r="B93" s="80"/>
+      <c r="C93" s="80"/>
+      <c r="D93" s="80"/>
+      <c r="E93" s="80"/>
+      <c r="F93" s="80"/>
+      <c r="G93" s="80"/>
+      <c r="H93" s="80"/>
+      <c r="I93" s="80"/>
+      <c r="J93" s="80"/>
+      <c r="K93" s="80"/>
+      <c r="L93" s="80"/>
+      <c r="M93" s="80"/>
+      <c r="N93" s="80"/>
+      <c r="O93" s="80"/>
+      <c r="P93" s="80"/>
+      <c r="Q93" s="80"/>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A94" s="72"/>
-      <c r="B94" s="72"/>
-      <c r="C94" s="72"/>
-      <c r="D94" s="72"/>
-      <c r="E94" s="72"/>
-      <c r="F94" s="72"/>
-      <c r="G94" s="72"/>
-      <c r="H94" s="72"/>
-      <c r="I94" s="72"/>
-      <c r="J94" s="72"/>
-      <c r="K94" s="72"/>
-      <c r="L94" s="72"/>
-      <c r="M94" s="72"/>
-      <c r="N94" s="72"/>
-      <c r="O94" s="72"/>
-      <c r="P94" s="72"/>
-      <c r="Q94" s="72"/>
+      <c r="A94" s="80"/>
+      <c r="B94" s="80"/>
+      <c r="C94" s="80"/>
+      <c r="D94" s="80"/>
+      <c r="E94" s="80"/>
+      <c r="F94" s="80"/>
+      <c r="G94" s="80"/>
+      <c r="H94" s="80"/>
+      <c r="I94" s="80"/>
+      <c r="J94" s="80"/>
+      <c r="K94" s="80"/>
+      <c r="L94" s="80"/>
+      <c r="M94" s="80"/>
+      <c r="N94" s="80"/>
+      <c r="O94" s="80"/>
+      <c r="P94" s="80"/>
+      <c r="Q94" s="80"/>
     </row>
     <row r="95" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="74" t="s">
+      <c r="A95" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B95" s="71" t="s">
+      <c r="B95" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C95" s="72"/>
-      <c r="D95" s="72"/>
-      <c r="E95" s="71" t="s">
+      <c r="C95" s="80"/>
+      <c r="D95" s="80"/>
+      <c r="E95" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="F95" s="72"/>
-      <c r="G95" s="72"/>
-      <c r="H95" s="71" t="s">
+      <c r="F95" s="80"/>
+      <c r="G95" s="80"/>
+      <c r="H95" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="I95" s="72"/>
-      <c r="J95" s="72"/>
-      <c r="K95" s="71" t="s">
+      <c r="I95" s="80"/>
+      <c r="J95" s="80"/>
+      <c r="K95" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="L95" s="72"/>
-      <c r="M95" s="72"/>
-      <c r="N95" s="72"/>
-      <c r="O95" s="72"/>
-      <c r="P95" s="71" t="s">
+      <c r="L95" s="80"/>
+      <c r="M95" s="80"/>
+      <c r="N95" s="80"/>
+      <c r="O95" s="80"/>
+      <c r="P95" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="Q95" s="71" t="s">
+      <c r="Q95" s="79" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A96" s="72"/>
+      <c r="A96" s="80"/>
       <c r="B96" s="43" t="s">
         <v>27</v>
       </c>
@@ -13776,8 +13985,8 @@
       <c r="O96" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P96" s="72"/>
-      <c r="Q96" s="72"/>
+      <c r="P96" s="80"/>
+      <c r="Q96" s="80"/>
     </row>
     <row r="97" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="43" t="s">
@@ -14780,80 +14989,80 @@
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A127" s="73" t="s">
+      <c r="A127" s="82" t="s">
         <v>562</v>
       </c>
-      <c r="B127" s="72"/>
-      <c r="C127" s="72"/>
-      <c r="D127" s="72"/>
-      <c r="E127" s="72"/>
-      <c r="F127" s="72"/>
-      <c r="G127" s="72"/>
-      <c r="H127" s="72"/>
-      <c r="I127" s="72"/>
-      <c r="J127" s="72"/>
-      <c r="K127" s="72"/>
-      <c r="L127" s="72"/>
-      <c r="M127" s="72"/>
-      <c r="N127" s="72"/>
-      <c r="O127" s="72"/>
-      <c r="P127" s="72"/>
-      <c r="Q127" s="72"/>
+      <c r="B127" s="80"/>
+      <c r="C127" s="80"/>
+      <c r="D127" s="80"/>
+      <c r="E127" s="80"/>
+      <c r="F127" s="80"/>
+      <c r="G127" s="80"/>
+      <c r="H127" s="80"/>
+      <c r="I127" s="80"/>
+      <c r="J127" s="80"/>
+      <c r="K127" s="80"/>
+      <c r="L127" s="80"/>
+      <c r="M127" s="80"/>
+      <c r="N127" s="80"/>
+      <c r="O127" s="80"/>
+      <c r="P127" s="80"/>
+      <c r="Q127" s="80"/>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A128" s="72"/>
-      <c r="B128" s="72"/>
-      <c r="C128" s="72"/>
-      <c r="D128" s="72"/>
-      <c r="E128" s="72"/>
-      <c r="F128" s="72"/>
-      <c r="G128" s="72"/>
-      <c r="H128" s="72"/>
-      <c r="I128" s="72"/>
-      <c r="J128" s="72"/>
-      <c r="K128" s="72"/>
-      <c r="L128" s="72"/>
-      <c r="M128" s="72"/>
-      <c r="N128" s="72"/>
-      <c r="O128" s="72"/>
-      <c r="P128" s="72"/>
-      <c r="Q128" s="72"/>
+      <c r="A128" s="80"/>
+      <c r="B128" s="80"/>
+      <c r="C128" s="80"/>
+      <c r="D128" s="80"/>
+      <c r="E128" s="80"/>
+      <c r="F128" s="80"/>
+      <c r="G128" s="80"/>
+      <c r="H128" s="80"/>
+      <c r="I128" s="80"/>
+      <c r="J128" s="80"/>
+      <c r="K128" s="80"/>
+      <c r="L128" s="80"/>
+      <c r="M128" s="80"/>
+      <c r="N128" s="80"/>
+      <c r="O128" s="80"/>
+      <c r="P128" s="80"/>
+      <c r="Q128" s="80"/>
     </row>
     <row r="129" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="74" t="s">
+      <c r="A129" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B129" s="71" t="s">
+      <c r="B129" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C129" s="72"/>
-      <c r="D129" s="72"/>
-      <c r="E129" s="71" t="s">
+      <c r="C129" s="80"/>
+      <c r="D129" s="80"/>
+      <c r="E129" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="F129" s="72"/>
-      <c r="G129" s="72"/>
-      <c r="H129" s="71" t="s">
+      <c r="F129" s="80"/>
+      <c r="G129" s="80"/>
+      <c r="H129" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="I129" s="72"/>
-      <c r="J129" s="72"/>
-      <c r="K129" s="71" t="s">
+      <c r="I129" s="80"/>
+      <c r="J129" s="80"/>
+      <c r="K129" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="L129" s="72"/>
-      <c r="M129" s="72"/>
-      <c r="N129" s="72"/>
-      <c r="O129" s="72"/>
-      <c r="P129" s="71" t="s">
+      <c r="L129" s="80"/>
+      <c r="M129" s="80"/>
+      <c r="N129" s="80"/>
+      <c r="O129" s="80"/>
+      <c r="P129" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="Q129" s="71" t="s">
+      <c r="Q129" s="79" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A130" s="72"/>
+      <c r="A130" s="80"/>
       <c r="B130" s="43" t="s">
         <v>27</v>
       </c>
@@ -14896,8 +15105,8 @@
       <c r="O130" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P130" s="72"/>
-      <c r="Q130" s="72"/>
+      <c r="P130" s="80"/>
+      <c r="Q130" s="80"/>
     </row>
     <row r="131" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="43" t="s">
@@ -16028,80 +16237,80 @@
       </c>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A159" s="73" t="s">
+      <c r="A159" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="B159" s="72"/>
-      <c r="C159" s="72"/>
-      <c r="D159" s="72"/>
-      <c r="E159" s="72"/>
-      <c r="F159" s="72"/>
-      <c r="G159" s="72"/>
-      <c r="H159" s="72"/>
-      <c r="I159" s="72"/>
-      <c r="J159" s="72"/>
-      <c r="K159" s="72"/>
-      <c r="L159" s="72"/>
-      <c r="M159" s="72"/>
-      <c r="N159" s="72"/>
-      <c r="O159" s="72"/>
-      <c r="P159" s="72"/>
-      <c r="Q159" s="72"/>
+      <c r="B159" s="80"/>
+      <c r="C159" s="80"/>
+      <c r="D159" s="80"/>
+      <c r="E159" s="80"/>
+      <c r="F159" s="80"/>
+      <c r="G159" s="80"/>
+      <c r="H159" s="80"/>
+      <c r="I159" s="80"/>
+      <c r="J159" s="80"/>
+      <c r="K159" s="80"/>
+      <c r="L159" s="80"/>
+      <c r="M159" s="80"/>
+      <c r="N159" s="80"/>
+      <c r="O159" s="80"/>
+      <c r="P159" s="80"/>
+      <c r="Q159" s="80"/>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A160" s="72"/>
-      <c r="B160" s="72"/>
-      <c r="C160" s="72"/>
-      <c r="D160" s="72"/>
-      <c r="E160" s="72"/>
-      <c r="F160" s="72"/>
-      <c r="G160" s="72"/>
-      <c r="H160" s="72"/>
-      <c r="I160" s="72"/>
-      <c r="J160" s="72"/>
-      <c r="K160" s="72"/>
-      <c r="L160" s="72"/>
-      <c r="M160" s="72"/>
-      <c r="N160" s="72"/>
-      <c r="O160" s="72"/>
-      <c r="P160" s="72"/>
-      <c r="Q160" s="72"/>
+      <c r="A160" s="80"/>
+      <c r="B160" s="80"/>
+      <c r="C160" s="80"/>
+      <c r="D160" s="80"/>
+      <c r="E160" s="80"/>
+      <c r="F160" s="80"/>
+      <c r="G160" s="80"/>
+      <c r="H160" s="80"/>
+      <c r="I160" s="80"/>
+      <c r="J160" s="80"/>
+      <c r="K160" s="80"/>
+      <c r="L160" s="80"/>
+      <c r="M160" s="80"/>
+      <c r="N160" s="80"/>
+      <c r="O160" s="80"/>
+      <c r="P160" s="80"/>
+      <c r="Q160" s="80"/>
     </row>
     <row r="161" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="74" t="s">
+      <c r="A161" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B161" s="71" t="s">
+      <c r="B161" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C161" s="72"/>
-      <c r="D161" s="72"/>
-      <c r="E161" s="71" t="s">
+      <c r="C161" s="80"/>
+      <c r="D161" s="80"/>
+      <c r="E161" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="F161" s="72"/>
-      <c r="G161" s="72"/>
-      <c r="H161" s="71" t="s">
+      <c r="F161" s="80"/>
+      <c r="G161" s="80"/>
+      <c r="H161" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="I161" s="72"/>
-      <c r="J161" s="72"/>
-      <c r="K161" s="71" t="s">
+      <c r="I161" s="80"/>
+      <c r="J161" s="80"/>
+      <c r="K161" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="L161" s="72"/>
-      <c r="M161" s="72"/>
-      <c r="N161" s="72"/>
-      <c r="O161" s="72"/>
-      <c r="P161" s="71" t="s">
+      <c r="L161" s="80"/>
+      <c r="M161" s="80"/>
+      <c r="N161" s="80"/>
+      <c r="O161" s="80"/>
+      <c r="P161" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="Q161" s="71" t="s">
+      <c r="Q161" s="79" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A162" s="72"/>
+      <c r="A162" s="80"/>
       <c r="B162" s="43" t="s">
         <v>27</v>
       </c>
@@ -16144,8 +16353,8 @@
       <c r="O162" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P162" s="72"/>
-      <c r="Q162" s="72"/>
+      <c r="P162" s="80"/>
+      <c r="Q162" s="80"/>
     </row>
     <row r="163" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="43" t="s">
@@ -16199,80 +16408,80 @@
       </c>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A164" s="73" t="s">
+      <c r="A164" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="B164" s="72"/>
-      <c r="C164" s="72"/>
-      <c r="D164" s="72"/>
-      <c r="E164" s="72"/>
-      <c r="F164" s="72"/>
-      <c r="G164" s="72"/>
-      <c r="H164" s="72"/>
-      <c r="I164" s="72"/>
-      <c r="J164" s="72"/>
-      <c r="K164" s="72"/>
-      <c r="L164" s="72"/>
-      <c r="M164" s="72"/>
-      <c r="N164" s="72"/>
-      <c r="O164" s="72"/>
-      <c r="P164" s="72"/>
-      <c r="Q164" s="72"/>
+      <c r="B164" s="80"/>
+      <c r="C164" s="80"/>
+      <c r="D164" s="80"/>
+      <c r="E164" s="80"/>
+      <c r="F164" s="80"/>
+      <c r="G164" s="80"/>
+      <c r="H164" s="80"/>
+      <c r="I164" s="80"/>
+      <c r="J164" s="80"/>
+      <c r="K164" s="80"/>
+      <c r="L164" s="80"/>
+      <c r="M164" s="80"/>
+      <c r="N164" s="80"/>
+      <c r="O164" s="80"/>
+      <c r="P164" s="80"/>
+      <c r="Q164" s="80"/>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A165" s="72"/>
-      <c r="B165" s="72"/>
-      <c r="C165" s="72"/>
-      <c r="D165" s="72"/>
-      <c r="E165" s="72"/>
-      <c r="F165" s="72"/>
-      <c r="G165" s="72"/>
-      <c r="H165" s="72"/>
-      <c r="I165" s="72"/>
-      <c r="J165" s="72"/>
-      <c r="K165" s="72"/>
-      <c r="L165" s="72"/>
-      <c r="M165" s="72"/>
-      <c r="N165" s="72"/>
-      <c r="O165" s="72"/>
-      <c r="P165" s="72"/>
-      <c r="Q165" s="72"/>
+      <c r="A165" s="80"/>
+      <c r="B165" s="80"/>
+      <c r="C165" s="80"/>
+      <c r="D165" s="80"/>
+      <c r="E165" s="80"/>
+      <c r="F165" s="80"/>
+      <c r="G165" s="80"/>
+      <c r="H165" s="80"/>
+      <c r="I165" s="80"/>
+      <c r="J165" s="80"/>
+      <c r="K165" s="80"/>
+      <c r="L165" s="80"/>
+      <c r="M165" s="80"/>
+      <c r="N165" s="80"/>
+      <c r="O165" s="80"/>
+      <c r="P165" s="80"/>
+      <c r="Q165" s="80"/>
     </row>
     <row r="166" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="74" t="s">
+      <c r="A166" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B166" s="71" t="s">
+      <c r="B166" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C166" s="72"/>
-      <c r="D166" s="72"/>
-      <c r="E166" s="71" t="s">
+      <c r="C166" s="80"/>
+      <c r="D166" s="80"/>
+      <c r="E166" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="F166" s="72"/>
-      <c r="G166" s="72"/>
-      <c r="H166" s="71" t="s">
+      <c r="F166" s="80"/>
+      <c r="G166" s="80"/>
+      <c r="H166" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="I166" s="72"/>
-      <c r="J166" s="72"/>
-      <c r="K166" s="71" t="s">
+      <c r="I166" s="80"/>
+      <c r="J166" s="80"/>
+      <c r="K166" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="L166" s="72"/>
-      <c r="M166" s="72"/>
-      <c r="N166" s="72"/>
-      <c r="O166" s="72"/>
-      <c r="P166" s="71" t="s">
+      <c r="L166" s="80"/>
+      <c r="M166" s="80"/>
+      <c r="N166" s="80"/>
+      <c r="O166" s="80"/>
+      <c r="P166" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="Q166" s="71" t="s">
+      <c r="Q166" s="79" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A167" s="72"/>
+      <c r="A167" s="80"/>
       <c r="B167" s="43" t="s">
         <v>27</v>
       </c>
@@ -16315,8 +16524,8 @@
       <c r="O167" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P167" s="72"/>
-      <c r="Q167" s="72"/>
+      <c r="P167" s="80"/>
+      <c r="Q167" s="80"/>
     </row>
     <row r="168" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="43" t="s">
@@ -16495,6 +16704,70 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="P35:P36"/>
+    <mergeCell ref="E161:G161"/>
+    <mergeCell ref="K30:O30"/>
+    <mergeCell ref="A164:Q165"/>
+    <mergeCell ref="B166:D166"/>
+    <mergeCell ref="K55:O55"/>
+    <mergeCell ref="E95:G95"/>
+    <mergeCell ref="A33:Q34"/>
+    <mergeCell ref="A72:Q73"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A53:Q54"/>
+    <mergeCell ref="H95:J95"/>
+    <mergeCell ref="P166:P167"/>
+    <mergeCell ref="A127:Q128"/>
+    <mergeCell ref="K161:O161"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A28:Q29"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A48:Q49"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="Q55:Q56"/>
+    <mergeCell ref="P50:P51"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="Q74:Q75"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="Q83:Q84"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="K35:O35"/>
+    <mergeCell ref="Q30:Q31"/>
+    <mergeCell ref="K50:O50"/>
+    <mergeCell ref="B161:D161"/>
+    <mergeCell ref="P129:P130"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="K74:O74"/>
+    <mergeCell ref="K83:O83"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="A129:A130"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="H166:J166"/>
+    <mergeCell ref="E129:G129"/>
+    <mergeCell ref="H161:J161"/>
+    <mergeCell ref="H129:J129"/>
+    <mergeCell ref="E74:G74"/>
+    <mergeCell ref="E166:G166"/>
+    <mergeCell ref="K95:O95"/>
+    <mergeCell ref="Q166:Q167"/>
+    <mergeCell ref="Q35:Q36"/>
+    <mergeCell ref="P161:P162"/>
+    <mergeCell ref="A159:Q160"/>
+    <mergeCell ref="A93:Q94"/>
+    <mergeCell ref="Q161:Q162"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="P83:P84"/>
+    <mergeCell ref="Q129:Q130"/>
+    <mergeCell ref="Q95:Q96"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="H55:J55"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="P55:P56"/>
     <mergeCell ref="K166:O166"/>
     <mergeCell ref="H74:J74"/>
     <mergeCell ref="H83:J83"/>
@@ -16511,70 +16784,6 @@
     <mergeCell ref="A81:Q82"/>
     <mergeCell ref="A95:A96"/>
     <mergeCell ref="B129:D129"/>
-    <mergeCell ref="Q166:Q167"/>
-    <mergeCell ref="Q35:Q36"/>
-    <mergeCell ref="P161:P162"/>
-    <mergeCell ref="A159:Q160"/>
-    <mergeCell ref="A93:Q94"/>
-    <mergeCell ref="Q161:Q162"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="P83:P84"/>
-    <mergeCell ref="Q129:Q130"/>
-    <mergeCell ref="Q95:Q96"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="H55:J55"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="B161:D161"/>
-    <mergeCell ref="P129:P130"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="K74:O74"/>
-    <mergeCell ref="K83:O83"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="A129:A130"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="H166:J166"/>
-    <mergeCell ref="E129:G129"/>
-    <mergeCell ref="H161:J161"/>
-    <mergeCell ref="H129:J129"/>
-    <mergeCell ref="E74:G74"/>
-    <mergeCell ref="E166:G166"/>
-    <mergeCell ref="K95:O95"/>
-    <mergeCell ref="A28:Q29"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A48:Q49"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="Q55:Q56"/>
-    <mergeCell ref="P50:P51"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="Q74:Q75"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="P30:P31"/>
-    <mergeCell ref="Q83:Q84"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="K35:O35"/>
-    <mergeCell ref="Q30:Q31"/>
-    <mergeCell ref="K50:O50"/>
-    <mergeCell ref="P35:P36"/>
-    <mergeCell ref="E161:G161"/>
-    <mergeCell ref="K30:O30"/>
-    <mergeCell ref="A164:Q165"/>
-    <mergeCell ref="B166:D166"/>
-    <mergeCell ref="K55:O55"/>
-    <mergeCell ref="E95:G95"/>
-    <mergeCell ref="A33:Q34"/>
-    <mergeCell ref="A72:Q73"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="A53:Q54"/>
-    <mergeCell ref="H95:J95"/>
-    <mergeCell ref="P166:P167"/>
-    <mergeCell ref="A127:Q128"/>
-    <mergeCell ref="K161:O161"/>
-    <mergeCell ref="H30:J30"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.scei-concours.fr/stat2025/bcpst.html" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -16710,80 +16919,80 @@
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="73" t="s">
+      <c r="A24" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="72"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="72"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="72"/>
-      <c r="K24" s="72"/>
-      <c r="L24" s="72"/>
-      <c r="M24" s="72"/>
-      <c r="N24" s="72"/>
-      <c r="O24" s="72"/>
-      <c r="P24" s="72"/>
-      <c r="Q24" s="72"/>
+      <c r="B24" s="80"/>
+      <c r="C24" s="80"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="80"/>
+      <c r="F24" s="80"/>
+      <c r="G24" s="80"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="80"/>
+      <c r="J24" s="80"/>
+      <c r="K24" s="80"/>
+      <c r="L24" s="80"/>
+      <c r="M24" s="80"/>
+      <c r="N24" s="80"/>
+      <c r="O24" s="80"/>
+      <c r="P24" s="80"/>
+      <c r="Q24" s="80"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="72"/>
-      <c r="B25" s="72"/>
-      <c r="C25" s="72"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="72"/>
-      <c r="F25" s="72"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="72"/>
-      <c r="I25" s="72"/>
-      <c r="J25" s="72"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="72"/>
-      <c r="M25" s="72"/>
-      <c r="N25" s="72"/>
-      <c r="O25" s="72"/>
-      <c r="P25" s="72"/>
-      <c r="Q25" s="72"/>
+      <c r="A25" s="80"/>
+      <c r="B25" s="80"/>
+      <c r="C25" s="80"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="80"/>
+      <c r="F25" s="80"/>
+      <c r="G25" s="80"/>
+      <c r="H25" s="80"/>
+      <c r="I25" s="80"/>
+      <c r="J25" s="80"/>
+      <c r="K25" s="80"/>
+      <c r="L25" s="80"/>
+      <c r="M25" s="80"/>
+      <c r="N25" s="80"/>
+      <c r="O25" s="80"/>
+      <c r="P25" s="80"/>
+      <c r="Q25" s="80"/>
     </row>
     <row r="26" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="74" t="s">
+      <c r="A26" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="71" t="s">
+      <c r="B26" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="72"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="71" t="s">
+      <c r="C26" s="80"/>
+      <c r="D26" s="80"/>
+      <c r="E26" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="72"/>
-      <c r="G26" s="72"/>
-      <c r="H26" s="71" t="s">
+      <c r="F26" s="80"/>
+      <c r="G26" s="80"/>
+      <c r="H26" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="I26" s="72"/>
-      <c r="J26" s="72"/>
-      <c r="K26" s="71" t="s">
+      <c r="I26" s="80"/>
+      <c r="J26" s="80"/>
+      <c r="K26" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="L26" s="72"/>
-      <c r="M26" s="72"/>
-      <c r="N26" s="72"/>
-      <c r="O26" s="72"/>
-      <c r="P26" s="71" t="s">
+      <c r="L26" s="80"/>
+      <c r="M26" s="80"/>
+      <c r="N26" s="80"/>
+      <c r="O26" s="80"/>
+      <c r="P26" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="Q26" s="71" t="s">
+      <c r="Q26" s="79" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="72"/>
+      <c r="A27" s="80"/>
       <c r="B27" s="43" t="s">
         <v>27</v>
       </c>
@@ -16826,8 +17035,8 @@
       <c r="O27" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P27" s="72"/>
-      <c r="Q27" s="72"/>
+      <c r="P27" s="80"/>
+      <c r="Q27" s="80"/>
     </row>
     <row r="28" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="43" t="s">
@@ -17335,80 +17544,80 @@
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="73" t="s">
+      <c r="A43" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="72"/>
-      <c r="C43" s="72"/>
-      <c r="D43" s="72"/>
-      <c r="E43" s="72"/>
-      <c r="F43" s="72"/>
-      <c r="G43" s="72"/>
-      <c r="H43" s="72"/>
-      <c r="I43" s="72"/>
-      <c r="J43" s="72"/>
-      <c r="K43" s="72"/>
-      <c r="L43" s="72"/>
-      <c r="M43" s="72"/>
-      <c r="N43" s="72"/>
-      <c r="O43" s="72"/>
-      <c r="P43" s="72"/>
-      <c r="Q43" s="72"/>
+      <c r="B43" s="80"/>
+      <c r="C43" s="80"/>
+      <c r="D43" s="80"/>
+      <c r="E43" s="80"/>
+      <c r="F43" s="80"/>
+      <c r="G43" s="80"/>
+      <c r="H43" s="80"/>
+      <c r="I43" s="80"/>
+      <c r="J43" s="80"/>
+      <c r="K43" s="80"/>
+      <c r="L43" s="80"/>
+      <c r="M43" s="80"/>
+      <c r="N43" s="80"/>
+      <c r="O43" s="80"/>
+      <c r="P43" s="80"/>
+      <c r="Q43" s="80"/>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="72"/>
-      <c r="B44" s="72"/>
-      <c r="C44" s="72"/>
-      <c r="D44" s="72"/>
-      <c r="E44" s="72"/>
-      <c r="F44" s="72"/>
-      <c r="G44" s="72"/>
-      <c r="H44" s="72"/>
-      <c r="I44" s="72"/>
-      <c r="J44" s="72"/>
-      <c r="K44" s="72"/>
-      <c r="L44" s="72"/>
-      <c r="M44" s="72"/>
-      <c r="N44" s="72"/>
-      <c r="O44" s="72"/>
-      <c r="P44" s="72"/>
-      <c r="Q44" s="72"/>
+      <c r="A44" s="80"/>
+      <c r="B44" s="80"/>
+      <c r="C44" s="80"/>
+      <c r="D44" s="80"/>
+      <c r="E44" s="80"/>
+      <c r="F44" s="80"/>
+      <c r="G44" s="80"/>
+      <c r="H44" s="80"/>
+      <c r="I44" s="80"/>
+      <c r="J44" s="80"/>
+      <c r="K44" s="80"/>
+      <c r="L44" s="80"/>
+      <c r="M44" s="80"/>
+      <c r="N44" s="80"/>
+      <c r="O44" s="80"/>
+      <c r="P44" s="80"/>
+      <c r="Q44" s="80"/>
     </row>
     <row r="45" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="74" t="s">
+      <c r="A45" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="71" t="s">
+      <c r="B45" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="72"/>
-      <c r="D45" s="72"/>
-      <c r="E45" s="71" t="s">
+      <c r="C45" s="80"/>
+      <c r="D45" s="80"/>
+      <c r="E45" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="F45" s="72"/>
-      <c r="G45" s="72"/>
-      <c r="H45" s="71" t="s">
+      <c r="F45" s="80"/>
+      <c r="G45" s="80"/>
+      <c r="H45" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="I45" s="72"/>
-      <c r="J45" s="72"/>
-      <c r="K45" s="71" t="s">
+      <c r="I45" s="80"/>
+      <c r="J45" s="80"/>
+      <c r="K45" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="72"/>
-      <c r="M45" s="72"/>
-      <c r="N45" s="72"/>
-      <c r="O45" s="72"/>
-      <c r="P45" s="71" t="s">
+      <c r="L45" s="80"/>
+      <c r="M45" s="80"/>
+      <c r="N45" s="80"/>
+      <c r="O45" s="80"/>
+      <c r="P45" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="Q45" s="71" t="s">
+      <c r="Q45" s="79" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" s="72"/>
+      <c r="A46" s="80"/>
       <c r="B46" s="43" t="s">
         <v>27</v>
       </c>
@@ -17451,8 +17660,8 @@
       <c r="O46" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P46" s="72"/>
-      <c r="Q46" s="72"/>
+      <c r="P46" s="80"/>
+      <c r="Q46" s="80"/>
     </row>
     <row r="47" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="43" t="s">
@@ -17506,80 +17715,80 @@
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="73" t="s">
+      <c r="A48" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="72"/>
-      <c r="C48" s="72"/>
-      <c r="D48" s="72"/>
-      <c r="E48" s="72"/>
-      <c r="F48" s="72"/>
-      <c r="G48" s="72"/>
-      <c r="H48" s="72"/>
-      <c r="I48" s="72"/>
-      <c r="J48" s="72"/>
-      <c r="K48" s="72"/>
-      <c r="L48" s="72"/>
-      <c r="M48" s="72"/>
-      <c r="N48" s="72"/>
-      <c r="O48" s="72"/>
-      <c r="P48" s="72"/>
-      <c r="Q48" s="72"/>
+      <c r="B48" s="80"/>
+      <c r="C48" s="80"/>
+      <c r="D48" s="80"/>
+      <c r="E48" s="80"/>
+      <c r="F48" s="80"/>
+      <c r="G48" s="80"/>
+      <c r="H48" s="80"/>
+      <c r="I48" s="80"/>
+      <c r="J48" s="80"/>
+      <c r="K48" s="80"/>
+      <c r="L48" s="80"/>
+      <c r="M48" s="80"/>
+      <c r="N48" s="80"/>
+      <c r="O48" s="80"/>
+      <c r="P48" s="80"/>
+      <c r="Q48" s="80"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="72"/>
-      <c r="B49" s="72"/>
-      <c r="C49" s="72"/>
-      <c r="D49" s="72"/>
-      <c r="E49" s="72"/>
-      <c r="F49" s="72"/>
-      <c r="G49" s="72"/>
-      <c r="H49" s="72"/>
-      <c r="I49" s="72"/>
-      <c r="J49" s="72"/>
-      <c r="K49" s="72"/>
-      <c r="L49" s="72"/>
-      <c r="M49" s="72"/>
-      <c r="N49" s="72"/>
-      <c r="O49" s="72"/>
-      <c r="P49" s="72"/>
-      <c r="Q49" s="72"/>
+      <c r="A49" s="80"/>
+      <c r="B49" s="80"/>
+      <c r="C49" s="80"/>
+      <c r="D49" s="80"/>
+      <c r="E49" s="80"/>
+      <c r="F49" s="80"/>
+      <c r="G49" s="80"/>
+      <c r="H49" s="80"/>
+      <c r="I49" s="80"/>
+      <c r="J49" s="80"/>
+      <c r="K49" s="80"/>
+      <c r="L49" s="80"/>
+      <c r="M49" s="80"/>
+      <c r="N49" s="80"/>
+      <c r="O49" s="80"/>
+      <c r="P49" s="80"/>
+      <c r="Q49" s="80"/>
     </row>
     <row r="50" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="74" t="s">
+      <c r="A50" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B50" s="71" t="s">
+      <c r="B50" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C50" s="72"/>
-      <c r="D50" s="72"/>
-      <c r="E50" s="71" t="s">
+      <c r="C50" s="80"/>
+      <c r="D50" s="80"/>
+      <c r="E50" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="F50" s="72"/>
-      <c r="G50" s="72"/>
-      <c r="H50" s="71" t="s">
+      <c r="F50" s="80"/>
+      <c r="G50" s="80"/>
+      <c r="H50" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="I50" s="72"/>
-      <c r="J50" s="72"/>
-      <c r="K50" s="71" t="s">
+      <c r="I50" s="80"/>
+      <c r="J50" s="80"/>
+      <c r="K50" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="72"/>
-      <c r="M50" s="72"/>
-      <c r="N50" s="72"/>
-      <c r="O50" s="72"/>
-      <c r="P50" s="71" t="s">
+      <c r="L50" s="80"/>
+      <c r="M50" s="80"/>
+      <c r="N50" s="80"/>
+      <c r="O50" s="80"/>
+      <c r="P50" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="Q50" s="71" t="s">
+      <c r="Q50" s="79" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51" s="72"/>
+      <c r="A51" s="80"/>
       <c r="B51" s="43" t="s">
         <v>27</v>
       </c>
@@ -17622,8 +17831,8 @@
       <c r="O51" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P51" s="72"/>
-      <c r="Q51" s="72"/>
+      <c r="P51" s="80"/>
+      <c r="Q51" s="80"/>
     </row>
     <row r="52" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="43" t="s">
@@ -17801,80 +18010,80 @@
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57" s="73" t="s">
+      <c r="A57" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="B57" s="72"/>
-      <c r="C57" s="72"/>
-      <c r="D57" s="72"/>
-      <c r="E57" s="72"/>
-      <c r="F57" s="72"/>
-      <c r="G57" s="72"/>
-      <c r="H57" s="72"/>
-      <c r="I57" s="72"/>
-      <c r="J57" s="72"/>
-      <c r="K57" s="72"/>
-      <c r="L57" s="72"/>
-      <c r="M57" s="72"/>
-      <c r="N57" s="72"/>
-      <c r="O57" s="72"/>
-      <c r="P57" s="72"/>
-      <c r="Q57" s="72"/>
+      <c r="B57" s="80"/>
+      <c r="C57" s="80"/>
+      <c r="D57" s="80"/>
+      <c r="E57" s="80"/>
+      <c r="F57" s="80"/>
+      <c r="G57" s="80"/>
+      <c r="H57" s="80"/>
+      <c r="I57" s="80"/>
+      <c r="J57" s="80"/>
+      <c r="K57" s="80"/>
+      <c r="L57" s="80"/>
+      <c r="M57" s="80"/>
+      <c r="N57" s="80"/>
+      <c r="O57" s="80"/>
+      <c r="P57" s="80"/>
+      <c r="Q57" s="80"/>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A58" s="72"/>
-      <c r="B58" s="72"/>
-      <c r="C58" s="72"/>
-      <c r="D58" s="72"/>
-      <c r="E58" s="72"/>
-      <c r="F58" s="72"/>
-      <c r="G58" s="72"/>
-      <c r="H58" s="72"/>
-      <c r="I58" s="72"/>
-      <c r="J58" s="72"/>
-      <c r="K58" s="72"/>
-      <c r="L58" s="72"/>
-      <c r="M58" s="72"/>
-      <c r="N58" s="72"/>
-      <c r="O58" s="72"/>
-      <c r="P58" s="72"/>
-      <c r="Q58" s="72"/>
+      <c r="A58" s="80"/>
+      <c r="B58" s="80"/>
+      <c r="C58" s="80"/>
+      <c r="D58" s="80"/>
+      <c r="E58" s="80"/>
+      <c r="F58" s="80"/>
+      <c r="G58" s="80"/>
+      <c r="H58" s="80"/>
+      <c r="I58" s="80"/>
+      <c r="J58" s="80"/>
+      <c r="K58" s="80"/>
+      <c r="L58" s="80"/>
+      <c r="M58" s="80"/>
+      <c r="N58" s="80"/>
+      <c r="O58" s="80"/>
+      <c r="P58" s="80"/>
+      <c r="Q58" s="80"/>
     </row>
     <row r="59" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="74" t="s">
+      <c r="A59" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B59" s="71" t="s">
+      <c r="B59" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C59" s="72"/>
-      <c r="D59" s="72"/>
-      <c r="E59" s="71" t="s">
+      <c r="C59" s="80"/>
+      <c r="D59" s="80"/>
+      <c r="E59" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="F59" s="72"/>
-      <c r="G59" s="72"/>
-      <c r="H59" s="71" t="s">
+      <c r="F59" s="80"/>
+      <c r="G59" s="80"/>
+      <c r="H59" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="I59" s="72"/>
-      <c r="J59" s="72"/>
-      <c r="K59" s="71" t="s">
+      <c r="I59" s="80"/>
+      <c r="J59" s="80"/>
+      <c r="K59" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="L59" s="72"/>
-      <c r="M59" s="72"/>
-      <c r="N59" s="72"/>
-      <c r="O59" s="72"/>
-      <c r="P59" s="71" t="s">
+      <c r="L59" s="80"/>
+      <c r="M59" s="80"/>
+      <c r="N59" s="80"/>
+      <c r="O59" s="80"/>
+      <c r="P59" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="Q59" s="71" t="s">
+      <c r="Q59" s="79" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A60" s="72"/>
+      <c r="A60" s="80"/>
       <c r="B60" s="43" t="s">
         <v>27</v>
       </c>
@@ -17917,8 +18126,8 @@
       <c r="O60" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P60" s="72"/>
-      <c r="Q60" s="72"/>
+      <c r="P60" s="80"/>
+      <c r="Q60" s="80"/>
     </row>
     <row r="61" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="43" t="s">
@@ -18393,80 +18602,80 @@
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75" s="73" t="s">
+      <c r="A75" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="B75" s="72"/>
-      <c r="C75" s="72"/>
-      <c r="D75" s="72"/>
-      <c r="E75" s="72"/>
-      <c r="F75" s="72"/>
-      <c r="G75" s="72"/>
-      <c r="H75" s="72"/>
-      <c r="I75" s="72"/>
-      <c r="J75" s="72"/>
-      <c r="K75" s="72"/>
-      <c r="L75" s="72"/>
-      <c r="M75" s="72"/>
-      <c r="N75" s="72"/>
-      <c r="O75" s="72"/>
-      <c r="P75" s="72"/>
-      <c r="Q75" s="72"/>
+      <c r="B75" s="80"/>
+      <c r="C75" s="80"/>
+      <c r="D75" s="80"/>
+      <c r="E75" s="80"/>
+      <c r="F75" s="80"/>
+      <c r="G75" s="80"/>
+      <c r="H75" s="80"/>
+      <c r="I75" s="80"/>
+      <c r="J75" s="80"/>
+      <c r="K75" s="80"/>
+      <c r="L75" s="80"/>
+      <c r="M75" s="80"/>
+      <c r="N75" s="80"/>
+      <c r="O75" s="80"/>
+      <c r="P75" s="80"/>
+      <c r="Q75" s="80"/>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A76" s="72"/>
-      <c r="B76" s="72"/>
-      <c r="C76" s="72"/>
-      <c r="D76" s="72"/>
-      <c r="E76" s="72"/>
-      <c r="F76" s="72"/>
-      <c r="G76" s="72"/>
-      <c r="H76" s="72"/>
-      <c r="I76" s="72"/>
-      <c r="J76" s="72"/>
-      <c r="K76" s="72"/>
-      <c r="L76" s="72"/>
-      <c r="M76" s="72"/>
-      <c r="N76" s="72"/>
-      <c r="O76" s="72"/>
-      <c r="P76" s="72"/>
-      <c r="Q76" s="72"/>
+      <c r="A76" s="80"/>
+      <c r="B76" s="80"/>
+      <c r="C76" s="80"/>
+      <c r="D76" s="80"/>
+      <c r="E76" s="80"/>
+      <c r="F76" s="80"/>
+      <c r="G76" s="80"/>
+      <c r="H76" s="80"/>
+      <c r="I76" s="80"/>
+      <c r="J76" s="80"/>
+      <c r="K76" s="80"/>
+      <c r="L76" s="80"/>
+      <c r="M76" s="80"/>
+      <c r="N76" s="80"/>
+      <c r="O76" s="80"/>
+      <c r="P76" s="80"/>
+      <c r="Q76" s="80"/>
     </row>
     <row r="77" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="74" t="s">
+      <c r="A77" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B77" s="71" t="s">
+      <c r="B77" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C77" s="72"/>
-      <c r="D77" s="72"/>
-      <c r="E77" s="71" t="s">
+      <c r="C77" s="80"/>
+      <c r="D77" s="80"/>
+      <c r="E77" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="F77" s="72"/>
-      <c r="G77" s="72"/>
-      <c r="H77" s="71" t="s">
+      <c r="F77" s="80"/>
+      <c r="G77" s="80"/>
+      <c r="H77" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="I77" s="72"/>
-      <c r="J77" s="72"/>
-      <c r="K77" s="71" t="s">
+      <c r="I77" s="80"/>
+      <c r="J77" s="80"/>
+      <c r="K77" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="L77" s="72"/>
-      <c r="M77" s="72"/>
-      <c r="N77" s="72"/>
-      <c r="O77" s="72"/>
-      <c r="P77" s="71" t="s">
+      <c r="L77" s="80"/>
+      <c r="M77" s="80"/>
+      <c r="N77" s="80"/>
+      <c r="O77" s="80"/>
+      <c r="P77" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="Q77" s="71" t="s">
+      <c r="Q77" s="79" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A78" s="72"/>
+      <c r="A78" s="80"/>
       <c r="B78" s="43" t="s">
         <v>27</v>
       </c>
@@ -18509,8 +18718,8 @@
       <c r="O78" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P78" s="72"/>
-      <c r="Q78" s="72"/>
+      <c r="P78" s="80"/>
+      <c r="Q78" s="80"/>
     </row>
     <row r="79" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="43" t="s">
@@ -18564,80 +18773,80 @@
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A80" s="73" t="s">
+      <c r="A80" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="B80" s="72"/>
-      <c r="C80" s="72"/>
-      <c r="D80" s="72"/>
-      <c r="E80" s="72"/>
-      <c r="F80" s="72"/>
-      <c r="G80" s="72"/>
-      <c r="H80" s="72"/>
-      <c r="I80" s="72"/>
-      <c r="J80" s="72"/>
-      <c r="K80" s="72"/>
-      <c r="L80" s="72"/>
-      <c r="M80" s="72"/>
-      <c r="N80" s="72"/>
-      <c r="O80" s="72"/>
-      <c r="P80" s="72"/>
-      <c r="Q80" s="72"/>
+      <c r="B80" s="80"/>
+      <c r="C80" s="80"/>
+      <c r="D80" s="80"/>
+      <c r="E80" s="80"/>
+      <c r="F80" s="80"/>
+      <c r="G80" s="80"/>
+      <c r="H80" s="80"/>
+      <c r="I80" s="80"/>
+      <c r="J80" s="80"/>
+      <c r="K80" s="80"/>
+      <c r="L80" s="80"/>
+      <c r="M80" s="80"/>
+      <c r="N80" s="80"/>
+      <c r="O80" s="80"/>
+      <c r="P80" s="80"/>
+      <c r="Q80" s="80"/>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A81" s="72"/>
-      <c r="B81" s="72"/>
-      <c r="C81" s="72"/>
-      <c r="D81" s="72"/>
-      <c r="E81" s="72"/>
-      <c r="F81" s="72"/>
-      <c r="G81" s="72"/>
-      <c r="H81" s="72"/>
-      <c r="I81" s="72"/>
-      <c r="J81" s="72"/>
-      <c r="K81" s="72"/>
-      <c r="L81" s="72"/>
-      <c r="M81" s="72"/>
-      <c r="N81" s="72"/>
-      <c r="O81" s="72"/>
-      <c r="P81" s="72"/>
-      <c r="Q81" s="72"/>
+      <c r="A81" s="80"/>
+      <c r="B81" s="80"/>
+      <c r="C81" s="80"/>
+      <c r="D81" s="80"/>
+      <c r="E81" s="80"/>
+      <c r="F81" s="80"/>
+      <c r="G81" s="80"/>
+      <c r="H81" s="80"/>
+      <c r="I81" s="80"/>
+      <c r="J81" s="80"/>
+      <c r="K81" s="80"/>
+      <c r="L81" s="80"/>
+      <c r="M81" s="80"/>
+      <c r="N81" s="80"/>
+      <c r="O81" s="80"/>
+      <c r="P81" s="80"/>
+      <c r="Q81" s="80"/>
     </row>
     <row r="82" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="74" t="s">
+      <c r="A82" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B82" s="71" t="s">
+      <c r="B82" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C82" s="72"/>
-      <c r="D82" s="72"/>
-      <c r="E82" s="71" t="s">
+      <c r="C82" s="80"/>
+      <c r="D82" s="80"/>
+      <c r="E82" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="F82" s="72"/>
-      <c r="G82" s="72"/>
-      <c r="H82" s="71" t="s">
+      <c r="F82" s="80"/>
+      <c r="G82" s="80"/>
+      <c r="H82" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="I82" s="72"/>
-      <c r="J82" s="72"/>
-      <c r="K82" s="71" t="s">
+      <c r="I82" s="80"/>
+      <c r="J82" s="80"/>
+      <c r="K82" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="L82" s="72"/>
-      <c r="M82" s="72"/>
-      <c r="N82" s="72"/>
-      <c r="O82" s="72"/>
-      <c r="P82" s="71" t="s">
+      <c r="L82" s="80"/>
+      <c r="M82" s="80"/>
+      <c r="N82" s="80"/>
+      <c r="O82" s="80"/>
+      <c r="P82" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="Q82" s="71" t="s">
+      <c r="Q82" s="79" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A83" s="72"/>
+      <c r="A83" s="80"/>
       <c r="B83" s="43" t="s">
         <v>27</v>
       </c>
@@ -18680,8 +18889,8 @@
       <c r="O83" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P83" s="72"/>
-      <c r="Q83" s="72"/>
+      <c r="P83" s="80"/>
+      <c r="Q83" s="80"/>
     </row>
     <row r="84" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="43" t="s">
@@ -18827,6 +19036,38 @@
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="K50:O50"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="Q50:Q51"/>
+    <mergeCell ref="A43:Q44"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="Q26:Q27"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="P50:P51"/>
+    <mergeCell ref="K45:O45"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="K26:O26"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="A75:Q76"/>
+    <mergeCell ref="P59:P60"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="A57:Q58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="P82:P83"/>
+    <mergeCell ref="Q59:Q60"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="K59:O59"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="Q82:Q83"/>
+    <mergeCell ref="K77:O77"/>
+    <mergeCell ref="P77:P78"/>
+    <mergeCell ref="E77:G77"/>
     <mergeCell ref="A24:Q25"/>
     <mergeCell ref="K82:O82"/>
     <mergeCell ref="H50:J50"/>
@@ -18843,38 +19084,6 @@
     <mergeCell ref="H82:J82"/>
     <mergeCell ref="Q45:Q46"/>
     <mergeCell ref="A48:Q49"/>
-    <mergeCell ref="P82:P83"/>
-    <mergeCell ref="Q59:Q60"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="K59:O59"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="Q82:Q83"/>
-    <mergeCell ref="K77:O77"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="A75:Q76"/>
-    <mergeCell ref="P59:P60"/>
-    <mergeCell ref="P77:P78"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="A57:Q58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="K50:O50"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="Q50:Q51"/>
-    <mergeCell ref="A43:Q44"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="P50:P51"/>
-    <mergeCell ref="K45:O45"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="K26:O26"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="B45:D45"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.scei-concours.fr/stat2025/tb.html" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
@@ -18913,15 +19122,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="84" t="s">
         <v>912</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
     </row>
     <row r="2" spans="1:7" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="48" t="s">
@@ -20495,15 +20704,15 @@
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="75" t="s">
+      <c r="A78" s="83" t="s">
         <v>948</v>
       </c>
-      <c r="B78" s="72"/>
-      <c r="C78" s="72"/>
-      <c r="D78" s="72"/>
-      <c r="E78" s="72"/>
-      <c r="F78" s="72"/>
-      <c r="G78" s="72"/>
+      <c r="B78" s="80"/>
+      <c r="C78" s="80"/>
+      <c r="D78" s="80"/>
+      <c r="E78" s="80"/>
+      <c r="F78" s="80"/>
+      <c r="G78" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud2\Boulot 2026\Site orientation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27C26428-42FD-4B4E-9ED2-4923990A402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B13632-30BE-4A0D-B9CA-E478148C6F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elèves_BCPST" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2418" uniqueCount="980">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2422" uniqueCount="981">
   <si>
     <t>Statistiques 2025</t>
   </si>
@@ -1574,9 +1574,6 @@
   </si>
   <si>
     <t>Nancy</t>
-  </si>
-  <si>
-    <t>https://www.ensia.univ-lorraine.fr</t>
   </si>
   <si>
     <t>[48.66190, 6.15570]</t>
@@ -2984,16 +2981,29 @@
   <si>
     <t>MERCIER</t>
   </si>
+  <si>
+    <t>https://ensaia.univ-lorraine.fr/</t>
+  </si>
+  <si>
+    <t>GARNIER</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3333,10 +3343,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3350,64 +3360,64 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3416,44 +3426,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3465,72 +3475,72 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3540,25 +3550,28 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3904,7 +3917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I109"/>
+  <dimension ref="A1:I110"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.42578125" customWidth="1"/>
@@ -3948,15 +3961,15 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="77" t="s">
-        <v>976</v>
+      <c r="A2" s="85" t="s">
+        <v>980</v>
       </c>
       <c r="B2" s="64" t="str">
         <f t="shared" ref="B2" si="0">LEFT(A2)</f>
         <v>G</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>977</v>
+        <v>178</v>
       </c>
       <c r="D2" s="64">
         <v>2026</v>
@@ -3965,22 +3978,22 @@
         <v>1</v>
       </c>
       <c r="F2" s="64" t="s">
-        <v>188</v>
+        <v>429</v>
       </c>
       <c r="G2" s="64"/>
       <c r="H2" s="78"/>
       <c r="I2" s="78"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="73" t="s">
-        <v>974</v>
+      <c r="A3" s="77" t="s">
+        <v>975</v>
       </c>
       <c r="B3" s="64" t="str">
         <f t="shared" ref="B3" si="1">LEFT(A3)</f>
-        <v>S</v>
+        <v>G</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D3" s="64">
         <v>2026</v>
@@ -3989,24 +4002,22 @@
         <v>1</v>
       </c>
       <c r="F3" s="64" t="s">
-        <v>104</v>
-      </c>
-      <c r="G3" s="65" t="s">
-        <v>182</v>
-      </c>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
+        <v>188</v>
+      </c>
+      <c r="G3" s="64"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
-        <v>347</v>
+        <v>973</v>
       </c>
       <c r="B4" s="64" t="str">
         <f t="shared" ref="B4" si="2">LEFT(A4)</f>
-        <v>T</v>
+        <v>S</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="D4" s="64">
         <v>2026</v>
@@ -4014,23 +4025,25 @@
       <c r="E4" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="74" t="s">
-        <v>253</v>
-      </c>
-      <c r="G4" s="64"/>
+      <c r="F4" s="64" t="s">
+        <v>104</v>
+      </c>
+      <c r="G4" s="65" t="s">
+        <v>182</v>
+      </c>
       <c r="H4" s="64"/>
       <c r="I4" s="64"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="68" t="s">
-        <v>965</v>
+      <c r="A5" s="73" t="s">
+        <v>347</v>
       </c>
       <c r="B5" s="64" t="str">
         <f t="shared" ref="B5" si="3">LEFT(A5)</f>
-        <v>B</v>
+        <v>T</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>172</v>
+        <v>972</v>
       </c>
       <c r="D5" s="64">
         <v>2026</v>
@@ -4038,23 +4051,23 @@
       <c r="E5" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="64" t="s">
-        <v>112</v>
-      </c>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
+      <c r="F5" s="74" t="s">
+        <v>253</v>
+      </c>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="68" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B6" s="64" t="str">
         <f t="shared" ref="B6" si="4">LEFT(A6)</f>
         <v>B</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>964</v>
+        <v>172</v>
       </c>
       <c r="D6" s="64">
         <v>2026</v>
@@ -4063,22 +4076,22 @@
         <v>1</v>
       </c>
       <c r="F6" s="64" t="s">
-        <v>188</v>
-      </c>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
+        <v>112</v>
+      </c>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="68" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="B7" s="64" t="str">
         <f t="shared" ref="B7" si="5">LEFT(A7)</f>
-        <v>K</v>
+        <v>B</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="D7" s="64">
         <v>2026</v>
@@ -4087,7 +4100,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="64" t="s">
-        <v>958</v>
+        <v>188</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="64"/>
@@ -4095,14 +4108,14 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="68" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B8" s="64" t="str">
         <f t="shared" ref="B8" si="6">LEFT(A8)</f>
-        <v>C</v>
+        <v>K</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="D8" s="64">
         <v>2026</v>
@@ -4111,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="64" t="s">
-        <v>136</v>
+        <v>957</v>
       </c>
       <c r="G8" s="64"/>
       <c r="H8" s="64"/>
@@ -4119,14 +4132,14 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="68" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B9" s="64" t="str">
-        <f t="shared" ref="B9:B73" si="7">LEFT(A9)</f>
-        <v>V</v>
+        <f t="shared" ref="B9" si="7">LEFT(A9)</f>
+        <v>C</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D9" s="64">
         <v>2026</v>
@@ -4135,24 +4148,22 @@
         <v>1</v>
       </c>
       <c r="F9" s="64" t="s">
-        <v>104</v>
-      </c>
-      <c r="G9" s="65" t="s">
-        <v>182</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="G9" s="64"/>
       <c r="H9" s="64"/>
       <c r="I9" s="64"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="69" t="s">
-        <v>950</v>
-      </c>
-      <c r="B10" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>H</v>
+      <c r="A10" s="68" t="s">
+        <v>951</v>
+      </c>
+      <c r="B10" s="64" t="str">
+        <f t="shared" ref="B10:B74" si="8">LEFT(A10)</f>
+        <v>V</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D10" s="64">
         <v>2026</v>
@@ -4161,69 +4172,72 @@
         <v>1</v>
       </c>
       <c r="F10" s="64" t="s">
-        <v>459</v>
-      </c>
-      <c r="G10" s="64"/>
+        <v>104</v>
+      </c>
+      <c r="G10" s="65" t="s">
+        <v>182</v>
+      </c>
       <c r="H10" s="64"/>
       <c r="I10" s="64"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="66" t="s">
+      <c r="A11" s="69" t="s">
+        <v>949</v>
+      </c>
+      <c r="B11" s="66" t="str">
+        <f t="shared" si="8"/>
+        <v>H</v>
+      </c>
+      <c r="C11" s="64" t="s">
+        <v>950</v>
+      </c>
+      <c r="D11" s="64">
+        <v>2026</v>
+      </c>
+      <c r="E11" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="64" t="s">
+        <v>459</v>
+      </c>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="B11" s="66" t="str">
-        <f t="shared" si="7"/>
+      <c r="B12" s="66" t="str">
+        <f t="shared" si="8"/>
         <v>A</v>
       </c>
-      <c r="C11" s="66" t="s">
+      <c r="C12" s="66" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="66">
+      <c r="D12" s="66">
         <v>2025</v>
       </c>
-      <c r="E11" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="66" t="s">
+      <c r="E12" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="G11" s="66"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>A</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" s="1">
-        <v>2025</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="76"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>B</v>
+        <f t="shared" si="8"/>
+        <v>A</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D13" s="1">
         <v>2025</v>
@@ -4232,20 +4246,21 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G13" s="1"/>
+      <c r="H13" s="76"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>C</v>
+        <f t="shared" si="8"/>
+        <v>B</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D14" s="1">
         <v>2025</v>
@@ -4254,20 +4269,20 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>D</v>
+        <f t="shared" si="8"/>
+        <v>C</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D15" s="1">
         <v>2025</v>
@@ -4276,20 +4291,20 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>D</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D16" s="1">
         <v>2025</v>
@@ -4298,20 +4313,20 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="36" t="s">
-        <v>100</v>
+      <c r="A17" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>F</v>
+        <f t="shared" si="8"/>
+        <v>D</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D17" s="1">
         <v>2025</v>
@@ -4320,20 +4335,20 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="36" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>F</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D18" s="1">
         <v>2025</v>
@@ -4342,20 +4357,20 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="36" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B19" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>G</v>
+        <f t="shared" si="8"/>
+        <v>F</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D19" s="1">
         <v>2025</v>
@@ -4364,20 +4379,20 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="36" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B20" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>H</v>
+        <f t="shared" si="8"/>
+        <v>G</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D20" s="1">
         <v>2025</v>
@@ -4386,20 +4401,20 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="36" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B21" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>J</v>
+        <f t="shared" si="8"/>
+        <v>H</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D21" s="1">
         <v>2025</v>
@@ -4408,20 +4423,20 @@
         <v>1</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="36" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B22" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>L</v>
+        <f t="shared" si="8"/>
+        <v>J</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D22" s="1">
         <v>2025</v>
@@ -4430,23 +4445,20 @@
         <v>1</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G22" s="1"/>
-      <c r="H22" t="s">
-        <v>116</v>
-      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="36" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B23" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>L</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D23" s="1">
         <v>2025</v>
@@ -4455,20 +4467,23 @@
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G23" s="1"/>
+      <c r="H23" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="36" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B24" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>L</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D24" s="1">
         <v>2025</v>
@@ -4477,20 +4492,20 @@
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="36" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B25" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>M</v>
+        <f t="shared" si="8"/>
+        <v>L</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D25" s="1">
         <v>2025</v>
@@ -4499,20 +4514,20 @@
         <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="36" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B26" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>P</v>
+        <f t="shared" si="8"/>
+        <v>M</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D26" s="1">
         <v>2025</v>
@@ -4521,20 +4536,20 @@
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="36" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B27" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>S</v>
+        <f t="shared" si="8"/>
+        <v>P</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D27" s="1">
         <v>2025</v>
@@ -4543,20 +4558,20 @@
         <v>1</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="36" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B28" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>V</v>
+        <f t="shared" si="8"/>
+        <v>S</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D28" s="1">
         <v>2025</v>
@@ -4565,20 +4580,20 @@
         <v>1</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G28" s="1"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="36" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B29" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>W</v>
+        <f t="shared" si="8"/>
+        <v>V</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D29" s="1">
         <v>2025</v>
@@ -4587,42 +4602,42 @@
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="B30" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v>W</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2025</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="G29" s="1"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="B30" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>B</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D30" s="1">
-        <v>2024</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="38" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B31" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>B</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D31" s="1">
         <v>2024</v>
@@ -4631,20 +4646,20 @@
         <v>1</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G31" s="1"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="38" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B32" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>C</v>
+        <f t="shared" si="8"/>
+        <v>B</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D32" s="1">
         <v>2024</v>
@@ -4653,20 +4668,20 @@
         <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G32" s="1"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="38" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B33" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>D</v>
+        <f t="shared" si="8"/>
+        <v>C</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D33" s="1">
         <v>2024</v>
@@ -4675,20 +4690,20 @@
         <v>1</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="G33" s="1"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="38" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B34" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>D</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D34" s="1">
         <v>2024</v>
@@ -4697,20 +4712,20 @@
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="38" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B35" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>F</v>
+        <f t="shared" si="8"/>
+        <v>D</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="D35" s="1">
         <v>2024</v>
@@ -4719,20 +4734,20 @@
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G35" s="1"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B36" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>H</v>
+        <f t="shared" si="8"/>
+        <v>F</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="D36" s="1">
         <v>2024</v>
@@ -4741,20 +4756,20 @@
         <v>1</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="G36" s="1"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="38" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B37" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>H</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D37" s="1">
         <v>2024</v>
@@ -4763,18 +4778,20 @@
         <v>1</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
+      <c r="A38" s="38" t="s">
+        <v>153</v>
+      </c>
       <c r="B38" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+        <f t="shared" si="8"/>
+        <v>H</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D38" s="1">
         <v>2024</v>
@@ -4782,19 +4799,19 @@
       <c r="E38" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F38" s="1"/>
+      <c r="F38" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="38" t="s">
-        <v>156</v>
-      </c>
+      <c r="A39" s="1"/>
       <c r="B39" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>J</v>
+        <f t="shared" si="8"/>
+        <v/>
       </c>
       <c r="C39" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D39" s="1">
         <v>2024</v>
@@ -4802,21 +4819,19 @@
       <c r="E39" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F39" s="1" t="s">
-        <v>94</v>
-      </c>
+      <c r="F39" s="1"/>
       <c r="G39" s="1"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B40" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>L</v>
+        <f t="shared" si="8"/>
+        <v>J</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D40" s="1">
         <v>2024</v>
@@ -4825,20 +4840,20 @@
         <v>1</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>139</v>
+        <v>94</v>
       </c>
       <c r="G40" s="1"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="38" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B41" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>N</v>
+        <f t="shared" si="8"/>
+        <v>L</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D41" s="1">
         <v>2024</v>
@@ -4847,23 +4862,20 @@
         <v>1</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="G41" s="1"/>
-      <c r="H41" t="s">
-        <v>162</v>
-      </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="38" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B42" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>N</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D42" s="1">
         <v>2024</v>
@@ -4875,15 +4887,20 @@
         <v>115</v>
       </c>
       <c r="G42" s="1"/>
+      <c r="H42" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
+      <c r="A43" s="38" t="s">
+        <v>163</v>
+      </c>
       <c r="B43" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+        <f t="shared" si="8"/>
+        <v>N</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D43" s="1">
         <v>2024</v>
@@ -4892,20 +4909,18 @@
         <v>1</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="G43" s="1"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="38" t="s">
-        <v>166</v>
-      </c>
+      <c r="A44" s="1"/>
       <c r="B44" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>P</v>
+        <f t="shared" si="8"/>
+        <v/>
       </c>
       <c r="C44" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D44" s="1">
         <v>2024</v>
@@ -4920,14 +4935,14 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="38" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B45" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>P</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D45" s="1">
         <v>2024</v>
@@ -4936,20 +4951,20 @@
         <v>1</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="G45" s="1"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="38" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B46" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>R</v>
+        <f t="shared" si="8"/>
+        <v>P</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="D46" s="1">
         <v>2024</v>
@@ -4958,20 +4973,20 @@
         <v>1</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>37</v>
+        <v>169</v>
       </c>
       <c r="G46" s="1"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="38" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B47" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>S</v>
+        <f t="shared" si="8"/>
+        <v>R</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="D47" s="1">
         <v>2024</v>
@@ -4980,20 +4995,20 @@
         <v>1</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="G47" s="1"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="38" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B48" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>S</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D48" s="1">
         <v>2024</v>
@@ -5008,14 +5023,14 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="38" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B49" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>T</v>
+        <f t="shared" si="8"/>
+        <v>S</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D49" s="1">
         <v>2024</v>
@@ -5024,42 +5039,42 @@
         <v>1</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="G49" s="1"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="38" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B50" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>B</v>
-      </c>
-      <c r="C50" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="D50" s="29">
-        <v>2023</v>
-      </c>
-      <c r="E50" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F50" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="G50" s="35"/>
+        <f t="shared" si="8"/>
+        <v>T</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D50" s="1">
+        <v>2024</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G50" s="1"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="38" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B51" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>B</v>
       </c>
       <c r="C51" s="34" t="s">
-        <v>128</v>
+        <v>178</v>
       </c>
       <c r="D51" s="29">
         <v>2023</v>
@@ -5068,20 +5083,20 @@
         <v>1</v>
       </c>
       <c r="F51" s="35" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="G51" s="35"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="38" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B52" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>C</v>
+        <f t="shared" si="8"/>
+        <v>B</v>
       </c>
       <c r="C52" s="34" t="s">
-        <v>181</v>
+        <v>128</v>
       </c>
       <c r="D52" s="29">
         <v>2023</v>
@@ -5089,21 +5104,21 @@
       <c r="E52" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F52" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="G52" s="35" t="s">
-        <v>182</v>
-      </c>
+      <c r="F52" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="G52" s="35"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="1"/>
+      <c r="A53" s="38" t="s">
+        <v>180</v>
+      </c>
       <c r="B53" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+        <f t="shared" si="8"/>
+        <v>C</v>
       </c>
       <c r="C53" s="34" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D53" s="29">
         <v>2023</v>
@@ -5121,11 +5136,11 @@
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="C54" s="34" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D54" s="29">
         <v>2023</v>
@@ -5143,11 +5158,11 @@
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="C55" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D55" s="29">
         <v>2023</v>
@@ -5155,21 +5170,21 @@
       <c r="E55" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F55" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="G55" s="35"/>
+      <c r="F55" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="G55" s="35" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="38" t="s">
-        <v>186</v>
-      </c>
+      <c r="A56" s="1"/>
       <c r="B56" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>H</v>
+        <f t="shared" si="8"/>
+        <v/>
       </c>
       <c r="C56" s="34" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D56" s="29">
         <v>2023</v>
@@ -5178,20 +5193,20 @@
         <v>1</v>
       </c>
       <c r="F56" s="35" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="G56" s="35"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B57" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>J</v>
+        <f t="shared" si="8"/>
+        <v>H</v>
       </c>
       <c r="C57" s="34" t="s">
-        <v>84</v>
+        <v>187</v>
       </c>
       <c r="D57" s="29">
         <v>2023</v>
@@ -5200,20 +5215,20 @@
         <v>1</v>
       </c>
       <c r="F57" s="35" t="s">
-        <v>112</v>
+        <v>188</v>
       </c>
       <c r="G57" s="35"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="38" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B58" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>K</v>
+        <f t="shared" si="8"/>
+        <v>J</v>
       </c>
       <c r="C58" s="34" t="s">
-        <v>191</v>
+        <v>84</v>
       </c>
       <c r="D58" s="29">
         <v>2023</v>
@@ -5228,14 +5243,14 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="38" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B59" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>L</v>
+        <f t="shared" si="8"/>
+        <v>K</v>
       </c>
       <c r="C59" s="34" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D59" s="29">
         <v>2023</v>
@@ -5244,20 +5259,20 @@
         <v>1</v>
       </c>
       <c r="F59" s="35" t="s">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="G59" s="35"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="38" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B60" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>M</v>
+        <f t="shared" si="8"/>
+        <v>L</v>
       </c>
       <c r="C60" s="34" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D60" s="29">
         <v>2023</v>
@@ -5266,20 +5281,20 @@
         <v>1</v>
       </c>
       <c r="F60" s="35" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G60" s="35"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="38" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B61" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>M</v>
       </c>
       <c r="C61" s="34" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D61" s="29">
         <v>2023</v>
@@ -5287,21 +5302,21 @@
       <c r="E61" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F61" s="30" t="s">
-        <v>104</v>
+      <c r="F61" s="35" t="s">
+        <v>197</v>
       </c>
       <c r="G61" s="35"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="38" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B62" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>M</v>
       </c>
       <c r="C62" s="34" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D62" s="29">
         <v>2023</v>
@@ -5309,21 +5324,21 @@
       <c r="E62" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F62" s="35" t="s">
-        <v>112</v>
+      <c r="F62" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G62" s="35"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="38" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B63" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>P</v>
+        <f t="shared" si="8"/>
+        <v>M</v>
       </c>
       <c r="C63" s="34" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D63" s="29">
         <v>2023</v>
@@ -5331,21 +5346,21 @@
       <c r="E63" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F63" s="30" t="s">
-        <v>104</v>
+      <c r="F63" s="35" t="s">
+        <v>112</v>
       </c>
       <c r="G63" s="35"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="38" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B64" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>T</v>
+        <f t="shared" si="8"/>
+        <v>P</v>
       </c>
       <c r="C64" s="34" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D64" s="29">
         <v>2023</v>
@@ -5353,21 +5368,21 @@
       <c r="E64" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F64" s="35" t="s">
-        <v>169</v>
+      <c r="F64" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G64" s="35"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="38" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B65" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>T</v>
       </c>
       <c r="C65" s="34" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D65" s="29">
         <v>2023</v>
@@ -5376,20 +5391,20 @@
         <v>1</v>
       </c>
       <c r="F65" s="35" t="s">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="G65" s="35"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="38" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B66" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>V</v>
+        <f t="shared" si="8"/>
+        <v>T</v>
       </c>
       <c r="C66" s="34" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D66" s="29">
         <v>2023</v>
@@ -5397,43 +5412,43 @@
       <c r="E66" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F66" s="30" t="s">
-        <v>104</v>
+      <c r="F66" s="35" t="s">
+        <v>85</v>
       </c>
       <c r="G66" s="35"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="38" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B67" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>A</v>
-      </c>
-      <c r="C67" s="35" t="s">
-        <v>211</v>
+        <f t="shared" si="8"/>
+        <v>V</v>
+      </c>
+      <c r="C67" s="34" t="s">
+        <v>209</v>
       </c>
       <c r="D67" s="29">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E67" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F67" s="35" t="s">
-        <v>212</v>
+      <c r="F67" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G67" s="35"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="38" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B68" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>A</v>
       </c>
       <c r="C68" s="35" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D68" s="29">
         <v>2022</v>
@@ -5442,20 +5457,20 @@
         <v>1</v>
       </c>
       <c r="F68" s="35" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="G68" s="35"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="38" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B69" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>B</v>
+        <f t="shared" si="8"/>
+        <v>A</v>
       </c>
       <c r="C69" s="35" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D69" s="29">
         <v>2022</v>
@@ -5464,20 +5479,20 @@
         <v>1</v>
       </c>
       <c r="F69" s="35" t="s">
-        <v>37</v>
+        <v>188</v>
       </c>
       <c r="G69" s="35"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="38" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B70" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>C</v>
+        <f t="shared" si="8"/>
+        <v>B</v>
       </c>
       <c r="C70" s="35" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D70" s="29">
         <v>2022</v>
@@ -5486,20 +5501,20 @@
         <v>1</v>
       </c>
       <c r="F70" s="35" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="G70" s="35"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="38" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B71" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>D</v>
+        <f t="shared" si="8"/>
+        <v>C</v>
       </c>
       <c r="C71" s="35" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D71" s="29">
         <v>2022</v>
@@ -5508,20 +5523,20 @@
         <v>1</v>
       </c>
       <c r="F71" s="35" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="G71" s="35"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="38" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B72" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>D</v>
       </c>
       <c r="C72" s="35" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D72" s="29">
         <v>2022</v>
@@ -5536,14 +5551,14 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="38" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B73" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>G</v>
+        <f t="shared" si="8"/>
+        <v>D</v>
       </c>
       <c r="C73" s="35" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D73" s="29">
         <v>2022</v>
@@ -5552,22 +5567,20 @@
         <v>1</v>
       </c>
       <c r="F73" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="G73" s="35" t="s">
-        <v>182</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="G73" s="35"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="38" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B74" s="1" t="str">
-        <f t="shared" ref="B74:B92" si="8">LEFT(A74)</f>
+        <f t="shared" si="8"/>
         <v>G</v>
       </c>
       <c r="C74" s="35" t="s">
-        <v>128</v>
+        <v>224</v>
       </c>
       <c r="D74" s="29">
         <v>2022</v>
@@ -5576,20 +5589,22 @@
         <v>1</v>
       </c>
       <c r="F74" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="G74" s="29"/>
+        <v>104</v>
+      </c>
+      <c r="G74" s="35" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="38" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B75" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>M</v>
+        <f t="shared" ref="B75:B93" si="9">LEFT(A75)</f>
+        <v>G</v>
       </c>
       <c r="C75" s="35" t="s">
-        <v>227</v>
+        <v>128</v>
       </c>
       <c r="D75" s="29">
         <v>2022</v>
@@ -5598,22 +5613,20 @@
         <v>1</v>
       </c>
       <c r="F75" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="G75" s="35" t="s">
-        <v>182</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G75" s="29"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="38" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B76" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>R</v>
+        <f t="shared" si="9"/>
+        <v>M</v>
       </c>
       <c r="C76" s="35" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D76" s="29">
         <v>2022</v>
@@ -5622,20 +5635,22 @@
         <v>1</v>
       </c>
       <c r="F76" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="G76" s="35"/>
+        <v>104</v>
+      </c>
+      <c r="G76" s="35" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="38" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B77" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>R</v>
       </c>
       <c r="C77" s="35" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D77" s="29">
         <v>2022</v>
@@ -5644,20 +5659,20 @@
         <v>1</v>
       </c>
       <c r="F77" s="35" t="s">
-        <v>232</v>
+        <v>122</v>
       </c>
       <c r="G77" s="35"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="38" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B78" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>V</v>
+        <f t="shared" si="9"/>
+        <v>R</v>
       </c>
       <c r="C78" s="35" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D78" s="29">
         <v>2022</v>
@@ -5666,42 +5681,42 @@
         <v>1</v>
       </c>
       <c r="F78" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="G78" s="35"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="B79" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>V</v>
+      </c>
+      <c r="C79" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="D79" s="29">
+        <v>2022</v>
+      </c>
+      <c r="E79" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F79" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="G78" s="35"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="35" t="s">
-        <v>235</v>
-      </c>
-      <c r="B79" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>A</v>
-      </c>
-      <c r="C79" s="35" t="s">
-        <v>236</v>
-      </c>
-      <c r="D79" s="29">
-        <v>2021</v>
-      </c>
-      <c r="E79" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F79" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="G79" s="1"/>
+      <c r="G79" s="35"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="35" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B80" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>B</v>
+        <f t="shared" si="9"/>
+        <v>A</v>
       </c>
       <c r="C80" s="35" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D80" s="29">
         <v>2021</v>
@@ -5710,20 +5725,20 @@
         <v>1</v>
       </c>
       <c r="F80" s="35" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="G80" s="1"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="35" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B81" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>B</v>
       </c>
       <c r="C81" s="35" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D81" s="29">
         <v>2021</v>
@@ -5732,20 +5747,20 @@
         <v>1</v>
       </c>
       <c r="F81" s="35" t="s">
-        <v>241</v>
+        <v>188</v>
       </c>
       <c r="G81" s="1"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="35" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B82" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>C</v>
+        <f t="shared" si="9"/>
+        <v>B</v>
       </c>
       <c r="C82" s="35" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D82" s="29">
         <v>2021</v>
@@ -5754,20 +5769,20 @@
         <v>1</v>
       </c>
       <c r="F82" s="35" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
       <c r="G82" s="1"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="35" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B83" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>C</v>
       </c>
       <c r="C83" s="35" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D83" s="29">
         <v>2021</v>
@@ -5776,20 +5791,20 @@
         <v>1</v>
       </c>
       <c r="F83" s="35" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="G83" s="1"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="35" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B84" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>C</v>
       </c>
       <c r="C84" s="35" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D84" s="29">
         <v>2021</v>
@@ -5798,20 +5813,20 @@
         <v>1</v>
       </c>
       <c r="F84" s="35" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="G84" s="1"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="35" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B85" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>C</v>
       </c>
       <c r="C85" s="35" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D85" s="29">
         <v>2021</v>
@@ -5820,20 +5835,20 @@
         <v>1</v>
       </c>
       <c r="F85" s="35" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="G85" s="1"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="35" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B86" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>E</v>
+        <f t="shared" si="9"/>
+        <v>C</v>
       </c>
       <c r="C86" s="35" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D86" s="29">
         <v>2021</v>
@@ -5842,20 +5857,20 @@
         <v>1</v>
       </c>
       <c r="F86" s="35" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="G86" s="1"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B87" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>G</v>
+        <f t="shared" si="9"/>
+        <v>E</v>
       </c>
       <c r="C87" s="35" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D87" s="29">
         <v>2021</v>
@@ -5864,20 +5879,20 @@
         <v>1</v>
       </c>
       <c r="F87" s="35" t="s">
-        <v>253</v>
+        <v>37</v>
       </c>
       <c r="G87" s="1"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="35" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B88" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>J</v>
+        <f t="shared" si="9"/>
+        <v>G</v>
       </c>
       <c r="C88" s="35" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D88" s="29">
         <v>2021</v>
@@ -5886,20 +5901,20 @@
         <v>1</v>
       </c>
       <c r="F88" s="35" t="s">
-        <v>104</v>
+        <v>253</v>
       </c>
       <c r="G88" s="1"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="35" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B89" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>L</v>
+        <f t="shared" si="9"/>
+        <v>J</v>
       </c>
       <c r="C89" s="35" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D89" s="29">
         <v>2021</v>
@@ -5908,20 +5923,20 @@
         <v>1</v>
       </c>
       <c r="F89" s="35" t="s">
-        <v>258</v>
+        <v>104</v>
       </c>
       <c r="G89" s="1"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="35" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B90" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>M</v>
+        <f t="shared" si="9"/>
+        <v>L</v>
       </c>
       <c r="C90" s="35" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D90" s="29">
         <v>2021</v>
@@ -5930,20 +5945,20 @@
         <v>1</v>
       </c>
       <c r="F90" s="35" t="s">
-        <v>112</v>
+        <v>258</v>
       </c>
       <c r="G90" s="1"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="35" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B91" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>M</v>
       </c>
       <c r="C91" s="35" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D91" s="29">
         <v>2021</v>
@@ -5951,21 +5966,21 @@
       <c r="E91" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F91" s="29" t="s">
-        <v>126</v>
+      <c r="F91" s="35" t="s">
+        <v>112</v>
       </c>
       <c r="G91" s="1"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="35" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B92" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>N</v>
+        <f t="shared" si="9"/>
+        <v>M</v>
       </c>
       <c r="C92" s="35" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D92" s="29">
         <v>2021</v>
@@ -5973,21 +5988,21 @@
       <c r="E92" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F92" s="35" t="s">
-        <v>122</v>
+      <c r="F92" s="29" t="s">
+        <v>126</v>
       </c>
       <c r="G92" s="1"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="35" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B93" s="1" t="str">
-        <f t="shared" ref="B93:B109" si="9">LEFT(A93)</f>
-        <v>P</v>
+        <f t="shared" si="9"/>
+        <v>N</v>
       </c>
       <c r="C93" s="35" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D93" s="29">
         <v>2021</v>
@@ -5996,20 +6011,20 @@
         <v>1</v>
       </c>
       <c r="F93" s="35" t="s">
-        <v>267</v>
+        <v>122</v>
       </c>
       <c r="G93" s="1"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="35" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B94" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>R</v>
+        <f t="shared" ref="B94:B110" si="10">LEFT(A94)</f>
+        <v>P</v>
       </c>
       <c r="C94" s="35" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D94" s="29">
         <v>2021</v>
@@ -6018,20 +6033,20 @@
         <v>1</v>
       </c>
       <c r="F94" s="35" t="s">
-        <v>212</v>
+        <v>267</v>
       </c>
       <c r="G94" s="1"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="35" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B95" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>R</v>
       </c>
       <c r="C95" s="35" t="s">
-        <v>236</v>
+        <v>269</v>
       </c>
       <c r="D95" s="29">
         <v>2021</v>
@@ -6040,41 +6055,42 @@
         <v>1</v>
       </c>
       <c r="F95" s="35" t="s">
-        <v>122</v>
+        <v>212</v>
       </c>
       <c r="G95" s="1"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="35" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B96" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>B</v>
+        <f t="shared" si="10"/>
+        <v>R</v>
       </c>
       <c r="C96" s="35" t="s">
-        <v>272</v>
+        <v>236</v>
       </c>
       <c r="D96" s="29">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E96" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F96" t="s">
-        <v>188</v>
-      </c>
+      <c r="F96" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="G96" s="1"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="35" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B97" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>A</v>
+        <f t="shared" si="10"/>
+        <v>B</v>
       </c>
       <c r="C97" s="35" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D97" s="29">
         <v>2020</v>
@@ -6083,23 +6099,34 @@
         <v>1</v>
       </c>
       <c r="F97" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="35" t="s">
+        <v>273</v>
+      </c>
+      <c r="B98" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>A</v>
+      </c>
+      <c r="C98" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="D98" s="29">
+        <v>2020</v>
+      </c>
+      <c r="E98" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F98" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="35"/>
-      <c r="B98" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E98" s="29" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="E99" s="29" t="s">
@@ -6109,7 +6136,7 @@
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="E100" s="29" t="s">
@@ -6119,7 +6146,7 @@
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="E101" s="29" t="s">
@@ -6129,7 +6156,7 @@
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="E102" s="29" t="s">
@@ -6139,7 +6166,7 @@
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="E103" s="29" t="s">
@@ -6149,7 +6176,7 @@
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="E104" s="29" t="s">
@@ -6159,7 +6186,7 @@
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="E105" s="29" t="s">
@@ -6169,7 +6196,7 @@
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="E106" s="29" t="s">
@@ -6179,7 +6206,7 @@
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="E107" s="29" t="s">
@@ -6187,8 +6214,9 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="35"/>
       <c r="B108" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="E108" s="29" t="s">
@@ -6197,7 +6225,16 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B109" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="E109" s="29" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B110" s="1" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -6211,13 +6248,13 @@
           <x14:formula1>
             <xm:f>Ecoles!$A$2:$A$70</xm:f>
           </x14:formula1>
-          <xm:sqref>F109</xm:sqref>
+          <xm:sqref>F110</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4FACBFD7-136B-4815-BD4C-3FC873C7A761}">
           <x14:formula1>
             <xm:f>Ecoles!$A$2:$A$71</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F108</xm:sqref>
+          <xm:sqref>F2:F109</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6265,7 +6302,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B2" s="1" t="str">
         <f t="shared" ref="B2" si="0">LEFT(A2)</f>
@@ -6288,7 +6325,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B3" s="1" t="str">
         <f t="shared" ref="B3" si="1">LEFT(A3)</f>
@@ -6311,14 +6348,14 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B4" s="1" t="str">
         <f t="shared" ref="B4" si="2">LEFT(A4)</f>
         <v>B</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="D4" s="64">
         <v>2026</v>
@@ -6327,7 +6364,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H4" s="64"/>
       <c r="I4" s="64"/>
@@ -8992,13 +9029,13 @@
         <v>515</v>
       </c>
       <c r="I5" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>517</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9021,19 +9058,19 @@
         <v>498</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>522</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9056,19 +9093,19 @@
         <v>498</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>527</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9091,19 +9128,19 @@
         <v>498</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>532</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9111,10 +9148,10 @@
         <v>136</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>497</v>
@@ -9126,19 +9163,19 @@
         <v>498</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>538</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9161,19 +9198,19 @@
         <v>498</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>543</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9181,10 +9218,10 @@
         <v>345</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>497</v>
@@ -9196,19 +9233,19 @@
         <v>498</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="I11" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="K11" s="3" t="s">
         <v>549</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9216,10 +9253,10 @@
         <v>370</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>497</v>
@@ -9231,19 +9268,19 @@
         <v>498</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="K12" s="3" t="s">
         <v>554</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9251,10 +9288,10 @@
         <v>142</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>497</v>
@@ -9266,19 +9303,19 @@
         <v>498</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="I13" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="J13" s="3" t="s">
+      <c r="K13" s="3" t="s">
         <v>558</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9286,10 +9323,10 @@
         <v>258</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>497</v>
@@ -9310,10 +9347,10 @@
         <v>506</v>
       </c>
       <c r="J14" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>560</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9321,10 +9358,10 @@
         <v>232</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>497</v>
@@ -9333,19 +9370,19 @@
         <v>1</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="I15" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="K15" s="3" t="s">
         <v>566</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9353,28 +9390,28 @@
         <v>88</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>1</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>500</v>
       </c>
       <c r="I16" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="K16" s="3" t="s">
         <v>570</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9382,34 +9419,34 @@
         <v>169</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>525</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="K17" s="3" t="s">
         <v>575</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9417,34 +9454,34 @@
         <v>91</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="I18" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="K18" s="3" t="s">
         <v>580</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9452,34 +9489,34 @@
         <v>194</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="I19" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="K19" s="5" t="s">
         <v>585</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9487,34 +9524,34 @@
         <v>145</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="K20" s="3" t="s">
         <v>589</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9522,34 +9559,34 @@
         <v>85</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="I21" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>594</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9557,69 +9594,69 @@
         <v>119</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>599</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G23" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="I23" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="K23" s="3" t="s">
         <v>605</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9627,69 +9664,69 @@
         <v>334</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G24" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="K24" s="3" t="s">
         <v>609</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="I25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>613</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="K25" s="3" t="s">
         <v>614</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9697,34 +9734,34 @@
         <v>107</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="I26" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="J26" s="3" t="s">
+      <c r="K26" s="3" t="s">
         <v>619</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9732,34 +9769,34 @@
         <v>94</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>621</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>622</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G27" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="I27" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="K27" s="3" t="s">
         <v>626</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9767,34 +9804,34 @@
         <v>129</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>621</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>622</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G28" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="I28" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="J28" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="K28" s="3" t="s">
         <v>631</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9802,34 +9839,34 @@
         <v>322</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G29" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>592</v>
-      </c>
       <c r="I29" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="J29" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="K29" s="5" t="s">
         <v>634</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9837,34 +9874,34 @@
         <v>324</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G30" s="10" t="s">
+        <v>635</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="I30" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="I30" s="3" t="s">
+      <c r="J30" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="J30" s="6" t="s">
+      <c r="K30" s="3" t="s">
         <v>639</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9872,34 +9909,34 @@
         <v>340</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G31" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="H31" s="6" t="s">
         <v>641</v>
       </c>
-      <c r="H31" s="6" t="s">
+      <c r="I31" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="J31" s="6" t="s">
         <v>643</v>
       </c>
-      <c r="J31" s="6" t="s">
+      <c r="K31" s="3" t="s">
         <v>644</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9907,34 +9944,34 @@
         <v>267</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H32" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="J32" s="6" t="s">
         <v>647</v>
       </c>
-      <c r="J32" s="6" t="s">
+      <c r="K32" s="3" t="s">
         <v>648</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9942,34 +9979,34 @@
         <v>353</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>500</v>
       </c>
       <c r="I33" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="J33" s="8" t="s">
         <v>652</v>
       </c>
-      <c r="J33" s="8" t="s">
+      <c r="K33" s="3" t="s">
         <v>653</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9992,19 +10029,19 @@
         <v>498</v>
       </c>
       <c r="G34" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="I34" s="3" t="s">
+      <c r="J34" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="J34" s="3" t="s">
+      <c r="K34" s="3" t="s">
         <v>657</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -10012,34 +10049,34 @@
         <v>407</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G35" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="I35" s="5" t="s">
         <v>659</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="I35" s="5" t="s">
+      <c r="J35" s="3" t="s">
         <v>660</v>
       </c>
-      <c r="J35" s="3" t="s">
+      <c r="K35" s="3" t="s">
         <v>661</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10047,34 +10084,34 @@
         <v>429</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H36" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="I36" s="3" t="s">
+      <c r="J36" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="J36" s="3" t="s">
+      <c r="K36" s="3" t="s">
         <v>665</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
@@ -10082,34 +10119,34 @@
         <v>445</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>621</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>622</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G37" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="I37" s="5" t="s">
         <v>667</v>
       </c>
-      <c r="H37" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="I37" s="5" t="s">
+      <c r="J37" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="J37" s="3" t="s">
+      <c r="K37" s="5" t="s">
         <v>669</v>
-      </c>
-      <c r="K37" s="5" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10117,34 +10154,34 @@
         <v>448</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>621</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>622</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G38" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="I38" s="5" t="s">
         <v>671</v>
       </c>
-      <c r="H38" s="3" t="s">
-        <v>525</v>
-      </c>
-      <c r="I38" s="5" t="s">
+      <c r="J38" s="4" t="s">
         <v>672</v>
       </c>
-      <c r="J38" s="4" t="s">
+      <c r="K38" s="3" t="s">
         <v>673</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -10152,34 +10189,34 @@
         <v>450</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="E39" s="3" t="s">
         <v>621</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>622</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G39" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="J39" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="H39" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>672</v>
-      </c>
-      <c r="J39" s="4" t="s">
+      <c r="K39" s="3" t="s">
         <v>676</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10187,34 +10224,34 @@
         <v>452</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="E40" s="3" t="s">
         <v>621</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>622</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G40" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="H40" s="3" t="s">
+      <c r="I40" s="4" t="s">
         <v>679</v>
       </c>
-      <c r="I40" s="4" t="s">
+      <c r="J40" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="K40" s="3" t="s">
         <v>681</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -10222,34 +10259,34 @@
         <v>455</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="E41" s="3" t="s">
         <v>621</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>622</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>500</v>
       </c>
       <c r="I41" s="14" t="s">
+        <v>683</v>
+      </c>
+      <c r="J41" s="13" t="s">
         <v>684</v>
       </c>
-      <c r="J41" s="13" t="s">
+      <c r="K41" s="3" t="s">
         <v>685</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
@@ -10257,34 +10294,34 @@
         <v>459</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H42" s="11" t="s">
+        <v>686</v>
+      </c>
+      <c r="I42" s="13" t="s">
         <v>687</v>
       </c>
-      <c r="I42" s="13" t="s">
+      <c r="J42" s="13" t="s">
         <v>688</v>
       </c>
-      <c r="J42" s="13" t="s">
+      <c r="K42" s="3" t="s">
         <v>689</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
@@ -10292,77 +10329,77 @@
         <v>477</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G43" s="11" t="s">
+        <v>690</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>556</v>
+      </c>
+      <c r="I43" s="5" t="s">
         <v>691</v>
       </c>
-      <c r="H43" s="11" t="s">
-        <v>557</v>
-      </c>
-      <c r="I43" s="5" t="s">
+      <c r="J43" s="11" t="s">
         <v>692</v>
       </c>
-      <c r="J43" s="11" t="s">
+      <c r="K43" s="5" t="s">
         <v>693</v>
-      </c>
-      <c r="K43" s="5" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>498</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H44" s="11" t="s">
         <v>500</v>
       </c>
       <c r="I44" s="5" t="s">
+        <v>696</v>
+      </c>
+      <c r="J44" s="11" t="s">
         <v>697</v>
       </c>
-      <c r="J44" s="11" t="s">
+      <c r="K44" s="5" t="s">
         <v>698</v>
-      </c>
-      <c r="K44" s="5" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
+        <v>699</v>
+      </c>
+      <c r="B45" s="28" t="s">
         <v>700</v>
-      </c>
-      <c r="B45" s="28" t="s">
-        <v>701</v>
       </c>
       <c r="C45" s="28"/>
       <c r="D45" s="3" t="s">
@@ -10373,24 +10410,24 @@
         <v>1</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H45" s="16" t="s">
         <v>500</v>
       </c>
       <c r="I45" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="J45" s="11" t="s">
         <v>703</v>
       </c>
-      <c r="J45" s="11" t="s">
+      <c r="K45" s="3" t="s">
         <v>704</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>496</v>
@@ -10408,310 +10445,310 @@
         <v>498</v>
       </c>
       <c r="G46" s="11" t="s">
+        <v>706</v>
+      </c>
+      <c r="H46" s="11" t="s">
         <v>707</v>
       </c>
-      <c r="H46" s="11" t="s">
+      <c r="I46" s="13" t="s">
         <v>708</v>
       </c>
-      <c r="I46" s="13" t="s">
+      <c r="J46" s="13" t="s">
         <v>709</v>
       </c>
-      <c r="J46" s="13" t="s">
+      <c r="K46" s="3" t="s">
         <v>710</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C47" s="11"/>
       <c r="D47" s="11" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E47" s="11"/>
       <c r="F47" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G47" s="13" t="s">
+        <v>712</v>
+      </c>
+      <c r="H47" s="11" t="s">
         <v>713</v>
       </c>
-      <c r="H47" s="11" t="s">
+      <c r="I47" s="11" t="s">
         <v>714</v>
       </c>
-      <c r="I47" s="11" t="s">
+      <c r="J47" s="13" t="s">
         <v>715</v>
       </c>
-      <c r="J47" s="13" t="s">
+      <c r="K47" s="3" t="s">
         <v>716</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E48" s="11"/>
       <c r="F48" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G48" s="13" t="s">
+        <v>718</v>
+      </c>
+      <c r="H48" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="H48" s="11" t="s">
+      <c r="I48" s="5" t="s">
         <v>720</v>
       </c>
-      <c r="I48" s="5" t="s">
+      <c r="J48" s="13" t="s">
         <v>721</v>
       </c>
-      <c r="J48" s="13" t="s">
+      <c r="K48" s="3" t="s">
         <v>722</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C49" s="11"/>
       <c r="D49" s="11" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E49" s="11"/>
       <c r="F49" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G49" s="13" t="s">
+        <v>724</v>
+      </c>
+      <c r="H49" s="11" t="s">
         <v>725</v>
       </c>
-      <c r="H49" s="11" t="s">
+      <c r="I49" s="5" t="s">
         <v>726</v>
       </c>
-      <c r="I49" s="5" t="s">
+      <c r="J49" s="13" t="s">
         <v>727</v>
       </c>
-      <c r="J49" s="13" t="s">
+      <c r="K49" s="3" t="s">
         <v>728</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F50" s="11" t="s">
         <v>498</v>
       </c>
       <c r="G50" s="13" t="s">
+        <v>730</v>
+      </c>
+      <c r="H50" s="13" t="s">
         <v>731</v>
       </c>
-      <c r="H50" s="13" t="s">
+      <c r="I50" s="11" t="s">
         <v>732</v>
       </c>
-      <c r="I50" s="11" t="s">
+      <c r="J50" s="13" t="s">
         <v>733</v>
       </c>
-      <c r="J50" s="13" t="s">
+      <c r="K50" s="3" t="s">
         <v>734</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F51" s="13" t="s">
         <v>498</v>
       </c>
       <c r="G51" s="24" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H51" s="13" t="s">
         <v>500</v>
       </c>
       <c r="I51" s="13" t="s">
+        <v>737</v>
+      </c>
+      <c r="J51" s="13" t="s">
         <v>738</v>
       </c>
-      <c r="J51" s="13" t="s">
+      <c r="K51" s="3" t="s">
         <v>739</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F52" s="13" t="s">
         <v>498</v>
       </c>
       <c r="G52" s="13" t="s">
+        <v>741</v>
+      </c>
+      <c r="H52" s="13" t="s">
+        <v>623</v>
+      </c>
+      <c r="I52" s="5" t="s">
         <v>742</v>
       </c>
-      <c r="H52" s="13" t="s">
-        <v>624</v>
-      </c>
-      <c r="I52" s="5" t="s">
+      <c r="J52" s="13" t="s">
         <v>743</v>
       </c>
-      <c r="J52" s="13" t="s">
+      <c r="K52" s="3" t="s">
         <v>744</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C53" s="11"/>
       <c r="D53" s="11" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E53" s="11"/>
       <c r="F53" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G53" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>556</v>
+      </c>
+      <c r="I53" s="13" t="s">
         <v>747</v>
       </c>
-      <c r="H53" s="11" t="s">
-        <v>557</v>
-      </c>
-      <c r="I53" s="13" t="s">
+      <c r="J53" s="13" t="s">
         <v>748</v>
       </c>
-      <c r="J53" s="13" t="s">
+      <c r="K53" s="3" t="s">
         <v>749</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E54" s="11"/>
       <c r="F54" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H54" s="11" t="s">
         <v>500</v>
       </c>
       <c r="I54" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="J54" s="13" t="s">
         <v>753</v>
       </c>
-      <c r="J54" s="13" t="s">
+      <c r="K54" s="3" t="s">
         <v>754</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G55" s="13" t="s">
+        <v>756</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>757</v>
       </c>
-      <c r="H55" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="I55" s="3" t="s">
+      <c r="J55" s="13" t="s">
         <v>758</v>
       </c>
-      <c r="J55" s="13" t="s">
+      <c r="K55" s="3" t="s">
         <v>759</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
@@ -10719,38 +10756,38 @@
         <v>253</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C56" s="13"/>
       <c r="D56" s="11" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E56" s="13"/>
       <c r="F56" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H56" s="13" t="s">
         <v>515</v>
       </c>
       <c r="I56" s="5" t="s">
+        <v>761</v>
+      </c>
+      <c r="J56" s="13" t="s">
         <v>762</v>
       </c>
-      <c r="J56" s="13" t="s">
+      <c r="K56" s="3" t="s">
         <v>763</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
+        <v>764</v>
+      </c>
+      <c r="B57" s="26" t="s">
         <v>765</v>
-      </c>
-      <c r="B57" s="26" t="s">
-        <v>766</v>
       </c>
       <c r="C57" s="26"/>
       <c r="D57" s="3" t="s">
@@ -10761,182 +10798,182 @@
         <v>1</v>
       </c>
       <c r="G57" s="13" t="s">
+        <v>766</v>
+      </c>
+      <c r="H57" s="11" t="s">
         <v>767</v>
       </c>
-      <c r="H57" s="11" t="s">
+      <c r="I57" s="14" t="s">
         <v>768</v>
       </c>
-      <c r="I57" s="14" t="s">
+      <c r="J57" s="3" t="s">
         <v>769</v>
       </c>
-      <c r="J57" s="3" t="s">
+      <c r="K57" s="3" t="s">
         <v>770</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
+        <v>771</v>
+      </c>
+      <c r="B58" s="19" t="s">
         <v>772</v>
-      </c>
-      <c r="B58" s="19" t="s">
-        <v>773</v>
       </c>
       <c r="C58" s="19"/>
       <c r="D58" s="11" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E58" s="11"/>
       <c r="F58" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G58" s="13" t="s">
+        <v>773</v>
+      </c>
+      <c r="H58" s="13" t="s">
         <v>774</v>
       </c>
-      <c r="H58" s="13" t="s">
+      <c r="I58" s="5" t="s">
         <v>775</v>
       </c>
-      <c r="I58" s="5" t="s">
+      <c r="J58" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="J58" s="13" t="s">
+      <c r="K58" s="5" t="s">
         <v>777</v>
-      </c>
-      <c r="K58" s="5" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C59" s="19"/>
       <c r="D59" s="11" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E59" s="11"/>
       <c r="F59" s="13" t="s">
         <v>1</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H59" s="11" t="s">
         <v>505</v>
       </c>
       <c r="I59" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="J59" s="17" t="s">
         <v>781</v>
       </c>
-      <c r="J59" s="17" t="s">
+      <c r="K59" s="3" t="s">
         <v>782</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C60" s="19"/>
       <c r="D60" s="11" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E60" s="11"/>
       <c r="F60" s="13" t="s">
         <v>1</v>
       </c>
       <c r="G60" s="13" t="s">
+        <v>784</v>
+      </c>
+      <c r="H60" s="11" t="s">
+        <v>686</v>
+      </c>
+      <c r="I60" s="5" t="s">
         <v>785</v>
       </c>
-      <c r="H60" s="11" t="s">
-        <v>687</v>
-      </c>
-      <c r="I60" s="5" t="s">
+      <c r="J60" s="13" t="s">
         <v>786</v>
       </c>
-      <c r="J60" s="13" t="s">
+      <c r="K60" s="3" t="s">
         <v>787</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="B61" s="11" t="s">
         <v>789</v>
-      </c>
-      <c r="B61" s="11" t="s">
-        <v>790</v>
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E61" s="11"/>
       <c r="F61" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H61" s="11" t="s">
         <v>500</v>
       </c>
       <c r="I61" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="J61" s="11" t="s">
         <v>792</v>
       </c>
-      <c r="J61" s="11" t="s">
+      <c r="K61" s="3" t="s">
         <v>793</v>
-      </c>
-      <c r="K61" s="3" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C62" s="11"/>
       <c r="D62" s="11" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E62" s="11"/>
       <c r="F62" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H62" s="13" t="s">
+        <v>795</v>
+      </c>
+      <c r="I62" s="3" t="s">
         <v>796</v>
       </c>
-      <c r="I62" s="3" t="s">
+      <c r="J62" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="J62" s="11" t="s">
+      <c r="K62" s="3" t="s">
         <v>798</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="18" t="s">
+        <v>799</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>800</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>801</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>497</v>
@@ -10945,27 +10982,27 @@
         <v>1</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H63" s="19" t="s">
         <v>510</v>
       </c>
       <c r="I63" s="5" t="s">
+        <v>802</v>
+      </c>
+      <c r="J63" s="19" t="s">
         <v>803</v>
       </c>
-      <c r="J63" s="19" t="s">
+      <c r="K63" s="5" t="s">
         <v>804</v>
-      </c>
-      <c r="K63" s="5" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="19" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>497</v>
@@ -10974,27 +11011,27 @@
         <v>1</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H64" s="19" t="s">
         <v>500</v>
       </c>
       <c r="I64" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="J64" s="19" t="s">
         <v>808</v>
       </c>
-      <c r="J64" s="19" t="s">
+      <c r="K64" s="3" t="s">
         <v>809</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="19" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>497</v>
@@ -11003,27 +11040,27 @@
         <v>1</v>
       </c>
       <c r="G65" s="25" t="s">
+        <v>811</v>
+      </c>
+      <c r="H65" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="I65" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="H65" s="19" t="s">
-        <v>646</v>
-      </c>
-      <c r="I65" s="3" t="s">
+      <c r="J65" s="19" t="s">
         <v>813</v>
       </c>
-      <c r="J65" s="19" t="s">
+      <c r="K65" s="3" t="s">
         <v>814</v>
-      </c>
-      <c r="K65" s="3" t="s">
-        <v>815</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="19" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>497</v>
@@ -11032,27 +11069,27 @@
         <v>1</v>
       </c>
       <c r="G66" s="25" t="s">
+        <v>816</v>
+      </c>
+      <c r="H66" s="19" t="s">
+        <v>540</v>
+      </c>
+      <c r="I66" s="5" t="s">
         <v>817</v>
       </c>
-      <c r="H66" s="19" t="s">
-        <v>541</v>
-      </c>
-      <c r="I66" s="5" t="s">
+      <c r="J66" s="19" t="s">
         <v>818</v>
       </c>
-      <c r="J66" s="19" t="s">
+      <c r="K66" s="5" t="s">
         <v>819</v>
-      </c>
-      <c r="K66" s="5" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="19" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>497</v>
@@ -11061,27 +11098,27 @@
         <v>1</v>
       </c>
       <c r="G67" s="25" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H67" s="19" t="s">
         <v>500</v>
       </c>
       <c r="I67" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="J67" s="19" t="s">
         <v>823</v>
       </c>
-      <c r="J67" s="19" t="s">
+      <c r="K67" s="3" t="s">
         <v>824</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="19" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>497</v>
@@ -11090,19 +11127,19 @@
         <v>1</v>
       </c>
       <c r="G68" s="25" t="s">
+        <v>826</v>
+      </c>
+      <c r="H68" s="19" t="s">
         <v>827</v>
       </c>
-      <c r="H68" s="19" t="s">
+      <c r="I68" s="5" t="s">
         <v>828</v>
       </c>
-      <c r="I68" s="5" t="s">
+      <c r="J68" s="19" t="s">
         <v>829</v>
       </c>
-      <c r="J68" s="19" t="s">
+      <c r="K68" s="3" t="s">
         <v>830</v>
-      </c>
-      <c r="K68" s="3" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -11110,34 +11147,34 @@
         <v>197</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H69" s="31" t="s">
         <v>505</v>
       </c>
       <c r="I69" s="14" t="s">
+        <v>831</v>
+      </c>
+      <c r="J69" s="32" t="s">
         <v>832</v>
       </c>
-      <c r="J69" s="32" t="s">
+      <c r="K69" s="3" t="s">
         <v>833</v>
-      </c>
-      <c r="K69" s="3" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -11160,24 +11197,24 @@
         <v>498</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H70" s="31" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="J70" s="33" t="s">
+        <v>834</v>
+      </c>
+      <c r="K70" s="3" t="s">
         <v>835</v>
-      </c>
-      <c r="K70" s="3" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>496</v>
@@ -11195,54 +11232,54 @@
         <v>498</v>
       </c>
       <c r="G71" s="46" t="s">
+        <v>959</v>
+      </c>
+      <c r="H71" s="63" t="s">
+        <v>582</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>958</v>
+      </c>
+      <c r="J71" s="33" t="s">
         <v>960</v>
       </c>
-      <c r="H71" s="63" t="s">
-        <v>583</v>
-      </c>
-      <c r="I71" s="5" t="s">
-        <v>959</v>
-      </c>
-      <c r="J71" s="33" t="s">
+      <c r="K71" s="3" t="s">
         <v>961</v>
-      </c>
-      <c r="K71" s="3" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G72" s="71" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H72" s="63" t="s">
         <v>510</v>
       </c>
       <c r="I72" s="5" t="s">
+        <v>969</v>
+      </c>
+      <c r="J72" s="33" t="s">
+        <v>968</v>
+      </c>
+      <c r="K72" s="72" t="s">
         <v>970</v>
-      </c>
-      <c r="J72" s="33" t="s">
-        <v>969</v>
-      </c>
-      <c r="K72" s="72" t="s">
-        <v>971</v>
       </c>
     </row>
   </sheetData>
@@ -11303,7 +11340,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23" t="s">
@@ -11311,10 +11348,10 @@
       </c>
       <c r="D1" s="23"/>
       <c r="E1" s="23" t="s">
+        <v>837</v>
+      </c>
+      <c r="F1" s="23" t="s">
         <v>838</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>839</v>
       </c>
       <c r="G1" s="1"/>
     </row>
@@ -11337,7 +11374,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="20" t="s">
@@ -11345,16 +11382,16 @@
       </c>
       <c r="D3" s="20"/>
       <c r="E3" s="20" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20" t="s">
@@ -11362,46 +11399,46 @@
       </c>
       <c r="D4" s="20"/>
       <c r="E4" s="20" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
       <c r="D5" s="20"/>
       <c r="E5" s="20" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
       <c r="D6" s="20"/>
       <c r="E6" s="22" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
@@ -11412,7 +11449,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
@@ -11423,7 +11460,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
@@ -11434,7 +11471,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
@@ -11445,7 +11482,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
@@ -11456,7 +11493,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
@@ -11467,7 +11504,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
@@ -11478,7 +11515,7 @@
     </row>
     <row r="14" spans="1:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="27" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
@@ -11589,7 +11626,7 @@
     </row>
     <row r="13" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="42" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
@@ -11597,42 +11634,42 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="41" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="41" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="41" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="41" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -11657,7 +11694,7 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="82" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B28" s="80"/>
       <c r="C28" s="80"/>
@@ -11777,7 +11814,7 @@
     </row>
     <row r="32" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="43" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B32" s="43">
         <v>376</v>
@@ -11828,7 +11865,7 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="82" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B33" s="80"/>
       <c r="C33" s="80"/>
@@ -11948,7 +11985,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="43" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B37" s="43">
         <v>910</v>
@@ -11999,7 +12036,7 @@
     </row>
     <row r="38" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="43" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B38" s="43">
         <v>919</v>
@@ -12101,7 +12138,7 @@
     </row>
     <row r="40" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="43" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B40" s="43"/>
       <c r="C40" s="43"/>
@@ -12134,7 +12171,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="43" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B41" s="43"/>
       <c r="C41" s="43"/>
@@ -12167,7 +12204,7 @@
     </row>
     <row r="42" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="46" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B42" s="46">
         <v>376</v>
@@ -12210,7 +12247,7 @@
     </row>
     <row r="43" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="43" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B43" s="43"/>
       <c r="C43" s="43"/>
@@ -12243,7 +12280,7 @@
     </row>
     <row r="44" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="43" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B44" s="43"/>
       <c r="C44" s="43"/>
@@ -12276,7 +12313,7 @@
     </row>
     <row r="45" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="43" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B45" s="43"/>
       <c r="C45" s="43"/>
@@ -12309,7 +12346,7 @@
     </row>
     <row r="46" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="43" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B46" s="43"/>
       <c r="C46" s="43"/>
@@ -12342,7 +12379,7 @@
     </row>
     <row r="47" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="46" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B47" s="46">
         <v>373</v>
@@ -12385,7 +12422,7 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="82" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B48" s="80"/>
       <c r="C48" s="80"/>
@@ -12505,7 +12542,7 @@
     </row>
     <row r="52" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="43" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B52" s="43">
         <v>551</v>
@@ -12556,7 +12593,7 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="82" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B53" s="80"/>
       <c r="C53" s="80"/>
@@ -12709,7 +12746,7 @@
     </row>
     <row r="58" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="43" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B58" s="43"/>
       <c r="C58" s="43"/>
@@ -13138,7 +13175,7 @@
     </row>
     <row r="71" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="46" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B71" s="46">
         <v>2642</v>
@@ -13181,7 +13218,7 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="82" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B72" s="80"/>
       <c r="C72" s="80"/>
@@ -13433,7 +13470,7 @@
     </row>
     <row r="80" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="46" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B80" s="46">
         <v>1680</v>
@@ -13476,7 +13513,7 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="82" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B81" s="80"/>
       <c r="C81" s="80"/>
@@ -13596,7 +13633,7 @@
     </row>
     <row r="85" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="43" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B85" s="43"/>
       <c r="C85" s="43"/>
@@ -13629,7 +13666,7 @@
     </row>
     <row r="86" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="43" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B86" s="43"/>
       <c r="C86" s="43"/>
@@ -13662,7 +13699,7 @@
     </row>
     <row r="87" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="43" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B87" s="43"/>
       <c r="C87" s="43"/>
@@ -13695,7 +13732,7 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="43" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B88" s="43"/>
       <c r="C88" s="43"/>
@@ -13728,7 +13765,7 @@
     </row>
     <row r="89" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="43" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B89" s="43"/>
       <c r="C89" s="43"/>
@@ -13761,7 +13798,7 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="43" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B90" s="43"/>
       <c r="C90" s="43"/>
@@ -13794,7 +13831,7 @@
     </row>
     <row r="91" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="43" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B91" s="43"/>
       <c r="C91" s="43"/>
@@ -13827,7 +13864,7 @@
     </row>
     <row r="92" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="46" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B92" s="46">
         <v>1003</v>
@@ -13870,7 +13907,7 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="82" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B93" s="80"/>
       <c r="C93" s="80"/>
@@ -13990,7 +14027,7 @@
     </row>
     <row r="97" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="43" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B97" s="43"/>
       <c r="C97" s="43"/>
@@ -14155,7 +14192,7 @@
     </row>
     <row r="102" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="43" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B102" s="43"/>
       <c r="C102" s="43"/>
@@ -14188,7 +14225,7 @@
     </row>
     <row r="103" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="43" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B103" s="43"/>
       <c r="C103" s="43"/>
@@ -14320,7 +14357,7 @@
     </row>
     <row r="107" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="43" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B107" s="43"/>
       <c r="C107" s="43"/>
@@ -14386,7 +14423,7 @@
     </row>
     <row r="109" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="43" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B109" s="43"/>
       <c r="C109" s="43"/>
@@ -14518,7 +14555,7 @@
     </row>
     <row r="113" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="43" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B113" s="43"/>
       <c r="C113" s="43"/>
@@ -14551,7 +14588,7 @@
     </row>
     <row r="114" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="43" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B114" s="43"/>
       <c r="C114" s="43"/>
@@ -14584,7 +14621,7 @@
     </row>
     <row r="115" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="43" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B115" s="43"/>
       <c r="C115" s="43"/>
@@ -14617,7 +14654,7 @@
     </row>
     <row r="116" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="43" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B116" s="43"/>
       <c r="C116" s="43"/>
@@ -14716,7 +14753,7 @@
     </row>
     <row r="119" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="43" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B119" s="43"/>
       <c r="C119" s="43"/>
@@ -14749,7 +14786,7 @@
     </row>
     <row r="120" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="43" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B120" s="43"/>
       <c r="C120" s="43"/>
@@ -14782,7 +14819,7 @@
     </row>
     <row r="121" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="43" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B121" s="43"/>
       <c r="C121" s="43"/>
@@ -14815,7 +14852,7 @@
     </row>
     <row r="122" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="43" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B122" s="43"/>
       <c r="C122" s="43"/>
@@ -14848,7 +14885,7 @@
     </row>
     <row r="123" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="43" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B123" s="43"/>
       <c r="C123" s="43"/>
@@ -14881,7 +14918,7 @@
     </row>
     <row r="124" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="43" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B124" s="43"/>
       <c r="C124" s="43"/>
@@ -14914,7 +14951,7 @@
     </row>
     <row r="125" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="43" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B125" s="43"/>
       <c r="C125" s="43"/>
@@ -14947,7 +14984,7 @@
     </row>
     <row r="126" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="46" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B126" s="46">
         <v>1390</v>
@@ -14990,7 +15027,7 @@
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="82" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B127" s="80"/>
       <c r="C127" s="80"/>
@@ -15110,7 +15147,7 @@
     </row>
     <row r="131" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="43" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B131" s="43">
         <v>1114</v>
@@ -15161,7 +15198,7 @@
     </row>
     <row r="132" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="43" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B132" s="43">
         <v>1114</v>
@@ -15212,7 +15249,7 @@
     </row>
     <row r="133" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="43" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B133" s="43">
         <v>1114</v>
@@ -15263,7 +15300,7 @@
     </row>
     <row r="134" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="43" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B134" s="43"/>
       <c r="C134" s="43"/>
@@ -15329,7 +15366,7 @@
     </row>
     <row r="136" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="43" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B136" s="43"/>
       <c r="C136" s="43"/>
@@ -15362,7 +15399,7 @@
     </row>
     <row r="137" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="46" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B137" s="46">
         <v>1114</v>
@@ -15405,7 +15442,7 @@
     </row>
     <row r="138" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="43" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B138" s="43">
         <v>1114</v>
@@ -15456,7 +15493,7 @@
     </row>
     <row r="139" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="43" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B139" s="43"/>
       <c r="C139" s="43"/>
@@ -15489,7 +15526,7 @@
     </row>
     <row r="140" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="43" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B140" s="43"/>
       <c r="C140" s="43"/>
@@ -15522,7 +15559,7 @@
     </row>
     <row r="141" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="46" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B141" s="46">
         <v>1114</v>
@@ -15565,7 +15602,7 @@
     </row>
     <row r="142" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="43" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B142" s="43"/>
       <c r="C142" s="43"/>
@@ -15598,7 +15635,7 @@
     </row>
     <row r="143" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="43" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B143" s="43"/>
       <c r="C143" s="43"/>
@@ -15631,7 +15668,7 @@
     </row>
     <row r="144" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="46" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B144" s="46">
         <v>1114</v>
@@ -15674,7 +15711,7 @@
     </row>
     <row r="145" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="43" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B145" s="43"/>
       <c r="C145" s="43"/>
@@ -15707,7 +15744,7 @@
     </row>
     <row r="146" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="43" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B146" s="43"/>
       <c r="C146" s="43"/>
@@ -15740,7 +15777,7 @@
     </row>
     <row r="147" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="46" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B147" s="46">
         <v>1114</v>
@@ -15783,7 +15820,7 @@
     </row>
     <row r="148" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="43" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B148" s="43">
         <v>1114</v>
@@ -15834,7 +15871,7 @@
     </row>
     <row r="149" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="43" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B149" s="43"/>
       <c r="C149" s="43"/>
@@ -15867,7 +15904,7 @@
     </row>
     <row r="150" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="43" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B150" s="43"/>
       <c r="C150" s="43"/>
@@ -15900,7 +15937,7 @@
     </row>
     <row r="151" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="46" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B151" s="46">
         <v>1114</v>
@@ -15943,7 +15980,7 @@
     </row>
     <row r="152" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="43" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B152" s="43">
         <v>1114</v>
@@ -15994,7 +16031,7 @@
     </row>
     <row r="153" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="43" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B153" s="43">
         <v>1114</v>
@@ -16045,7 +16082,7 @@
     </row>
     <row r="154" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="43" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B154" s="43">
         <v>1114</v>
@@ -16096,7 +16133,7 @@
     </row>
     <row r="155" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="43" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B155" s="43"/>
       <c r="C155" s="43"/>
@@ -16129,7 +16166,7 @@
     </row>
     <row r="156" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="43" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B156" s="43"/>
       <c r="C156" s="43"/>
@@ -16162,7 +16199,7 @@
     </row>
     <row r="157" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="43" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B157" s="43"/>
       <c r="C157" s="43"/>
@@ -16195,7 +16232,7 @@
     </row>
     <row r="158" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="46" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B158" s="46">
         <v>1114</v>
@@ -16529,7 +16566,7 @@
     </row>
     <row r="168" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="43" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B168" s="43"/>
       <c r="C168" s="43"/>
@@ -16661,7 +16698,7 @@
     </row>
     <row r="172" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="46" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B172" s="46">
         <v>728</v>
@@ -19123,7 +19160,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="84" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -19134,48 +19171,48 @@
     </row>
     <row r="2" spans="1:7" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="48" t="s">
+        <v>912</v>
+      </c>
+      <c r="B2" s="48" t="s">
         <v>913</v>
       </c>
-      <c r="B2" s="48" t="s">
+      <c r="C2" s="48" t="s">
         <v>914</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="D2" s="48" t="s">
         <v>915</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="E2" s="48" t="s">
         <v>916</v>
       </c>
-      <c r="E2" s="48" t="s">
+      <c r="F2" s="48" t="s">
         <v>917</v>
       </c>
-      <c r="F2" s="48" t="s">
+      <c r="G2" s="48" t="s">
         <v>918</v>
-      </c>
-      <c r="G2" s="48" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="55" t="s">
+        <v>919</v>
+      </c>
+      <c r="B3" s="55" t="s">
         <v>920</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="C3" s="55" t="s">
         <v>921</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="D3" s="55" t="s">
         <v>922</v>
       </c>
-      <c r="D3" s="55" t="s">
+      <c r="E3" s="55" t="s">
         <v>923</v>
       </c>
-      <c r="E3" s="55" t="s">
+      <c r="F3" s="55" t="s">
         <v>924</v>
       </c>
-      <c r="F3" s="55" t="s">
+      <c r="G3" s="55" t="s">
         <v>925</v>
-      </c>
-      <c r="G3" s="55" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -19264,7 +19301,7 @@
     </row>
     <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="49" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B8" s="49" t="s">
         <v>1</v>
@@ -19291,7 +19328,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D9" s="50">
         <v>1544</v>
@@ -19314,7 +19351,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="49" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D10" s="50">
         <v>1858</v>
@@ -19337,7 +19374,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D11" s="50">
         <v>2006</v>
@@ -19360,7 +19397,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="50">
@@ -19381,7 +19418,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="49" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="D13" s="50"/>
       <c r="E13" s="50">
@@ -19402,7 +19439,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="49" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="D14" s="50"/>
       <c r="E14" s="50">
@@ -19423,7 +19460,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="49" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D15" s="50"/>
       <c r="E15" s="50">
@@ -19564,7 +19601,7 @@
     </row>
     <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="49" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B22" s="49" t="s">
         <v>1</v>
@@ -19585,7 +19622,7 @@
     </row>
     <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="49" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B23" s="49" t="s">
         <v>1</v>
@@ -19606,7 +19643,7 @@
     </row>
     <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="49" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B24" s="49" t="s">
         <v>1</v>
@@ -19627,7 +19664,7 @@
     </row>
     <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="49" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B25" s="49" t="s">
         <v>1</v>
@@ -19648,7 +19685,7 @@
     </row>
     <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="49" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B26" s="49" t="s">
         <v>1</v>
@@ -19669,7 +19706,7 @@
     </row>
     <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="49" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B27" s="49" t="s">
         <v>1</v>
@@ -19717,7 +19754,7 @@
         <v>8</v>
       </c>
       <c r="C29" s="51" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="D29" s="52"/>
       <c r="E29" s="52">
@@ -19738,7 +19775,7 @@
         <v>8</v>
       </c>
       <c r="C30" s="51" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D30" s="52"/>
       <c r="E30" s="52">
@@ -19759,7 +19796,7 @@
         <v>8</v>
       </c>
       <c r="C31" s="51" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D31" s="52">
         <v>71</v>
@@ -19782,7 +19819,7 @@
         <v>8</v>
       </c>
       <c r="C32" s="51" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D32" s="52"/>
       <c r="E32" s="52">
@@ -19885,7 +19922,7 @@
         <v>8</v>
       </c>
       <c r="C37" s="51" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="D37" s="52"/>
       <c r="E37" s="52">
@@ -19906,7 +19943,7 @@
         <v>8</v>
       </c>
       <c r="C38" s="51" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="D38" s="52"/>
       <c r="E38" s="52">
@@ -19979,7 +20016,7 @@
         <v>2</v>
       </c>
       <c r="G41" s="56" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20042,15 +20079,15 @@
         <v>3</v>
       </c>
       <c r="G44" s="56" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="60" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B45" s="60" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C45" s="60"/>
       <c r="D45" s="61">
@@ -20063,7 +20100,7 @@
         <v>8</v>
       </c>
       <c r="G45" s="60" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20071,7 +20108,7 @@
         <v>232</v>
       </c>
       <c r="B46" s="53" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C46" s="53"/>
       <c r="D46" s="54"/>
@@ -20082,7 +20119,7 @@
         <v>8</v>
       </c>
       <c r="G46" s="53" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20090,7 +20127,7 @@
         <v>88</v>
       </c>
       <c r="B47" s="53" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C47" s="53"/>
       <c r="D47" s="54">
@@ -20101,7 +20138,7 @@
         <v>3</v>
       </c>
       <c r="G47" s="53" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20109,10 +20146,10 @@
         <v>88</v>
       </c>
       <c r="B48" s="53" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C48" s="53" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D48" s="54">
         <v>190</v>
@@ -20122,7 +20159,7 @@
         <v>70</v>
       </c>
       <c r="G48" s="53" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20130,7 +20167,7 @@
         <v>88</v>
       </c>
       <c r="B49" s="53" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C49" s="53" t="s">
         <v>80</v>
@@ -20143,15 +20180,15 @@
         <v>4</v>
       </c>
       <c r="G49" s="53" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="56" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B50" s="56" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C50" s="56"/>
       <c r="D50" s="57">
@@ -20164,15 +20201,15 @@
         <v>20</v>
       </c>
       <c r="G50" s="56" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="58" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B51" s="58" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C51" s="58"/>
       <c r="D51" s="59">
@@ -20185,15 +20222,15 @@
         <v>3</v>
       </c>
       <c r="G51" s="58" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="53" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B52" s="53" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C52" s="53"/>
       <c r="D52" s="54"/>
@@ -20204,15 +20241,15 @@
         <v>7</v>
       </c>
       <c r="G52" s="53" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="53" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B53" s="53" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C53" s="53"/>
       <c r="D53" s="54"/>
@@ -20223,15 +20260,15 @@
         <v>5</v>
       </c>
       <c r="G53" s="53" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="53" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B54" s="53" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C54" s="53"/>
       <c r="D54" s="54"/>
@@ -20242,7 +20279,7 @@
         <v>3</v>
       </c>
       <c r="G54" s="53" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20261,7 +20298,7 @@
         <v>11</v>
       </c>
       <c r="G55" s="56" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20280,7 +20317,7 @@
         <v>1</v>
       </c>
       <c r="G56" s="56" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20291,7 +20328,7 @@
         <v>1</v>
       </c>
       <c r="C57" s="58" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D57" s="59">
         <v>904</v>
@@ -20301,7 +20338,7 @@
         <v>6</v>
       </c>
       <c r="G57" s="58" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20312,7 +20349,7 @@
         <v>8</v>
       </c>
       <c r="C58" s="58" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D58" s="59">
         <v>30</v>
@@ -20322,7 +20359,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="58" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20333,7 +20370,7 @@
         <v>1</v>
       </c>
       <c r="C59" s="58" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D59" s="59">
         <v>733</v>
@@ -20343,7 +20380,7 @@
         <v>3</v>
       </c>
       <c r="G59" s="58" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20354,7 +20391,7 @@
         <v>1</v>
       </c>
       <c r="C60" s="58" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="D60" s="59">
         <v>821</v>
@@ -20364,7 +20401,7 @@
         <v>14</v>
       </c>
       <c r="G60" s="58" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20375,7 +20412,7 @@
         <v>8</v>
       </c>
       <c r="C61" s="58" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="D61" s="59">
         <v>55</v>
@@ -20385,7 +20422,7 @@
         <v>1</v>
       </c>
       <c r="G61" s="58" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20396,7 +20433,7 @@
         <v>1</v>
       </c>
       <c r="C62" s="58" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D62" s="59">
         <v>828</v>
@@ -20406,7 +20443,7 @@
         <v>3</v>
       </c>
       <c r="G62" s="58" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20417,7 +20454,7 @@
         <v>8</v>
       </c>
       <c r="C63" s="58" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D63" s="59">
         <v>52</v>
@@ -20427,7 +20464,7 @@
         <v>1</v>
       </c>
       <c r="G63" s="58" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20438,7 +20475,7 @@
         <v>1</v>
       </c>
       <c r="C64" s="58" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="D64" s="59">
         <v>817</v>
@@ -20448,7 +20485,7 @@
         <v>8</v>
       </c>
       <c r="G64" s="58" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20459,7 +20496,7 @@
         <v>8</v>
       </c>
       <c r="C65" s="58" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="D65" s="59">
         <v>48</v>
@@ -20469,7 +20506,7 @@
         <v>1</v>
       </c>
       <c r="G65" s="58" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20480,7 +20517,7 @@
         <v>1</v>
       </c>
       <c r="C66" s="58" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D66" s="59">
         <v>910</v>
@@ -20490,7 +20527,7 @@
         <v>6</v>
       </c>
       <c r="G66" s="58" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20501,7 +20538,7 @@
         <v>1</v>
       </c>
       <c r="C67" s="58" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="D67" s="59">
         <v>612</v>
@@ -20511,7 +20548,7 @@
         <v>9</v>
       </c>
       <c r="G67" s="58" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20522,7 +20559,7 @@
         <v>8</v>
       </c>
       <c r="C68" s="58" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="D68" s="59">
         <v>26</v>
@@ -20532,7 +20569,7 @@
         <v>1</v>
       </c>
       <c r="G68" s="58" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20543,7 +20580,7 @@
         <v>1</v>
       </c>
       <c r="C69" s="58" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D69" s="59">
         <v>834</v>
@@ -20553,7 +20590,7 @@
         <v>6</v>
       </c>
       <c r="G69" s="58" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20564,7 +20601,7 @@
         <v>8</v>
       </c>
       <c r="C70" s="58" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D70" s="59">
         <v>49</v>
@@ -20574,7 +20611,7 @@
         <v>1</v>
       </c>
       <c r="G70" s="58" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20585,7 +20622,7 @@
         <v>1</v>
       </c>
       <c r="C71" s="58" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D71" s="59">
         <v>1021</v>
@@ -20595,7 +20632,7 @@
         <v>1</v>
       </c>
       <c r="G71" s="58" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20606,7 +20643,7 @@
         <v>1</v>
       </c>
       <c r="C72" s="58" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="D72" s="59">
         <v>489</v>
@@ -20616,18 +20653,18 @@
         <v>5</v>
       </c>
       <c r="G72" s="58" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="58" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B73" s="58" t="s">
         <v>1</v>
       </c>
       <c r="C73" s="58" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="D73" s="59">
         <v>1000</v>
@@ -20637,18 +20674,18 @@
         <v>6</v>
       </c>
       <c r="G73" s="58" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="58" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B74" s="58" t="s">
         <v>1</v>
       </c>
       <c r="C74" s="58" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="D74" s="59">
         <v>1025</v>
@@ -20658,7 +20695,7 @@
         <v>4</v>
       </c>
       <c r="G74" s="58" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20669,7 +20706,7 @@
         <v>1</v>
       </c>
       <c r="C75" s="58" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="D75" s="59">
         <v>784</v>
@@ -20679,7 +20716,7 @@
         <v>3</v>
       </c>
       <c r="G75" s="58" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20690,7 +20727,7 @@
         <v>8</v>
       </c>
       <c r="C76" s="58" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="D76" s="59">
         <v>72</v>
@@ -20700,12 +20737,12 @@
         <v>1</v>
       </c>
       <c r="G76" s="58" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="83" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B78" s="80"/>
       <c r="C78" s="80"/>

--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud2\Boulot 2026\Site orientation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B13632-30BE-4A0D-B9CA-E478148C6F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C94744-4FB4-4E35-82C1-F85D1A99738F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elèves_BCPST" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2422" uniqueCount="981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2422" uniqueCount="983">
   <si>
     <t>Statistiques 2025</t>
   </si>
@@ -1570,9 +1570,6 @@
     <t>https://external-content.duckduckgo.com/iu/?u=https%3A%2F%2Ftse1.mm.bing.net%2Fth%2Fid%2FOIP.xYe4yBtGhVh08OGHlaGfmgHaEx%3Fcb%3Ducfimg2%26pid%3DApi%26ucfimg%3D1&amp;f=1&amp;ipt=8129abcaa9a8d9abfbf023b6b02b28d790b0efb11e35b1e7250dd0805698e681&amp;ipo=images</t>
   </si>
   <si>
-    <t>École d’ingénieurs spécialisée en agronomie et industries alimentaires.</t>
-  </si>
-  <si>
     <t>Nancy</t>
   </si>
   <si>
@@ -1582,9 +1579,6 @@
     <t>https://external-content.duckduckgo.com/iu/?u=https%3A%2F%2Ftse3.mm.bing.net%2Fth%2Fid%2FOIP.RUy9dPHDqmlaA0tTt40z3AHaEK%3Fcb%3Ducfimgc2%26pid%3DApi&amp;f=1&amp;ipt=44ad9df2f0ec58c894d8b14ae9328bd6db488b0c39c378cb41eeae2629a3b410&amp;ipo=images</t>
   </si>
   <si>
-    <t>École d’ingénieurs en agriculture, agroalimentaire et environnement.</t>
-  </si>
-  <si>
     <t>Dijon</t>
   </si>
   <si>
@@ -1612,9 +1606,6 @@
     <t>https://external-content.duckduckgo.com/iu/?u=https%3A%2F%2Ftse3.mm.bing.net%2Fth%2Fid%2FOIP.bp5b40fFhZ9o_m1nxfZ0ZQHaDt%3Fcb%3Ducfimg2%26pid%3DApi%26ucfimg%3D1&amp;f=1&amp;ipt=1b15b2a219abacf9092787bd7800a68460b820cdbf71f79372cb2b06edced77a&amp;ipo=images</t>
   </si>
   <si>
-    <t>Campus agronomique de VetAgro Sup, école d'ingénieurs en sciences du vivant et de l'agroalimentaire.</t>
-  </si>
-  <si>
     <t>Clermont-Ferrand</t>
   </si>
   <si>
@@ -1628,9 +1619,6 @@
   </si>
   <si>
     <t>ENSTIB</t>
-  </si>
-  <si>
-    <t>École d’ingénieurs spécialisée en bois et matériaux durables.</t>
   </si>
   <si>
     <t>Épinal</t>
@@ -2986,6 +2974,30 @@
   </si>
   <si>
     <t>GARNIER</t>
+  </si>
+  <si>
+    <t>Grande école d’Ingénieur, dans les domaines de l’agronomie, des industries alimentaires et de la production agroalimentaire. Elle propose une belle diversité de spécialisations : Sciences et Génie de l’Environnement, Biotechnologies, protection des cultures, Formulation alimentaire, Développement industriel…
+Mots-clés : Agronomie ; Biotechnologies ; Génie de l’environnement ; Protection des cultures ; Développement durable des filières agricoles ; Industries alimentaires ; Microbiologie ; Formulation alimentaire ; Packaging et conditionnement ; Génie des procédés ; Qualité ; Ferme expérimentale ; Double diplôme</t>
+  </si>
+  <si>
+    <t>L’ENSTIB forme des ingénieurs spécialisés dans la filière bois : production, bureau d’études, recherche et développement, qualité… Les enseignements incluent l’étude de la mécanique du bois, la rétro-ingénierie (robotique), l’énergétique du bâtiment … et propose plusieurs doubles diplômes avec les écoles d’Ingénieur AgroParisTech, Ingénieur Mines d'Alès, ENS Architecture de Nancy, l’Université du Québec… 
+Mots-clés : Bois ; Matériaux biosourcés ; Conception ; Construction bois ; Valorisation énergétique ; Production ; Recherche ; Stages ; Projet de recherche ; Double diplôme</t>
+  </si>
+  <si>
+    <t>L’Institut Agro-Dijon est une Grande école formant des Ingénieurs dans les domaines de l’agronomie et de l’alimentation. La formation Ingénieur en alimentation permet d’étudier la nutrition, la microbiologie, le génie des procédés alimentaires … La formation Ingénieur agronome inclus l’étude des élevages, des productions végétales, de l’agroéquipement, … Les deux formations proposent plusieurs spécialisations parmi lesquelles biotechnologies microbiennes et fermentations alimentaires, connaissances et commerce des vins, gestion et protection des sols… 
+Mots-clés : Agroalimentaire ; Sciences des aliments ; Nutrition ; Toxicologie ; Génie des procédés alimentaires ; Qualité ; Sécurité sanitaire ; Vigne ; Vin ; Agroécologie ; Elevage ; Agroéquipements ; Microbiologie ; Voie Apprentissage ; Elèves fonctionnaires ; Double diplôme ; Mobilité internationale</t>
+  </si>
+  <si>
+    <t>VetAgro Sup est un Institut d’enseignement supérieur et de recherche qui forme notamment des ingénieurs agronomes. Le socle commun permet de se former aux systèmes de production agricole, à l’alimentation et aux procédés, aux politiques publiques. Plusieurs voies d’approfondissement sont possibles et permettent d’intégrer différentes filières en santé animale et humaines, l’innovation en agronomie, développement éco-territorial…
+Mots-clés : Production agricole ; Alimentation ; Elevage ; Environnement ; Territoires ; Santé animale et humaine ; Politiques publiques ; Innovation ; Management ; Contrat de professionnalisation ; Voie Apprentissage ; Mobilité internationale</t>
+  </si>
+  <si>
+    <t>Le campus d’Angers de l’Institut Agro Rennes-Angers forme des ingénieurs en horticulture et des ingénieurs en paysage. Les domaines d’activité de l’ingénieur en horticulture sont divers, depuis la création de matériel végétal jusqu’au pilotage de structures ou entreprises impliquées dans les filières de l'horticulture, en passant par le contrôle de la qualité des produits dans les filières du végétal. L’ingénieur en paysage est plutôt spécialisé dans la conception et la réalisation de projets en paysage. 
+Mots-clés : Horticulture ; Semences ; Protection des cultures ; Agroécologie ; Paysage ; Environnement ; Productions végétales ; Sélection variétale ; Entrepreneuriat ; Double diplôme ; Voie Apprentissage/Alternance ; Mobilité internationale</t>
+  </si>
+  <si>
+    <t>Oniris VetAgroBio est une école qui forme aux métiers de vétérinaire et aux métiers d’ingénieurs dans les domaines agroalimentaires, alimentation ou des bioprocédés et biotechnologies. Le cursus ingénieur s’appuie sur des enseignements sur les propriétés des aliments, la microbiologie, la gestion de projets. L’école propose des doubles diplômes dans les domaines de la bioproduction santé, sur la thématique One Health-Emerge et en Nutrition et sciences des aliments. 
+Mots-clés : Alimentation ; Nutrition ; Agroalimentaire ; Qualité sanitaire ; Sécurité des aliments ; Biotechnologies ; Santé publique ; Innovation ; Double diplôme ; Voie Apprentissage ; Mobilité internationale.</t>
   </si>
 </sst>
 </file>
@@ -3556,22 +3568,22 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3961,8 +3973,8 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="85" t="s">
-        <v>980</v>
+      <c r="A2" s="79" t="s">
+        <v>976</v>
       </c>
       <c r="B2" s="64" t="str">
         <f t="shared" ref="B2" si="0">LEFT(A2)</f>
@@ -3986,14 +3998,14 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="77" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="B3" s="64" t="str">
         <f t="shared" ref="B3" si="1">LEFT(A3)</f>
         <v>G</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="D3" s="64">
         <v>2026</v>
@@ -4010,14 +4022,14 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="B4" s="64" t="str">
         <f t="shared" ref="B4" si="2">LEFT(A4)</f>
         <v>S</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="D4" s="64">
         <v>2026</v>
@@ -4043,7 +4055,7 @@
         <v>T</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="D5" s="64">
         <v>2026</v>
@@ -4060,7 +4072,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="68" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="B6" s="64" t="str">
         <f t="shared" ref="B6" si="4">LEFT(A6)</f>
@@ -4084,14 +4096,14 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="68" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="B7" s="64" t="str">
         <f t="shared" ref="B7" si="5">LEFT(A7)</f>
         <v>B</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="D7" s="64">
         <v>2026</v>
@@ -4108,14 +4120,14 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="68" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="B8" s="64" t="str">
         <f t="shared" ref="B8" si="6">LEFT(A8)</f>
         <v>K</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="D8" s="64">
         <v>2026</v>
@@ -4124,7 +4136,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="64" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="G8" s="64"/>
       <c r="H8" s="64"/>
@@ -4132,14 +4144,14 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="68" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="B9" s="64" t="str">
         <f t="shared" ref="B9" si="7">LEFT(A9)</f>
         <v>C</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="D9" s="64">
         <v>2026</v>
@@ -4156,14 +4168,14 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="68" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="B10" s="64" t="str">
         <f t="shared" ref="B10:B74" si="8">LEFT(A10)</f>
         <v>V</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="D10" s="64">
         <v>2026</v>
@@ -4182,14 +4194,14 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="69" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="B11" s="66" t="str">
         <f t="shared" si="8"/>
         <v>H</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="D11" s="64">
         <v>2026</v>
@@ -6302,7 +6314,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="B2" s="1" t="str">
         <f t="shared" ref="B2" si="0">LEFT(A2)</f>
@@ -6325,7 +6337,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="B3" s="1" t="str">
         <f t="shared" ref="B3" si="1">LEFT(A3)</f>
@@ -6348,14 +6360,14 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="B4" s="1" t="str">
         <f t="shared" ref="B4" si="2">LEFT(A4)</f>
         <v>B</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="D4" s="64">
         <v>2026</v>
@@ -6364,7 +6376,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="H4" s="64"/>
       <c r="I4" s="64"/>
@@ -8953,7 +8965,7 @@
         <v>498</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>504</v>
+        <v>982</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>505</v>
@@ -9023,19 +9035,19 @@
         <v>498</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="I5" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>979</v>
-      </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>516</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9058,19 +9070,19 @@
         <v>498</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>520</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9093,19 +9105,19 @@
         <v>498</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>525</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>526</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9128,19 +9140,19 @@
         <v>498</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>529</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9148,10 +9160,10 @@
         <v>136</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>497</v>
@@ -9163,19 +9175,19 @@
         <v>498</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>534</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9198,19 +9210,19 @@
         <v>498</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>539</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9218,10 +9230,10 @@
         <v>345</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>497</v>
@@ -9233,19 +9245,19 @@
         <v>498</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>545</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9253,10 +9265,10 @@
         <v>370</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>497</v>
@@ -9268,19 +9280,19 @@
         <v>498</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>550</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9288,10 +9300,10 @@
         <v>142</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>497</v>
@@ -9303,19 +9315,19 @@
         <v>498</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9323,10 +9335,10 @@
         <v>258</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>497</v>
@@ -9347,10 +9359,10 @@
         <v>506</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9358,10 +9370,10 @@
         <v>232</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>497</v>
@@ -9370,19 +9382,19 @@
         <v>1</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>562</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>565</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9390,28 +9402,28 @@
         <v>88</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>1</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>500</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9419,34 +9431,34 @@
         <v>169</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9454,34 +9466,34 @@
         <v>91</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>576</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9489,34 +9501,34 @@
         <v>194</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="K19" s="5" t="s">
         <v>581</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9524,34 +9536,34 @@
         <v>145</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9559,34 +9571,34 @@
         <v>85</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>590</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>591</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9594,69 +9606,69 @@
         <v>119</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G23" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>601</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9664,69 +9676,69 @@
         <v>334</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9734,34 +9746,34 @@
         <v>107</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>615</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9769,34 +9781,34 @@
         <v>94</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G27" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>622</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>625</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9804,34 +9816,34 @@
         <v>129</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G28" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="K28" s="3" t="s">
         <v>627</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>628</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>629</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>630</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9839,34 +9851,34 @@
         <v>322</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9874,34 +9886,34 @@
         <v>324</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G30" s="10" t="s">
+        <v>631</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>635</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>636</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>637</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>638</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9909,34 +9921,34 @@
         <v>340</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G31" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="K31" s="3" t="s">
         <v>640</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>641</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>643</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9944,34 +9956,34 @@
         <v>267</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9979,34 +9991,34 @@
         <v>353</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>500</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -10029,19 +10041,19 @@
         <v>498</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -10049,34 +10061,34 @@
         <v>407</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10084,34 +10096,34 @@
         <v>429</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
@@ -10119,34 +10131,34 @@
         <v>445</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10154,34 +10166,34 @@
         <v>448</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -10189,34 +10201,34 @@
         <v>450</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="I39" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="J39" s="4" t="s">
         <v>671</v>
       </c>
-      <c r="J39" s="4" t="s">
-        <v>675</v>
-      </c>
       <c r="K39" s="3" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10224,34 +10236,34 @@
         <v>452</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G40" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="K40" s="3" t="s">
         <v>677</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>679</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>680</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -10259,34 +10271,34 @@
         <v>455</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>500</v>
       </c>
       <c r="I41" s="14" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="J41" s="13" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
@@ -10294,34 +10306,34 @@
         <v>459</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
@@ -10329,77 +10341,77 @@
         <v>477</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>498</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="H44" s="11" t="s">
         <v>500</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B45" s="28" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="C45" s="28"/>
       <c r="D45" s="3" t="s">
@@ -10410,24 +10422,24 @@
         <v>1</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="H45" s="16" t="s">
         <v>500</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>496</v>
@@ -10445,310 +10457,310 @@
         <v>498</v>
       </c>
       <c r="G46" s="11" t="s">
+        <v>702</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>703</v>
+      </c>
+      <c r="I46" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="J46" s="13" t="s">
+        <v>705</v>
+      </c>
+      <c r="K46" s="3" t="s">
         <v>706</v>
-      </c>
-      <c r="H46" s="11" t="s">
-        <v>707</v>
-      </c>
-      <c r="I46" s="13" t="s">
-        <v>708</v>
-      </c>
-      <c r="J46" s="13" t="s">
-        <v>709</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C47" s="11"/>
       <c r="D47" s="11" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="E47" s="11"/>
       <c r="F47" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G47" s="13" t="s">
+        <v>708</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>709</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>710</v>
+      </c>
+      <c r="J47" s="13" t="s">
+        <v>711</v>
+      </c>
+      <c r="K47" s="3" t="s">
         <v>712</v>
-      </c>
-      <c r="H47" s="11" t="s">
-        <v>713</v>
-      </c>
-      <c r="I47" s="11" t="s">
-        <v>714</v>
-      </c>
-      <c r="J47" s="13" t="s">
-        <v>715</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="E48" s="11"/>
       <c r="F48" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G48" s="13" t="s">
+        <v>714</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>715</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="J48" s="13" t="s">
+        <v>717</v>
+      </c>
+      <c r="K48" s="3" t="s">
         <v>718</v>
-      </c>
-      <c r="H48" s="11" t="s">
-        <v>719</v>
-      </c>
-      <c r="I48" s="5" t="s">
-        <v>720</v>
-      </c>
-      <c r="J48" s="13" t="s">
-        <v>721</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C49" s="11"/>
       <c r="D49" s="11" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="E49" s="11"/>
       <c r="F49" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G49" s="13" t="s">
+        <v>720</v>
+      </c>
+      <c r="H49" s="11" t="s">
+        <v>721</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="J49" s="13" t="s">
+        <v>723</v>
+      </c>
+      <c r="K49" s="3" t="s">
         <v>724</v>
-      </c>
-      <c r="H49" s="11" t="s">
-        <v>725</v>
-      </c>
-      <c r="I49" s="5" t="s">
-        <v>726</v>
-      </c>
-      <c r="J49" s="13" t="s">
-        <v>727</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F50" s="11" t="s">
         <v>498</v>
       </c>
       <c r="G50" s="13" t="s">
+        <v>726</v>
+      </c>
+      <c r="H50" s="13" t="s">
+        <v>727</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>728</v>
+      </c>
+      <c r="J50" s="13" t="s">
+        <v>729</v>
+      </c>
+      <c r="K50" s="3" t="s">
         <v>730</v>
-      </c>
-      <c r="H50" s="13" t="s">
-        <v>731</v>
-      </c>
-      <c r="I50" s="11" t="s">
-        <v>732</v>
-      </c>
-      <c r="J50" s="13" t="s">
-        <v>733</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F51" s="13" t="s">
         <v>498</v>
       </c>
       <c r="G51" s="24" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="H51" s="13" t="s">
         <v>500</v>
       </c>
       <c r="I51" s="13" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="J51" s="13" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F52" s="13" t="s">
         <v>498</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="H52" s="13" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="J52" s="13" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C53" s="11"/>
       <c r="D53" s="11" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="E53" s="11"/>
       <c r="F53" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="I53" s="13" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="J53" s="13" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="E54" s="11"/>
       <c r="F54" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="H54" s="11" t="s">
         <v>500</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
@@ -10756,38 +10768,38 @@
         <v>253</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C56" s="13"/>
       <c r="D56" s="11" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="E56" s="13"/>
       <c r="F56" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="C57" s="26"/>
       <c r="D57" s="3" t="s">
@@ -10798,182 +10810,182 @@
         <v>1</v>
       </c>
       <c r="G57" s="13" t="s">
+        <v>762</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>763</v>
+      </c>
+      <c r="I57" s="14" t="s">
+        <v>764</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="K57" s="3" t="s">
         <v>766</v>
-      </c>
-      <c r="H57" s="11" t="s">
-        <v>767</v>
-      </c>
-      <c r="I57" s="14" t="s">
-        <v>768</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="C58" s="19"/>
       <c r="D58" s="11" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E58" s="11"/>
       <c r="F58" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G58" s="13" t="s">
+        <v>769</v>
+      </c>
+      <c r="H58" s="13" t="s">
+        <v>770</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="J58" s="13" t="s">
+        <v>772</v>
+      </c>
+      <c r="K58" s="5" t="s">
         <v>773</v>
-      </c>
-      <c r="H58" s="13" t="s">
-        <v>774</v>
-      </c>
-      <c r="I58" s="5" t="s">
-        <v>775</v>
-      </c>
-      <c r="J58" s="13" t="s">
-        <v>776</v>
-      </c>
-      <c r="K58" s="5" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="C59" s="19"/>
       <c r="D59" s="11" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E59" s="11"/>
       <c r="F59" s="13" t="s">
         <v>1</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="H59" s="11" t="s">
         <v>505</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="J59" s="17" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="C60" s="19"/>
       <c r="D60" s="11" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E60" s="11"/>
       <c r="F60" s="13" t="s">
         <v>1</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="J60" s="13" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E61" s="11"/>
       <c r="F61" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="H61" s="11" t="s">
         <v>500</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="C62" s="11"/>
       <c r="D62" s="11" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E62" s="11"/>
       <c r="F62" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="18" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>497</v>
@@ -10982,27 +10994,27 @@
         <v>1</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="H63" s="19" t="s">
         <v>510</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="J63" s="19" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="19" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>497</v>
@@ -11011,27 +11023,27 @@
         <v>1</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="H64" s="19" t="s">
         <v>500</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="J64" s="19" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="19" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>497</v>
@@ -11040,27 +11052,27 @@
         <v>1</v>
       </c>
       <c r="G65" s="25" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="J65" s="19" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="19" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>497</v>
@@ -11069,27 +11081,27 @@
         <v>1</v>
       </c>
       <c r="G66" s="25" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="J66" s="19" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="19" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>497</v>
@@ -11098,27 +11110,27 @@
         <v>1</v>
       </c>
       <c r="G67" s="25" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="H67" s="19" t="s">
         <v>500</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="J67" s="19" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="19" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>497</v>
@@ -11127,19 +11139,19 @@
         <v>1</v>
       </c>
       <c r="G68" s="25" t="s">
+        <v>822</v>
+      </c>
+      <c r="H68" s="19" t="s">
+        <v>823</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>824</v>
+      </c>
+      <c r="J68" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="K68" s="3" t="s">
         <v>826</v>
-      </c>
-      <c r="H68" s="19" t="s">
-        <v>827</v>
-      </c>
-      <c r="I68" s="5" t="s">
-        <v>828</v>
-      </c>
-      <c r="J68" s="19" t="s">
-        <v>829</v>
-      </c>
-      <c r="K68" s="3" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -11147,34 +11159,34 @@
         <v>197</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="H69" s="31" t="s">
         <v>505</v>
       </c>
       <c r="I69" s="14" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="J69" s="32" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -11197,24 +11209,24 @@
         <v>498</v>
       </c>
       <c r="G70" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="H70" s="31" t="s">
+        <v>578</v>
+      </c>
+      <c r="I70" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="H70" s="31" t="s">
-        <v>582</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>525</v>
-      </c>
       <c r="J70" s="33" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>496</v>
@@ -11232,54 +11244,54 @@
         <v>498</v>
       </c>
       <c r="G71" s="46" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="H71" s="63" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="J71" s="33" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>497</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>498</v>
       </c>
       <c r="G72" s="71" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="H72" s="63" t="s">
         <v>510</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="J72" s="33" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="K72" s="72" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
     </row>
   </sheetData>
@@ -11340,7 +11352,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23" t="s">
@@ -11348,10 +11360,10 @@
       </c>
       <c r="D1" s="23"/>
       <c r="E1" s="23" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="G1" s="1"/>
     </row>
@@ -11374,7 +11386,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="20" t="s">
@@ -11382,16 +11394,16 @@
       </c>
       <c r="D3" s="20"/>
       <c r="E3" s="20" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20" t="s">
@@ -11399,46 +11411,46 @@
       </c>
       <c r="D4" s="20"/>
       <c r="E4" s="20" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
       <c r="D5" s="20"/>
       <c r="E5" s="20" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
       <c r="D6" s="20"/>
       <c r="E6" s="22" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
@@ -11449,7 +11461,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
@@ -11460,7 +11472,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
@@ -11471,7 +11483,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
@@ -11482,7 +11494,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
@@ -11493,7 +11505,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
@@ -11504,7 +11516,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
@@ -11515,7 +11527,7 @@
     </row>
     <row r="14" spans="1:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="27" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
@@ -11626,7 +11638,7 @@
     </row>
     <row r="13" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="42" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
@@ -11634,42 +11646,42 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="41" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="41" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="41" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="41" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -11694,79 +11706,79 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="82" t="s">
-        <v>848</v>
-      </c>
-      <c r="B28" s="80"/>
-      <c r="C28" s="80"/>
-      <c r="D28" s="80"/>
-      <c r="E28" s="80"/>
-      <c r="F28" s="80"/>
-      <c r="G28" s="80"/>
-      <c r="H28" s="80"/>
-      <c r="I28" s="80"/>
-      <c r="J28" s="80"/>
-      <c r="K28" s="80"/>
-      <c r="L28" s="80"/>
-      <c r="M28" s="80"/>
-      <c r="N28" s="80"/>
-      <c r="O28" s="80"/>
-      <c r="P28" s="80"/>
-      <c r="Q28" s="80"/>
+        <v>844</v>
+      </c>
+      <c r="B28" s="81"/>
+      <c r="C28" s="81"/>
+      <c r="D28" s="81"/>
+      <c r="E28" s="81"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="81"/>
+      <c r="H28" s="81"/>
+      <c r="I28" s="81"/>
+      <c r="J28" s="81"/>
+      <c r="K28" s="81"/>
+      <c r="L28" s="81"/>
+      <c r="M28" s="81"/>
+      <c r="N28" s="81"/>
+      <c r="O28" s="81"/>
+      <c r="P28" s="81"/>
+      <c r="Q28" s="81"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="80"/>
-      <c r="B29" s="80"/>
-      <c r="C29" s="80"/>
-      <c r="D29" s="80"/>
-      <c r="E29" s="80"/>
-      <c r="F29" s="80"/>
-      <c r="G29" s="80"/>
-      <c r="H29" s="80"/>
-      <c r="I29" s="80"/>
-      <c r="J29" s="80"/>
-      <c r="K29" s="80"/>
-      <c r="L29" s="80"/>
-      <c r="M29" s="80"/>
-      <c r="N29" s="80"/>
-      <c r="O29" s="80"/>
-      <c r="P29" s="80"/>
-      <c r="Q29" s="80"/>
+      <c r="A29" s="81"/>
+      <c r="B29" s="81"/>
+      <c r="C29" s="81"/>
+      <c r="D29" s="81"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="81"/>
+      <c r="G29" s="81"/>
+      <c r="H29" s="81"/>
+      <c r="I29" s="81"/>
+      <c r="J29" s="81"/>
+      <c r="K29" s="81"/>
+      <c r="L29" s="81"/>
+      <c r="M29" s="81"/>
+      <c r="N29" s="81"/>
+      <c r="O29" s="81"/>
+      <c r="P29" s="81"/>
+      <c r="Q29" s="81"/>
     </row>
     <row r="30" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="81" t="s">
+      <c r="A30" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="79" t="s">
+      <c r="B30" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="80"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="79" t="s">
+      <c r="C30" s="81"/>
+      <c r="D30" s="81"/>
+      <c r="E30" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="80"/>
-      <c r="G30" s="80"/>
-      <c r="H30" s="79" t="s">
+      <c r="F30" s="81"/>
+      <c r="G30" s="81"/>
+      <c r="H30" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="I30" s="80"/>
-      <c r="J30" s="80"/>
-      <c r="K30" s="79" t="s">
+      <c r="I30" s="81"/>
+      <c r="J30" s="81"/>
+      <c r="K30" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="L30" s="80"/>
-      <c r="M30" s="80"/>
-      <c r="N30" s="80"/>
-      <c r="O30" s="80"/>
-      <c r="P30" s="79" t="s">
+      <c r="L30" s="81"/>
+      <c r="M30" s="81"/>
+      <c r="N30" s="81"/>
+      <c r="O30" s="81"/>
+      <c r="P30" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="Q30" s="79" t="s">
+      <c r="Q30" s="80" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="80"/>
+      <c r="A31" s="81"/>
       <c r="B31" s="43" t="s">
         <v>27</v>
       </c>
@@ -11809,12 +11821,12 @@
       <c r="O31" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P31" s="80"/>
-      <c r="Q31" s="80"/>
+      <c r="P31" s="81"/>
+      <c r="Q31" s="81"/>
     </row>
     <row r="32" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="43" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="B32" s="43">
         <v>376</v>
@@ -11865,79 +11877,79 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="82" t="s">
-        <v>649</v>
-      </c>
-      <c r="B33" s="80"/>
-      <c r="C33" s="80"/>
-      <c r="D33" s="80"/>
-      <c r="E33" s="80"/>
-      <c r="F33" s="80"/>
-      <c r="G33" s="80"/>
-      <c r="H33" s="80"/>
-      <c r="I33" s="80"/>
-      <c r="J33" s="80"/>
-      <c r="K33" s="80"/>
-      <c r="L33" s="80"/>
-      <c r="M33" s="80"/>
-      <c r="N33" s="80"/>
-      <c r="O33" s="80"/>
-      <c r="P33" s="80"/>
-      <c r="Q33" s="80"/>
+        <v>645</v>
+      </c>
+      <c r="B33" s="81"/>
+      <c r="C33" s="81"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="81"/>
+      <c r="H33" s="81"/>
+      <c r="I33" s="81"/>
+      <c r="J33" s="81"/>
+      <c r="K33" s="81"/>
+      <c r="L33" s="81"/>
+      <c r="M33" s="81"/>
+      <c r="N33" s="81"/>
+      <c r="O33" s="81"/>
+      <c r="P33" s="81"/>
+      <c r="Q33" s="81"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="80"/>
-      <c r="B34" s="80"/>
-      <c r="C34" s="80"/>
-      <c r="D34" s="80"/>
-      <c r="E34" s="80"/>
-      <c r="F34" s="80"/>
-      <c r="G34" s="80"/>
-      <c r="H34" s="80"/>
-      <c r="I34" s="80"/>
-      <c r="J34" s="80"/>
-      <c r="K34" s="80"/>
-      <c r="L34" s="80"/>
-      <c r="M34" s="80"/>
-      <c r="N34" s="80"/>
-      <c r="O34" s="80"/>
-      <c r="P34" s="80"/>
-      <c r="Q34" s="80"/>
+      <c r="A34" s="81"/>
+      <c r="B34" s="81"/>
+      <c r="C34" s="81"/>
+      <c r="D34" s="81"/>
+      <c r="E34" s="81"/>
+      <c r="F34" s="81"/>
+      <c r="G34" s="81"/>
+      <c r="H34" s="81"/>
+      <c r="I34" s="81"/>
+      <c r="J34" s="81"/>
+      <c r="K34" s="81"/>
+      <c r="L34" s="81"/>
+      <c r="M34" s="81"/>
+      <c r="N34" s="81"/>
+      <c r="O34" s="81"/>
+      <c r="P34" s="81"/>
+      <c r="Q34" s="81"/>
     </row>
     <row r="35" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="81" t="s">
+      <c r="A35" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="79" t="s">
+      <c r="B35" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="80"/>
-      <c r="D35" s="80"/>
-      <c r="E35" s="79" t="s">
+      <c r="C35" s="81"/>
+      <c r="D35" s="81"/>
+      <c r="E35" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="F35" s="80"/>
-      <c r="G35" s="80"/>
-      <c r="H35" s="79" t="s">
+      <c r="F35" s="81"/>
+      <c r="G35" s="81"/>
+      <c r="H35" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="I35" s="80"/>
-      <c r="J35" s="80"/>
-      <c r="K35" s="79" t="s">
+      <c r="I35" s="81"/>
+      <c r="J35" s="81"/>
+      <c r="K35" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="80"/>
-      <c r="M35" s="80"/>
-      <c r="N35" s="80"/>
-      <c r="O35" s="80"/>
-      <c r="P35" s="79" t="s">
+      <c r="L35" s="81"/>
+      <c r="M35" s="81"/>
+      <c r="N35" s="81"/>
+      <c r="O35" s="81"/>
+      <c r="P35" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="Q35" s="79" t="s">
+      <c r="Q35" s="80" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="80"/>
+      <c r="A36" s="81"/>
       <c r="B36" s="43" t="s">
         <v>27</v>
       </c>
@@ -11980,12 +11992,12 @@
       <c r="O36" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P36" s="80"/>
-      <c r="Q36" s="80"/>
+      <c r="P36" s="81"/>
+      <c r="Q36" s="81"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="43" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="B37" s="43">
         <v>910</v>
@@ -12036,7 +12048,7 @@
     </row>
     <row r="38" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="43" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="B38" s="43">
         <v>919</v>
@@ -12138,7 +12150,7 @@
     </row>
     <row r="40" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="43" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="B40" s="43"/>
       <c r="C40" s="43"/>
@@ -12171,7 +12183,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="43" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="B41" s="43"/>
       <c r="C41" s="43"/>
@@ -12204,7 +12216,7 @@
     </row>
     <row r="42" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="46" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="B42" s="46">
         <v>376</v>
@@ -12247,7 +12259,7 @@
     </row>
     <row r="43" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="43" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="B43" s="43"/>
       <c r="C43" s="43"/>
@@ -12280,7 +12292,7 @@
     </row>
     <row r="44" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="43" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="B44" s="43"/>
       <c r="C44" s="43"/>
@@ -12313,7 +12325,7 @@
     </row>
     <row r="45" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="43" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="B45" s="43"/>
       <c r="C45" s="43"/>
@@ -12346,7 +12358,7 @@
     </row>
     <row r="46" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="43" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="B46" s="43"/>
       <c r="C46" s="43"/>
@@ -12379,7 +12391,7 @@
     </row>
     <row r="47" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="46" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="B47" s="46">
         <v>373</v>
@@ -12422,79 +12434,79 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="82" t="s">
-        <v>856</v>
-      </c>
-      <c r="B48" s="80"/>
-      <c r="C48" s="80"/>
-      <c r="D48" s="80"/>
-      <c r="E48" s="80"/>
-      <c r="F48" s="80"/>
-      <c r="G48" s="80"/>
-      <c r="H48" s="80"/>
-      <c r="I48" s="80"/>
-      <c r="J48" s="80"/>
-      <c r="K48" s="80"/>
-      <c r="L48" s="80"/>
-      <c r="M48" s="80"/>
-      <c r="N48" s="80"/>
-      <c r="O48" s="80"/>
-      <c r="P48" s="80"/>
-      <c r="Q48" s="80"/>
+        <v>852</v>
+      </c>
+      <c r="B48" s="81"/>
+      <c r="C48" s="81"/>
+      <c r="D48" s="81"/>
+      <c r="E48" s="81"/>
+      <c r="F48" s="81"/>
+      <c r="G48" s="81"/>
+      <c r="H48" s="81"/>
+      <c r="I48" s="81"/>
+      <c r="J48" s="81"/>
+      <c r="K48" s="81"/>
+      <c r="L48" s="81"/>
+      <c r="M48" s="81"/>
+      <c r="N48" s="81"/>
+      <c r="O48" s="81"/>
+      <c r="P48" s="81"/>
+      <c r="Q48" s="81"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="80"/>
-      <c r="B49" s="80"/>
-      <c r="C49" s="80"/>
-      <c r="D49" s="80"/>
-      <c r="E49" s="80"/>
-      <c r="F49" s="80"/>
-      <c r="G49" s="80"/>
-      <c r="H49" s="80"/>
-      <c r="I49" s="80"/>
-      <c r="J49" s="80"/>
-      <c r="K49" s="80"/>
-      <c r="L49" s="80"/>
-      <c r="M49" s="80"/>
-      <c r="N49" s="80"/>
-      <c r="O49" s="80"/>
-      <c r="P49" s="80"/>
-      <c r="Q49" s="80"/>
+      <c r="A49" s="81"/>
+      <c r="B49" s="81"/>
+      <c r="C49" s="81"/>
+      <c r="D49" s="81"/>
+      <c r="E49" s="81"/>
+      <c r="F49" s="81"/>
+      <c r="G49" s="81"/>
+      <c r="H49" s="81"/>
+      <c r="I49" s="81"/>
+      <c r="J49" s="81"/>
+      <c r="K49" s="81"/>
+      <c r="L49" s="81"/>
+      <c r="M49" s="81"/>
+      <c r="N49" s="81"/>
+      <c r="O49" s="81"/>
+      <c r="P49" s="81"/>
+      <c r="Q49" s="81"/>
     </row>
     <row r="50" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="81" t="s">
+      <c r="A50" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B50" s="79" t="s">
+      <c r="B50" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C50" s="80"/>
-      <c r="D50" s="80"/>
-      <c r="E50" s="79" t="s">
+      <c r="C50" s="81"/>
+      <c r="D50" s="81"/>
+      <c r="E50" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="F50" s="80"/>
-      <c r="G50" s="80"/>
-      <c r="H50" s="79" t="s">
+      <c r="F50" s="81"/>
+      <c r="G50" s="81"/>
+      <c r="H50" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="I50" s="80"/>
-      <c r="J50" s="80"/>
-      <c r="K50" s="79" t="s">
+      <c r="I50" s="81"/>
+      <c r="J50" s="81"/>
+      <c r="K50" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="80"/>
-      <c r="M50" s="80"/>
-      <c r="N50" s="80"/>
-      <c r="O50" s="80"/>
-      <c r="P50" s="79" t="s">
+      <c r="L50" s="81"/>
+      <c r="M50" s="81"/>
+      <c r="N50" s="81"/>
+      <c r="O50" s="81"/>
+      <c r="P50" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="Q50" s="79" t="s">
+      <c r="Q50" s="80" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51" s="80"/>
+      <c r="A51" s="81"/>
       <c r="B51" s="43" t="s">
         <v>27</v>
       </c>
@@ -12537,12 +12549,12 @@
       <c r="O51" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P51" s="80"/>
-      <c r="Q51" s="80"/>
+      <c r="P51" s="81"/>
+      <c r="Q51" s="81"/>
     </row>
     <row r="52" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="43" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="B52" s="43">
         <v>551</v>
@@ -12593,79 +12605,79 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="82" t="s">
-        <v>858</v>
-      </c>
-      <c r="B53" s="80"/>
-      <c r="C53" s="80"/>
-      <c r="D53" s="80"/>
-      <c r="E53" s="80"/>
-      <c r="F53" s="80"/>
-      <c r="G53" s="80"/>
-      <c r="H53" s="80"/>
-      <c r="I53" s="80"/>
-      <c r="J53" s="80"/>
-      <c r="K53" s="80"/>
-      <c r="L53" s="80"/>
-      <c r="M53" s="80"/>
-      <c r="N53" s="80"/>
-      <c r="O53" s="80"/>
-      <c r="P53" s="80"/>
-      <c r="Q53" s="80"/>
+        <v>854</v>
+      </c>
+      <c r="B53" s="81"/>
+      <c r="C53" s="81"/>
+      <c r="D53" s="81"/>
+      <c r="E53" s="81"/>
+      <c r="F53" s="81"/>
+      <c r="G53" s="81"/>
+      <c r="H53" s="81"/>
+      <c r="I53" s="81"/>
+      <c r="J53" s="81"/>
+      <c r="K53" s="81"/>
+      <c r="L53" s="81"/>
+      <c r="M53" s="81"/>
+      <c r="N53" s="81"/>
+      <c r="O53" s="81"/>
+      <c r="P53" s="81"/>
+      <c r="Q53" s="81"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="80"/>
-      <c r="B54" s="80"/>
-      <c r="C54" s="80"/>
-      <c r="D54" s="80"/>
-      <c r="E54" s="80"/>
-      <c r="F54" s="80"/>
-      <c r="G54" s="80"/>
-      <c r="H54" s="80"/>
-      <c r="I54" s="80"/>
-      <c r="J54" s="80"/>
-      <c r="K54" s="80"/>
-      <c r="L54" s="80"/>
-      <c r="M54" s="80"/>
-      <c r="N54" s="80"/>
-      <c r="O54" s="80"/>
-      <c r="P54" s="80"/>
-      <c r="Q54" s="80"/>
+      <c r="A54" s="81"/>
+      <c r="B54" s="81"/>
+      <c r="C54" s="81"/>
+      <c r="D54" s="81"/>
+      <c r="E54" s="81"/>
+      <c r="F54" s="81"/>
+      <c r="G54" s="81"/>
+      <c r="H54" s="81"/>
+      <c r="I54" s="81"/>
+      <c r="J54" s="81"/>
+      <c r="K54" s="81"/>
+      <c r="L54" s="81"/>
+      <c r="M54" s="81"/>
+      <c r="N54" s="81"/>
+      <c r="O54" s="81"/>
+      <c r="P54" s="81"/>
+      <c r="Q54" s="81"/>
     </row>
     <row r="55" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="81" t="s">
+      <c r="A55" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B55" s="79" t="s">
+      <c r="B55" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C55" s="80"/>
-      <c r="D55" s="80"/>
-      <c r="E55" s="79" t="s">
+      <c r="C55" s="81"/>
+      <c r="D55" s="81"/>
+      <c r="E55" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="F55" s="80"/>
-      <c r="G55" s="80"/>
-      <c r="H55" s="79" t="s">
+      <c r="F55" s="81"/>
+      <c r="G55" s="81"/>
+      <c r="H55" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="I55" s="80"/>
-      <c r="J55" s="80"/>
-      <c r="K55" s="79" t="s">
+      <c r="I55" s="81"/>
+      <c r="J55" s="81"/>
+      <c r="K55" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="L55" s="80"/>
-      <c r="M55" s="80"/>
-      <c r="N55" s="80"/>
-      <c r="O55" s="80"/>
-      <c r="P55" s="79" t="s">
+      <c r="L55" s="81"/>
+      <c r="M55" s="81"/>
+      <c r="N55" s="81"/>
+      <c r="O55" s="81"/>
+      <c r="P55" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="Q55" s="79" t="s">
+      <c r="Q55" s="80" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="80"/>
+      <c r="A56" s="81"/>
       <c r="B56" s="43" t="s">
         <v>27</v>
       </c>
@@ -12708,8 +12720,8 @@
       <c r="O56" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P56" s="80"/>
-      <c r="Q56" s="80"/>
+      <c r="P56" s="81"/>
+      <c r="Q56" s="81"/>
     </row>
     <row r="57" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="43" t="s">
@@ -12746,7 +12758,7 @@
     </row>
     <row r="58" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="43" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="B58" s="43"/>
       <c r="C58" s="43"/>
@@ -13175,7 +13187,7 @@
     </row>
     <row r="71" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="46" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B71" s="46">
         <v>2642</v>
@@ -13218,79 +13230,79 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="82" t="s">
-        <v>861</v>
-      </c>
-      <c r="B72" s="80"/>
-      <c r="C72" s="80"/>
-      <c r="D72" s="80"/>
-      <c r="E72" s="80"/>
-      <c r="F72" s="80"/>
-      <c r="G72" s="80"/>
-      <c r="H72" s="80"/>
-      <c r="I72" s="80"/>
-      <c r="J72" s="80"/>
-      <c r="K72" s="80"/>
-      <c r="L72" s="80"/>
-      <c r="M72" s="80"/>
-      <c r="N72" s="80"/>
-      <c r="O72" s="80"/>
-      <c r="P72" s="80"/>
-      <c r="Q72" s="80"/>
+        <v>857</v>
+      </c>
+      <c r="B72" s="81"/>
+      <c r="C72" s="81"/>
+      <c r="D72" s="81"/>
+      <c r="E72" s="81"/>
+      <c r="F72" s="81"/>
+      <c r="G72" s="81"/>
+      <c r="H72" s="81"/>
+      <c r="I72" s="81"/>
+      <c r="J72" s="81"/>
+      <c r="K72" s="81"/>
+      <c r="L72" s="81"/>
+      <c r="M72" s="81"/>
+      <c r="N72" s="81"/>
+      <c r="O72" s="81"/>
+      <c r="P72" s="81"/>
+      <c r="Q72" s="81"/>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A73" s="80"/>
-      <c r="B73" s="80"/>
-      <c r="C73" s="80"/>
-      <c r="D73" s="80"/>
-      <c r="E73" s="80"/>
-      <c r="F73" s="80"/>
-      <c r="G73" s="80"/>
-      <c r="H73" s="80"/>
-      <c r="I73" s="80"/>
-      <c r="J73" s="80"/>
-      <c r="K73" s="80"/>
-      <c r="L73" s="80"/>
-      <c r="M73" s="80"/>
-      <c r="N73" s="80"/>
-      <c r="O73" s="80"/>
-      <c r="P73" s="80"/>
-      <c r="Q73" s="80"/>
+      <c r="A73" s="81"/>
+      <c r="B73" s="81"/>
+      <c r="C73" s="81"/>
+      <c r="D73" s="81"/>
+      <c r="E73" s="81"/>
+      <c r="F73" s="81"/>
+      <c r="G73" s="81"/>
+      <c r="H73" s="81"/>
+      <c r="I73" s="81"/>
+      <c r="J73" s="81"/>
+      <c r="K73" s="81"/>
+      <c r="L73" s="81"/>
+      <c r="M73" s="81"/>
+      <c r="N73" s="81"/>
+      <c r="O73" s="81"/>
+      <c r="P73" s="81"/>
+      <c r="Q73" s="81"/>
     </row>
     <row r="74" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="81" t="s">
+      <c r="A74" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B74" s="79" t="s">
+      <c r="B74" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C74" s="80"/>
-      <c r="D74" s="80"/>
-      <c r="E74" s="79" t="s">
+      <c r="C74" s="81"/>
+      <c r="D74" s="81"/>
+      <c r="E74" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="F74" s="80"/>
-      <c r="G74" s="80"/>
-      <c r="H74" s="79" t="s">
+      <c r="F74" s="81"/>
+      <c r="G74" s="81"/>
+      <c r="H74" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="I74" s="80"/>
-      <c r="J74" s="80"/>
-      <c r="K74" s="79" t="s">
+      <c r="I74" s="81"/>
+      <c r="J74" s="81"/>
+      <c r="K74" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="L74" s="80"/>
-      <c r="M74" s="80"/>
-      <c r="N74" s="80"/>
-      <c r="O74" s="80"/>
-      <c r="P74" s="79" t="s">
+      <c r="L74" s="81"/>
+      <c r="M74" s="81"/>
+      <c r="N74" s="81"/>
+      <c r="O74" s="81"/>
+      <c r="P74" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="Q74" s="79" t="s">
+      <c r="Q74" s="80" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75" s="80"/>
+      <c r="A75" s="81"/>
       <c r="B75" s="43" t="s">
         <v>27</v>
       </c>
@@ -13333,8 +13345,8 @@
       <c r="O75" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P75" s="80"/>
-      <c r="Q75" s="80"/>
+      <c r="P75" s="81"/>
+      <c r="Q75" s="81"/>
     </row>
     <row r="76" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="43" t="s">
@@ -13470,7 +13482,7 @@
     </row>
     <row r="80" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="46" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="B80" s="46">
         <v>1680</v>
@@ -13513,79 +13525,79 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="82" t="s">
-        <v>863</v>
-      </c>
-      <c r="B81" s="80"/>
-      <c r="C81" s="80"/>
-      <c r="D81" s="80"/>
-      <c r="E81" s="80"/>
-      <c r="F81" s="80"/>
-      <c r="G81" s="80"/>
-      <c r="H81" s="80"/>
-      <c r="I81" s="80"/>
-      <c r="J81" s="80"/>
-      <c r="K81" s="80"/>
-      <c r="L81" s="80"/>
-      <c r="M81" s="80"/>
-      <c r="N81" s="80"/>
-      <c r="O81" s="80"/>
-      <c r="P81" s="80"/>
-      <c r="Q81" s="80"/>
+        <v>859</v>
+      </c>
+      <c r="B81" s="81"/>
+      <c r="C81" s="81"/>
+      <c r="D81" s="81"/>
+      <c r="E81" s="81"/>
+      <c r="F81" s="81"/>
+      <c r="G81" s="81"/>
+      <c r="H81" s="81"/>
+      <c r="I81" s="81"/>
+      <c r="J81" s="81"/>
+      <c r="K81" s="81"/>
+      <c r="L81" s="81"/>
+      <c r="M81" s="81"/>
+      <c r="N81" s="81"/>
+      <c r="O81" s="81"/>
+      <c r="P81" s="81"/>
+      <c r="Q81" s="81"/>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A82" s="80"/>
-      <c r="B82" s="80"/>
-      <c r="C82" s="80"/>
-      <c r="D82" s="80"/>
-      <c r="E82" s="80"/>
-      <c r="F82" s="80"/>
-      <c r="G82" s="80"/>
-      <c r="H82" s="80"/>
-      <c r="I82" s="80"/>
-      <c r="J82" s="80"/>
-      <c r="K82" s="80"/>
-      <c r="L82" s="80"/>
-      <c r="M82" s="80"/>
-      <c r="N82" s="80"/>
-      <c r="O82" s="80"/>
-      <c r="P82" s="80"/>
-      <c r="Q82" s="80"/>
+      <c r="A82" s="81"/>
+      <c r="B82" s="81"/>
+      <c r="C82" s="81"/>
+      <c r="D82" s="81"/>
+      <c r="E82" s="81"/>
+      <c r="F82" s="81"/>
+      <c r="G82" s="81"/>
+      <c r="H82" s="81"/>
+      <c r="I82" s="81"/>
+      <c r="J82" s="81"/>
+      <c r="K82" s="81"/>
+      <c r="L82" s="81"/>
+      <c r="M82" s="81"/>
+      <c r="N82" s="81"/>
+      <c r="O82" s="81"/>
+      <c r="P82" s="81"/>
+      <c r="Q82" s="81"/>
     </row>
     <row r="83" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="81" t="s">
+      <c r="A83" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B83" s="79" t="s">
+      <c r="B83" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C83" s="80"/>
-      <c r="D83" s="80"/>
-      <c r="E83" s="79" t="s">
+      <c r="C83" s="81"/>
+      <c r="D83" s="81"/>
+      <c r="E83" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="F83" s="80"/>
-      <c r="G83" s="80"/>
-      <c r="H83" s="79" t="s">
+      <c r="F83" s="81"/>
+      <c r="G83" s="81"/>
+      <c r="H83" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="I83" s="80"/>
-      <c r="J83" s="80"/>
-      <c r="K83" s="79" t="s">
+      <c r="I83" s="81"/>
+      <c r="J83" s="81"/>
+      <c r="K83" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="L83" s="80"/>
-      <c r="M83" s="80"/>
-      <c r="N83" s="80"/>
-      <c r="O83" s="80"/>
-      <c r="P83" s="79" t="s">
+      <c r="L83" s="81"/>
+      <c r="M83" s="81"/>
+      <c r="N83" s="81"/>
+      <c r="O83" s="81"/>
+      <c r="P83" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="Q83" s="79" t="s">
+      <c r="Q83" s="80" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A84" s="80"/>
+      <c r="A84" s="81"/>
       <c r="B84" s="43" t="s">
         <v>27</v>
       </c>
@@ -13628,12 +13640,12 @@
       <c r="O84" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P84" s="80"/>
-      <c r="Q84" s="80"/>
+      <c r="P84" s="81"/>
+      <c r="Q84" s="81"/>
     </row>
     <row r="85" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="43" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="B85" s="43"/>
       <c r="C85" s="43"/>
@@ -13666,7 +13678,7 @@
     </row>
     <row r="86" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="43" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="B86" s="43"/>
       <c r="C86" s="43"/>
@@ -13699,7 +13711,7 @@
     </row>
     <row r="87" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="43" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="B87" s="43"/>
       <c r="C87" s="43"/>
@@ -13732,7 +13744,7 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="43" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="B88" s="43"/>
       <c r="C88" s="43"/>
@@ -13765,7 +13777,7 @@
     </row>
     <row r="89" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="43" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="B89" s="43"/>
       <c r="C89" s="43"/>
@@ -13798,7 +13810,7 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="43" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="B90" s="43"/>
       <c r="C90" s="43"/>
@@ -13831,7 +13843,7 @@
     </row>
     <row r="91" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="43" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B91" s="43"/>
       <c r="C91" s="43"/>
@@ -13864,7 +13876,7 @@
     </row>
     <row r="92" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="46" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="B92" s="46">
         <v>1003</v>
@@ -13907,79 +13919,79 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="82" t="s">
-        <v>868</v>
-      </c>
-      <c r="B93" s="80"/>
-      <c r="C93" s="80"/>
-      <c r="D93" s="80"/>
-      <c r="E93" s="80"/>
-      <c r="F93" s="80"/>
-      <c r="G93" s="80"/>
-      <c r="H93" s="80"/>
-      <c r="I93" s="80"/>
-      <c r="J93" s="80"/>
-      <c r="K93" s="80"/>
-      <c r="L93" s="80"/>
-      <c r="M93" s="80"/>
-      <c r="N93" s="80"/>
-      <c r="O93" s="80"/>
-      <c r="P93" s="80"/>
-      <c r="Q93" s="80"/>
+        <v>864</v>
+      </c>
+      <c r="B93" s="81"/>
+      <c r="C93" s="81"/>
+      <c r="D93" s="81"/>
+      <c r="E93" s="81"/>
+      <c r="F93" s="81"/>
+      <c r="G93" s="81"/>
+      <c r="H93" s="81"/>
+      <c r="I93" s="81"/>
+      <c r="J93" s="81"/>
+      <c r="K93" s="81"/>
+      <c r="L93" s="81"/>
+      <c r="M93" s="81"/>
+      <c r="N93" s="81"/>
+      <c r="O93" s="81"/>
+      <c r="P93" s="81"/>
+      <c r="Q93" s="81"/>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A94" s="80"/>
-      <c r="B94" s="80"/>
-      <c r="C94" s="80"/>
-      <c r="D94" s="80"/>
-      <c r="E94" s="80"/>
-      <c r="F94" s="80"/>
-      <c r="G94" s="80"/>
-      <c r="H94" s="80"/>
-      <c r="I94" s="80"/>
-      <c r="J94" s="80"/>
-      <c r="K94" s="80"/>
-      <c r="L94" s="80"/>
-      <c r="M94" s="80"/>
-      <c r="N94" s="80"/>
-      <c r="O94" s="80"/>
-      <c r="P94" s="80"/>
-      <c r="Q94" s="80"/>
+      <c r="A94" s="81"/>
+      <c r="B94" s="81"/>
+      <c r="C94" s="81"/>
+      <c r="D94" s="81"/>
+      <c r="E94" s="81"/>
+      <c r="F94" s="81"/>
+      <c r="G94" s="81"/>
+      <c r="H94" s="81"/>
+      <c r="I94" s="81"/>
+      <c r="J94" s="81"/>
+      <c r="K94" s="81"/>
+      <c r="L94" s="81"/>
+      <c r="M94" s="81"/>
+      <c r="N94" s="81"/>
+      <c r="O94" s="81"/>
+      <c r="P94" s="81"/>
+      <c r="Q94" s="81"/>
     </row>
     <row r="95" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="81" t="s">
+      <c r="A95" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B95" s="79" t="s">
+      <c r="B95" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C95" s="80"/>
-      <c r="D95" s="80"/>
-      <c r="E95" s="79" t="s">
+      <c r="C95" s="81"/>
+      <c r="D95" s="81"/>
+      <c r="E95" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="F95" s="80"/>
-      <c r="G95" s="80"/>
-      <c r="H95" s="79" t="s">
+      <c r="F95" s="81"/>
+      <c r="G95" s="81"/>
+      <c r="H95" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="I95" s="80"/>
-      <c r="J95" s="80"/>
-      <c r="K95" s="79" t="s">
+      <c r="I95" s="81"/>
+      <c r="J95" s="81"/>
+      <c r="K95" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="L95" s="80"/>
-      <c r="M95" s="80"/>
-      <c r="N95" s="80"/>
-      <c r="O95" s="80"/>
-      <c r="P95" s="79" t="s">
+      <c r="L95" s="81"/>
+      <c r="M95" s="81"/>
+      <c r="N95" s="81"/>
+      <c r="O95" s="81"/>
+      <c r="P95" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="Q95" s="79" t="s">
+      <c r="Q95" s="80" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A96" s="80"/>
+      <c r="A96" s="81"/>
       <c r="B96" s="43" t="s">
         <v>27</v>
       </c>
@@ -14022,12 +14034,12 @@
       <c r="O96" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P96" s="80"/>
-      <c r="Q96" s="80"/>
+      <c r="P96" s="81"/>
+      <c r="Q96" s="81"/>
     </row>
     <row r="97" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="43" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="B97" s="43"/>
       <c r="C97" s="43"/>
@@ -14192,7 +14204,7 @@
     </row>
     <row r="102" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="43" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="B102" s="43"/>
       <c r="C102" s="43"/>
@@ -14225,7 +14237,7 @@
     </row>
     <row r="103" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="43" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="B103" s="43"/>
       <c r="C103" s="43"/>
@@ -14357,7 +14369,7 @@
     </row>
     <row r="107" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="43" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="B107" s="43"/>
       <c r="C107" s="43"/>
@@ -14423,7 +14435,7 @@
     </row>
     <row r="109" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="43" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="B109" s="43"/>
       <c r="C109" s="43"/>
@@ -14555,7 +14567,7 @@
     </row>
     <row r="113" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="43" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="B113" s="43"/>
       <c r="C113" s="43"/>
@@ -14588,7 +14600,7 @@
     </row>
     <row r="114" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="43" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="B114" s="43"/>
       <c r="C114" s="43"/>
@@ -14621,7 +14633,7 @@
     </row>
     <row r="115" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="43" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="B115" s="43"/>
       <c r="C115" s="43"/>
@@ -14654,7 +14666,7 @@
     </row>
     <row r="116" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="43" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="B116" s="43"/>
       <c r="C116" s="43"/>
@@ -14753,7 +14765,7 @@
     </row>
     <row r="119" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="43" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="B119" s="43"/>
       <c r="C119" s="43"/>
@@ -14786,7 +14798,7 @@
     </row>
     <row r="120" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="43" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="B120" s="43"/>
       <c r="C120" s="43"/>
@@ -14819,7 +14831,7 @@
     </row>
     <row r="121" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="43" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="B121" s="43"/>
       <c r="C121" s="43"/>
@@ -14852,7 +14864,7 @@
     </row>
     <row r="122" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="43" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="B122" s="43"/>
       <c r="C122" s="43"/>
@@ -14885,7 +14897,7 @@
     </row>
     <row r="123" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="43" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="B123" s="43"/>
       <c r="C123" s="43"/>
@@ -14918,7 +14930,7 @@
     </row>
     <row r="124" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="43" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="B124" s="43"/>
       <c r="C124" s="43"/>
@@ -14951,7 +14963,7 @@
     </row>
     <row r="125" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="43" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="B125" s="43"/>
       <c r="C125" s="43"/>
@@ -14984,7 +14996,7 @@
     </row>
     <row r="126" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="46" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="B126" s="46">
         <v>1390</v>
@@ -15027,79 +15039,79 @@
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="82" t="s">
-        <v>561</v>
-      </c>
-      <c r="B127" s="80"/>
-      <c r="C127" s="80"/>
-      <c r="D127" s="80"/>
-      <c r="E127" s="80"/>
-      <c r="F127" s="80"/>
-      <c r="G127" s="80"/>
-      <c r="H127" s="80"/>
-      <c r="I127" s="80"/>
-      <c r="J127" s="80"/>
-      <c r="K127" s="80"/>
-      <c r="L127" s="80"/>
-      <c r="M127" s="80"/>
-      <c r="N127" s="80"/>
-      <c r="O127" s="80"/>
-      <c r="P127" s="80"/>
-      <c r="Q127" s="80"/>
+        <v>557</v>
+      </c>
+      <c r="B127" s="81"/>
+      <c r="C127" s="81"/>
+      <c r="D127" s="81"/>
+      <c r="E127" s="81"/>
+      <c r="F127" s="81"/>
+      <c r="G127" s="81"/>
+      <c r="H127" s="81"/>
+      <c r="I127" s="81"/>
+      <c r="J127" s="81"/>
+      <c r="K127" s="81"/>
+      <c r="L127" s="81"/>
+      <c r="M127" s="81"/>
+      <c r="N127" s="81"/>
+      <c r="O127" s="81"/>
+      <c r="P127" s="81"/>
+      <c r="Q127" s="81"/>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A128" s="80"/>
-      <c r="B128" s="80"/>
-      <c r="C128" s="80"/>
-      <c r="D128" s="80"/>
-      <c r="E128" s="80"/>
-      <c r="F128" s="80"/>
-      <c r="G128" s="80"/>
-      <c r="H128" s="80"/>
-      <c r="I128" s="80"/>
-      <c r="J128" s="80"/>
-      <c r="K128" s="80"/>
-      <c r="L128" s="80"/>
-      <c r="M128" s="80"/>
-      <c r="N128" s="80"/>
-      <c r="O128" s="80"/>
-      <c r="P128" s="80"/>
-      <c r="Q128" s="80"/>
+      <c r="A128" s="81"/>
+      <c r="B128" s="81"/>
+      <c r="C128" s="81"/>
+      <c r="D128" s="81"/>
+      <c r="E128" s="81"/>
+      <c r="F128" s="81"/>
+      <c r="G128" s="81"/>
+      <c r="H128" s="81"/>
+      <c r="I128" s="81"/>
+      <c r="J128" s="81"/>
+      <c r="K128" s="81"/>
+      <c r="L128" s="81"/>
+      <c r="M128" s="81"/>
+      <c r="N128" s="81"/>
+      <c r="O128" s="81"/>
+      <c r="P128" s="81"/>
+      <c r="Q128" s="81"/>
     </row>
     <row r="129" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="81" t="s">
+      <c r="A129" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B129" s="79" t="s">
+      <c r="B129" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C129" s="80"/>
-      <c r="D129" s="80"/>
-      <c r="E129" s="79" t="s">
+      <c r="C129" s="81"/>
+      <c r="D129" s="81"/>
+      <c r="E129" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="F129" s="80"/>
-      <c r="G129" s="80"/>
-      <c r="H129" s="79" t="s">
+      <c r="F129" s="81"/>
+      <c r="G129" s="81"/>
+      <c r="H129" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="I129" s="80"/>
-      <c r="J129" s="80"/>
-      <c r="K129" s="79" t="s">
+      <c r="I129" s="81"/>
+      <c r="J129" s="81"/>
+      <c r="K129" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="L129" s="80"/>
-      <c r="M129" s="80"/>
-      <c r="N129" s="80"/>
-      <c r="O129" s="80"/>
-      <c r="P129" s="79" t="s">
+      <c r="L129" s="81"/>
+      <c r="M129" s="81"/>
+      <c r="N129" s="81"/>
+      <c r="O129" s="81"/>
+      <c r="P129" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="Q129" s="79" t="s">
+      <c r="Q129" s="80" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A130" s="80"/>
+      <c r="A130" s="81"/>
       <c r="B130" s="43" t="s">
         <v>27</v>
       </c>
@@ -15142,12 +15154,12 @@
       <c r="O130" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P130" s="80"/>
-      <c r="Q130" s="80"/>
+      <c r="P130" s="81"/>
+      <c r="Q130" s="81"/>
     </row>
     <row r="131" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="43" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="B131" s="43">
         <v>1114</v>
@@ -15198,7 +15210,7 @@
     </row>
     <row r="132" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="43" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="B132" s="43">
         <v>1114</v>
@@ -15249,7 +15261,7 @@
     </row>
     <row r="133" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="43" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="B133" s="43">
         <v>1114</v>
@@ -15300,7 +15312,7 @@
     </row>
     <row r="134" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="43" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="B134" s="43"/>
       <c r="C134" s="43"/>
@@ -15366,7 +15378,7 @@
     </row>
     <row r="136" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="43" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="B136" s="43"/>
       <c r="C136" s="43"/>
@@ -15399,7 +15411,7 @@
     </row>
     <row r="137" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="46" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="B137" s="46">
         <v>1114</v>
@@ -15442,7 +15454,7 @@
     </row>
     <row r="138" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="43" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="B138" s="43">
         <v>1114</v>
@@ -15493,7 +15505,7 @@
     </row>
     <row r="139" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="43" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="B139" s="43"/>
       <c r="C139" s="43"/>
@@ -15526,7 +15538,7 @@
     </row>
     <row r="140" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="43" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="B140" s="43"/>
       <c r="C140" s="43"/>
@@ -15559,7 +15571,7 @@
     </row>
     <row r="141" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="46" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="B141" s="46">
         <v>1114</v>
@@ -15602,7 +15614,7 @@
     </row>
     <row r="142" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="43" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="B142" s="43"/>
       <c r="C142" s="43"/>
@@ -15635,7 +15647,7 @@
     </row>
     <row r="143" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="43" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B143" s="43"/>
       <c r="C143" s="43"/>
@@ -15668,7 +15680,7 @@
     </row>
     <row r="144" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="46" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="B144" s="46">
         <v>1114</v>
@@ -15711,7 +15723,7 @@
     </row>
     <row r="145" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="43" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="B145" s="43"/>
       <c r="C145" s="43"/>
@@ -15744,7 +15756,7 @@
     </row>
     <row r="146" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="43" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="B146" s="43"/>
       <c r="C146" s="43"/>
@@ -15777,7 +15789,7 @@
     </row>
     <row r="147" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="46" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="B147" s="46">
         <v>1114</v>
@@ -15820,7 +15832,7 @@
     </row>
     <row r="148" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="43" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="B148" s="43">
         <v>1114</v>
@@ -15871,7 +15883,7 @@
     </row>
     <row r="149" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="43" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="B149" s="43"/>
       <c r="C149" s="43"/>
@@ -15904,7 +15916,7 @@
     </row>
     <row r="150" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="43" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="B150" s="43"/>
       <c r="C150" s="43"/>
@@ -15937,7 +15949,7 @@
     </row>
     <row r="151" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="46" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="B151" s="46">
         <v>1114</v>
@@ -15980,7 +15992,7 @@
     </row>
     <row r="152" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="43" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="B152" s="43">
         <v>1114</v>
@@ -16031,7 +16043,7 @@
     </row>
     <row r="153" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="43" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B153" s="43">
         <v>1114</v>
@@ -16082,7 +16094,7 @@
     </row>
     <row r="154" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="43" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="B154" s="43">
         <v>1114</v>
@@ -16133,7 +16145,7 @@
     </row>
     <row r="155" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="43" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B155" s="43"/>
       <c r="C155" s="43"/>
@@ -16166,7 +16178,7 @@
     </row>
     <row r="156" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="43" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B156" s="43"/>
       <c r="C156" s="43"/>
@@ -16199,7 +16211,7 @@
     </row>
     <row r="157" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="43" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="B157" s="43"/>
       <c r="C157" s="43"/>
@@ -16232,7 +16244,7 @@
     </row>
     <row r="158" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="46" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="B158" s="46">
         <v>1114</v>
@@ -16277,77 +16289,77 @@
       <c r="A159" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="B159" s="80"/>
-      <c r="C159" s="80"/>
-      <c r="D159" s="80"/>
-      <c r="E159" s="80"/>
-      <c r="F159" s="80"/>
-      <c r="G159" s="80"/>
-      <c r="H159" s="80"/>
-      <c r="I159" s="80"/>
-      <c r="J159" s="80"/>
-      <c r="K159" s="80"/>
-      <c r="L159" s="80"/>
-      <c r="M159" s="80"/>
-      <c r="N159" s="80"/>
-      <c r="O159" s="80"/>
-      <c r="P159" s="80"/>
-      <c r="Q159" s="80"/>
+      <c r="B159" s="81"/>
+      <c r="C159" s="81"/>
+      <c r="D159" s="81"/>
+      <c r="E159" s="81"/>
+      <c r="F159" s="81"/>
+      <c r="G159" s="81"/>
+      <c r="H159" s="81"/>
+      <c r="I159" s="81"/>
+      <c r="J159" s="81"/>
+      <c r="K159" s="81"/>
+      <c r="L159" s="81"/>
+      <c r="M159" s="81"/>
+      <c r="N159" s="81"/>
+      <c r="O159" s="81"/>
+      <c r="P159" s="81"/>
+      <c r="Q159" s="81"/>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A160" s="80"/>
-      <c r="B160" s="80"/>
-      <c r="C160" s="80"/>
-      <c r="D160" s="80"/>
-      <c r="E160" s="80"/>
-      <c r="F160" s="80"/>
-      <c r="G160" s="80"/>
-      <c r="H160" s="80"/>
-      <c r="I160" s="80"/>
-      <c r="J160" s="80"/>
-      <c r="K160" s="80"/>
-      <c r="L160" s="80"/>
-      <c r="M160" s="80"/>
-      <c r="N160" s="80"/>
-      <c r="O160" s="80"/>
-      <c r="P160" s="80"/>
-      <c r="Q160" s="80"/>
+      <c r="A160" s="81"/>
+      <c r="B160" s="81"/>
+      <c r="C160" s="81"/>
+      <c r="D160" s="81"/>
+      <c r="E160" s="81"/>
+      <c r="F160" s="81"/>
+      <c r="G160" s="81"/>
+      <c r="H160" s="81"/>
+      <c r="I160" s="81"/>
+      <c r="J160" s="81"/>
+      <c r="K160" s="81"/>
+      <c r="L160" s="81"/>
+      <c r="M160" s="81"/>
+      <c r="N160" s="81"/>
+      <c r="O160" s="81"/>
+      <c r="P160" s="81"/>
+      <c r="Q160" s="81"/>
     </row>
     <row r="161" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="81" t="s">
+      <c r="A161" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B161" s="79" t="s">
+      <c r="B161" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C161" s="80"/>
-      <c r="D161" s="80"/>
-      <c r="E161" s="79" t="s">
+      <c r="C161" s="81"/>
+      <c r="D161" s="81"/>
+      <c r="E161" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="F161" s="80"/>
-      <c r="G161" s="80"/>
-      <c r="H161" s="79" t="s">
+      <c r="F161" s="81"/>
+      <c r="G161" s="81"/>
+      <c r="H161" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="I161" s="80"/>
-      <c r="J161" s="80"/>
-      <c r="K161" s="79" t="s">
+      <c r="I161" s="81"/>
+      <c r="J161" s="81"/>
+      <c r="K161" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="L161" s="80"/>
-      <c r="M161" s="80"/>
-      <c r="N161" s="80"/>
-      <c r="O161" s="80"/>
-      <c r="P161" s="79" t="s">
+      <c r="L161" s="81"/>
+      <c r="M161" s="81"/>
+      <c r="N161" s="81"/>
+      <c r="O161" s="81"/>
+      <c r="P161" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="Q161" s="79" t="s">
+      <c r="Q161" s="80" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A162" s="80"/>
+      <c r="A162" s="81"/>
       <c r="B162" s="43" t="s">
         <v>27</v>
       </c>
@@ -16390,8 +16402,8 @@
       <c r="O162" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P162" s="80"/>
-      <c r="Q162" s="80"/>
+      <c r="P162" s="81"/>
+      <c r="Q162" s="81"/>
     </row>
     <row r="163" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="43" t="s">
@@ -16448,77 +16460,77 @@
       <c r="A164" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="B164" s="80"/>
-      <c r="C164" s="80"/>
-      <c r="D164" s="80"/>
-      <c r="E164" s="80"/>
-      <c r="F164" s="80"/>
-      <c r="G164" s="80"/>
-      <c r="H164" s="80"/>
-      <c r="I164" s="80"/>
-      <c r="J164" s="80"/>
-      <c r="K164" s="80"/>
-      <c r="L164" s="80"/>
-      <c r="M164" s="80"/>
-      <c r="N164" s="80"/>
-      <c r="O164" s="80"/>
-      <c r="P164" s="80"/>
-      <c r="Q164" s="80"/>
+      <c r="B164" s="81"/>
+      <c r="C164" s="81"/>
+      <c r="D164" s="81"/>
+      <c r="E164" s="81"/>
+      <c r="F164" s="81"/>
+      <c r="G164" s="81"/>
+      <c r="H164" s="81"/>
+      <c r="I164" s="81"/>
+      <c r="J164" s="81"/>
+      <c r="K164" s="81"/>
+      <c r="L164" s="81"/>
+      <c r="M164" s="81"/>
+      <c r="N164" s="81"/>
+      <c r="O164" s="81"/>
+      <c r="P164" s="81"/>
+      <c r="Q164" s="81"/>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A165" s="80"/>
-      <c r="B165" s="80"/>
-      <c r="C165" s="80"/>
-      <c r="D165" s="80"/>
-      <c r="E165" s="80"/>
-      <c r="F165" s="80"/>
-      <c r="G165" s="80"/>
-      <c r="H165" s="80"/>
-      <c r="I165" s="80"/>
-      <c r="J165" s="80"/>
-      <c r="K165" s="80"/>
-      <c r="L165" s="80"/>
-      <c r="M165" s="80"/>
-      <c r="N165" s="80"/>
-      <c r="O165" s="80"/>
-      <c r="P165" s="80"/>
-      <c r="Q165" s="80"/>
+      <c r="A165" s="81"/>
+      <c r="B165" s="81"/>
+      <c r="C165" s="81"/>
+      <c r="D165" s="81"/>
+      <c r="E165" s="81"/>
+      <c r="F165" s="81"/>
+      <c r="G165" s="81"/>
+      <c r="H165" s="81"/>
+      <c r="I165" s="81"/>
+      <c r="J165" s="81"/>
+      <c r="K165" s="81"/>
+      <c r="L165" s="81"/>
+      <c r="M165" s="81"/>
+      <c r="N165" s="81"/>
+      <c r="O165" s="81"/>
+      <c r="P165" s="81"/>
+      <c r="Q165" s="81"/>
     </row>
     <row r="166" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="81" t="s">
+      <c r="A166" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B166" s="79" t="s">
+      <c r="B166" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C166" s="80"/>
-      <c r="D166" s="80"/>
-      <c r="E166" s="79" t="s">
+      <c r="C166" s="81"/>
+      <c r="D166" s="81"/>
+      <c r="E166" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="F166" s="80"/>
-      <c r="G166" s="80"/>
-      <c r="H166" s="79" t="s">
+      <c r="F166" s="81"/>
+      <c r="G166" s="81"/>
+      <c r="H166" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="I166" s="80"/>
-      <c r="J166" s="80"/>
-      <c r="K166" s="79" t="s">
+      <c r="I166" s="81"/>
+      <c r="J166" s="81"/>
+      <c r="K166" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="L166" s="80"/>
-      <c r="M166" s="80"/>
-      <c r="N166" s="80"/>
-      <c r="O166" s="80"/>
-      <c r="P166" s="79" t="s">
+      <c r="L166" s="81"/>
+      <c r="M166" s="81"/>
+      <c r="N166" s="81"/>
+      <c r="O166" s="81"/>
+      <c r="P166" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="Q166" s="79" t="s">
+      <c r="Q166" s="80" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A167" s="80"/>
+      <c r="A167" s="81"/>
       <c r="B167" s="43" t="s">
         <v>27</v>
       </c>
@@ -16561,12 +16573,12 @@
       <c r="O167" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P167" s="80"/>
-      <c r="Q167" s="80"/>
+      <c r="P167" s="81"/>
+      <c r="Q167" s="81"/>
     </row>
     <row r="168" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="43" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="B168" s="43"/>
       <c r="C168" s="43"/>
@@ -16698,7 +16710,7 @@
     </row>
     <row r="172" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="46" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B172" s="46">
         <v>728</v>
@@ -16741,6 +16753,70 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="K166:O166"/>
+    <mergeCell ref="H74:J74"/>
+    <mergeCell ref="H83:J83"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="Q50:Q51"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="P74:P75"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="K129:O129"/>
+    <mergeCell ref="P95:P96"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A81:Q82"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B129:D129"/>
+    <mergeCell ref="Q166:Q167"/>
+    <mergeCell ref="Q35:Q36"/>
+    <mergeCell ref="P161:P162"/>
+    <mergeCell ref="A159:Q160"/>
+    <mergeCell ref="A93:Q94"/>
+    <mergeCell ref="Q161:Q162"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="P83:P84"/>
+    <mergeCell ref="Q129:Q130"/>
+    <mergeCell ref="Q95:Q96"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="H55:J55"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="P55:P56"/>
+    <mergeCell ref="B161:D161"/>
+    <mergeCell ref="P129:P130"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="K74:O74"/>
+    <mergeCell ref="K83:O83"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="A129:A130"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="H166:J166"/>
+    <mergeCell ref="E129:G129"/>
+    <mergeCell ref="H161:J161"/>
+    <mergeCell ref="H129:J129"/>
+    <mergeCell ref="E74:G74"/>
+    <mergeCell ref="E166:G166"/>
+    <mergeCell ref="K95:O95"/>
+    <mergeCell ref="A28:Q29"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A48:Q49"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="Q55:Q56"/>
+    <mergeCell ref="P50:P51"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="Q74:Q75"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="Q83:Q84"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="K35:O35"/>
+    <mergeCell ref="Q30:Q31"/>
+    <mergeCell ref="K50:O50"/>
     <mergeCell ref="P35:P36"/>
     <mergeCell ref="E161:G161"/>
     <mergeCell ref="K30:O30"/>
@@ -16757,70 +16833,6 @@
     <mergeCell ref="A127:Q128"/>
     <mergeCell ref="K161:O161"/>
     <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A28:Q29"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A48:Q49"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="Q55:Q56"/>
-    <mergeCell ref="P50:P51"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="Q74:Q75"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="P30:P31"/>
-    <mergeCell ref="Q83:Q84"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="K35:O35"/>
-    <mergeCell ref="Q30:Q31"/>
-    <mergeCell ref="K50:O50"/>
-    <mergeCell ref="B161:D161"/>
-    <mergeCell ref="P129:P130"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="K74:O74"/>
-    <mergeCell ref="K83:O83"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="A129:A130"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="H166:J166"/>
-    <mergeCell ref="E129:G129"/>
-    <mergeCell ref="H161:J161"/>
-    <mergeCell ref="H129:J129"/>
-    <mergeCell ref="E74:G74"/>
-    <mergeCell ref="E166:G166"/>
-    <mergeCell ref="K95:O95"/>
-    <mergeCell ref="Q166:Q167"/>
-    <mergeCell ref="Q35:Q36"/>
-    <mergeCell ref="P161:P162"/>
-    <mergeCell ref="A159:Q160"/>
-    <mergeCell ref="A93:Q94"/>
-    <mergeCell ref="Q161:Q162"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="P83:P84"/>
-    <mergeCell ref="Q129:Q130"/>
-    <mergeCell ref="Q95:Q96"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="H55:J55"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="K166:O166"/>
-    <mergeCell ref="H74:J74"/>
-    <mergeCell ref="H83:J83"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="Q50:Q51"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="P74:P75"/>
-    <mergeCell ref="E55:G55"/>
-    <mergeCell ref="K129:O129"/>
-    <mergeCell ref="P95:P96"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A81:Q82"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B129:D129"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.scei-concours.fr/stat2025/bcpst.html" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -16959,77 +16971,77 @@
       <c r="A24" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="80"/>
-      <c r="C24" s="80"/>
-      <c r="D24" s="80"/>
-      <c r="E24" s="80"/>
-      <c r="F24" s="80"/>
-      <c r="G24" s="80"/>
-      <c r="H24" s="80"/>
-      <c r="I24" s="80"/>
-      <c r="J24" s="80"/>
-      <c r="K24" s="80"/>
-      <c r="L24" s="80"/>
-      <c r="M24" s="80"/>
-      <c r="N24" s="80"/>
-      <c r="O24" s="80"/>
-      <c r="P24" s="80"/>
-      <c r="Q24" s="80"/>
+      <c r="B24" s="81"/>
+      <c r="C24" s="81"/>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="81"/>
+      <c r="H24" s="81"/>
+      <c r="I24" s="81"/>
+      <c r="J24" s="81"/>
+      <c r="K24" s="81"/>
+      <c r="L24" s="81"/>
+      <c r="M24" s="81"/>
+      <c r="N24" s="81"/>
+      <c r="O24" s="81"/>
+      <c r="P24" s="81"/>
+      <c r="Q24" s="81"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="80"/>
-      <c r="B25" s="80"/>
-      <c r="C25" s="80"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="80"/>
-      <c r="G25" s="80"/>
-      <c r="H25" s="80"/>
-      <c r="I25" s="80"/>
-      <c r="J25" s="80"/>
-      <c r="K25" s="80"/>
-      <c r="L25" s="80"/>
-      <c r="M25" s="80"/>
-      <c r="N25" s="80"/>
-      <c r="O25" s="80"/>
-      <c r="P25" s="80"/>
-      <c r="Q25" s="80"/>
+      <c r="A25" s="81"/>
+      <c r="B25" s="81"/>
+      <c r="C25" s="81"/>
+      <c r="D25" s="81"/>
+      <c r="E25" s="81"/>
+      <c r="F25" s="81"/>
+      <c r="G25" s="81"/>
+      <c r="H25" s="81"/>
+      <c r="I25" s="81"/>
+      <c r="J25" s="81"/>
+      <c r="K25" s="81"/>
+      <c r="L25" s="81"/>
+      <c r="M25" s="81"/>
+      <c r="N25" s="81"/>
+      <c r="O25" s="81"/>
+      <c r="P25" s="81"/>
+      <c r="Q25" s="81"/>
     </row>
     <row r="26" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="81" t="s">
+      <c r="A26" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="79" t="s">
+      <c r="B26" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="80"/>
-      <c r="D26" s="80"/>
-      <c r="E26" s="79" t="s">
+      <c r="C26" s="81"/>
+      <c r="D26" s="81"/>
+      <c r="E26" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="80"/>
-      <c r="G26" s="80"/>
-      <c r="H26" s="79" t="s">
+      <c r="F26" s="81"/>
+      <c r="G26" s="81"/>
+      <c r="H26" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="I26" s="80"/>
-      <c r="J26" s="80"/>
-      <c r="K26" s="79" t="s">
+      <c r="I26" s="81"/>
+      <c r="J26" s="81"/>
+      <c r="K26" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="L26" s="80"/>
-      <c r="M26" s="80"/>
-      <c r="N26" s="80"/>
-      <c r="O26" s="80"/>
-      <c r="P26" s="79" t="s">
+      <c r="L26" s="81"/>
+      <c r="M26" s="81"/>
+      <c r="N26" s="81"/>
+      <c r="O26" s="81"/>
+      <c r="P26" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="Q26" s="79" t="s">
+      <c r="Q26" s="80" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="80"/>
+      <c r="A27" s="81"/>
       <c r="B27" s="43" t="s">
         <v>27</v>
       </c>
@@ -17072,8 +17084,8 @@
       <c r="O27" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P27" s="80"/>
-      <c r="Q27" s="80"/>
+      <c r="P27" s="81"/>
+      <c r="Q27" s="81"/>
     </row>
     <row r="28" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="43" t="s">
@@ -17584,77 +17596,77 @@
       <c r="A43" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="80"/>
-      <c r="C43" s="80"/>
-      <c r="D43" s="80"/>
-      <c r="E43" s="80"/>
-      <c r="F43" s="80"/>
-      <c r="G43" s="80"/>
-      <c r="H43" s="80"/>
-      <c r="I43" s="80"/>
-      <c r="J43" s="80"/>
-      <c r="K43" s="80"/>
-      <c r="L43" s="80"/>
-      <c r="M43" s="80"/>
-      <c r="N43" s="80"/>
-      <c r="O43" s="80"/>
-      <c r="P43" s="80"/>
-      <c r="Q43" s="80"/>
+      <c r="B43" s="81"/>
+      <c r="C43" s="81"/>
+      <c r="D43" s="81"/>
+      <c r="E43" s="81"/>
+      <c r="F43" s="81"/>
+      <c r="G43" s="81"/>
+      <c r="H43" s="81"/>
+      <c r="I43" s="81"/>
+      <c r="J43" s="81"/>
+      <c r="K43" s="81"/>
+      <c r="L43" s="81"/>
+      <c r="M43" s="81"/>
+      <c r="N43" s="81"/>
+      <c r="O43" s="81"/>
+      <c r="P43" s="81"/>
+      <c r="Q43" s="81"/>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="80"/>
-      <c r="B44" s="80"/>
-      <c r="C44" s="80"/>
-      <c r="D44" s="80"/>
-      <c r="E44" s="80"/>
-      <c r="F44" s="80"/>
-      <c r="G44" s="80"/>
-      <c r="H44" s="80"/>
-      <c r="I44" s="80"/>
-      <c r="J44" s="80"/>
-      <c r="K44" s="80"/>
-      <c r="L44" s="80"/>
-      <c r="M44" s="80"/>
-      <c r="N44" s="80"/>
-      <c r="O44" s="80"/>
-      <c r="P44" s="80"/>
-      <c r="Q44" s="80"/>
+      <c r="A44" s="81"/>
+      <c r="B44" s="81"/>
+      <c r="C44" s="81"/>
+      <c r="D44" s="81"/>
+      <c r="E44" s="81"/>
+      <c r="F44" s="81"/>
+      <c r="G44" s="81"/>
+      <c r="H44" s="81"/>
+      <c r="I44" s="81"/>
+      <c r="J44" s="81"/>
+      <c r="K44" s="81"/>
+      <c r="L44" s="81"/>
+      <c r="M44" s="81"/>
+      <c r="N44" s="81"/>
+      <c r="O44" s="81"/>
+      <c r="P44" s="81"/>
+      <c r="Q44" s="81"/>
     </row>
     <row r="45" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="81" t="s">
+      <c r="A45" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="79" t="s">
+      <c r="B45" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="80"/>
-      <c r="D45" s="80"/>
-      <c r="E45" s="79" t="s">
+      <c r="C45" s="81"/>
+      <c r="D45" s="81"/>
+      <c r="E45" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="F45" s="80"/>
-      <c r="G45" s="80"/>
-      <c r="H45" s="79" t="s">
+      <c r="F45" s="81"/>
+      <c r="G45" s="81"/>
+      <c r="H45" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="I45" s="80"/>
-      <c r="J45" s="80"/>
-      <c r="K45" s="79" t="s">
+      <c r="I45" s="81"/>
+      <c r="J45" s="81"/>
+      <c r="K45" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="80"/>
-      <c r="M45" s="80"/>
-      <c r="N45" s="80"/>
-      <c r="O45" s="80"/>
-      <c r="P45" s="79" t="s">
+      <c r="L45" s="81"/>
+      <c r="M45" s="81"/>
+      <c r="N45" s="81"/>
+      <c r="O45" s="81"/>
+      <c r="P45" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="Q45" s="79" t="s">
+      <c r="Q45" s="80" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" s="80"/>
+      <c r="A46" s="81"/>
       <c r="B46" s="43" t="s">
         <v>27</v>
       </c>
@@ -17697,8 +17709,8 @@
       <c r="O46" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P46" s="80"/>
-      <c r="Q46" s="80"/>
+      <c r="P46" s="81"/>
+      <c r="Q46" s="81"/>
     </row>
     <row r="47" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="43" t="s">
@@ -17755,77 +17767,77 @@
       <c r="A48" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="80"/>
-      <c r="C48" s="80"/>
-      <c r="D48" s="80"/>
-      <c r="E48" s="80"/>
-      <c r="F48" s="80"/>
-      <c r="G48" s="80"/>
-      <c r="H48" s="80"/>
-      <c r="I48" s="80"/>
-      <c r="J48" s="80"/>
-      <c r="K48" s="80"/>
-      <c r="L48" s="80"/>
-      <c r="M48" s="80"/>
-      <c r="N48" s="80"/>
-      <c r="O48" s="80"/>
-      <c r="P48" s="80"/>
-      <c r="Q48" s="80"/>
+      <c r="B48" s="81"/>
+      <c r="C48" s="81"/>
+      <c r="D48" s="81"/>
+      <c r="E48" s="81"/>
+      <c r="F48" s="81"/>
+      <c r="G48" s="81"/>
+      <c r="H48" s="81"/>
+      <c r="I48" s="81"/>
+      <c r="J48" s="81"/>
+      <c r="K48" s="81"/>
+      <c r="L48" s="81"/>
+      <c r="M48" s="81"/>
+      <c r="N48" s="81"/>
+      <c r="O48" s="81"/>
+      <c r="P48" s="81"/>
+      <c r="Q48" s="81"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="80"/>
-      <c r="B49" s="80"/>
-      <c r="C49" s="80"/>
-      <c r="D49" s="80"/>
-      <c r="E49" s="80"/>
-      <c r="F49" s="80"/>
-      <c r="G49" s="80"/>
-      <c r="H49" s="80"/>
-      <c r="I49" s="80"/>
-      <c r="J49" s="80"/>
-      <c r="K49" s="80"/>
-      <c r="L49" s="80"/>
-      <c r="M49" s="80"/>
-      <c r="N49" s="80"/>
-      <c r="O49" s="80"/>
-      <c r="P49" s="80"/>
-      <c r="Q49" s="80"/>
+      <c r="A49" s="81"/>
+      <c r="B49" s="81"/>
+      <c r="C49" s="81"/>
+      <c r="D49" s="81"/>
+      <c r="E49" s="81"/>
+      <c r="F49" s="81"/>
+      <c r="G49" s="81"/>
+      <c r="H49" s="81"/>
+      <c r="I49" s="81"/>
+      <c r="J49" s="81"/>
+      <c r="K49" s="81"/>
+      <c r="L49" s="81"/>
+      <c r="M49" s="81"/>
+      <c r="N49" s="81"/>
+      <c r="O49" s="81"/>
+      <c r="P49" s="81"/>
+      <c r="Q49" s="81"/>
     </row>
     <row r="50" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="81" t="s">
+      <c r="A50" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B50" s="79" t="s">
+      <c r="B50" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C50" s="80"/>
-      <c r="D50" s="80"/>
-      <c r="E50" s="79" t="s">
+      <c r="C50" s="81"/>
+      <c r="D50" s="81"/>
+      <c r="E50" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="F50" s="80"/>
-      <c r="G50" s="80"/>
-      <c r="H50" s="79" t="s">
+      <c r="F50" s="81"/>
+      <c r="G50" s="81"/>
+      <c r="H50" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="I50" s="80"/>
-      <c r="J50" s="80"/>
-      <c r="K50" s="79" t="s">
+      <c r="I50" s="81"/>
+      <c r="J50" s="81"/>
+      <c r="K50" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="80"/>
-      <c r="M50" s="80"/>
-      <c r="N50" s="80"/>
-      <c r="O50" s="80"/>
-      <c r="P50" s="79" t="s">
+      <c r="L50" s="81"/>
+      <c r="M50" s="81"/>
+      <c r="N50" s="81"/>
+      <c r="O50" s="81"/>
+      <c r="P50" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="Q50" s="79" t="s">
+      <c r="Q50" s="80" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51" s="80"/>
+      <c r="A51" s="81"/>
       <c r="B51" s="43" t="s">
         <v>27</v>
       </c>
@@ -17868,8 +17880,8 @@
       <c r="O51" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P51" s="80"/>
-      <c r="Q51" s="80"/>
+      <c r="P51" s="81"/>
+      <c r="Q51" s="81"/>
     </row>
     <row r="52" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="43" t="s">
@@ -18050,77 +18062,77 @@
       <c r="A57" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="B57" s="80"/>
-      <c r="C57" s="80"/>
-      <c r="D57" s="80"/>
-      <c r="E57" s="80"/>
-      <c r="F57" s="80"/>
-      <c r="G57" s="80"/>
-      <c r="H57" s="80"/>
-      <c r="I57" s="80"/>
-      <c r="J57" s="80"/>
-      <c r="K57" s="80"/>
-      <c r="L57" s="80"/>
-      <c r="M57" s="80"/>
-      <c r="N57" s="80"/>
-      <c r="O57" s="80"/>
-      <c r="P57" s="80"/>
-      <c r="Q57" s="80"/>
+      <c r="B57" s="81"/>
+      <c r="C57" s="81"/>
+      <c r="D57" s="81"/>
+      <c r="E57" s="81"/>
+      <c r="F57" s="81"/>
+      <c r="G57" s="81"/>
+      <c r="H57" s="81"/>
+      <c r="I57" s="81"/>
+      <c r="J57" s="81"/>
+      <c r="K57" s="81"/>
+      <c r="L57" s="81"/>
+      <c r="M57" s="81"/>
+      <c r="N57" s="81"/>
+      <c r="O57" s="81"/>
+      <c r="P57" s="81"/>
+      <c r="Q57" s="81"/>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A58" s="80"/>
-      <c r="B58" s="80"/>
-      <c r="C58" s="80"/>
-      <c r="D58" s="80"/>
-      <c r="E58" s="80"/>
-      <c r="F58" s="80"/>
-      <c r="G58" s="80"/>
-      <c r="H58" s="80"/>
-      <c r="I58" s="80"/>
-      <c r="J58" s="80"/>
-      <c r="K58" s="80"/>
-      <c r="L58" s="80"/>
-      <c r="M58" s="80"/>
-      <c r="N58" s="80"/>
-      <c r="O58" s="80"/>
-      <c r="P58" s="80"/>
-      <c r="Q58" s="80"/>
+      <c r="A58" s="81"/>
+      <c r="B58" s="81"/>
+      <c r="C58" s="81"/>
+      <c r="D58" s="81"/>
+      <c r="E58" s="81"/>
+      <c r="F58" s="81"/>
+      <c r="G58" s="81"/>
+      <c r="H58" s="81"/>
+      <c r="I58" s="81"/>
+      <c r="J58" s="81"/>
+      <c r="K58" s="81"/>
+      <c r="L58" s="81"/>
+      <c r="M58" s="81"/>
+      <c r="N58" s="81"/>
+      <c r="O58" s="81"/>
+      <c r="P58" s="81"/>
+      <c r="Q58" s="81"/>
     </row>
     <row r="59" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="81" t="s">
+      <c r="A59" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B59" s="79" t="s">
+      <c r="B59" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C59" s="80"/>
-      <c r="D59" s="80"/>
-      <c r="E59" s="79" t="s">
+      <c r="C59" s="81"/>
+      <c r="D59" s="81"/>
+      <c r="E59" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="F59" s="80"/>
-      <c r="G59" s="80"/>
-      <c r="H59" s="79" t="s">
+      <c r="F59" s="81"/>
+      <c r="G59" s="81"/>
+      <c r="H59" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="I59" s="80"/>
-      <c r="J59" s="80"/>
-      <c r="K59" s="79" t="s">
+      <c r="I59" s="81"/>
+      <c r="J59" s="81"/>
+      <c r="K59" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="L59" s="80"/>
-      <c r="M59" s="80"/>
-      <c r="N59" s="80"/>
-      <c r="O59" s="80"/>
-      <c r="P59" s="79" t="s">
+      <c r="L59" s="81"/>
+      <c r="M59" s="81"/>
+      <c r="N59" s="81"/>
+      <c r="O59" s="81"/>
+      <c r="P59" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="Q59" s="79" t="s">
+      <c r="Q59" s="80" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A60" s="80"/>
+      <c r="A60" s="81"/>
       <c r="B60" s="43" t="s">
         <v>27</v>
       </c>
@@ -18163,8 +18175,8 @@
       <c r="O60" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P60" s="80"/>
-      <c r="Q60" s="80"/>
+      <c r="P60" s="81"/>
+      <c r="Q60" s="81"/>
     </row>
     <row r="61" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="43" t="s">
@@ -18642,77 +18654,77 @@
       <c r="A75" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="B75" s="80"/>
-      <c r="C75" s="80"/>
-      <c r="D75" s="80"/>
-      <c r="E75" s="80"/>
-      <c r="F75" s="80"/>
-      <c r="G75" s="80"/>
-      <c r="H75" s="80"/>
-      <c r="I75" s="80"/>
-      <c r="J75" s="80"/>
-      <c r="K75" s="80"/>
-      <c r="L75" s="80"/>
-      <c r="M75" s="80"/>
-      <c r="N75" s="80"/>
-      <c r="O75" s="80"/>
-      <c r="P75" s="80"/>
-      <c r="Q75" s="80"/>
+      <c r="B75" s="81"/>
+      <c r="C75" s="81"/>
+      <c r="D75" s="81"/>
+      <c r="E75" s="81"/>
+      <c r="F75" s="81"/>
+      <c r="G75" s="81"/>
+      <c r="H75" s="81"/>
+      <c r="I75" s="81"/>
+      <c r="J75" s="81"/>
+      <c r="K75" s="81"/>
+      <c r="L75" s="81"/>
+      <c r="M75" s="81"/>
+      <c r="N75" s="81"/>
+      <c r="O75" s="81"/>
+      <c r="P75" s="81"/>
+      <c r="Q75" s="81"/>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A76" s="80"/>
-      <c r="B76" s="80"/>
-      <c r="C76" s="80"/>
-      <c r="D76" s="80"/>
-      <c r="E76" s="80"/>
-      <c r="F76" s="80"/>
-      <c r="G76" s="80"/>
-      <c r="H76" s="80"/>
-      <c r="I76" s="80"/>
-      <c r="J76" s="80"/>
-      <c r="K76" s="80"/>
-      <c r="L76" s="80"/>
-      <c r="M76" s="80"/>
-      <c r="N76" s="80"/>
-      <c r="O76" s="80"/>
-      <c r="P76" s="80"/>
-      <c r="Q76" s="80"/>
+      <c r="A76" s="81"/>
+      <c r="B76" s="81"/>
+      <c r="C76" s="81"/>
+      <c r="D76" s="81"/>
+      <c r="E76" s="81"/>
+      <c r="F76" s="81"/>
+      <c r="G76" s="81"/>
+      <c r="H76" s="81"/>
+      <c r="I76" s="81"/>
+      <c r="J76" s="81"/>
+      <c r="K76" s="81"/>
+      <c r="L76" s="81"/>
+      <c r="M76" s="81"/>
+      <c r="N76" s="81"/>
+      <c r="O76" s="81"/>
+      <c r="P76" s="81"/>
+      <c r="Q76" s="81"/>
     </row>
     <row r="77" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="81" t="s">
+      <c r="A77" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B77" s="79" t="s">
+      <c r="B77" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C77" s="80"/>
-      <c r="D77" s="80"/>
-      <c r="E77" s="79" t="s">
+      <c r="C77" s="81"/>
+      <c r="D77" s="81"/>
+      <c r="E77" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="F77" s="80"/>
-      <c r="G77" s="80"/>
-      <c r="H77" s="79" t="s">
+      <c r="F77" s="81"/>
+      <c r="G77" s="81"/>
+      <c r="H77" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="I77" s="80"/>
-      <c r="J77" s="80"/>
-      <c r="K77" s="79" t="s">
+      <c r="I77" s="81"/>
+      <c r="J77" s="81"/>
+      <c r="K77" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="L77" s="80"/>
-      <c r="M77" s="80"/>
-      <c r="N77" s="80"/>
-      <c r="O77" s="80"/>
-      <c r="P77" s="79" t="s">
+      <c r="L77" s="81"/>
+      <c r="M77" s="81"/>
+      <c r="N77" s="81"/>
+      <c r="O77" s="81"/>
+      <c r="P77" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="Q77" s="79" t="s">
+      <c r="Q77" s="80" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A78" s="80"/>
+      <c r="A78" s="81"/>
       <c r="B78" s="43" t="s">
         <v>27</v>
       </c>
@@ -18755,8 +18767,8 @@
       <c r="O78" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P78" s="80"/>
-      <c r="Q78" s="80"/>
+      <c r="P78" s="81"/>
+      <c r="Q78" s="81"/>
     </row>
     <row r="79" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="43" t="s">
@@ -18813,77 +18825,77 @@
       <c r="A80" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="B80" s="80"/>
-      <c r="C80" s="80"/>
-      <c r="D80" s="80"/>
-      <c r="E80" s="80"/>
-      <c r="F80" s="80"/>
-      <c r="G80" s="80"/>
-      <c r="H80" s="80"/>
-      <c r="I80" s="80"/>
-      <c r="J80" s="80"/>
-      <c r="K80" s="80"/>
-      <c r="L80" s="80"/>
-      <c r="M80" s="80"/>
-      <c r="N80" s="80"/>
-      <c r="O80" s="80"/>
-      <c r="P80" s="80"/>
-      <c r="Q80" s="80"/>
+      <c r="B80" s="81"/>
+      <c r="C80" s="81"/>
+      <c r="D80" s="81"/>
+      <c r="E80" s="81"/>
+      <c r="F80" s="81"/>
+      <c r="G80" s="81"/>
+      <c r="H80" s="81"/>
+      <c r="I80" s="81"/>
+      <c r="J80" s="81"/>
+      <c r="K80" s="81"/>
+      <c r="L80" s="81"/>
+      <c r="M80" s="81"/>
+      <c r="N80" s="81"/>
+      <c r="O80" s="81"/>
+      <c r="P80" s="81"/>
+      <c r="Q80" s="81"/>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A81" s="80"/>
-      <c r="B81" s="80"/>
-      <c r="C81" s="80"/>
-      <c r="D81" s="80"/>
-      <c r="E81" s="80"/>
-      <c r="F81" s="80"/>
-      <c r="G81" s="80"/>
-      <c r="H81" s="80"/>
-      <c r="I81" s="80"/>
-      <c r="J81" s="80"/>
-      <c r="K81" s="80"/>
-      <c r="L81" s="80"/>
-      <c r="M81" s="80"/>
-      <c r="N81" s="80"/>
-      <c r="O81" s="80"/>
-      <c r="P81" s="80"/>
-      <c r="Q81" s="80"/>
+      <c r="A81" s="81"/>
+      <c r="B81" s="81"/>
+      <c r="C81" s="81"/>
+      <c r="D81" s="81"/>
+      <c r="E81" s="81"/>
+      <c r="F81" s="81"/>
+      <c r="G81" s="81"/>
+      <c r="H81" s="81"/>
+      <c r="I81" s="81"/>
+      <c r="J81" s="81"/>
+      <c r="K81" s="81"/>
+      <c r="L81" s="81"/>
+      <c r="M81" s="81"/>
+      <c r="N81" s="81"/>
+      <c r="O81" s="81"/>
+      <c r="P81" s="81"/>
+      <c r="Q81" s="81"/>
     </row>
     <row r="82" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="81" t="s">
+      <c r="A82" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B82" s="79" t="s">
+      <c r="B82" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C82" s="80"/>
-      <c r="D82" s="80"/>
-      <c r="E82" s="79" t="s">
+      <c r="C82" s="81"/>
+      <c r="D82" s="81"/>
+      <c r="E82" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="F82" s="80"/>
-      <c r="G82" s="80"/>
-      <c r="H82" s="79" t="s">
+      <c r="F82" s="81"/>
+      <c r="G82" s="81"/>
+      <c r="H82" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="I82" s="80"/>
-      <c r="J82" s="80"/>
-      <c r="K82" s="79" t="s">
+      <c r="I82" s="81"/>
+      <c r="J82" s="81"/>
+      <c r="K82" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="L82" s="80"/>
-      <c r="M82" s="80"/>
-      <c r="N82" s="80"/>
-      <c r="O82" s="80"/>
-      <c r="P82" s="79" t="s">
+      <c r="L82" s="81"/>
+      <c r="M82" s="81"/>
+      <c r="N82" s="81"/>
+      <c r="O82" s="81"/>
+      <c r="P82" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="Q82" s="79" t="s">
+      <c r="Q82" s="80" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A83" s="80"/>
+      <c r="A83" s="81"/>
       <c r="B83" s="43" t="s">
         <v>27</v>
       </c>
@@ -18926,8 +18938,8 @@
       <c r="O83" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P83" s="80"/>
-      <c r="Q83" s="80"/>
+      <c r="P83" s="81"/>
+      <c r="Q83" s="81"/>
     </row>
     <row r="84" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="43" t="s">
@@ -19073,6 +19085,38 @@
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="A24:Q25"/>
+    <mergeCell ref="K82:O82"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="Q77:Q78"/>
+    <mergeCell ref="E82:G82"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="P45:P46"/>
+    <mergeCell ref="A80:Q81"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="Q45:Q46"/>
+    <mergeCell ref="A48:Q49"/>
+    <mergeCell ref="P82:P83"/>
+    <mergeCell ref="Q59:Q60"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="K59:O59"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="Q82:Q83"/>
+    <mergeCell ref="K77:O77"/>
+    <mergeCell ref="P77:P78"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="A75:Q76"/>
+    <mergeCell ref="P59:P60"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="A57:Q58"/>
+    <mergeCell ref="B59:D59"/>
     <mergeCell ref="A26:A27"/>
     <mergeCell ref="K50:O50"/>
     <mergeCell ref="E26:G26"/>
@@ -19089,38 +19133,6 @@
     <mergeCell ref="E45:G45"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B50:D50"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="A75:Q76"/>
-    <mergeCell ref="P59:P60"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="A57:Q58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="P82:P83"/>
-    <mergeCell ref="Q59:Q60"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="K59:O59"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="Q82:Q83"/>
-    <mergeCell ref="K77:O77"/>
-    <mergeCell ref="P77:P78"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="A24:Q25"/>
-    <mergeCell ref="K82:O82"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="Q77:Q78"/>
-    <mergeCell ref="E82:G82"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="P45:P46"/>
-    <mergeCell ref="A80:Q81"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="Q45:Q46"/>
-    <mergeCell ref="A48:Q49"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.scei-concours.fr/stat2025/tb.html" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
@@ -19159,60 +19171,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="84" t="s">
-        <v>911</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
+      <c r="A1" s="85" t="s">
+        <v>907</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
     </row>
     <row r="2" spans="1:7" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="48" t="s">
+        <v>908</v>
+      </c>
+      <c r="B2" s="48" t="s">
+        <v>909</v>
+      </c>
+      <c r="C2" s="48" t="s">
+        <v>910</v>
+      </c>
+      <c r="D2" s="48" t="s">
+        <v>911</v>
+      </c>
+      <c r="E2" s="48" t="s">
         <v>912</v>
       </c>
-      <c r="B2" s="48" t="s">
+      <c r="F2" s="48" t="s">
         <v>913</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="G2" s="48" t="s">
         <v>914</v>
-      </c>
-      <c r="D2" s="48" t="s">
-        <v>915</v>
-      </c>
-      <c r="E2" s="48" t="s">
-        <v>916</v>
-      </c>
-      <c r="F2" s="48" t="s">
-        <v>917</v>
-      </c>
-      <c r="G2" s="48" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="55" t="s">
+        <v>915</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>916</v>
+      </c>
+      <c r="C3" s="55" t="s">
+        <v>917</v>
+      </c>
+      <c r="D3" s="55" t="s">
+        <v>918</v>
+      </c>
+      <c r="E3" s="55" t="s">
         <v>919</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="F3" s="55" t="s">
         <v>920</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="G3" s="55" t="s">
         <v>921</v>
-      </c>
-      <c r="D3" s="55" t="s">
-        <v>922</v>
-      </c>
-      <c r="E3" s="55" t="s">
-        <v>923</v>
-      </c>
-      <c r="F3" s="55" t="s">
-        <v>924</v>
-      </c>
-      <c r="G3" s="55" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -19301,7 +19313,7 @@
     </row>
     <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="49" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B8" s="49" t="s">
         <v>1</v>
@@ -19328,7 +19340,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="D9" s="50">
         <v>1544</v>
@@ -19351,7 +19363,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="49" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D10" s="50">
         <v>1858</v>
@@ -19374,7 +19386,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="D11" s="50">
         <v>2006</v>
@@ -19397,7 +19409,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="50">
@@ -19418,7 +19430,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="49" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="D13" s="50"/>
       <c r="E13" s="50">
@@ -19439,7 +19451,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="49" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="D14" s="50"/>
       <c r="E14" s="50">
@@ -19460,7 +19472,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="49" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="D15" s="50"/>
       <c r="E15" s="50">
@@ -19601,7 +19613,7 @@
     </row>
     <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="49" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="B22" s="49" t="s">
         <v>1</v>
@@ -19622,7 +19634,7 @@
     </row>
     <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="49" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="B23" s="49" t="s">
         <v>1</v>
@@ -19643,7 +19655,7 @@
     </row>
     <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="49" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="B24" s="49" t="s">
         <v>1</v>
@@ -19664,7 +19676,7 @@
     </row>
     <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="49" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="B25" s="49" t="s">
         <v>1</v>
@@ -19685,7 +19697,7 @@
     </row>
     <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="49" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="B26" s="49" t="s">
         <v>1</v>
@@ -19706,7 +19718,7 @@
     </row>
     <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="49" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="B27" s="49" t="s">
         <v>1</v>
@@ -19754,7 +19766,7 @@
         <v>8</v>
       </c>
       <c r="C29" s="51" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="D29" s="52"/>
       <c r="E29" s="52">
@@ -19775,7 +19787,7 @@
         <v>8</v>
       </c>
       <c r="C30" s="51" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="D30" s="52"/>
       <c r="E30" s="52">
@@ -19796,7 +19808,7 @@
         <v>8</v>
       </c>
       <c r="C31" s="51" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="D31" s="52">
         <v>71</v>
@@ -19819,7 +19831,7 @@
         <v>8</v>
       </c>
       <c r="C32" s="51" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="D32" s="52"/>
       <c r="E32" s="52">
@@ -19922,7 +19934,7 @@
         <v>8</v>
       </c>
       <c r="C37" s="51" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="D37" s="52"/>
       <c r="E37" s="52">
@@ -19943,7 +19955,7 @@
         <v>8</v>
       </c>
       <c r="C38" s="51" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="D38" s="52"/>
       <c r="E38" s="52">
@@ -20016,7 +20028,7 @@
         <v>2</v>
       </c>
       <c r="G41" s="56" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20079,15 +20091,15 @@
         <v>3</v>
       </c>
       <c r="G44" s="56" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="60" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B45" s="60" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C45" s="60"/>
       <c r="D45" s="61">
@@ -20100,7 +20112,7 @@
         <v>8</v>
       </c>
       <c r="G45" s="60" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20108,7 +20120,7 @@
         <v>232</v>
       </c>
       <c r="B46" s="53" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C46" s="53"/>
       <c r="D46" s="54"/>
@@ -20119,7 +20131,7 @@
         <v>8</v>
       </c>
       <c r="G46" s="53" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20127,7 +20139,7 @@
         <v>88</v>
       </c>
       <c r="B47" s="53" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C47" s="53"/>
       <c r="D47" s="54">
@@ -20138,7 +20150,7 @@
         <v>3</v>
       </c>
       <c r="G47" s="53" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20146,10 +20158,10 @@
         <v>88</v>
       </c>
       <c r="B48" s="53" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C48" s="53" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="D48" s="54">
         <v>190</v>
@@ -20159,7 +20171,7 @@
         <v>70</v>
       </c>
       <c r="G48" s="53" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20167,7 +20179,7 @@
         <v>88</v>
       </c>
       <c r="B49" s="53" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C49" s="53" t="s">
         <v>80</v>
@@ -20180,15 +20192,15 @@
         <v>4</v>
       </c>
       <c r="G49" s="53" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="56" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="B50" s="56" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C50" s="56"/>
       <c r="D50" s="57">
@@ -20201,15 +20213,15 @@
         <v>20</v>
       </c>
       <c r="G50" s="56" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="58" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B51" s="58" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C51" s="58"/>
       <c r="D51" s="59">
@@ -20222,15 +20234,15 @@
         <v>3</v>
       </c>
       <c r="G51" s="58" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="53" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B52" s="53" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C52" s="53"/>
       <c r="D52" s="54"/>
@@ -20241,15 +20253,15 @@
         <v>7</v>
       </c>
       <c r="G52" s="53" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="53" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B53" s="53" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C53" s="53"/>
       <c r="D53" s="54"/>
@@ -20260,15 +20272,15 @@
         <v>5</v>
       </c>
       <c r="G53" s="53" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="53" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="B54" s="53" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C54" s="53"/>
       <c r="D54" s="54"/>
@@ -20279,7 +20291,7 @@
         <v>3</v>
       </c>
       <c r="G54" s="53" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20298,7 +20310,7 @@
         <v>11</v>
       </c>
       <c r="G55" s="56" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20317,7 +20329,7 @@
         <v>1</v>
       </c>
       <c r="G56" s="56" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20328,7 +20340,7 @@
         <v>1</v>
       </c>
       <c r="C57" s="58" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="D57" s="59">
         <v>904</v>
@@ -20338,7 +20350,7 @@
         <v>6</v>
       </c>
       <c r="G57" s="58" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20349,7 +20361,7 @@
         <v>8</v>
       </c>
       <c r="C58" s="58" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="D58" s="59">
         <v>30</v>
@@ -20359,7 +20371,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="58" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20370,7 +20382,7 @@
         <v>1</v>
       </c>
       <c r="C59" s="58" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="D59" s="59">
         <v>733</v>
@@ -20380,7 +20392,7 @@
         <v>3</v>
       </c>
       <c r="G59" s="58" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20391,7 +20403,7 @@
         <v>1</v>
       </c>
       <c r="C60" s="58" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="D60" s="59">
         <v>821</v>
@@ -20401,7 +20413,7 @@
         <v>14</v>
       </c>
       <c r="G60" s="58" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20412,7 +20424,7 @@
         <v>8</v>
       </c>
       <c r="C61" s="58" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="D61" s="59">
         <v>55</v>
@@ -20422,7 +20434,7 @@
         <v>1</v>
       </c>
       <c r="G61" s="58" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20433,7 +20445,7 @@
         <v>1</v>
       </c>
       <c r="C62" s="58" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="D62" s="59">
         <v>828</v>
@@ -20443,7 +20455,7 @@
         <v>3</v>
       </c>
       <c r="G62" s="58" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20454,7 +20466,7 @@
         <v>8</v>
       </c>
       <c r="C63" s="58" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="D63" s="59">
         <v>52</v>
@@ -20464,7 +20476,7 @@
         <v>1</v>
       </c>
       <c r="G63" s="58" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20475,7 +20487,7 @@
         <v>1</v>
       </c>
       <c r="C64" s="58" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="D64" s="59">
         <v>817</v>
@@ -20485,7 +20497,7 @@
         <v>8</v>
       </c>
       <c r="G64" s="58" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20496,7 +20508,7 @@
         <v>8</v>
       </c>
       <c r="C65" s="58" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="D65" s="59">
         <v>48</v>
@@ -20506,7 +20518,7 @@
         <v>1</v>
       </c>
       <c r="G65" s="58" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20517,7 +20529,7 @@
         <v>1</v>
       </c>
       <c r="C66" s="58" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="D66" s="59">
         <v>910</v>
@@ -20527,7 +20539,7 @@
         <v>6</v>
       </c>
       <c r="G66" s="58" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20538,7 +20550,7 @@
         <v>1</v>
       </c>
       <c r="C67" s="58" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="D67" s="59">
         <v>612</v>
@@ -20548,7 +20560,7 @@
         <v>9</v>
       </c>
       <c r="G67" s="58" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20559,7 +20571,7 @@
         <v>8</v>
       </c>
       <c r="C68" s="58" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="D68" s="59">
         <v>26</v>
@@ -20569,7 +20581,7 @@
         <v>1</v>
       </c>
       <c r="G68" s="58" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20580,7 +20592,7 @@
         <v>1</v>
       </c>
       <c r="C69" s="58" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="D69" s="59">
         <v>834</v>
@@ -20590,7 +20602,7 @@
         <v>6</v>
       </c>
       <c r="G69" s="58" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20601,7 +20613,7 @@
         <v>8</v>
       </c>
       <c r="C70" s="58" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="D70" s="59">
         <v>49</v>
@@ -20611,7 +20623,7 @@
         <v>1</v>
       </c>
       <c r="G70" s="58" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20622,7 +20634,7 @@
         <v>1</v>
       </c>
       <c r="C71" s="58" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="D71" s="59">
         <v>1021</v>
@@ -20632,7 +20644,7 @@
         <v>1</v>
       </c>
       <c r="G71" s="58" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20643,7 +20655,7 @@
         <v>1</v>
       </c>
       <c r="C72" s="58" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="D72" s="59">
         <v>489</v>
@@ -20653,18 +20665,18 @@
         <v>5</v>
       </c>
       <c r="G72" s="58" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="58" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B73" s="58" t="s">
         <v>1</v>
       </c>
       <c r="C73" s="58" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="D73" s="59">
         <v>1000</v>
@@ -20674,18 +20686,18 @@
         <v>6</v>
       </c>
       <c r="G73" s="58" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="58" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="B74" s="58" t="s">
         <v>1</v>
       </c>
       <c r="C74" s="58" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="D74" s="59">
         <v>1025</v>
@@ -20695,7 +20707,7 @@
         <v>4</v>
       </c>
       <c r="G74" s="58" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20706,7 +20718,7 @@
         <v>1</v>
       </c>
       <c r="C75" s="58" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="D75" s="59">
         <v>784</v>
@@ -20716,7 +20728,7 @@
         <v>3</v>
       </c>
       <c r="G75" s="58" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -20727,7 +20739,7 @@
         <v>8</v>
       </c>
       <c r="C76" s="58" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="D76" s="59">
         <v>72</v>
@@ -20737,19 +20749,19 @@
         <v>1</v>
       </c>
       <c r="G76" s="58" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="83" t="s">
-        <v>947</v>
-      </c>
-      <c r="B78" s="80"/>
-      <c r="C78" s="80"/>
-      <c r="D78" s="80"/>
-      <c r="E78" s="80"/>
-      <c r="F78" s="80"/>
-      <c r="G78" s="80"/>
+      <c r="A78" s="84" t="s">
+        <v>943</v>
+      </c>
+      <c r="B78" s="81"/>
+      <c r="C78" s="81"/>
+      <c r="D78" s="81"/>
+      <c r="E78" s="81"/>
+      <c r="F78" s="81"/>
+      <c r="G78" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud2\Boulot 2026\Site orientation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{215F906E-68D6-40DD-B367-F574EE31691E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBAED635-362D-4F8E-B090-F96C9B7154DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elèves_BCPST" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2440" uniqueCount="999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2442" uniqueCount="1001">
   <si>
     <t>Statistiques 2025</t>
   </si>
@@ -3030,6 +3030,12 @@
   </si>
   <si>
     <t>POLYTECH Grenoble est une école d’ingénieur propose plusieurs spécialités. La spécialité Gestion des risques QHSE (Qualité Hygiène Sécurité Environnement) traite des questions de sécurité associées aux risques industriels et environnementaux mais aussi celles concernant la santé de l’Homme au travail. La spécialité Technologies de l'information pour la santé forme à l’analyse des besoins et la conception des systèmes d’information, des logiciels et des dispositifs dédiés à la santé. Cette spécialité est en partenariat avec le CHU de Grenoble Alpes, des laboratoires de recherche du bassin… La spécialité Géotechnique et Génie civil, proposée aux étudiants de BCPST/TB, permet d’étudier risques géologiques et géotechniques, la conception d’ouvrages, la gestion de projets d’ouvrage, … L’école propose plusieurs doubles diplômes, des échanges et des stages à l’étranger.</t>
+  </si>
+  <si>
+    <t>https://eekez.github.io/chesnoy-orientation/fiches/ficheAnaisB.pdf</t>
+  </si>
+  <si>
+    <t>https://eekez.github.io/chesnoy-orientation/fiches/ficheBenoitL.pdf</t>
   </si>
 </sst>
 </file>
@@ -3620,11 +3626,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -7376,6 +7382,9 @@
       <c r="F49" t="s">
         <v>115</v>
       </c>
+      <c r="I49" s="39" t="s">
+        <v>999</v>
+      </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
@@ -7570,6 +7579,9 @@
       </c>
       <c r="F58" t="s">
         <v>115</v>
+      </c>
+      <c r="I58" s="39" t="s">
+        <v>1000</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -8904,6 +8916,8 @@
   <hyperlinks>
     <hyperlink ref="H51" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
     <hyperlink ref="I51" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="I49" r:id="rId3" xr:uid="{B53F0185-E12A-4B2F-B690-A355769CD3F8}"/>
+    <hyperlink ref="I58" r:id="rId4" xr:uid="{65BCD137-8AB5-49F1-9E6E-D630706BF1D1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -11816,7 +11830,7 @@
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="85" t="s">
+      <c r="A28" s="84" t="s">
         <v>843</v>
       </c>
       <c r="B28" s="83"/>
@@ -11856,7 +11870,7 @@
       <c r="Q29" s="83"/>
     </row>
     <row r="30" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="84" t="s">
+      <c r="A30" s="85" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="82" t="s">
@@ -11987,7 +12001,7 @@
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="85" t="s">
+      <c r="A33" s="84" t="s">
         <v>644</v>
       </c>
       <c r="B33" s="83"/>
@@ -12027,7 +12041,7 @@
       <c r="Q34" s="83"/>
     </row>
     <row r="35" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="84" t="s">
+      <c r="A35" s="85" t="s">
         <v>20</v>
       </c>
       <c r="B35" s="82" t="s">
@@ -12544,7 +12558,7 @@
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="85" t="s">
+      <c r="A48" s="84" t="s">
         <v>851</v>
       </c>
       <c r="B48" s="83"/>
@@ -12584,7 +12598,7 @@
       <c r="Q49" s="83"/>
     </row>
     <row r="50" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="84" t="s">
+      <c r="A50" s="85" t="s">
         <v>20</v>
       </c>
       <c r="B50" s="82" t="s">
@@ -12715,7 +12729,7 @@
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53" s="85" t="s">
+      <c r="A53" s="84" t="s">
         <v>853</v>
       </c>
       <c r="B53" s="83"/>
@@ -12755,7 +12769,7 @@
       <c r="Q54" s="83"/>
     </row>
     <row r="55" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="84" t="s">
+      <c r="A55" s="85" t="s">
         <v>20</v>
       </c>
       <c r="B55" s="82" t="s">
@@ -13340,7 +13354,7 @@
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A72" s="85" t="s">
+      <c r="A72" s="84" t="s">
         <v>856</v>
       </c>
       <c r="B72" s="83"/>
@@ -13380,7 +13394,7 @@
       <c r="Q73" s="83"/>
     </row>
     <row r="74" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="84" t="s">
+      <c r="A74" s="85" t="s">
         <v>20</v>
       </c>
       <c r="B74" s="82" t="s">
@@ -13635,7 +13649,7 @@
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A81" s="85" t="s">
+      <c r="A81" s="84" t="s">
         <v>858</v>
       </c>
       <c r="B81" s="83"/>
@@ -13675,7 +13689,7 @@
       <c r="Q82" s="83"/>
     </row>
     <row r="83" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="84" t="s">
+      <c r="A83" s="85" t="s">
         <v>20</v>
       </c>
       <c r="B83" s="82" t="s">
@@ -14029,7 +14043,7 @@
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A93" s="85" t="s">
+      <c r="A93" s="84" t="s">
         <v>863</v>
       </c>
       <c r="B93" s="83"/>
@@ -14069,7 +14083,7 @@
       <c r="Q94" s="83"/>
     </row>
     <row r="95" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="84" t="s">
+      <c r="A95" s="85" t="s">
         <v>20</v>
       </c>
       <c r="B95" s="82" t="s">
@@ -15149,7 +15163,7 @@
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A127" s="85" t="s">
+      <c r="A127" s="84" t="s">
         <v>557</v>
       </c>
       <c r="B127" s="83"/>
@@ -15189,7 +15203,7 @@
       <c r="Q128" s="83"/>
     </row>
     <row r="129" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="84" t="s">
+      <c r="A129" s="85" t="s">
         <v>20</v>
       </c>
       <c r="B129" s="82" t="s">
@@ -16397,7 +16411,7 @@
       </c>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A159" s="85" t="s">
+      <c r="A159" s="84" t="s">
         <v>46</v>
       </c>
       <c r="B159" s="83"/>
@@ -16437,7 +16451,7 @@
       <c r="Q160" s="83"/>
     </row>
     <row r="161" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="84" t="s">
+      <c r="A161" s="85" t="s">
         <v>20</v>
       </c>
       <c r="B161" s="82" t="s">
@@ -16568,7 +16582,7 @@
       </c>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A164" s="85" t="s">
+      <c r="A164" s="84" t="s">
         <v>69</v>
       </c>
       <c r="B164" s="83"/>
@@ -16608,7 +16622,7 @@
       <c r="Q165" s="83"/>
     </row>
     <row r="166" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="84" t="s">
+      <c r="A166" s="85" t="s">
         <v>20</v>
       </c>
       <c r="B166" s="82" t="s">
@@ -16864,6 +16878,70 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="K166:O166"/>
+    <mergeCell ref="H74:J74"/>
+    <mergeCell ref="H83:J83"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="Q50:Q51"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="P74:P75"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="K129:O129"/>
+    <mergeCell ref="P95:P96"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A81:Q82"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B129:D129"/>
+    <mergeCell ref="Q166:Q167"/>
+    <mergeCell ref="Q35:Q36"/>
+    <mergeCell ref="P161:P162"/>
+    <mergeCell ref="A159:Q160"/>
+    <mergeCell ref="A93:Q94"/>
+    <mergeCell ref="Q161:Q162"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="P83:P84"/>
+    <mergeCell ref="Q129:Q130"/>
+    <mergeCell ref="Q95:Q96"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="H55:J55"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="P55:P56"/>
+    <mergeCell ref="B161:D161"/>
+    <mergeCell ref="P129:P130"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="K74:O74"/>
+    <mergeCell ref="K83:O83"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="A129:A130"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="H166:J166"/>
+    <mergeCell ref="E129:G129"/>
+    <mergeCell ref="H161:J161"/>
+    <mergeCell ref="H129:J129"/>
+    <mergeCell ref="E74:G74"/>
+    <mergeCell ref="E166:G166"/>
+    <mergeCell ref="K95:O95"/>
+    <mergeCell ref="A28:Q29"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A48:Q49"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="Q55:Q56"/>
+    <mergeCell ref="P50:P51"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="Q74:Q75"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="Q83:Q84"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="K35:O35"/>
+    <mergeCell ref="Q30:Q31"/>
+    <mergeCell ref="K50:O50"/>
     <mergeCell ref="P35:P36"/>
     <mergeCell ref="E161:G161"/>
     <mergeCell ref="K30:O30"/>
@@ -16880,70 +16958,6 @@
     <mergeCell ref="A127:Q128"/>
     <mergeCell ref="K161:O161"/>
     <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A28:Q29"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A48:Q49"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="Q55:Q56"/>
-    <mergeCell ref="P50:P51"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="Q74:Q75"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="P30:P31"/>
-    <mergeCell ref="Q83:Q84"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="K35:O35"/>
-    <mergeCell ref="Q30:Q31"/>
-    <mergeCell ref="K50:O50"/>
-    <mergeCell ref="B161:D161"/>
-    <mergeCell ref="P129:P130"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="K74:O74"/>
-    <mergeCell ref="K83:O83"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="A129:A130"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="H166:J166"/>
-    <mergeCell ref="E129:G129"/>
-    <mergeCell ref="H161:J161"/>
-    <mergeCell ref="H129:J129"/>
-    <mergeCell ref="E74:G74"/>
-    <mergeCell ref="E166:G166"/>
-    <mergeCell ref="K95:O95"/>
-    <mergeCell ref="Q166:Q167"/>
-    <mergeCell ref="Q35:Q36"/>
-    <mergeCell ref="P161:P162"/>
-    <mergeCell ref="A159:Q160"/>
-    <mergeCell ref="A93:Q94"/>
-    <mergeCell ref="Q161:Q162"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="P83:P84"/>
-    <mergeCell ref="Q129:Q130"/>
-    <mergeCell ref="Q95:Q96"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="H55:J55"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="K166:O166"/>
-    <mergeCell ref="H74:J74"/>
-    <mergeCell ref="H83:J83"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="Q50:Q51"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="P74:P75"/>
-    <mergeCell ref="E55:G55"/>
-    <mergeCell ref="K129:O129"/>
-    <mergeCell ref="P95:P96"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A81:Q82"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B129:D129"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.scei-concours.fr/stat2025/bcpst.html" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -17079,7 +17093,7 @@
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="85" t="s">
+      <c r="A24" s="84" t="s">
         <v>19</v>
       </c>
       <c r="B24" s="83"/>
@@ -17119,7 +17133,7 @@
       <c r="Q25" s="83"/>
     </row>
     <row r="26" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="84" t="s">
+      <c r="A26" s="85" t="s">
         <v>20</v>
       </c>
       <c r="B26" s="82" t="s">
@@ -17704,7 +17718,7 @@
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="85" t="s">
+      <c r="A43" s="84" t="s">
         <v>46</v>
       </c>
       <c r="B43" s="83"/>
@@ -17744,7 +17758,7 @@
       <c r="Q44" s="83"/>
     </row>
     <row r="45" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="84" t="s">
+      <c r="A45" s="85" t="s">
         <v>20</v>
       </c>
       <c r="B45" s="82" t="s">
@@ -17875,7 +17889,7 @@
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="85" t="s">
+      <c r="A48" s="84" t="s">
         <v>47</v>
       </c>
       <c r="B48" s="83"/>
@@ -17915,7 +17929,7 @@
       <c r="Q49" s="83"/>
     </row>
     <row r="50" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="84" t="s">
+      <c r="A50" s="85" t="s">
         <v>20</v>
       </c>
       <c r="B50" s="82" t="s">
@@ -18170,7 +18184,7 @@
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57" s="85" t="s">
+      <c r="A57" s="84" t="s">
         <v>53</v>
       </c>
       <c r="B57" s="83"/>
@@ -18210,7 +18224,7 @@
       <c r="Q58" s="83"/>
     </row>
     <row r="59" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="84" t="s">
+      <c r="A59" s="85" t="s">
         <v>20</v>
       </c>
       <c r="B59" s="82" t="s">
@@ -18762,7 +18776,7 @@
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75" s="85" t="s">
+      <c r="A75" s="84" t="s">
         <v>67</v>
       </c>
       <c r="B75" s="83"/>
@@ -18802,7 +18816,7 @@
       <c r="Q76" s="83"/>
     </row>
     <row r="77" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="84" t="s">
+      <c r="A77" s="85" t="s">
         <v>20</v>
       </c>
       <c r="B77" s="82" t="s">
@@ -18933,7 +18947,7 @@
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A80" s="85" t="s">
+      <c r="A80" s="84" t="s">
         <v>69</v>
       </c>
       <c r="B80" s="83"/>
@@ -18973,7 +18987,7 @@
       <c r="Q81" s="83"/>
     </row>
     <row r="82" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="84" t="s">
+      <c r="A82" s="85" t="s">
         <v>20</v>
       </c>
       <c r="B82" s="82" t="s">
@@ -19196,6 +19210,38 @@
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="A24:Q25"/>
+    <mergeCell ref="K82:O82"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="Q77:Q78"/>
+    <mergeCell ref="E82:G82"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="P45:P46"/>
+    <mergeCell ref="A80:Q81"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="Q45:Q46"/>
+    <mergeCell ref="A48:Q49"/>
+    <mergeCell ref="P82:P83"/>
+    <mergeCell ref="Q59:Q60"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="K59:O59"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="Q82:Q83"/>
+    <mergeCell ref="K77:O77"/>
+    <mergeCell ref="P77:P78"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="A75:Q76"/>
+    <mergeCell ref="P59:P60"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="A57:Q58"/>
+    <mergeCell ref="B59:D59"/>
     <mergeCell ref="A26:A27"/>
     <mergeCell ref="K50:O50"/>
     <mergeCell ref="E26:G26"/>
@@ -19212,38 +19258,6 @@
     <mergeCell ref="E45:G45"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B50:D50"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="A75:Q76"/>
-    <mergeCell ref="P59:P60"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="A57:Q58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="P82:P83"/>
-    <mergeCell ref="Q59:Q60"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="K59:O59"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="Q82:Q83"/>
-    <mergeCell ref="K77:O77"/>
-    <mergeCell ref="P77:P78"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="A24:Q25"/>
-    <mergeCell ref="K82:O82"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="Q77:Q78"/>
-    <mergeCell ref="E82:G82"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="P45:P46"/>
-    <mergeCell ref="A80:Q81"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="Q45:Q46"/>
-    <mergeCell ref="A48:Q49"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.scei-concours.fr/stat2025/tb.html" xr:uid="{00000000-0004-0000-0500-000000000000}"/>

--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud2\Boulot 2026\Site orientation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBAED635-362D-4F8E-B090-F96C9B7154DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E940984-3C4B-4992-B349-5CFD68C12847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elèves_BCPST" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2442" uniqueCount="1001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2470" uniqueCount="1015">
   <si>
     <t>Statistiques 2025</t>
   </si>
@@ -3036,13 +3036,55 @@
   </si>
   <si>
     <t>https://eekez.github.io/chesnoy-orientation/fiches/ficheBenoitL.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAURY </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BATUT </t>
+  </si>
+  <si>
+    <t>Siriane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHOCHOY </t>
+  </si>
+  <si>
+    <t>Emy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COURTHIAL </t>
+  </si>
+  <si>
+    <t>UTC Compiègne</t>
+  </si>
+  <si>
+    <t>Grande école d’ingénieurs généraliste proposant des formations en génie biologique, génie des procédés, informatique, mécanique, génie urbain et systèmes urbains. L’UTC met l’accent sur l’innovation, la recherche et la personnalisation du parcours de formation.</t>
+  </si>
+  <si>
+    <t>Compiègne</t>
+  </si>
+  <si>
+    <t>https://www.utc.fr</t>
+  </si>
+  <si>
+    <t>[49.41570, 2.82300]</t>
+  </si>
+  <si>
+    <t>Mécanique ; Informatique ; Génie biologique ; Génie des procédés ; Génie urbain ; Systèmes urbains ; Innovation ; Recherche ; International ; Ingénierie</t>
+  </si>
+  <si>
+    <t>https://external-content.duckduckgo.com/iu/?u=https%3A%2F%2Fcareers.recruiteecdn.com%2Fimage%2Fupload%2Fq_auto%2Cw_1920%2Cc_limit%2Fproduction%2Fimages%2FBQC2%2FwIFApRbvNKFd.jpeg&amp;f=1&amp;nofb=1&amp;ipt=04c93c67c5ef840175d2e39636a76e85966178ae1c56d63ab1894ed4ca9f3ad3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3235,6 +3277,11 @@
       <color rgb="FFAA4400"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -3403,7 +3450,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3626,15 +3673,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -6327,7 +6380,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I122"/>
+  <dimension ref="A1:N127"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
@@ -6337,7 +6390,7 @@
     <col min="9" max="9" width="96.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>275</v>
       </c>
@@ -6363,16 +6416,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>974</v>
+        <v>1007</v>
       </c>
       <c r="B2" s="1" t="str">
         <f t="shared" ref="B2" si="0">LEFT(A2)</f>
         <v>C</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="D2" s="64">
         <v>2026</v>
@@ -6381,21 +6434,21 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>267</v>
+        <v>115</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="37"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>971</v>
+        <v>1005</v>
       </c>
       <c r="B3" s="1" t="str">
         <f t="shared" ref="B3" si="1">LEFT(A3)</f>
-        <v>M</v>
+        <v>C</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>96</v>
+        <v>1006</v>
       </c>
       <c r="D3" s="64">
         <v>2026</v>
@@ -6406,19 +6459,19 @@
       <c r="F3" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H3" s="2"/>
+      <c r="I3" s="37"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>970</v>
+        <v>1003</v>
       </c>
       <c r="B4" s="1" t="str">
         <f t="shared" ref="B4" si="2">LEFT(A4)</f>
         <v>B</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>421</v>
+        <v>1004</v>
       </c>
       <c r="D4" s="64">
         <v>2026</v>
@@ -6427,21 +6480,21 @@
         <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="37"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>959</v>
+        <v>1002</v>
       </c>
       <c r="B5" s="1" t="str">
         <f t="shared" ref="B5" si="3">LEFT(A5)</f>
-        <v>B</v>
+        <v>M</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>960</v>
+        <v>406</v>
       </c>
       <c r="D5" s="64">
         <v>2026</v>
@@ -6450,21 +6503,21 @@
         <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>961</v>
-      </c>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="37"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>276</v>
+        <v>1001</v>
       </c>
       <c r="B6" s="1" t="str">
-        <f t="shared" ref="B6:B37" si="4">LEFT(A6)</f>
-        <v>G</v>
+        <f t="shared" ref="B6" si="4">LEFT(A6)</f>
+        <v>M</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>277</v>
+        <v>234</v>
       </c>
       <c r="D6" s="64">
         <v>2026</v>
@@ -6473,21 +6526,21 @@
         <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="37"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>278</v>
+        <v>974</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>R</v>
+        <f t="shared" ref="B7" si="5">LEFT(A7)</f>
+        <v>C</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>279</v>
+        <v>125</v>
       </c>
       <c r="D7" s="64">
         <v>2026</v>
@@ -6496,126 +6549,136 @@
         <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="37"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="B8" s="1" t="str">
+        <f t="shared" ref="B8" si="6">LEFT(A8)</f>
+        <v>M</v>
+      </c>
+      <c r="C8" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="64">
+        <v>2026</v>
+      </c>
+      <c r="E8" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="B9" s="1" t="str">
+        <f t="shared" ref="B9" si="7">LEFT(A9)</f>
+        <v>B</v>
+      </c>
+      <c r="C9" s="64" t="s">
+        <v>421</v>
+      </c>
+      <c r="D9" s="64">
+        <v>2026</v>
+      </c>
+      <c r="E9" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="B10" s="1" t="str">
+        <f t="shared" ref="B10" si="8">LEFT(A10)</f>
+        <v>B</v>
+      </c>
+      <c r="C10" s="64" t="s">
+        <v>960</v>
+      </c>
+      <c r="D10" s="64">
+        <v>2026</v>
+      </c>
+      <c r="E10" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B11" s="1" t="str">
+        <f t="shared" ref="B11:B42" si="9">LEFT(A11)</f>
+        <v>G</v>
+      </c>
+      <c r="C11" s="64" t="s">
+        <v>277</v>
+      </c>
+      <c r="D11" s="64">
+        <v>2026</v>
+      </c>
+      <c r="E11" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B12" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>R</v>
+      </c>
+      <c r="C12" s="64" t="s">
+        <v>279</v>
+      </c>
+      <c r="D12" s="64">
+        <v>2026</v>
+      </c>
+      <c r="E12" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B8" s="1" t="str">
-        <f t="shared" si="4"/>
+      <c r="B13" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>B</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="D8" s="1">
-        <v>2025</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="B9" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>C</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="D9" s="1">
-        <v>2025</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="B10" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>D</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="D10" s="1">
-        <v>2025</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B11" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>F</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="D11" s="1">
-        <v>2025</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B12" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>S</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D12" s="1">
-        <v>2025</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="B13" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>U</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>291</v>
       </c>
       <c r="D13" s="1">
         <v>2025</v>
@@ -6624,19 +6687,19 @@
         <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="B14" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>W</v>
+        <v>281</v>
+      </c>
+      <c r="B14" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>C</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="D14" s="1">
         <v>2025</v>
@@ -6645,19 +6708,19 @@
         <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="B15" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>T</v>
+        <v>284</v>
+      </c>
+      <c r="B15" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>D</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="D15" s="1">
         <v>2025</v>
@@ -6666,19 +6729,25 @@
         <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="64"/>
+      <c r="L15" s="64"/>
+      <c r="M15" s="64"/>
+      <c r="N15" s="1"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>105</v>
+        <v>286</v>
       </c>
       <c r="B16" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>G</v>
+        <f t="shared" si="9"/>
+        <v>F</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="D16" s="1">
         <v>2025</v>
@@ -6687,19 +6756,19 @@
         <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>122</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="B17" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>S</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="D17" s="1">
         <v>2025</v>
@@ -6708,124 +6777,124 @@
         <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B18" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>B</v>
+        <f t="shared" si="9"/>
+        <v>U</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="D18" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B19" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>E</v>
+        <f t="shared" si="9"/>
+        <v>W</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="D19" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>122</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="B20" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>G</v>
+        <f t="shared" si="9"/>
+        <v>T</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="D20" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>115</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>305</v>
+        <v>105</v>
       </c>
       <c r="B21" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>H</v>
+        <f t="shared" si="9"/>
+        <v>G</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D21" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B22" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>P</v>
+        <f t="shared" si="9"/>
+        <v>S</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="D22" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="B23" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>R</v>
+        <f t="shared" si="9"/>
+        <v>B</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="D23" s="1">
         <v>2024</v>
@@ -6834,19 +6903,19 @@
         <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="B24" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>L</v>
+        <f t="shared" si="9"/>
+        <v>E</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="D24" s="1">
         <v>2024</v>
@@ -6855,19 +6924,19 @@
         <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>313</v>
+      <c r="A25" s="1" t="s">
+        <v>303</v>
       </c>
       <c r="B25" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>M</v>
-      </c>
-      <c r="C25" t="s">
-        <v>314</v>
+        <f t="shared" si="9"/>
+        <v>G</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>304</v>
       </c>
       <c r="D25" s="1">
         <v>2024</v>
@@ -6880,15 +6949,15 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>315</v>
+      <c r="A26" s="1" t="s">
+        <v>305</v>
       </c>
       <c r="B26" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>R</v>
-      </c>
-      <c r="C26" t="s">
-        <v>101</v>
+        <f t="shared" si="9"/>
+        <v>H</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>306</v>
       </c>
       <c r="D26" s="1">
         <v>2024</v>
@@ -6897,124 +6966,124 @@
         <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B27" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>F</v>
-      </c>
-      <c r="C27" t="s">
-        <v>317</v>
+        <f t="shared" si="9"/>
+        <v>P</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>308</v>
       </c>
       <c r="D27" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="B28" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>G</v>
-      </c>
-      <c r="C28" t="s">
-        <v>319</v>
+        <f t="shared" si="9"/>
+        <v>R</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>310</v>
       </c>
       <c r="D28" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>320</v>
+      <c r="A29" s="1" t="s">
+        <v>311</v>
       </c>
       <c r="B29" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>J</v>
+        <f t="shared" si="9"/>
+        <v>L</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>149</v>
+        <v>312</v>
       </c>
       <c r="D29" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>258</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>321</v>
+      <c r="A30" t="s">
+        <v>313</v>
       </c>
       <c r="B30" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>L</v>
+        <f t="shared" si="9"/>
+        <v>M</v>
       </c>
       <c r="C30" t="s">
-        <v>277</v>
+        <v>314</v>
       </c>
       <c r="D30" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>322</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>323</v>
+      <c r="A31" s="7" t="s">
+        <v>315</v>
       </c>
       <c r="B31" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>P</v>
+        <f t="shared" si="9"/>
+        <v>R</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>101</v>
       </c>
       <c r="D31" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>324</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>325</v>
+      <c r="A32" s="1" t="s">
+        <v>316</v>
       </c>
       <c r="B32" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>S</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>326</v>
+        <f t="shared" si="9"/>
+        <v>F</v>
+      </c>
+      <c r="C32" t="s">
+        <v>317</v>
       </c>
       <c r="D32" s="1">
         <v>2023</v>
@@ -7022,20 +7091,20 @@
       <c r="E32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F32" t="s">
-        <v>37</v>
+      <c r="F32" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>327</v>
+      <c r="A33" s="1" t="s">
+        <v>318</v>
       </c>
       <c r="B33" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>V</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>328</v>
+        <f t="shared" si="9"/>
+        <v>G</v>
+      </c>
+      <c r="C33" t="s">
+        <v>319</v>
       </c>
       <c r="D33" s="1">
         <v>2023</v>
@@ -7043,20 +7112,20 @@
       <c r="E33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F33" t="s">
-        <v>112</v>
+      <c r="F33" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
-        <v>329</v>
+      <c r="A34" t="s">
+        <v>320</v>
       </c>
       <c r="B34" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>B</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>330</v>
+        <f t="shared" si="9"/>
+        <v>J</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="D34" s="1">
         <v>2023</v>
@@ -7064,20 +7133,20 @@
       <c r="E34" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F34" t="s">
-        <v>112</v>
+      <c r="F34" s="1" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
-        <v>331</v>
+      <c r="A35" s="1" t="s">
+        <v>321</v>
       </c>
       <c r="B35" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>D</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>229</v>
+        <f t="shared" si="9"/>
+        <v>L</v>
+      </c>
+      <c r="C35" t="s">
+        <v>277</v>
       </c>
       <c r="D35" s="1">
         <v>2023</v>
@@ -7085,65 +7154,65 @@
       <c r="E35" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F35" t="s">
-        <v>104</v>
+      <c r="F35" s="1" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
-        <v>332</v>
+      <c r="A36" t="s">
+        <v>323</v>
       </c>
       <c r="B36" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>B</v>
+        <f t="shared" si="9"/>
+        <v>P</v>
       </c>
       <c r="C36" t="s">
-        <v>333</v>
+        <v>262</v>
       </c>
       <c r="D36" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F36" t="s">
-        <v>334</v>
+      <c r="F36" s="1" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="B37" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>C</v>
+        <f t="shared" si="9"/>
+        <v>S</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="D37" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="B38" s="4" t="str">
-        <f t="shared" ref="B38:B69" si="5">LEFT(A38)</f>
-        <v>C</v>
+        <f t="shared" si="9"/>
+        <v>V</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="D38" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>8</v>
@@ -7154,56 +7223,56 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="B39" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v>F</v>
+        <f t="shared" si="9"/>
+        <v>B</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>101</v>
+        <v>330</v>
       </c>
       <c r="D39" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>340</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="B40" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v>G</v>
+        <f t="shared" si="9"/>
+        <v>D</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>342</v>
+        <v>229</v>
       </c>
       <c r="D40" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>188</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="B41" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>J</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>344</v>
+        <v>332</v>
+      </c>
+      <c r="B41" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>B</v>
+      </c>
+      <c r="C41" t="s">
+        <v>333</v>
       </c>
       <c r="D41" s="1">
         <v>2022</v>
@@ -7212,19 +7281,19 @@
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="B42" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>L</v>
+        <v>335</v>
+      </c>
+      <c r="B42" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>C</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="D42" s="1">
         <v>2022</v>
@@ -7233,19 +7302,19 @@
         <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>283</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="B43" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>R</v>
+        <v>337</v>
+      </c>
+      <c r="B43" s="4" t="str">
+        <f t="shared" ref="B43:B74" si="10">LEFT(A43)</f>
+        <v>C</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="D43" s="1">
         <v>2022</v>
@@ -7254,19 +7323,19 @@
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="B44" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>V</v>
+        <v>339</v>
+      </c>
+      <c r="B44" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>F</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>342</v>
+        <v>101</v>
       </c>
       <c r="D44" s="1">
         <v>2022</v>
@@ -7275,19 +7344,19 @@
         <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>267</v>
+        <v>340</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>351</v>
-      </c>
-      <c r="B45" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>W</v>
+      <c r="A45" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="B45" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>G</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="D45" s="1">
         <v>2022</v>
@@ -7296,19 +7365,19 @@
         <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>353</v>
+        <v>188</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="B46" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>B</v>
+        <f t="shared" si="10"/>
+        <v>J</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="D46" s="1">
         <v>2022</v>
@@ -7317,19 +7386,19 @@
         <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="B47" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>M</v>
+        <f t="shared" si="10"/>
+        <v>L</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>133</v>
+        <v>347</v>
       </c>
       <c r="D47" s="1">
         <v>2022</v>
@@ -7338,19 +7407,19 @@
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>188</v>
+        <v>283</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B48" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>P</v>
+        <f t="shared" si="10"/>
+        <v>R</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="D48" s="1">
         <v>2022</v>
@@ -7359,133 +7428,124 @@
         <v>8</v>
       </c>
       <c r="F48" t="s">
-        <v>188</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B49" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>B</v>
+        <f t="shared" si="10"/>
+        <v>V</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>149</v>
+        <v>342</v>
       </c>
       <c r="D49" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>115</v>
-      </c>
-      <c r="I49" s="39" t="s">
-        <v>999</v>
+        <v>267</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
-        <v>360</v>
+      <c r="A50" t="s">
+        <v>351</v>
       </c>
       <c r="B50" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>E</v>
+        <f t="shared" si="10"/>
+        <v>W</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="D50" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F50" t="s">
-        <v>232</v>
+        <v>353</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B51" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>R</v>
+        <f t="shared" si="10"/>
+        <v>B</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>269</v>
+        <v>355</v>
       </c>
       <c r="D51" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F51" t="s">
-        <v>145</v>
-      </c>
-      <c r="H51" s="39" t="s">
-        <v>363</v>
-      </c>
-      <c r="I51" s="39" t="s">
-        <v>364</v>
+        <v>324</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="B52" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>R</v>
+        <f t="shared" si="10"/>
+        <v>M</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>269</v>
+        <v>133</v>
       </c>
       <c r="D52" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F52" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>288</v>
+        <v>357</v>
       </c>
       <c r="B53" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>S</v>
+        <f t="shared" si="10"/>
+        <v>P</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D53" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F53" t="s">
-        <v>142</v>
+        <v>188</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B54" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>A</v>
+        <f t="shared" si="10"/>
+        <v>B</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>255</v>
+        <v>149</v>
       </c>
       <c r="D54" s="1">
         <v>2021</v>
@@ -7494,19 +7554,22 @@
         <v>8</v>
       </c>
       <c r="F54" t="s">
-        <v>258</v>
+        <v>115</v>
+      </c>
+      <c r="I54" s="39" t="s">
+        <v>999</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B55" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>B</v>
+        <f t="shared" si="10"/>
+        <v>E</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="D55" s="1">
         <v>2021</v>
@@ -7515,19 +7578,19 @@
         <v>8</v>
       </c>
       <c r="F55" t="s">
-        <v>370</v>
+        <v>232</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="B56" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>K</v>
+        <f t="shared" si="10"/>
+        <v>R</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>372</v>
+        <v>269</v>
       </c>
       <c r="D56" s="1">
         <v>2021</v>
@@ -7536,19 +7599,25 @@
         <v>8</v>
       </c>
       <c r="F56" t="s">
-        <v>122</v>
+        <v>145</v>
+      </c>
+      <c r="H56" s="39" t="s">
+        <v>363</v>
+      </c>
+      <c r="I56" s="39" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="B57" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>L</v>
+        <f t="shared" si="10"/>
+        <v>R</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>374</v>
+        <v>269</v>
       </c>
       <c r="D57" s="1">
         <v>2021</v>
@@ -7557,19 +7626,19 @@
         <v>8</v>
       </c>
       <c r="F57" t="s">
-        <v>340</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>375</v>
+        <v>288</v>
       </c>
       <c r="B58" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>L</v>
+        <f t="shared" si="10"/>
+        <v>S</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="D58" s="1">
         <v>2021</v>
@@ -7578,22 +7647,19 @@
         <v>8</v>
       </c>
       <c r="F58" t="s">
-        <v>115</v>
-      </c>
-      <c r="I58" s="39" t="s">
-        <v>1000</v>
+        <v>142</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="B59" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>P</v>
+        <f t="shared" si="10"/>
+        <v>A</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>133</v>
+        <v>255</v>
       </c>
       <c r="D59" s="1">
         <v>2021</v>
@@ -7602,19 +7668,19 @@
         <v>8</v>
       </c>
       <c r="F59" t="s">
-        <v>112</v>
+        <v>258</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>378</v>
+      <c r="A60" s="7" t="s">
+        <v>368</v>
       </c>
       <c r="B60" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>P</v>
-      </c>
-      <c r="C60" t="s">
-        <v>379</v>
+        <f t="shared" si="10"/>
+        <v>B</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>369</v>
       </c>
       <c r="D60" s="1">
         <v>2021</v>
@@ -7623,124 +7689,127 @@
         <v>8</v>
       </c>
       <c r="F60" t="s">
-        <v>122</v>
+        <v>370</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="B61" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>A</v>
+        <f t="shared" si="10"/>
+        <v>K</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D61" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F61" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="B62" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>C</v>
+        <f t="shared" si="10"/>
+        <v>L</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>128</v>
+        <v>374</v>
       </c>
       <c r="D62" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F62" t="s">
-        <v>122</v>
+        <v>340</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="B63" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>M</v>
+        <f t="shared" si="10"/>
+        <v>L</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="D63" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F63" t="s">
-        <v>104</v>
+        <v>115</v>
+      </c>
+      <c r="I63" s="39" t="s">
+        <v>1000</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>385</v>
+      <c r="A64" s="7" t="s">
+        <v>377</v>
       </c>
       <c r="B64" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>A</v>
-      </c>
-      <c r="C64" s="9" t="s">
-        <v>386</v>
+        <f t="shared" si="10"/>
+        <v>P</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>133</v>
       </c>
       <c r="D64" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F64" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="B65" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>D</v>
-      </c>
-      <c r="C65" s="9" t="s">
-        <v>388</v>
+        <f t="shared" si="10"/>
+        <v>P</v>
+      </c>
+      <c r="C65" t="s">
+        <v>379</v>
       </c>
       <c r="D65" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F65" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>389</v>
+      <c r="A66" s="7" t="s">
+        <v>380</v>
       </c>
       <c r="B66" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>M</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>390</v>
+        <f t="shared" si="10"/>
+        <v>A</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>381</v>
       </c>
       <c r="D66" s="1">
         <v>2020</v>
@@ -7749,19 +7818,19 @@
         <v>8</v>
       </c>
       <c r="F66" t="s">
-        <v>322</v>
+        <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>391</v>
+      <c r="A67" s="7" t="s">
+        <v>382</v>
       </c>
       <c r="B67" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>P</v>
-      </c>
-      <c r="C67" s="9" t="s">
-        <v>392</v>
+        <f t="shared" si="10"/>
+        <v>C</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>128</v>
       </c>
       <c r="D67" s="1">
         <v>2020</v>
@@ -7770,19 +7839,19 @@
         <v>8</v>
       </c>
       <c r="F67" t="s">
-        <v>188</v>
+        <v>122</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>393</v>
+      <c r="A68" s="7" t="s">
+        <v>383</v>
       </c>
       <c r="B68" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>V</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>138</v>
+        <f t="shared" si="10"/>
+        <v>M</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>384</v>
       </c>
       <c r="D68" s="1">
         <v>2020</v>
@@ -7791,124 +7860,124 @@
         <v>8</v>
       </c>
       <c r="F68" t="s">
-        <v>258</v>
+        <v>104</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B69" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>C</v>
+        <f t="shared" si="10"/>
+        <v>A</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="D69" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F69" t="s">
-        <v>212</v>
+        <v>145</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="B70" s="1" t="str">
-        <f t="shared" ref="B70:B101" si="6">LEFT(A70)</f>
-        <v>C</v>
+        <f t="shared" si="10"/>
+        <v>D</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>252</v>
+        <v>388</v>
       </c>
       <c r="D70" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F70" t="s">
-        <v>322</v>
+        <v>99</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="B71" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>L</v>
-      </c>
-      <c r="C71" t="s">
-        <v>398</v>
+        <f t="shared" si="10"/>
+        <v>M</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>390</v>
       </c>
       <c r="D71" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F71" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="B72" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>R</v>
-      </c>
-      <c r="C72" t="s">
-        <v>161</v>
+        <f t="shared" si="10"/>
+        <v>P</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>392</v>
       </c>
       <c r="D72" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F72" t="s">
-        <v>122</v>
+        <v>188</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="B73" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>R</v>
-      </c>
-      <c r="C73" t="s">
-        <v>401</v>
+        <f t="shared" si="10"/>
+        <v>V</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>138</v>
       </c>
       <c r="D73" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F73" t="s">
-        <v>283</v>
+        <v>258</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="B74" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>V</v>
-      </c>
-      <c r="C74" t="s">
-        <v>262</v>
+        <f t="shared" si="10"/>
+        <v>C</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>395</v>
       </c>
       <c r="D74" s="1">
         <v>2019</v>
@@ -7917,19 +7986,19 @@
         <v>8</v>
       </c>
       <c r="F74" t="s">
-        <v>104</v>
+        <v>212</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="B75" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>H</v>
-      </c>
-      <c r="C75" t="s">
-        <v>404</v>
+        <f t="shared" ref="B75:B106" si="11">LEFT(A75)</f>
+        <v>C</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>252</v>
       </c>
       <c r="D75" s="1">
         <v>2019</v>
@@ -7938,124 +8007,124 @@
         <v>8</v>
       </c>
       <c r="F75" t="s">
-        <v>283</v>
+        <v>322</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="B76" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>M</v>
+        <f t="shared" si="11"/>
+        <v>L</v>
       </c>
       <c r="C76" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="D76" s="1">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F76" t="s">
-        <v>407</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="B77" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>R</v>
       </c>
       <c r="C77" t="s">
-        <v>347</v>
+        <v>161</v>
       </c>
       <c r="D77" s="1">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F77" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="B78" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>T</v>
+        <f t="shared" si="11"/>
+        <v>R</v>
       </c>
       <c r="C78" t="s">
-        <v>298</v>
+        <v>401</v>
       </c>
       <c r="D78" s="1">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F78" t="s">
-        <v>115</v>
+        <v>283</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="B79" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>V</v>
       </c>
       <c r="C79" t="s">
-        <v>411</v>
+        <v>262</v>
       </c>
       <c r="D79" s="1">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F79" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="B80" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>B</v>
+        <f t="shared" si="11"/>
+        <v>H</v>
       </c>
       <c r="C80" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="D80" s="1">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F80" t="s">
-        <v>232</v>
+        <v>283</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="B81" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>B</v>
+        <f t="shared" si="11"/>
+        <v>M</v>
       </c>
       <c r="C81" t="s">
-        <v>269</v>
+        <v>406</v>
       </c>
       <c r="D81" s="1">
         <v>2018</v>
@@ -8064,19 +8133,19 @@
         <v>8</v>
       </c>
       <c r="F81" t="s">
-        <v>99</v>
+        <v>407</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="B82" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>D</v>
+        <f t="shared" si="11"/>
+        <v>R</v>
       </c>
       <c r="C82" t="s">
-        <v>416</v>
+        <v>347</v>
       </c>
       <c r="D82" s="1">
         <v>2018</v>
@@ -8085,19 +8154,19 @@
         <v>8</v>
       </c>
       <c r="F82" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="B83" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>G</v>
+        <f t="shared" si="11"/>
+        <v>T</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="D83" s="1">
         <v>2018</v>
@@ -8106,19 +8175,19 @@
         <v>8</v>
       </c>
       <c r="F83" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="B84" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>P</v>
+        <f t="shared" si="11"/>
+        <v>V</v>
       </c>
       <c r="C84" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="D84" s="1">
         <v>2018</v>
@@ -8127,22 +8196,22 @@
         <v>8</v>
       </c>
       <c r="F84" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="B85" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>B</v>
       </c>
       <c r="C85" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="D85" s="1">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>8</v>
@@ -8153,98 +8222,98 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B86" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>D</v>
+        <f t="shared" si="11"/>
+        <v>B</v>
       </c>
       <c r="C86" t="s">
-        <v>423</v>
+        <v>269</v>
       </c>
       <c r="D86" s="1">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F86" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="B87" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>F</v>
+        <f t="shared" si="11"/>
+        <v>D</v>
       </c>
       <c r="C87" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="D87" s="1">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F87" s="1" t="s">
-        <v>136</v>
+      <c r="F87" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="B88" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>F</v>
+        <f t="shared" si="11"/>
+        <v>G</v>
       </c>
       <c r="C88" t="s">
-        <v>426</v>
+        <v>262</v>
       </c>
       <c r="D88" s="1">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F88" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="B89" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>H</v>
+        <f t="shared" si="11"/>
+        <v>P</v>
       </c>
       <c r="C89" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="D89" s="1">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F89" t="s">
-        <v>429</v>
+        <v>142</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="B90" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>L</v>
+        <f t="shared" si="11"/>
+        <v>B</v>
       </c>
       <c r="C90" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="D90" s="1">
         <v>2017</v>
@@ -8253,19 +8322,19 @@
         <v>8</v>
       </c>
       <c r="F90" t="s">
-        <v>37</v>
+        <v>232</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="B91" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>V</v>
+        <f t="shared" si="11"/>
+        <v>D</v>
       </c>
       <c r="C91" t="s">
-        <v>205</v>
+        <v>423</v>
       </c>
       <c r="D91" s="1">
         <v>2017</v>
@@ -8274,19 +8343,19 @@
         <v>8</v>
       </c>
       <c r="F91" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="B92" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>G</v>
+        <f t="shared" si="11"/>
+        <v>F</v>
       </c>
       <c r="C92" t="s">
-        <v>434</v>
+        <v>401</v>
       </c>
       <c r="D92" s="1">
         <v>2017</v>
@@ -8294,125 +8363,125 @@
       <c r="E92" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F92" t="s">
-        <v>407</v>
+      <c r="F92" s="1" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="B93" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>B</v>
+        <f t="shared" si="11"/>
+        <v>F</v>
       </c>
       <c r="C93" t="s">
-        <v>128</v>
+        <v>426</v>
       </c>
       <c r="D93" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F93" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="B94" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>C</v>
+        <f t="shared" si="11"/>
+        <v>H</v>
       </c>
       <c r="C94" t="s">
-        <v>269</v>
+        <v>428</v>
       </c>
       <c r="D94" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F94" t="s">
-        <v>188</v>
+        <v>429</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="B95" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>F</v>
+        <f t="shared" si="11"/>
+        <v>L</v>
       </c>
       <c r="C95" t="s">
-        <v>209</v>
+        <v>431</v>
       </c>
       <c r="D95" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F95" t="s">
-        <v>232</v>
+        <v>37</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="B96" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>P</v>
+        <f t="shared" si="11"/>
+        <v>V</v>
       </c>
       <c r="C96" t="s">
-        <v>439</v>
+        <v>205</v>
       </c>
       <c r="D96" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F96" t="s">
-        <v>283</v>
+        <v>122</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="B97" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>R</v>
+        <f t="shared" si="11"/>
+        <v>G</v>
       </c>
       <c r="C97" t="s">
-        <v>152</v>
+        <v>434</v>
       </c>
       <c r="D97" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F97" t="s">
-        <v>122</v>
+        <v>407</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B98" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>P</v>
+        <f t="shared" si="11"/>
+        <v>B</v>
       </c>
       <c r="C98" t="s">
-        <v>442</v>
+        <v>128</v>
       </c>
       <c r="D98" s="1">
         <v>2016</v>
@@ -8421,19 +8490,19 @@
         <v>8</v>
       </c>
       <c r="F98" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="B99" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>M</v>
+        <f t="shared" si="11"/>
+        <v>C</v>
       </c>
       <c r="C99" t="s">
-        <v>444</v>
+        <v>269</v>
       </c>
       <c r="D99" s="1">
         <v>2016</v>
@@ -8442,19 +8511,19 @@
         <v>8</v>
       </c>
       <c r="F99" t="s">
-        <v>445</v>
+        <v>188</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B100" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>M</v>
+        <f t="shared" si="11"/>
+        <v>F</v>
       </c>
       <c r="C100" t="s">
-        <v>447</v>
+        <v>209</v>
       </c>
       <c r="D100" s="1">
         <v>2016</v>
@@ -8463,19 +8532,19 @@
         <v>8</v>
       </c>
       <c r="F100" t="s">
-        <v>448</v>
+        <v>232</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="B101" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>O</v>
+        <f t="shared" si="11"/>
+        <v>P</v>
       </c>
       <c r="C101" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="D101" s="1">
         <v>2016</v>
@@ -8484,19 +8553,19 @@
         <v>8</v>
       </c>
       <c r="F101" t="s">
-        <v>450</v>
+        <v>283</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="B102" s="1" t="str">
-        <f t="shared" ref="B102" si="7">LEFT(A102)</f>
-        <v>W</v>
+        <f t="shared" si="11"/>
+        <v>R</v>
       </c>
       <c r="C102" t="s">
-        <v>234</v>
+        <v>152</v>
       </c>
       <c r="D102" s="1">
         <v>2016</v>
@@ -8505,18 +8574,19 @@
         <v>8</v>
       </c>
       <c r="F102" t="s">
-        <v>452</v>
+        <v>122</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="B103" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="C103" s="9" t="s">
-        <v>454</v>
+      <c r="A103" t="s">
+        <v>441</v>
+      </c>
+      <c r="B103" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>P</v>
+      </c>
+      <c r="C103" t="s">
+        <v>442</v>
       </c>
       <c r="D103" s="1">
         <v>2016</v>
@@ -8525,19 +8595,19 @@
         <v>8</v>
       </c>
       <c r="F103" t="s">
-        <v>455</v>
+        <v>94</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="9" t="s">
-        <v>456</v>
+      <c r="A104" t="s">
+        <v>443</v>
       </c>
       <c r="B104" s="1" t="str">
-        <f t="shared" ref="B104:B122" si="8">LEFT(A104)</f>
-        <v>D</v>
-      </c>
-      <c r="C104" s="9" t="s">
-        <v>178</v>
+        <f t="shared" si="11"/>
+        <v>M</v>
+      </c>
+      <c r="C104" t="s">
+        <v>444</v>
       </c>
       <c r="D104" s="1">
         <v>2016</v>
@@ -8546,19 +8616,19 @@
         <v>8</v>
       </c>
       <c r="F104" t="s">
-        <v>232</v>
+        <v>445</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="9" t="s">
-        <v>457</v>
+      <c r="A105" t="s">
+        <v>446</v>
       </c>
       <c r="B105" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>F</v>
-      </c>
-      <c r="C105" s="9" t="s">
-        <v>458</v>
+        <f t="shared" si="11"/>
+        <v>M</v>
+      </c>
+      <c r="C105" t="s">
+        <v>447</v>
       </c>
       <c r="D105" s="1">
         <v>2016</v>
@@ -8567,19 +8637,19 @@
         <v>8</v>
       </c>
       <c r="F105" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="9" t="s">
-        <v>460</v>
+      <c r="A106" t="s">
+        <v>449</v>
       </c>
       <c r="B106" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>G</v>
-      </c>
-      <c r="C106" s="9" t="s">
-        <v>461</v>
+        <f t="shared" si="11"/>
+        <v>O</v>
+      </c>
+      <c r="C106" t="s">
+        <v>431</v>
       </c>
       <c r="D106" s="1">
         <v>2016</v>
@@ -8588,19 +8658,19 @@
         <v>8</v>
       </c>
       <c r="F106" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="9" t="s">
-        <v>462</v>
+      <c r="A107" t="s">
+        <v>451</v>
       </c>
       <c r="B107" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>M</v>
-      </c>
-      <c r="C107" s="9" t="s">
-        <v>463</v>
+        <f t="shared" ref="B107" si="12">LEFT(A107)</f>
+        <v>W</v>
+      </c>
+      <c r="C107" t="s">
+        <v>234</v>
       </c>
       <c r="D107" s="1">
         <v>2016</v>
@@ -8609,19 +8679,18 @@
         <v>8</v>
       </c>
       <c r="F107" t="s">
-        <v>91</v>
+        <v>452</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="9" t="s">
-        <v>464</v>
-      </c>
-      <c r="B108" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>M</v>
+        <v>453</v>
+      </c>
+      <c r="B108" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>191</v>
+        <v>454</v>
       </c>
       <c r="D108" s="1">
         <v>2016</v>
@@ -8630,19 +8699,19 @@
         <v>8</v>
       </c>
       <c r="F108" t="s">
-        <v>267</v>
+        <v>455</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="9" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="B109" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>P</v>
+        <f t="shared" ref="B109:B127" si="13">LEFT(A109)</f>
+        <v>D</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>466</v>
+        <v>178</v>
       </c>
       <c r="D109" s="1">
         <v>2016</v>
@@ -8651,273 +8720,378 @@
         <v>8</v>
       </c>
       <c r="F109" t="s">
-        <v>104</v>
+        <v>232</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="9" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="B110" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>B</v>
+        <f t="shared" si="13"/>
+        <v>F</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="D110" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F110" t="s">
-        <v>136</v>
+        <v>459</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="9" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="B111" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>C</v>
+        <f t="shared" si="13"/>
+        <v>G</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="D111" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F111" t="s">
-        <v>142</v>
+        <v>429</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="9" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="B112" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>M</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="D112" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F112" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="9" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="B113" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>S</v>
+        <f t="shared" si="13"/>
+        <v>M</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>474</v>
+        <v>191</v>
       </c>
       <c r="D113" s="1">
-        <v>2015</v>
-      </c>
-      <c r="E113" s="12" t="s">
+        <v>2016</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F113" t="s">
-        <v>99</v>
+        <v>267</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="9" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="B114" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>V</v>
+        <f t="shared" si="13"/>
+        <v>P</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>401</v>
+        <v>466</v>
       </c>
       <c r="D114" s="1">
-        <v>2015</v>
-      </c>
-      <c r="E114" s="12" t="s">
+        <v>2016</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F114" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="9" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="B115" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>P</v>
+        <f t="shared" si="13"/>
+        <v>B</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>310</v>
+        <v>468</v>
       </c>
       <c r="D115" s="1">
         <v>2015</v>
       </c>
-      <c r="E115" s="12" t="s">
+      <c r="E115" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F115" t="s">
-        <v>477</v>
+        <v>136</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="9" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="B116" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>P</v>
+        <f t="shared" si="13"/>
+        <v>C</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="D116" s="1">
         <v>2015</v>
       </c>
-      <c r="E116" s="12" t="s">
+      <c r="E116" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F116" t="s">
-        <v>91</v>
+        <v>142</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="9" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="B117" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>Z</v>
+        <f t="shared" si="13"/>
+        <v>M</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="D117" s="1">
         <v>2015</v>
       </c>
-      <c r="E117" s="12" t="s">
+      <c r="E117" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F117" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="9" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="B118" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>B</v>
-      </c>
-      <c r="C118" s="12" t="s">
-        <v>347</v>
+        <f t="shared" si="13"/>
+        <v>S</v>
+      </c>
+      <c r="C118" s="9" t="s">
+        <v>474</v>
       </c>
       <c r="D118" s="1">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="E118" s="12" t="s">
         <v>8</v>
       </c>
       <c r="F118" t="s">
-        <v>459</v>
+        <v>99</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="9" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="B119" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>B</v>
+        <f t="shared" si="13"/>
+        <v>V</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>234</v>
+        <v>401</v>
       </c>
       <c r="D119" s="1">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="E119" s="12" t="s">
         <v>8</v>
       </c>
       <c r="F119" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>484</v>
+      <c r="A120" s="9" t="s">
+        <v>476</v>
       </c>
       <c r="B120" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>D</v>
+        <f t="shared" si="13"/>
+        <v>P</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>125</v>
+        <v>310</v>
       </c>
       <c r="D120" s="1">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="E120" s="12" t="s">
         <v>8</v>
       </c>
       <c r="F120" t="s">
-        <v>283</v>
+        <v>477</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="9" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="B121" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>M</v>
+        <f t="shared" si="13"/>
+        <v>P</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>304</v>
+        <v>479</v>
       </c>
       <c r="D121" s="1">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="E121" s="12" t="s">
         <v>8</v>
       </c>
       <c r="F121" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="B122" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>Z</v>
+      </c>
+      <c r="C122" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="D122" s="1">
+        <v>2015</v>
+      </c>
+      <c r="E122" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F122" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="B123" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>B</v>
+      </c>
+      <c r="C123" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="D123" s="1">
+        <v>2014</v>
+      </c>
+      <c r="E123" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F123" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="B124" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>B</v>
+      </c>
+      <c r="C124" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="D124" s="1">
+        <v>2014</v>
+      </c>
+      <c r="E124" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F124" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>484</v>
+      </c>
+      <c r="B125" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>D</v>
+      </c>
+      <c r="C125" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="D125" s="1">
+        <v>2014</v>
+      </c>
+      <c r="E125" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F125" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B122" s="1" t="str">
-        <f t="shared" si="8"/>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="B126" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>M</v>
+      </c>
+      <c r="C126" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="D126" s="1">
+        <v>2014</v>
+      </c>
+      <c r="E126" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F126" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B127" s="1" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H51" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="I51" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="I49" r:id="rId3" xr:uid="{B53F0185-E12A-4B2F-B690-A355769CD3F8}"/>
-    <hyperlink ref="I58" r:id="rId4" xr:uid="{65BCD137-8AB5-49F1-9E6E-D630706BF1D1}"/>
+    <hyperlink ref="H56" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="I56" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="I54" r:id="rId3" xr:uid="{B53F0185-E12A-4B2F-B690-A355769CD3F8}"/>
+    <hyperlink ref="I63" r:id="rId4" xr:uid="{65BCD137-8AB5-49F1-9E6E-D630706BF1D1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -8927,13 +9101,13 @@
           <x14:formula1>
             <xm:f>Ecoles!$A$2:$A$71</xm:f>
           </x14:formula1>
-          <xm:sqref>F123:F128</xm:sqref>
+          <xm:sqref>F128:F133</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{986D1C62-C1E8-4BE3-9C02-C464CE3171CD}">
           <x14:formula1>
             <xm:f>Ecoles!$A$2:$A$72</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F122</xm:sqref>
+          <xm:sqref>F2:F127 N15</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8943,7 +9117,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" style="3" customWidth="1"/>
@@ -11416,6 +11590,32 @@
       </c>
       <c r="L72" t="s">
         <v>992</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="G73" s="43" t="s">
+        <v>1009</v>
+      </c>
+      <c r="H73" s="88" t="s">
+        <v>1010</v>
+      </c>
+      <c r="I73" s="88" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J73" s="88" t="s">
+        <v>1012</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="L73" s="89" t="s">
+        <v>1013</v>
       </c>
     </row>
   </sheetData>
@@ -11462,7 +11662,7 @@
     <hyperlink ref="K36" r:id="rId40" xr:uid="{87C06C5F-822D-43FA-82C9-715CB2262286}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId41"/>
 </worksheet>
 </file>
 
@@ -11830,7 +12030,7 @@
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="84" t="s">
+      <c r="A28" s="85" t="s">
         <v>843</v>
       </c>
       <c r="B28" s="83"/>
@@ -11870,7 +12070,7 @@
       <c r="Q29" s="83"/>
     </row>
     <row r="30" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="85" t="s">
+      <c r="A30" s="84" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="82" t="s">
@@ -12001,7 +12201,7 @@
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="84" t="s">
+      <c r="A33" s="85" t="s">
         <v>644</v>
       </c>
       <c r="B33" s="83"/>
@@ -12041,7 +12241,7 @@
       <c r="Q34" s="83"/>
     </row>
     <row r="35" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="85" t="s">
+      <c r="A35" s="84" t="s">
         <v>20</v>
       </c>
       <c r="B35" s="82" t="s">
@@ -12558,7 +12758,7 @@
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="84" t="s">
+      <c r="A48" s="85" t="s">
         <v>851</v>
       </c>
       <c r="B48" s="83"/>
@@ -12598,7 +12798,7 @@
       <c r="Q49" s="83"/>
     </row>
     <row r="50" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="85" t="s">
+      <c r="A50" s="84" t="s">
         <v>20</v>
       </c>
       <c r="B50" s="82" t="s">
@@ -12729,7 +12929,7 @@
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53" s="84" t="s">
+      <c r="A53" s="85" t="s">
         <v>853</v>
       </c>
       <c r="B53" s="83"/>
@@ -12769,7 +12969,7 @@
       <c r="Q54" s="83"/>
     </row>
     <row r="55" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="85" t="s">
+      <c r="A55" s="84" t="s">
         <v>20</v>
       </c>
       <c r="B55" s="82" t="s">
@@ -13354,7 +13554,7 @@
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A72" s="84" t="s">
+      <c r="A72" s="85" t="s">
         <v>856</v>
       </c>
       <c r="B72" s="83"/>
@@ -13394,7 +13594,7 @@
       <c r="Q73" s="83"/>
     </row>
     <row r="74" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="85" t="s">
+      <c r="A74" s="84" t="s">
         <v>20</v>
       </c>
       <c r="B74" s="82" t="s">
@@ -13649,7 +13849,7 @@
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A81" s="84" t="s">
+      <c r="A81" s="85" t="s">
         <v>858</v>
       </c>
       <c r="B81" s="83"/>
@@ -13689,7 +13889,7 @@
       <c r="Q82" s="83"/>
     </row>
     <row r="83" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="85" t="s">
+      <c r="A83" s="84" t="s">
         <v>20</v>
       </c>
       <c r="B83" s="82" t="s">
@@ -14043,7 +14243,7 @@
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A93" s="84" t="s">
+      <c r="A93" s="85" t="s">
         <v>863</v>
       </c>
       <c r="B93" s="83"/>
@@ -14083,7 +14283,7 @@
       <c r="Q94" s="83"/>
     </row>
     <row r="95" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="85" t="s">
+      <c r="A95" s="84" t="s">
         <v>20</v>
       </c>
       <c r="B95" s="82" t="s">
@@ -15163,7 +15363,7 @@
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A127" s="84" t="s">
+      <c r="A127" s="85" t="s">
         <v>557</v>
       </c>
       <c r="B127" s="83"/>
@@ -15203,7 +15403,7 @@
       <c r="Q128" s="83"/>
     </row>
     <row r="129" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="85" t="s">
+      <c r="A129" s="84" t="s">
         <v>20</v>
       </c>
       <c r="B129" s="82" t="s">
@@ -16411,7 +16611,7 @@
       </c>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A159" s="84" t="s">
+      <c r="A159" s="85" t="s">
         <v>46</v>
       </c>
       <c r="B159" s="83"/>
@@ -16451,7 +16651,7 @@
       <c r="Q160" s="83"/>
     </row>
     <row r="161" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="85" t="s">
+      <c r="A161" s="84" t="s">
         <v>20</v>
       </c>
       <c r="B161" s="82" t="s">
@@ -16582,7 +16782,7 @@
       </c>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A164" s="84" t="s">
+      <c r="A164" s="85" t="s">
         <v>69</v>
       </c>
       <c r="B164" s="83"/>
@@ -16622,7 +16822,7 @@
       <c r="Q165" s="83"/>
     </row>
     <row r="166" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="85" t="s">
+      <c r="A166" s="84" t="s">
         <v>20</v>
       </c>
       <c r="B166" s="82" t="s">
@@ -16878,6 +17078,70 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="P35:P36"/>
+    <mergeCell ref="E161:G161"/>
+    <mergeCell ref="K30:O30"/>
+    <mergeCell ref="A164:Q165"/>
+    <mergeCell ref="B166:D166"/>
+    <mergeCell ref="K55:O55"/>
+    <mergeCell ref="E95:G95"/>
+    <mergeCell ref="A33:Q34"/>
+    <mergeCell ref="A72:Q73"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A53:Q54"/>
+    <mergeCell ref="H95:J95"/>
+    <mergeCell ref="P166:P167"/>
+    <mergeCell ref="A127:Q128"/>
+    <mergeCell ref="K161:O161"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A28:Q29"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A48:Q49"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="Q55:Q56"/>
+    <mergeCell ref="P50:P51"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="Q74:Q75"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="Q83:Q84"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="K35:O35"/>
+    <mergeCell ref="Q30:Q31"/>
+    <mergeCell ref="K50:O50"/>
+    <mergeCell ref="B161:D161"/>
+    <mergeCell ref="P129:P130"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="K74:O74"/>
+    <mergeCell ref="K83:O83"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="A129:A130"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="H166:J166"/>
+    <mergeCell ref="E129:G129"/>
+    <mergeCell ref="H161:J161"/>
+    <mergeCell ref="H129:J129"/>
+    <mergeCell ref="E74:G74"/>
+    <mergeCell ref="E166:G166"/>
+    <mergeCell ref="K95:O95"/>
+    <mergeCell ref="Q166:Q167"/>
+    <mergeCell ref="Q35:Q36"/>
+    <mergeCell ref="P161:P162"/>
+    <mergeCell ref="A159:Q160"/>
+    <mergeCell ref="A93:Q94"/>
+    <mergeCell ref="Q161:Q162"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="P83:P84"/>
+    <mergeCell ref="Q129:Q130"/>
+    <mergeCell ref="Q95:Q96"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="H55:J55"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="P55:P56"/>
     <mergeCell ref="K166:O166"/>
     <mergeCell ref="H74:J74"/>
     <mergeCell ref="H83:J83"/>
@@ -16894,70 +17158,6 @@
     <mergeCell ref="A81:Q82"/>
     <mergeCell ref="A95:A96"/>
     <mergeCell ref="B129:D129"/>
-    <mergeCell ref="Q166:Q167"/>
-    <mergeCell ref="Q35:Q36"/>
-    <mergeCell ref="P161:P162"/>
-    <mergeCell ref="A159:Q160"/>
-    <mergeCell ref="A93:Q94"/>
-    <mergeCell ref="Q161:Q162"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="P83:P84"/>
-    <mergeCell ref="Q129:Q130"/>
-    <mergeCell ref="Q95:Q96"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="H55:J55"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="B161:D161"/>
-    <mergeCell ref="P129:P130"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="K74:O74"/>
-    <mergeCell ref="K83:O83"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="A129:A130"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="H166:J166"/>
-    <mergeCell ref="E129:G129"/>
-    <mergeCell ref="H161:J161"/>
-    <mergeCell ref="H129:J129"/>
-    <mergeCell ref="E74:G74"/>
-    <mergeCell ref="E166:G166"/>
-    <mergeCell ref="K95:O95"/>
-    <mergeCell ref="A28:Q29"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A48:Q49"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="Q55:Q56"/>
-    <mergeCell ref="P50:P51"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="Q74:Q75"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="P30:P31"/>
-    <mergeCell ref="Q83:Q84"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="K35:O35"/>
-    <mergeCell ref="Q30:Q31"/>
-    <mergeCell ref="K50:O50"/>
-    <mergeCell ref="P35:P36"/>
-    <mergeCell ref="E161:G161"/>
-    <mergeCell ref="K30:O30"/>
-    <mergeCell ref="A164:Q165"/>
-    <mergeCell ref="B166:D166"/>
-    <mergeCell ref="K55:O55"/>
-    <mergeCell ref="E95:G95"/>
-    <mergeCell ref="A33:Q34"/>
-    <mergeCell ref="A72:Q73"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="A53:Q54"/>
-    <mergeCell ref="H95:J95"/>
-    <mergeCell ref="P166:P167"/>
-    <mergeCell ref="A127:Q128"/>
-    <mergeCell ref="K161:O161"/>
-    <mergeCell ref="H30:J30"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.scei-concours.fr/stat2025/bcpst.html" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -17093,7 +17293,7 @@
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="84" t="s">
+      <c r="A24" s="85" t="s">
         <v>19</v>
       </c>
       <c r="B24" s="83"/>
@@ -17133,7 +17333,7 @@
       <c r="Q25" s="83"/>
     </row>
     <row r="26" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="85" t="s">
+      <c r="A26" s="84" t="s">
         <v>20</v>
       </c>
       <c r="B26" s="82" t="s">
@@ -17718,7 +17918,7 @@
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="84" t="s">
+      <c r="A43" s="85" t="s">
         <v>46</v>
       </c>
       <c r="B43" s="83"/>
@@ -17758,7 +17958,7 @@
       <c r="Q44" s="83"/>
     </row>
     <row r="45" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="85" t="s">
+      <c r="A45" s="84" t="s">
         <v>20</v>
       </c>
       <c r="B45" s="82" t="s">
@@ -17889,7 +18089,7 @@
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="84" t="s">
+      <c r="A48" s="85" t="s">
         <v>47</v>
       </c>
       <c r="B48" s="83"/>
@@ -17929,7 +18129,7 @@
       <c r="Q49" s="83"/>
     </row>
     <row r="50" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="85" t="s">
+      <c r="A50" s="84" t="s">
         <v>20</v>
       </c>
       <c r="B50" s="82" t="s">
@@ -18184,7 +18384,7 @@
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57" s="84" t="s">
+      <c r="A57" s="85" t="s">
         <v>53</v>
       </c>
       <c r="B57" s="83"/>
@@ -18224,7 +18424,7 @@
       <c r="Q58" s="83"/>
     </row>
     <row r="59" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="85" t="s">
+      <c r="A59" s="84" t="s">
         <v>20</v>
       </c>
       <c r="B59" s="82" t="s">
@@ -18776,7 +18976,7 @@
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75" s="84" t="s">
+      <c r="A75" s="85" t="s">
         <v>67</v>
       </c>
       <c r="B75" s="83"/>
@@ -18816,7 +19016,7 @@
       <c r="Q76" s="83"/>
     </row>
     <row r="77" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="85" t="s">
+      <c r="A77" s="84" t="s">
         <v>20</v>
       </c>
       <c r="B77" s="82" t="s">
@@ -18947,7 +19147,7 @@
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A80" s="84" t="s">
+      <c r="A80" s="85" t="s">
         <v>69</v>
       </c>
       <c r="B80" s="83"/>
@@ -18987,7 +19187,7 @@
       <c r="Q81" s="83"/>
     </row>
     <row r="82" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="85" t="s">
+      <c r="A82" s="84" t="s">
         <v>20</v>
       </c>
       <c r="B82" s="82" t="s">
@@ -19210,6 +19410,38 @@
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="K50:O50"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="Q50:Q51"/>
+    <mergeCell ref="A43:Q44"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="Q26:Q27"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="P50:P51"/>
+    <mergeCell ref="K45:O45"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="K26:O26"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="A75:Q76"/>
+    <mergeCell ref="P59:P60"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="A57:Q58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="P82:P83"/>
+    <mergeCell ref="Q59:Q60"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="K59:O59"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="Q82:Q83"/>
+    <mergeCell ref="K77:O77"/>
+    <mergeCell ref="P77:P78"/>
+    <mergeCell ref="E77:G77"/>
     <mergeCell ref="A24:Q25"/>
     <mergeCell ref="K82:O82"/>
     <mergeCell ref="H50:J50"/>
@@ -19226,38 +19458,6 @@
     <mergeCell ref="H82:J82"/>
     <mergeCell ref="Q45:Q46"/>
     <mergeCell ref="A48:Q49"/>
-    <mergeCell ref="P82:P83"/>
-    <mergeCell ref="Q59:Q60"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="K59:O59"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="Q82:Q83"/>
-    <mergeCell ref="K77:O77"/>
-    <mergeCell ref="P77:P78"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="A75:Q76"/>
-    <mergeCell ref="P59:P60"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="A57:Q58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="K50:O50"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="Q50:Q51"/>
-    <mergeCell ref="A43:Q44"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="P50:P51"/>
-    <mergeCell ref="K45:O45"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="K26:O26"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B50:D50"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.scei-concours.fr/stat2025/tb.html" xr:uid="{00000000-0004-0000-0500-000000000000}"/>

--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud2\Boulot 2026\Site orientation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E940984-3C4B-4992-B349-5CFD68C12847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA5455E-D69E-4FDF-8EC2-1371C1877342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elèves_BCPST" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2470" uniqueCount="1015">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2471" uniqueCount="1016">
   <si>
     <t>Statistiques 2025</t>
   </si>
@@ -3078,13 +3078,16 @@
   </si>
   <si>
     <t>https://external-content.duckduckgo.com/iu/?u=https%3A%2F%2Fcareers.recruiteecdn.com%2Fimage%2Fupload%2Fq_auto%2Cw_1920%2Cc_limit%2Fproduction%2Fimages%2FBQC2%2FwIFApRbvNKFd.jpeg&amp;f=1&amp;nofb=1&amp;ipt=04c93c67c5ef840175d2e39636a76e85966178ae1c56d63ab1894ed4ca9f3ad3</t>
+  </si>
+  <si>
+    <t>https://youtu.be/mUE_eBgYsfk</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3354,7 +3357,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -3444,13 +3447,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3669,6 +3687,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3682,12 +3709,6 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4034,7 +4055,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.42578125" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" customWidth="1"/>
@@ -4047,7 +4068,7 @@
     <col min="9" max="9" width="21.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="70" t="s">
         <v>74</v>
       </c>
@@ -4076,7 +4097,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9">
       <c r="A2" s="78" t="s">
         <v>973</v>
       </c>
@@ -4100,7 +4121,7 @@
       <c r="H2" s="77"/>
       <c r="I2" s="77"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9">
       <c r="A3" s="76" t="s">
         <v>968</v>
       </c>
@@ -4124,7 +4145,7 @@
       <c r="H3" s="77"/>
       <c r="I3" s="77"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9">
       <c r="A4" s="72" t="s">
         <v>966</v>
       </c>
@@ -4150,7 +4171,7 @@
       <c r="H4" s="64"/>
       <c r="I4" s="64"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9">
       <c r="A5" s="72" t="s">
         <v>347</v>
       </c>
@@ -4174,7 +4195,7 @@
       <c r="H5" s="64"/>
       <c r="I5" s="64"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6" s="68" t="s">
         <v>958</v>
       </c>
@@ -4198,7 +4219,7 @@
       <c r="H6" s="74"/>
       <c r="I6" s="74"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="A7" s="68" t="s">
         <v>956</v>
       </c>
@@ -4222,7 +4243,7 @@
       <c r="H7" s="64"/>
       <c r="I7" s="64"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9">
       <c r="A8" s="68" t="s">
         <v>950</v>
       </c>
@@ -4246,7 +4267,7 @@
       <c r="H8" s="64"/>
       <c r="I8" s="64"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9">
       <c r="A9" s="68" t="s">
         <v>948</v>
       </c>
@@ -4270,7 +4291,7 @@
       <c r="H9" s="64"/>
       <c r="I9" s="64"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" s="68" t="s">
         <v>946</v>
       </c>
@@ -4296,7 +4317,7 @@
       <c r="H10" s="64"/>
       <c r="I10" s="64"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="A11" s="69" t="s">
         <v>944</v>
       </c>
@@ -4320,7 +4341,7 @@
       <c r="H11" s="64"/>
       <c r="I11" s="64"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="A12" s="66" t="s">
         <v>83</v>
       </c>
@@ -4344,7 +4365,7 @@
       <c r="H12" s="67"/>
       <c r="I12" s="67"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
         <v>86</v>
       </c>
@@ -4367,7 +4388,7 @@
       <c r="G13" s="1"/>
       <c r="H13" s="75"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
         <v>89</v>
       </c>
@@ -4389,7 +4410,7 @@
       </c>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
         <v>92</v>
       </c>
@@ -4411,7 +4432,7 @@
       </c>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
         <v>95</v>
       </c>
@@ -4433,7 +4454,7 @@
       </c>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
         <v>97</v>
       </c>
@@ -4455,7 +4476,7 @@
       </c>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8">
       <c r="A18" s="36" t="s">
         <v>100</v>
       </c>
@@ -4477,7 +4498,7 @@
       </c>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="A19" s="36" t="s">
         <v>102</v>
       </c>
@@ -4499,7 +4520,7 @@
       </c>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="36" t="s">
         <v>105</v>
       </c>
@@ -4521,7 +4542,7 @@
       </c>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="36" t="s">
         <v>108</v>
       </c>
@@ -4543,7 +4564,7 @@
       </c>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" s="36" t="s">
         <v>110</v>
       </c>
@@ -4565,7 +4586,7 @@
       </c>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" s="36" t="s">
         <v>113</v>
       </c>
@@ -4590,7 +4611,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8">
       <c r="A24" s="36" t="s">
         <v>117</v>
       </c>
@@ -4612,7 +4633,7 @@
       </c>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" s="36" t="s">
         <v>120</v>
       </c>
@@ -4634,7 +4655,7 @@
       </c>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" s="36" t="s">
         <v>123</v>
       </c>
@@ -4656,7 +4677,7 @@
       </c>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" s="36" t="s">
         <v>127</v>
       </c>
@@ -4678,7 +4699,7 @@
       </c>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" s="36" t="s">
         <v>130</v>
       </c>
@@ -4700,7 +4721,7 @@
       </c>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="A29" s="36" t="s">
         <v>132</v>
       </c>
@@ -4722,7 +4743,7 @@
       </c>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8">
       <c r="A30" s="36" t="s">
         <v>134</v>
       </c>
@@ -4744,7 +4765,7 @@
       </c>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8">
       <c r="A31" s="38" t="s">
         <v>137</v>
       </c>
@@ -4766,7 +4787,7 @@
       </c>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8">
       <c r="A32" s="38" t="s">
         <v>140</v>
       </c>
@@ -4788,7 +4809,7 @@
       </c>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8">
       <c r="A33" s="38" t="s">
         <v>143</v>
       </c>
@@ -4810,7 +4831,7 @@
       </c>
       <c r="G33" s="1"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8">
       <c r="A34" s="38" t="s">
         <v>146</v>
       </c>
@@ -4832,7 +4853,7 @@
       </c>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8">
       <c r="A35" s="38" t="s">
         <v>148</v>
       </c>
@@ -4854,7 +4875,7 @@
       </c>
       <c r="G35" s="1"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8">
       <c r="A36" s="38" t="s">
         <v>150</v>
       </c>
@@ -4876,7 +4897,7 @@
       </c>
       <c r="G36" s="1"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8">
       <c r="A37" s="38" t="s">
         <v>151</v>
       </c>
@@ -4898,7 +4919,7 @@
       </c>
       <c r="G37" s="1"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8">
       <c r="A38" s="38" t="s">
         <v>153</v>
       </c>
@@ -4920,7 +4941,7 @@
       </c>
       <c r="G38" s="1"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8">
       <c r="A39" s="1"/>
       <c r="B39" s="1" t="str">
         <f t="shared" si="8"/>
@@ -4938,7 +4959,7 @@
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8">
       <c r="A40" s="38" t="s">
         <v>156</v>
       </c>
@@ -4960,7 +4981,7 @@
       </c>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8">
       <c r="A41" s="38" t="s">
         <v>158</v>
       </c>
@@ -4982,7 +5003,7 @@
       </c>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8">
       <c r="A42" s="38" t="s">
         <v>160</v>
       </c>
@@ -5007,7 +5028,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8">
       <c r="A43" s="38" t="s">
         <v>163</v>
       </c>
@@ -5029,7 +5050,7 @@
       </c>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8">
       <c r="A44" s="1"/>
       <c r="B44" s="1" t="str">
         <f t="shared" si="8"/>
@@ -5049,7 +5070,7 @@
       </c>
       <c r="G44" s="1"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8">
       <c r="A45" s="38" t="s">
         <v>166</v>
       </c>
@@ -5071,7 +5092,7 @@
       </c>
       <c r="G45" s="1"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8">
       <c r="A46" s="38" t="s">
         <v>167</v>
       </c>
@@ -5093,7 +5114,7 @@
       </c>
       <c r="G46" s="1"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8">
       <c r="A47" s="38" t="s">
         <v>170</v>
       </c>
@@ -5115,7 +5136,7 @@
       </c>
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8">
       <c r="A48" s="38" t="s">
         <v>171</v>
       </c>
@@ -5137,7 +5158,7 @@
       </c>
       <c r="G48" s="1"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7">
       <c r="A49" s="38" t="s">
         <v>173</v>
       </c>
@@ -5159,7 +5180,7 @@
       </c>
       <c r="G49" s="1"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7">
       <c r="A50" s="38" t="s">
         <v>175</v>
       </c>
@@ -5181,7 +5202,7 @@
       </c>
       <c r="G50" s="1"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7">
       <c r="A51" s="38" t="s">
         <v>177</v>
       </c>
@@ -5203,7 +5224,7 @@
       </c>
       <c r="G51" s="35"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7">
       <c r="A52" s="38" t="s">
         <v>179</v>
       </c>
@@ -5225,7 +5246,7 @@
       </c>
       <c r="G52" s="35"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7">
       <c r="A53" s="38" t="s">
         <v>180</v>
       </c>
@@ -5249,7 +5270,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="str">
         <f t="shared" si="8"/>
@@ -5271,7 +5292,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="str">
         <f t="shared" si="8"/>
@@ -5293,7 +5314,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="str">
         <f t="shared" si="8"/>
@@ -5313,7 +5334,7 @@
       </c>
       <c r="G56" s="35"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7">
       <c r="A57" s="38" t="s">
         <v>186</v>
       </c>
@@ -5335,7 +5356,7 @@
       </c>
       <c r="G57" s="35"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7">
       <c r="A58" s="38" t="s">
         <v>189</v>
       </c>
@@ -5357,7 +5378,7 @@
       </c>
       <c r="G58" s="35"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7">
       <c r="A59" s="38" t="s">
         <v>190</v>
       </c>
@@ -5379,7 +5400,7 @@
       </c>
       <c r="G59" s="35"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7">
       <c r="A60" s="38" t="s">
         <v>192</v>
       </c>
@@ -5401,7 +5422,7 @@
       </c>
       <c r="G60" s="35"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7">
       <c r="A61" s="38" t="s">
         <v>195</v>
       </c>
@@ -5423,7 +5444,7 @@
       </c>
       <c r="G61" s="35"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7">
       <c r="A62" s="38" t="s">
         <v>198</v>
       </c>
@@ -5445,7 +5466,7 @@
       </c>
       <c r="G62" s="35"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7">
       <c r="A63" s="38" t="s">
         <v>200</v>
       </c>
@@ -5467,7 +5488,7 @@
       </c>
       <c r="G63" s="35"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7">
       <c r="A64" s="38" t="s">
         <v>202</v>
       </c>
@@ -5489,7 +5510,7 @@
       </c>
       <c r="G64" s="35"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7">
       <c r="A65" s="38" t="s">
         <v>204</v>
       </c>
@@ -5511,7 +5532,7 @@
       </c>
       <c r="G65" s="35"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7">
       <c r="A66" s="38" t="s">
         <v>206</v>
       </c>
@@ -5533,7 +5554,7 @@
       </c>
       <c r="G66" s="35"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7">
       <c r="A67" s="38" t="s">
         <v>208</v>
       </c>
@@ -5555,7 +5576,7 @@
       </c>
       <c r="G67" s="35"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7">
       <c r="A68" s="38" t="s">
         <v>210</v>
       </c>
@@ -5577,7 +5598,7 @@
       </c>
       <c r="G68" s="35"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7">
       <c r="A69" s="38" t="s">
         <v>213</v>
       </c>
@@ -5599,7 +5620,7 @@
       </c>
       <c r="G69" s="35"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7">
       <c r="A70" s="38" t="s">
         <v>215</v>
       </c>
@@ -5621,7 +5642,7 @@
       </c>
       <c r="G70" s="35"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7">
       <c r="A71" s="38" t="s">
         <v>217</v>
       </c>
@@ -5643,7 +5664,7 @@
       </c>
       <c r="G71" s="35"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7">
       <c r="A72" s="38" t="s">
         <v>219</v>
       </c>
@@ -5665,7 +5686,7 @@
       </c>
       <c r="G72" s="35"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7">
       <c r="A73" s="38" t="s">
         <v>221</v>
       </c>
@@ -5687,7 +5708,7 @@
       </c>
       <c r="G73" s="35"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7">
       <c r="A74" s="38" t="s">
         <v>223</v>
       </c>
@@ -5711,7 +5732,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7">
       <c r="A75" s="38" t="s">
         <v>225</v>
       </c>
@@ -5733,7 +5754,7 @@
       </c>
       <c r="G75" s="29"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7">
       <c r="A76" s="38" t="s">
         <v>226</v>
       </c>
@@ -5757,7 +5778,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7">
       <c r="A77" s="38" t="s">
         <v>228</v>
       </c>
@@ -5779,7 +5800,7 @@
       </c>
       <c r="G77" s="35"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7">
       <c r="A78" s="38" t="s">
         <v>230</v>
       </c>
@@ -5801,7 +5822,7 @@
       </c>
       <c r="G78" s="35"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7">
       <c r="A79" s="38" t="s">
         <v>233</v>
       </c>
@@ -5823,7 +5844,7 @@
       </c>
       <c r="G79" s="35"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7">
       <c r="A80" s="35" t="s">
         <v>235</v>
       </c>
@@ -5845,7 +5866,7 @@
       </c>
       <c r="G80" s="1"/>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7">
       <c r="A81" s="35" t="s">
         <v>237</v>
       </c>
@@ -5867,7 +5888,7 @@
       </c>
       <c r="G81" s="1"/>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7">
       <c r="A82" s="35" t="s">
         <v>239</v>
       </c>
@@ -5889,7 +5910,7 @@
       </c>
       <c r="G82" s="1"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7">
       <c r="A83" s="35" t="s">
         <v>242</v>
       </c>
@@ -5911,7 +5932,7 @@
       </c>
       <c r="G83" s="1"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7">
       <c r="A84" s="35" t="s">
         <v>244</v>
       </c>
@@ -5933,7 +5954,7 @@
       </c>
       <c r="G84" s="1"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7">
       <c r="A85" s="35" t="s">
         <v>245</v>
       </c>
@@ -5955,7 +5976,7 @@
       </c>
       <c r="G85" s="1"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7">
       <c r="A86" s="35" t="s">
         <v>247</v>
       </c>
@@ -5977,7 +5998,7 @@
       </c>
       <c r="G86" s="1"/>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7">
       <c r="A87" s="35" t="s">
         <v>249</v>
       </c>
@@ -5999,7 +6020,7 @@
       </c>
       <c r="G87" s="1"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7">
       <c r="A88" s="35" t="s">
         <v>251</v>
       </c>
@@ -6021,7 +6042,7 @@
       </c>
       <c r="G88" s="1"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7">
       <c r="A89" s="35" t="s">
         <v>254</v>
       </c>
@@ -6043,7 +6064,7 @@
       </c>
       <c r="G89" s="1"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7">
       <c r="A90" s="35" t="s">
         <v>256</v>
       </c>
@@ -6065,7 +6086,7 @@
       </c>
       <c r="G90" s="1"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7">
       <c r="A91" s="35" t="s">
         <v>259</v>
       </c>
@@ -6087,7 +6108,7 @@
       </c>
       <c r="G91" s="1"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7">
       <c r="A92" s="35" t="s">
         <v>261</v>
       </c>
@@ -6109,7 +6130,7 @@
       </c>
       <c r="G92" s="1"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7">
       <c r="A93" s="35" t="s">
         <v>263</v>
       </c>
@@ -6131,7 +6152,7 @@
       </c>
       <c r="G93" s="1"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7">
       <c r="A94" s="35" t="s">
         <v>265</v>
       </c>
@@ -6153,7 +6174,7 @@
       </c>
       <c r="G94" s="1"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7">
       <c r="A95" s="35" t="s">
         <v>268</v>
       </c>
@@ -6175,7 +6196,7 @@
       </c>
       <c r="G95" s="1"/>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7">
       <c r="A96" s="35" t="s">
         <v>270</v>
       </c>
@@ -6197,7 +6218,7 @@
       </c>
       <c r="G96" s="1"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6">
       <c r="A97" s="35" t="s">
         <v>271</v>
       </c>
@@ -6218,7 +6239,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6">
       <c r="A98" s="35" t="s">
         <v>273</v>
       </c>
@@ -6239,7 +6260,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6">
       <c r="A99" s="35"/>
       <c r="B99" s="1" t="str">
         <f t="shared" si="10"/>
@@ -6249,7 +6270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6">
       <c r="A100" s="35"/>
       <c r="B100" s="1" t="str">
         <f t="shared" si="10"/>
@@ -6259,7 +6280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6">
       <c r="A101" s="35"/>
       <c r="B101" s="1" t="str">
         <f t="shared" si="10"/>
@@ -6269,7 +6290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6">
       <c r="A102" s="35"/>
       <c r="B102" s="1" t="str">
         <f t="shared" si="10"/>
@@ -6279,7 +6300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6">
       <c r="A103" s="35"/>
       <c r="B103" s="1" t="str">
         <f t="shared" si="10"/>
@@ -6289,7 +6310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6">
       <c r="A104" s="35"/>
       <c r="B104" s="1" t="str">
         <f t="shared" si="10"/>
@@ -6299,7 +6320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6">
       <c r="A105" s="35"/>
       <c r="B105" s="1" t="str">
         <f t="shared" si="10"/>
@@ -6309,7 +6330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6">
       <c r="A106" s="35"/>
       <c r="B106" s="1" t="str">
         <f t="shared" si="10"/>
@@ -6319,7 +6340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6">
       <c r="A107" s="35"/>
       <c r="B107" s="1" t="str">
         <f t="shared" si="10"/>
@@ -6329,7 +6350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6">
       <c r="A108" s="35"/>
       <c r="B108" s="1" t="str">
         <f t="shared" si="10"/>
@@ -6339,7 +6360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6">
       <c r="B109" s="1" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -6348,7 +6369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6">
       <c r="B110" s="1" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -6381,7 +6402,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N127"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
@@ -6390,7 +6411,7 @@
     <col min="9" max="9" width="96.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>275</v>
       </c>
@@ -6416,7 +6437,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
         <v>1007</v>
       </c>
@@ -6434,12 +6455,12 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="37"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1008</v>
+      </c>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
         <v>1005</v>
       </c>
@@ -6459,10 +6480,10 @@
       <c r="F3" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="37"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
         <v>1003</v>
       </c>
@@ -6482,10 +6503,10 @@
       <c r="F4" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="37"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
         <v>1002</v>
       </c>
@@ -6505,10 +6526,10 @@
       <c r="F5" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="37"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
         <v>1001</v>
       </c>
@@ -6528,10 +6549,10 @@
       <c r="F6" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="37"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H6" s="84"/>
+      <c r="I6" s="84"/>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
         <v>974</v>
       </c>
@@ -6551,10 +6572,10 @@
       <c r="F7" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="37"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H7" s="84"/>
+      <c r="I7" s="84"/>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
         <v>971</v>
       </c>
@@ -6574,10 +6595,10 @@
       <c r="F8" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H8" s="84"/>
+      <c r="I8" s="84"/>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
         <v>970</v>
       </c>
@@ -6597,10 +6618,10 @@
       <c r="F9" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H9" s="84"/>
+      <c r="I9" s="84"/>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
         <v>959</v>
       </c>
@@ -6620,10 +6641,10 @@
       <c r="F10" s="1" t="s">
         <v>961</v>
       </c>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H10" s="74"/>
+      <c r="I10" s="74"/>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
         <v>276</v>
       </c>
@@ -6646,7 +6667,7 @@
       <c r="H11" s="64"/>
       <c r="I11" s="64"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
         <v>278</v>
       </c>
@@ -6669,7 +6690,7 @@
       <c r="H12" s="64"/>
       <c r="I12" s="64"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14">
       <c r="A13" s="1" t="s">
         <v>280</v>
       </c>
@@ -6690,7 +6711,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
         <v>281</v>
       </c>
@@ -6711,7 +6732,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14">
       <c r="A15" s="1" t="s">
         <v>284</v>
       </c>
@@ -6738,7 +6759,7 @@
       <c r="M15" s="64"/>
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14">
       <c r="A16" s="1" t="s">
         <v>286</v>
       </c>
@@ -6759,7 +6780,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
         <v>288</v>
       </c>
@@ -6780,7 +6801,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
         <v>290</v>
       </c>
@@ -6801,7 +6822,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
         <v>292</v>
       </c>
@@ -6822,7 +6843,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
         <v>294</v>
       </c>
@@ -6843,7 +6864,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
         <v>105</v>
       </c>
@@ -6864,7 +6885,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
         <v>297</v>
       </c>
@@ -6885,7 +6906,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
         <v>299</v>
       </c>
@@ -6906,7 +6927,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
         <v>301</v>
       </c>
@@ -6927,7 +6948,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
         <v>303</v>
       </c>
@@ -6948,7 +6969,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
         <v>305</v>
       </c>
@@ -6969,7 +6990,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
         <v>307</v>
       </c>
@@ -6990,7 +7011,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28" s="1" t="s">
         <v>309</v>
       </c>
@@ -7011,7 +7032,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29" s="1" t="s">
         <v>311</v>
       </c>
@@ -7032,7 +7053,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>313</v>
       </c>
@@ -7053,7 +7074,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31" s="7" t="s">
         <v>315</v>
       </c>
@@ -7074,7 +7095,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32" s="1" t="s">
         <v>316</v>
       </c>
@@ -7095,7 +7116,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
         <v>318</v>
       </c>
@@ -7116,7 +7137,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8">
       <c r="A34" t="s">
         <v>320</v>
       </c>
@@ -7137,7 +7158,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
         <v>321</v>
       </c>
@@ -7158,7 +7179,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8">
       <c r="A36" t="s">
         <v>323</v>
       </c>
@@ -7179,7 +7200,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8">
       <c r="A37" s="7" t="s">
         <v>325</v>
       </c>
@@ -7197,10 +7218,13 @@
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="H37" s="39" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="7" t="s">
         <v>327</v>
       </c>
@@ -7221,7 +7245,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8">
       <c r="A39" s="7" t="s">
         <v>329</v>
       </c>
@@ -7242,7 +7266,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8">
       <c r="A40" s="7" t="s">
         <v>331</v>
       </c>
@@ -7263,7 +7287,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8">
       <c r="A41" s="7" t="s">
         <v>332</v>
       </c>
@@ -7284,7 +7308,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8">
       <c r="A42" s="7" t="s">
         <v>335</v>
       </c>
@@ -7305,7 +7329,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8">
       <c r="A43" s="7" t="s">
         <v>337</v>
       </c>
@@ -7326,7 +7350,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8">
       <c r="A44" s="7" t="s">
         <v>339</v>
       </c>
@@ -7347,7 +7371,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8">
       <c r="A45" s="7" t="s">
         <v>341</v>
       </c>
@@ -7368,7 +7392,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8">
       <c r="A46" s="7" t="s">
         <v>343</v>
       </c>
@@ -7389,7 +7413,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8">
       <c r="A47" s="7" t="s">
         <v>346</v>
       </c>
@@ -7410,7 +7434,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8">
       <c r="A48" s="7" t="s">
         <v>348</v>
       </c>
@@ -7431,7 +7455,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9">
       <c r="A49" s="7" t="s">
         <v>350</v>
       </c>
@@ -7452,7 +7476,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9">
       <c r="A50" t="s">
         <v>351</v>
       </c>
@@ -7473,7 +7497,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9">
       <c r="A51" s="7" t="s">
         <v>354</v>
       </c>
@@ -7494,7 +7518,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9">
       <c r="A52" s="7" t="s">
         <v>356</v>
       </c>
@@ -7515,7 +7539,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9">
       <c r="A53" s="7" t="s">
         <v>357</v>
       </c>
@@ -7536,7 +7560,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9">
       <c r="A54" s="7" t="s">
         <v>359</v>
       </c>
@@ -7560,7 +7584,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9">
       <c r="A55" s="7" t="s">
         <v>360</v>
       </c>
@@ -7581,7 +7605,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9">
       <c r="A56" s="7" t="s">
         <v>362</v>
       </c>
@@ -7608,7 +7632,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9">
       <c r="A57" s="7" t="s">
         <v>365</v>
       </c>
@@ -7629,7 +7653,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9">
       <c r="A58" s="7" t="s">
         <v>288</v>
       </c>
@@ -7650,7 +7674,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9">
       <c r="A59" s="7" t="s">
         <v>367</v>
       </c>
@@ -7671,7 +7695,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9">
       <c r="A60" s="7" t="s">
         <v>368</v>
       </c>
@@ -7692,7 +7716,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9">
       <c r="A61" s="7" t="s">
         <v>371</v>
       </c>
@@ -7713,7 +7737,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9">
       <c r="A62" s="7" t="s">
         <v>373</v>
       </c>
@@ -7734,7 +7758,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9">
       <c r="A63" s="7" t="s">
         <v>375</v>
       </c>
@@ -7758,7 +7782,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9">
       <c r="A64" s="7" t="s">
         <v>377</v>
       </c>
@@ -7779,7 +7803,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>378</v>
       </c>
@@ -7800,7 +7824,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6">
       <c r="A66" s="7" t="s">
         <v>380</v>
       </c>
@@ -7821,7 +7845,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6">
       <c r="A67" s="7" t="s">
         <v>382</v>
       </c>
@@ -7842,7 +7866,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6">
       <c r="A68" s="7" t="s">
         <v>383</v>
       </c>
@@ -7863,7 +7887,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>385</v>
       </c>
@@ -7884,7 +7908,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>387</v>
       </c>
@@ -7905,7 +7929,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>389</v>
       </c>
@@ -7926,7 +7950,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
         <v>391</v>
       </c>
@@ -7947,7 +7971,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
         <v>393</v>
       </c>
@@ -7968,7 +7992,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>394</v>
       </c>
@@ -7989,7 +8013,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>396</v>
       </c>
@@ -8010,7 +8034,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>397</v>
       </c>
@@ -8031,7 +8055,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>399</v>
       </c>
@@ -8052,7 +8076,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>400</v>
       </c>
@@ -8073,7 +8097,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>402</v>
       </c>
@@ -8094,7 +8118,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
         <v>403</v>
       </c>
@@ -8115,7 +8139,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>405</v>
       </c>
@@ -8136,7 +8160,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>408</v>
       </c>
@@ -8157,7 +8181,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>409</v>
       </c>
@@ -8178,7 +8202,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>410</v>
       </c>
@@ -8199,7 +8223,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>412</v>
       </c>
@@ -8220,7 +8244,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
         <v>414</v>
       </c>
@@ -8241,7 +8265,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>415</v>
       </c>
@@ -8262,7 +8286,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
         <v>417</v>
       </c>
@@ -8283,7 +8307,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>418</v>
       </c>
@@ -8304,7 +8328,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>420</v>
       </c>
@@ -8325,7 +8349,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>422</v>
       </c>
@@ -8346,7 +8370,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>424</v>
       </c>
@@ -8367,7 +8391,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>425</v>
       </c>
@@ -8388,7 +8412,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
         <v>427</v>
       </c>
@@ -8409,7 +8433,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
         <v>430</v>
       </c>
@@ -8430,7 +8454,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>432</v>
       </c>
@@ -8451,7 +8475,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
         <v>433</v>
       </c>
@@ -8472,7 +8496,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>435</v>
       </c>
@@ -8493,7 +8517,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>436</v>
       </c>
@@ -8514,7 +8538,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
         <v>437</v>
       </c>
@@ -8535,7 +8559,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
         <v>438</v>
       </c>
@@ -8556,7 +8580,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
         <v>440</v>
       </c>
@@ -8577,7 +8601,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
         <v>441</v>
       </c>
@@ -8598,7 +8622,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
         <v>443</v>
       </c>
@@ -8619,7 +8643,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
         <v>446</v>
       </c>
@@ -8640,7 +8664,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
         <v>449</v>
       </c>
@@ -8661,7 +8685,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
         <v>451</v>
       </c>
@@ -8682,7 +8706,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6">
       <c r="A108" s="9" t="s">
         <v>453</v>
       </c>
@@ -8702,7 +8726,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6">
       <c r="A109" s="9" t="s">
         <v>456</v>
       </c>
@@ -8723,7 +8747,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6">
       <c r="A110" s="9" t="s">
         <v>457</v>
       </c>
@@ -8744,7 +8768,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6">
       <c r="A111" s="9" t="s">
         <v>460</v>
       </c>
@@ -8765,7 +8789,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6">
       <c r="A112" s="9" t="s">
         <v>462</v>
       </c>
@@ -8786,7 +8810,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6">
       <c r="A113" s="9" t="s">
         <v>464</v>
       </c>
@@ -8807,7 +8831,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6">
       <c r="A114" s="9" t="s">
         <v>465</v>
       </c>
@@ -8828,7 +8852,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6">
       <c r="A115" s="9" t="s">
         <v>467</v>
       </c>
@@ -8849,7 +8873,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6">
       <c r="A116" s="9" t="s">
         <v>469</v>
       </c>
@@ -8870,7 +8894,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6">
       <c r="A117" s="9" t="s">
         <v>471</v>
       </c>
@@ -8891,7 +8915,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6">
       <c r="A118" s="9" t="s">
         <v>473</v>
       </c>
@@ -8912,7 +8936,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6">
       <c r="A119" s="9" t="s">
         <v>475</v>
       </c>
@@ -8933,7 +8957,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6">
       <c r="A120" s="9" t="s">
         <v>476</v>
       </c>
@@ -8954,7 +8978,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6">
       <c r="A121" s="9" t="s">
         <v>478</v>
       </c>
@@ -8975,7 +8999,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6">
       <c r="A122" s="9" t="s">
         <v>480</v>
       </c>
@@ -8996,7 +9020,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6">
       <c r="A123" s="9" t="s">
         <v>482</v>
       </c>
@@ -9017,7 +9041,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6">
       <c r="A124" s="9" t="s">
         <v>483</v>
       </c>
@@ -9038,7 +9062,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>484</v>
       </c>
@@ -9059,7 +9083,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6">
       <c r="A126" s="9" t="s">
         <v>485</v>
       </c>
@@ -9080,7 +9104,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6">
       <c r="B127" s="1" t="str">
         <f t="shared" si="13"/>
         <v/>
@@ -9092,11 +9116,12 @@
     <hyperlink ref="I56" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
     <hyperlink ref="I54" r:id="rId3" xr:uid="{B53F0185-E12A-4B2F-B690-A355769CD3F8}"/>
     <hyperlink ref="I63" r:id="rId4" xr:uid="{65BCD137-8AB5-49F1-9E6E-D630706BF1D1}"/>
+    <hyperlink ref="H37" r:id="rId5" xr:uid="{E6008756-EABF-4007-B406-8FDB469A944B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{98F871A1-25E1-4B53-8B18-4D217B6E5DD0}">
           <x14:formula1>
             <xm:f>Ecoles!$A$2:$A$71</xm:f>
@@ -9107,7 +9132,13 @@
           <x14:formula1>
             <xm:f>Ecoles!$A$2:$A$72</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F127 N15</xm:sqref>
+          <xm:sqref>N15 F3:F127</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9E5868A2-5D00-445E-88D7-95E4AC81F094}">
+          <x14:formula1>
+            <xm:f>Ecoles!$A$2:$A$73</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -9118,7 +9149,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M73"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.28515625" style="3" customWidth="1"/>
     <col min="2" max="6" width="11.42578125" style="3" customWidth="1"/>
@@ -9131,7 +9162,7 @@
     <col min="13" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>74</v>
       </c>
@@ -9169,7 +9200,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>126</v>
       </c>
@@ -9204,7 +9235,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>115</v>
       </c>
@@ -9242,7 +9273,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
@@ -9277,7 +9308,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>122</v>
       </c>
@@ -9315,7 +9346,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>104</v>
       </c>
@@ -9353,7 +9384,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>283</v>
       </c>
@@ -9388,7 +9419,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>112</v>
       </c>
@@ -9426,7 +9457,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>136</v>
       </c>
@@ -9464,7 +9495,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>99</v>
       </c>
@@ -9499,7 +9530,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>345</v>
       </c>
@@ -9534,7 +9565,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>370</v>
       </c>
@@ -9569,7 +9600,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>142</v>
       </c>
@@ -9604,7 +9635,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>258</v>
       </c>
@@ -9639,7 +9670,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>232</v>
       </c>
@@ -9671,7 +9702,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>88</v>
       </c>
@@ -9700,7 +9731,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>169</v>
       </c>
@@ -9735,7 +9766,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>91</v>
       </c>
@@ -9770,7 +9801,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>194</v>
       </c>
@@ -9808,7 +9839,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>145</v>
       </c>
@@ -9843,7 +9874,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>85</v>
       </c>
@@ -9878,7 +9909,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>119</v>
       </c>
@@ -9913,7 +9944,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>595</v>
       </c>
@@ -9948,7 +9979,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>334</v>
       </c>
@@ -9983,7 +10014,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>605</v>
       </c>
@@ -10018,7 +10049,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>107</v>
       </c>
@@ -10053,7 +10084,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>94</v>
       </c>
@@ -10088,7 +10119,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>129</v>
       </c>
@@ -10123,7 +10154,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>322</v>
       </c>
@@ -10158,7 +10189,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>324</v>
       </c>
@@ -10193,7 +10224,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A31" s="6" t="s">
         <v>340</v>
       </c>
@@ -10228,7 +10259,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A32" s="6" t="s">
         <v>267</v>
       </c>
@@ -10266,7 +10297,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A33" s="6" t="s">
         <v>353</v>
       </c>
@@ -10301,7 +10332,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A34" s="3" t="s">
         <v>212</v>
       </c>
@@ -10336,7 +10367,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A35" s="3" t="s">
         <v>407</v>
       </c>
@@ -10371,7 +10402,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="44.25" customHeight="1">
       <c r="A36" s="3" t="s">
         <v>429</v>
       </c>
@@ -10409,7 +10440,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="72" customHeight="1">
       <c r="A37" s="3" t="s">
         <v>445</v>
       </c>
@@ -10444,7 +10475,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="29.25" customHeight="1">
       <c r="A38" s="3" t="s">
         <v>448</v>
       </c>
@@ -10479,7 +10510,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="34.5" customHeight="1">
       <c r="A39" s="3" t="s">
         <v>450</v>
       </c>
@@ -10514,7 +10545,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="47.25" customHeight="1">
       <c r="A40" s="3" t="s">
         <v>452</v>
       </c>
@@ -10549,7 +10580,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="49.5" customHeight="1">
       <c r="A41" s="3" t="s">
         <v>455</v>
       </c>
@@ -10584,7 +10615,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="72" customHeight="1">
       <c r="A42" s="11" t="s">
         <v>459</v>
       </c>
@@ -10622,7 +10653,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="72" customHeight="1">
       <c r="A43" s="11" t="s">
         <v>477</v>
       </c>
@@ -10657,7 +10688,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="72" customHeight="1">
       <c r="A44" s="11" t="s">
         <v>689</v>
       </c>
@@ -10692,7 +10723,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" ht="72" customHeight="1">
       <c r="A45" s="15" t="s">
         <v>694</v>
       </c>
@@ -10723,7 +10754,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="72" customHeight="1">
       <c r="A46" s="13" t="s">
         <v>700</v>
       </c>
@@ -10758,7 +10789,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" ht="72" customHeight="1">
       <c r="A47" s="13" t="s">
         <v>706</v>
       </c>
@@ -10789,7 +10820,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="72" customHeight="1">
       <c r="A48" s="13" t="s">
         <v>712</v>
       </c>
@@ -10820,7 +10851,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" ht="72" customHeight="1">
       <c r="A49" s="13" t="s">
         <v>718</v>
       </c>
@@ -10851,7 +10882,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" ht="51" customHeight="1">
       <c r="A50" s="13" t="s">
         <v>724</v>
       </c>
@@ -10886,7 +10917,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" ht="72" customHeight="1">
       <c r="A51" s="13" t="s">
         <v>730</v>
       </c>
@@ -10921,7 +10952,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" ht="72" customHeight="1">
       <c r="A52" s="13" t="s">
         <v>735</v>
       </c>
@@ -10956,7 +10987,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" ht="57.6" customHeight="1">
       <c r="A53" s="13" t="s">
         <v>740</v>
       </c>
@@ -10987,7 +11018,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" ht="57.6" customHeight="1">
       <c r="A54" s="13" t="s">
         <v>745</v>
       </c>
@@ -11018,7 +11049,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" ht="72" customHeight="1">
       <c r="A55" s="13" t="s">
         <v>750</v>
       </c>
@@ -11049,7 +11080,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" ht="72" customHeight="1">
       <c r="A56" s="13" t="s">
         <v>253</v>
       </c>
@@ -11080,7 +11111,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" ht="72" customHeight="1">
       <c r="A57" s="13" t="s">
         <v>759</v>
       </c>
@@ -11111,7 +11142,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" ht="86.45" customHeight="1">
       <c r="A58" s="13" t="s">
         <v>766</v>
       </c>
@@ -11142,7 +11173,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" ht="72" customHeight="1">
       <c r="A59" s="13" t="s">
         <v>773</v>
       </c>
@@ -11173,7 +11204,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" ht="72" customHeight="1">
       <c r="A60" s="13" t="s">
         <v>778</v>
       </c>
@@ -11204,7 +11235,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" ht="72" customHeight="1">
       <c r="A61" s="3" t="s">
         <v>783</v>
       </c>
@@ -11235,7 +11266,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" ht="72" customHeight="1">
       <c r="A62" s="11" t="s">
         <v>789</v>
       </c>
@@ -11266,7 +11297,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" ht="48" customHeight="1">
       <c r="A63" s="18" t="s">
         <v>794</v>
       </c>
@@ -11295,7 +11326,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" ht="42" customHeight="1">
       <c r="A64" s="19" t="s">
         <v>800</v>
       </c>
@@ -11324,7 +11355,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" ht="45" customHeight="1">
       <c r="A65" s="19" t="s">
         <v>805</v>
       </c>
@@ -11353,7 +11384,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" ht="72" customHeight="1">
       <c r="A66" s="19" t="s">
         <v>810</v>
       </c>
@@ -11382,7 +11413,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="72" customHeight="1">
       <c r="A67" s="19" t="s">
         <v>815</v>
       </c>
@@ -11411,7 +11442,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="72" customHeight="1">
       <c r="A68" s="19" t="s">
         <v>820</v>
       </c>
@@ -11440,7 +11471,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="409.6" customHeight="1">
       <c r="A69" s="31" t="s">
         <v>197</v>
       </c>
@@ -11475,7 +11506,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="409.6" customHeight="1">
       <c r="A70" s="31" t="s">
         <v>188</v>
       </c>
@@ -11516,7 +11547,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="105">
       <c r="A71" s="3" t="s">
         <v>952</v>
       </c>
@@ -11554,7 +11585,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="150">
       <c r="A72" s="3" t="s">
         <v>961</v>
       </c>
@@ -11592,7 +11623,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" ht="75">
       <c r="A73" s="3" t="s">
         <v>1008</v>
       </c>
@@ -11602,19 +11633,19 @@
       <c r="G73" s="43" t="s">
         <v>1009</v>
       </c>
-      <c r="H73" s="88" t="s">
+      <c r="H73" s="82" t="s">
         <v>1010</v>
       </c>
-      <c r="I73" s="88" t="s">
+      <c r="I73" s="82" t="s">
         <v>1011</v>
       </c>
-      <c r="J73" s="88" t="s">
+      <c r="J73" s="82" t="s">
         <v>1012</v>
       </c>
       <c r="K73" s="3" t="s">
         <v>1014</v>
       </c>
-      <c r="L73" s="89" t="s">
+      <c r="L73" s="83" t="s">
         <v>1013</v>
       </c>
     </row>
@@ -11669,13 +11700,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="23.7109375" customWidth="1"/>
     <col min="6" max="6" width="24.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="23" t="s">
         <v>831</v>
       </c>
@@ -11692,7 +11723,7 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="20" t="s">
         <v>496</v>
       </c>
@@ -11709,7 +11740,7 @@
       </c>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="20" t="s">
         <v>557</v>
       </c>
@@ -11726,7 +11757,7 @@
       </c>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="20" t="s">
         <v>567</v>
       </c>
@@ -11743,7 +11774,7 @@
       </c>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="20" t="s">
         <v>590</v>
       </c>
@@ -11758,7 +11789,7 @@
       </c>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="20" t="s">
         <v>615</v>
       </c>
@@ -11773,7 +11804,7 @@
       </c>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="20" t="s">
         <v>540</v>
       </c>
@@ -11784,7 +11815,7 @@
       <c r="F7" s="20"/>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="21" t="s">
         <v>644</v>
       </c>
@@ -11795,7 +11826,7 @@
       <c r="F8" s="20"/>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="22" t="s">
         <v>767</v>
       </c>
@@ -11806,7 +11837,7 @@
       <c r="F9" s="20"/>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="20" t="s">
         <v>784</v>
       </c>
@@ -11817,7 +11848,7 @@
       <c r="F10" s="20"/>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="22" t="s">
         <v>795</v>
       </c>
@@ -11828,7 +11859,7 @@
       <c r="F11" s="20"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="20" t="s">
         <v>760</v>
       </c>
@@ -11839,7 +11870,7 @@
       <c r="F12" s="20"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="20" t="s">
         <v>530</v>
       </c>
@@ -11850,7 +11881,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="28.9" customHeight="1">
       <c r="A14" s="27" t="s">
         <v>695</v>
       </c>
@@ -11861,7 +11892,7 @@
       <c r="F14" s="20"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="20"/>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -11870,7 +11901,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="20"/>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
@@ -11879,7 +11910,7 @@
       <c r="F16" s="20"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="20"/>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
@@ -11888,7 +11919,7 @@
       <c r="F17" s="20"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -11906,204 +11937,204 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Q172"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" s="40"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1">
       <c r="A2" s="41" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1">
       <c r="A3" s="41" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1">
       <c r="A4" s="41" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1">
       <c r="A5" s="41" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1">
       <c r="A6" s="41" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1">
       <c r="A7" s="41" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1">
       <c r="A8" s="41" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1">
       <c r="A9" s="41" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1">
       <c r="A10" s="41" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1">
       <c r="A11" s="41" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" ht="15.6" customHeight="1">
       <c r="A13" s="42" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1">
       <c r="A14" s="40"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1">
       <c r="A15" s="41" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1">
       <c r="A16" s="41" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17">
       <c r="A17" s="41" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17">
       <c r="A18" s="41" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17">
       <c r="A19" s="41" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17">
       <c r="A20" s="41" t="s">
         <v>840</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17">
       <c r="A21" s="41" t="s">
         <v>841</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17">
       <c r="A22" s="41" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17">
       <c r="A23" s="41" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17">
       <c r="A24" s="41" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17">
       <c r="A26" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17">
       <c r="A27" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="85" t="s">
+    <row r="28" spans="1:17">
+      <c r="A28" s="88" t="s">
         <v>843</v>
       </c>
-      <c r="B28" s="83"/>
-      <c r="C28" s="83"/>
-      <c r="D28" s="83"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="83"/>
-      <c r="G28" s="83"/>
-      <c r="H28" s="83"/>
-      <c r="I28" s="83"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="83"/>
-      <c r="L28" s="83"/>
-      <c r="M28" s="83"/>
-      <c r="N28" s="83"/>
-      <c r="O28" s="83"/>
-      <c r="P28" s="83"/>
-      <c r="Q28" s="83"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="83"/>
-      <c r="B29" s="83"/>
-      <c r="C29" s="83"/>
-      <c r="D29" s="83"/>
-      <c r="E29" s="83"/>
-      <c r="F29" s="83"/>
-      <c r="G29" s="83"/>
-      <c r="H29" s="83"/>
-      <c r="I29" s="83"/>
-      <c r="J29" s="83"/>
-      <c r="K29" s="83"/>
-      <c r="L29" s="83"/>
-      <c r="M29" s="83"/>
-      <c r="N29" s="83"/>
-      <c r="O29" s="83"/>
-      <c r="P29" s="83"/>
-      <c r="Q29" s="83"/>
-    </row>
-    <row r="30" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="84" t="s">
+      <c r="B28" s="86"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="86"/>
+      <c r="F28" s="86"/>
+      <c r="G28" s="86"/>
+      <c r="H28" s="86"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="86"/>
+      <c r="K28" s="86"/>
+      <c r="L28" s="86"/>
+      <c r="M28" s="86"/>
+      <c r="N28" s="86"/>
+      <c r="O28" s="86"/>
+      <c r="P28" s="86"/>
+      <c r="Q28" s="86"/>
+    </row>
+    <row r="29" spans="1:17">
+      <c r="A29" s="86"/>
+      <c r="B29" s="86"/>
+      <c r="C29" s="86"/>
+      <c r="D29" s="86"/>
+      <c r="E29" s="86"/>
+      <c r="F29" s="86"/>
+      <c r="G29" s="86"/>
+      <c r="H29" s="86"/>
+      <c r="I29" s="86"/>
+      <c r="J29" s="86"/>
+      <c r="K29" s="86"/>
+      <c r="L29" s="86"/>
+      <c r="M29" s="86"/>
+      <c r="N29" s="86"/>
+      <c r="O29" s="86"/>
+      <c r="P29" s="86"/>
+      <c r="Q29" s="86"/>
+    </row>
+    <row r="30" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A30" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="82" t="s">
+      <c r="B30" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="83"/>
-      <c r="D30" s="83"/>
-      <c r="E30" s="82" t="s">
+      <c r="C30" s="86"/>
+      <c r="D30" s="86"/>
+      <c r="E30" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="83"/>
-      <c r="G30" s="83"/>
-      <c r="H30" s="82" t="s">
+      <c r="F30" s="86"/>
+      <c r="G30" s="86"/>
+      <c r="H30" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I30" s="83"/>
-      <c r="J30" s="83"/>
-      <c r="K30" s="82" t="s">
+      <c r="I30" s="86"/>
+      <c r="J30" s="86"/>
+      <c r="K30" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L30" s="83"/>
-      <c r="M30" s="83"/>
-      <c r="N30" s="83"/>
-      <c r="O30" s="83"/>
-      <c r="P30" s="82" t="s">
+      <c r="L30" s="86"/>
+      <c r="M30" s="86"/>
+      <c r="N30" s="86"/>
+      <c r="O30" s="86"/>
+      <c r="P30" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q30" s="82" t="s">
+      <c r="Q30" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="83"/>
+    <row r="31" spans="1:17">
+      <c r="A31" s="86"/>
       <c r="B31" s="43" t="s">
         <v>27</v>
       </c>
@@ -12146,10 +12177,10 @@
       <c r="O31" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P31" s="83"/>
-      <c r="Q31" s="83"/>
-    </row>
-    <row r="32" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P31" s="86"/>
+      <c r="Q31" s="86"/>
+    </row>
+    <row r="32" spans="1:17" ht="43.15" customHeight="1">
       <c r="A32" s="43" t="s">
         <v>844</v>
       </c>
@@ -12200,81 +12231,81 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="85" t="s">
+    <row r="33" spans="1:17">
+      <c r="A33" s="88" t="s">
         <v>644</v>
       </c>
-      <c r="B33" s="83"/>
-      <c r="C33" s="83"/>
-      <c r="D33" s="83"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="83"/>
-      <c r="G33" s="83"/>
-      <c r="H33" s="83"/>
-      <c r="I33" s="83"/>
-      <c r="J33" s="83"/>
-      <c r="K33" s="83"/>
-      <c r="L33" s="83"/>
-      <c r="M33" s="83"/>
-      <c r="N33" s="83"/>
-      <c r="O33" s="83"/>
-      <c r="P33" s="83"/>
-      <c r="Q33" s="83"/>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="83"/>
-      <c r="B34" s="83"/>
-      <c r="C34" s="83"/>
-      <c r="D34" s="83"/>
-      <c r="E34" s="83"/>
-      <c r="F34" s="83"/>
-      <c r="G34" s="83"/>
-      <c r="H34" s="83"/>
-      <c r="I34" s="83"/>
-      <c r="J34" s="83"/>
-      <c r="K34" s="83"/>
-      <c r="L34" s="83"/>
-      <c r="M34" s="83"/>
-      <c r="N34" s="83"/>
-      <c r="O34" s="83"/>
-      <c r="P34" s="83"/>
-      <c r="Q34" s="83"/>
-    </row>
-    <row r="35" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="84" t="s">
+      <c r="B33" s="86"/>
+      <c r="C33" s="86"/>
+      <c r="D33" s="86"/>
+      <c r="E33" s="86"/>
+      <c r="F33" s="86"/>
+      <c r="G33" s="86"/>
+      <c r="H33" s="86"/>
+      <c r="I33" s="86"/>
+      <c r="J33" s="86"/>
+      <c r="K33" s="86"/>
+      <c r="L33" s="86"/>
+      <c r="M33" s="86"/>
+      <c r="N33" s="86"/>
+      <c r="O33" s="86"/>
+      <c r="P33" s="86"/>
+      <c r="Q33" s="86"/>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34" s="86"/>
+      <c r="B34" s="86"/>
+      <c r="C34" s="86"/>
+      <c r="D34" s="86"/>
+      <c r="E34" s="86"/>
+      <c r="F34" s="86"/>
+      <c r="G34" s="86"/>
+      <c r="H34" s="86"/>
+      <c r="I34" s="86"/>
+      <c r="J34" s="86"/>
+      <c r="K34" s="86"/>
+      <c r="L34" s="86"/>
+      <c r="M34" s="86"/>
+      <c r="N34" s="86"/>
+      <c r="O34" s="86"/>
+      <c r="P34" s="86"/>
+      <c r="Q34" s="86"/>
+    </row>
+    <row r="35" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A35" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="82" t="s">
+      <c r="B35" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="83"/>
-      <c r="D35" s="83"/>
-      <c r="E35" s="82" t="s">
+      <c r="C35" s="86"/>
+      <c r="D35" s="86"/>
+      <c r="E35" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F35" s="83"/>
-      <c r="G35" s="83"/>
-      <c r="H35" s="82" t="s">
+      <c r="F35" s="86"/>
+      <c r="G35" s="86"/>
+      <c r="H35" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I35" s="83"/>
-      <c r="J35" s="83"/>
-      <c r="K35" s="82" t="s">
+      <c r="I35" s="86"/>
+      <c r="J35" s="86"/>
+      <c r="K35" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="83"/>
-      <c r="M35" s="83"/>
-      <c r="N35" s="83"/>
-      <c r="O35" s="83"/>
-      <c r="P35" s="82" t="s">
+      <c r="L35" s="86"/>
+      <c r="M35" s="86"/>
+      <c r="N35" s="86"/>
+      <c r="O35" s="86"/>
+      <c r="P35" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q35" s="82" t="s">
+      <c r="Q35" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="83"/>
+    <row r="36" spans="1:17">
+      <c r="A36" s="86"/>
       <c r="B36" s="43" t="s">
         <v>27</v>
       </c>
@@ -12317,10 +12348,10 @@
       <c r="O36" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P36" s="83"/>
-      <c r="Q36" s="83"/>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P36" s="86"/>
+      <c r="Q36" s="86"/>
+    </row>
+    <row r="37" spans="1:17">
       <c r="A37" s="43" t="s">
         <v>689</v>
       </c>
@@ -12371,7 +12402,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" ht="30">
       <c r="A38" s="43" t="s">
         <v>845</v>
       </c>
@@ -12422,7 +12453,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" ht="28.9" customHeight="1">
       <c r="A39" s="43" t="s">
         <v>68</v>
       </c>
@@ -12473,7 +12504,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" ht="57.6" customHeight="1">
       <c r="A40" s="43" t="s">
         <v>846</v>
       </c>
@@ -12506,7 +12537,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17">
       <c r="A41" s="43" t="s">
         <v>847</v>
       </c>
@@ -12539,7 +12570,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" ht="43.15" customHeight="1">
       <c r="A42" s="46" t="s">
         <v>848</v>
       </c>
@@ -12582,7 +12613,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" ht="30">
       <c r="A43" s="43" t="s">
         <v>849</v>
       </c>
@@ -12615,7 +12646,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" ht="28.9" customHeight="1">
       <c r="A44" s="43" t="s">
         <v>773</v>
       </c>
@@ -12648,7 +12679,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="28.9" customHeight="1">
       <c r="A45" s="43" t="s">
         <v>766</v>
       </c>
@@ -12681,7 +12712,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" ht="43.15" customHeight="1">
       <c r="A46" s="43" t="s">
         <v>778</v>
       </c>
@@ -12714,7 +12745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" ht="57.6" customHeight="1">
       <c r="A47" s="46" t="s">
         <v>850</v>
       </c>
@@ -12757,81 +12788,81 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="85" t="s">
+    <row r="48" spans="1:17">
+      <c r="A48" s="88" t="s">
         <v>851</v>
       </c>
-      <c r="B48" s="83"/>
-      <c r="C48" s="83"/>
-      <c r="D48" s="83"/>
-      <c r="E48" s="83"/>
-      <c r="F48" s="83"/>
-      <c r="G48" s="83"/>
-      <c r="H48" s="83"/>
-      <c r="I48" s="83"/>
-      <c r="J48" s="83"/>
-      <c r="K48" s="83"/>
-      <c r="L48" s="83"/>
-      <c r="M48" s="83"/>
-      <c r="N48" s="83"/>
-      <c r="O48" s="83"/>
-      <c r="P48" s="83"/>
-      <c r="Q48" s="83"/>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="83"/>
-      <c r="B49" s="83"/>
-      <c r="C49" s="83"/>
-      <c r="D49" s="83"/>
-      <c r="E49" s="83"/>
-      <c r="F49" s="83"/>
-      <c r="G49" s="83"/>
-      <c r="H49" s="83"/>
-      <c r="I49" s="83"/>
-      <c r="J49" s="83"/>
-      <c r="K49" s="83"/>
-      <c r="L49" s="83"/>
-      <c r="M49" s="83"/>
-      <c r="N49" s="83"/>
-      <c r="O49" s="83"/>
-      <c r="P49" s="83"/>
-      <c r="Q49" s="83"/>
-    </row>
-    <row r="50" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="84" t="s">
+      <c r="B48" s="86"/>
+      <c r="C48" s="86"/>
+      <c r="D48" s="86"/>
+      <c r="E48" s="86"/>
+      <c r="F48" s="86"/>
+      <c r="G48" s="86"/>
+      <c r="H48" s="86"/>
+      <c r="I48" s="86"/>
+      <c r="J48" s="86"/>
+      <c r="K48" s="86"/>
+      <c r="L48" s="86"/>
+      <c r="M48" s="86"/>
+      <c r="N48" s="86"/>
+      <c r="O48" s="86"/>
+      <c r="P48" s="86"/>
+      <c r="Q48" s="86"/>
+    </row>
+    <row r="49" spans="1:17">
+      <c r="A49" s="86"/>
+      <c r="B49" s="86"/>
+      <c r="C49" s="86"/>
+      <c r="D49" s="86"/>
+      <c r="E49" s="86"/>
+      <c r="F49" s="86"/>
+      <c r="G49" s="86"/>
+      <c r="H49" s="86"/>
+      <c r="I49" s="86"/>
+      <c r="J49" s="86"/>
+      <c r="K49" s="86"/>
+      <c r="L49" s="86"/>
+      <c r="M49" s="86"/>
+      <c r="N49" s="86"/>
+      <c r="O49" s="86"/>
+      <c r="P49" s="86"/>
+      <c r="Q49" s="86"/>
+    </row>
+    <row r="50" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A50" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B50" s="82" t="s">
+      <c r="B50" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C50" s="83"/>
-      <c r="D50" s="83"/>
-      <c r="E50" s="82" t="s">
+      <c r="C50" s="86"/>
+      <c r="D50" s="86"/>
+      <c r="E50" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F50" s="83"/>
-      <c r="G50" s="83"/>
-      <c r="H50" s="82" t="s">
+      <c r="F50" s="86"/>
+      <c r="G50" s="86"/>
+      <c r="H50" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I50" s="83"/>
-      <c r="J50" s="83"/>
-      <c r="K50" s="82" t="s">
+      <c r="I50" s="86"/>
+      <c r="J50" s="86"/>
+      <c r="K50" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="83"/>
-      <c r="M50" s="83"/>
-      <c r="N50" s="83"/>
-      <c r="O50" s="83"/>
-      <c r="P50" s="82" t="s">
+      <c r="L50" s="86"/>
+      <c r="M50" s="86"/>
+      <c r="N50" s="86"/>
+      <c r="O50" s="86"/>
+      <c r="P50" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q50" s="82" t="s">
+      <c r="Q50" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51" s="83"/>
+    <row r="51" spans="1:17">
+      <c r="A51" s="86"/>
       <c r="B51" s="43" t="s">
         <v>27</v>
       </c>
@@ -12874,10 +12905,10 @@
       <c r="O51" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P51" s="83"/>
-      <c r="Q51" s="83"/>
-    </row>
-    <row r="52" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P51" s="86"/>
+      <c r="Q51" s="86"/>
+    </row>
+    <row r="52" spans="1:17" ht="57.6" customHeight="1">
       <c r="A52" s="43" t="s">
         <v>852</v>
       </c>
@@ -12928,81 +12959,81 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53" s="85" t="s">
+    <row r="53" spans="1:17">
+      <c r="A53" s="88" t="s">
         <v>853</v>
       </c>
-      <c r="B53" s="83"/>
-      <c r="C53" s="83"/>
-      <c r="D53" s="83"/>
-      <c r="E53" s="83"/>
-      <c r="F53" s="83"/>
-      <c r="G53" s="83"/>
-      <c r="H53" s="83"/>
-      <c r="I53" s="83"/>
-      <c r="J53" s="83"/>
-      <c r="K53" s="83"/>
-      <c r="L53" s="83"/>
-      <c r="M53" s="83"/>
-      <c r="N53" s="83"/>
-      <c r="O53" s="83"/>
-      <c r="P53" s="83"/>
-      <c r="Q53" s="83"/>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="83"/>
-      <c r="B54" s="83"/>
-      <c r="C54" s="83"/>
-      <c r="D54" s="83"/>
-      <c r="E54" s="83"/>
-      <c r="F54" s="83"/>
-      <c r="G54" s="83"/>
-      <c r="H54" s="83"/>
-      <c r="I54" s="83"/>
-      <c r="J54" s="83"/>
-      <c r="K54" s="83"/>
-      <c r="L54" s="83"/>
-      <c r="M54" s="83"/>
-      <c r="N54" s="83"/>
-      <c r="O54" s="83"/>
-      <c r="P54" s="83"/>
-      <c r="Q54" s="83"/>
-    </row>
-    <row r="55" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="84" t="s">
+      <c r="B53" s="86"/>
+      <c r="C53" s="86"/>
+      <c r="D53" s="86"/>
+      <c r="E53" s="86"/>
+      <c r="F53" s="86"/>
+      <c r="G53" s="86"/>
+      <c r="H53" s="86"/>
+      <c r="I53" s="86"/>
+      <c r="J53" s="86"/>
+      <c r="K53" s="86"/>
+      <c r="L53" s="86"/>
+      <c r="M53" s="86"/>
+      <c r="N53" s="86"/>
+      <c r="O53" s="86"/>
+      <c r="P53" s="86"/>
+      <c r="Q53" s="86"/>
+    </row>
+    <row r="54" spans="1:17">
+      <c r="A54" s="86"/>
+      <c r="B54" s="86"/>
+      <c r="C54" s="86"/>
+      <c r="D54" s="86"/>
+      <c r="E54" s="86"/>
+      <c r="F54" s="86"/>
+      <c r="G54" s="86"/>
+      <c r="H54" s="86"/>
+      <c r="I54" s="86"/>
+      <c r="J54" s="86"/>
+      <c r="K54" s="86"/>
+      <c r="L54" s="86"/>
+      <c r="M54" s="86"/>
+      <c r="N54" s="86"/>
+      <c r="O54" s="86"/>
+      <c r="P54" s="86"/>
+      <c r="Q54" s="86"/>
+    </row>
+    <row r="55" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A55" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B55" s="82" t="s">
+      <c r="B55" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C55" s="83"/>
-      <c r="D55" s="83"/>
-      <c r="E55" s="82" t="s">
+      <c r="C55" s="86"/>
+      <c r="D55" s="86"/>
+      <c r="E55" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F55" s="83"/>
-      <c r="G55" s="83"/>
-      <c r="H55" s="82" t="s">
+      <c r="F55" s="86"/>
+      <c r="G55" s="86"/>
+      <c r="H55" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I55" s="83"/>
-      <c r="J55" s="83"/>
-      <c r="K55" s="82" t="s">
+      <c r="I55" s="86"/>
+      <c r="J55" s="86"/>
+      <c r="K55" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L55" s="83"/>
-      <c r="M55" s="83"/>
-      <c r="N55" s="83"/>
-      <c r="O55" s="83"/>
-      <c r="P55" s="82" t="s">
+      <c r="L55" s="86"/>
+      <c r="M55" s="86"/>
+      <c r="N55" s="86"/>
+      <c r="O55" s="86"/>
+      <c r="P55" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q55" s="82" t="s">
+      <c r="Q55" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="83"/>
+    <row r="56" spans="1:17">
+      <c r="A56" s="86"/>
       <c r="B56" s="43" t="s">
         <v>27</v>
       </c>
@@ -13045,10 +13076,10 @@
       <c r="O56" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P56" s="83"/>
-      <c r="Q56" s="83"/>
-    </row>
-    <row r="57" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P56" s="86"/>
+      <c r="Q56" s="86"/>
+    </row>
+    <row r="57" spans="1:17" ht="28.9" customHeight="1">
       <c r="A57" s="43" t="s">
         <v>34</v>
       </c>
@@ -13081,7 +13112,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" ht="57.6" customHeight="1">
       <c r="A58" s="43" t="s">
         <v>854</v>
       </c>
@@ -13114,7 +13145,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" ht="43.15" customHeight="1">
       <c r="A59" s="43" t="s">
         <v>37</v>
       </c>
@@ -13147,7 +13178,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" ht="43.15" customHeight="1">
       <c r="A60" s="43" t="s">
         <v>40</v>
       </c>
@@ -13180,7 +13211,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" ht="28.9" customHeight="1">
       <c r="A61" s="43" t="s">
         <v>39</v>
       </c>
@@ -13213,7 +13244,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" ht="100.9" customHeight="1">
       <c r="A62" s="43" t="s">
         <v>36</v>
       </c>
@@ -13246,7 +13277,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" ht="144" customHeight="1">
       <c r="A63" s="43" t="s">
         <v>35</v>
       </c>
@@ -13279,7 +13310,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" ht="115.15" customHeight="1">
       <c r="A64" s="43" t="s">
         <v>44</v>
       </c>
@@ -13312,7 +13343,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" ht="100.9" customHeight="1">
       <c r="A65" s="43" t="s">
         <v>41</v>
       </c>
@@ -13345,7 +13376,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" ht="144" customHeight="1">
       <c r="A66" s="43" t="s">
         <v>32</v>
       </c>
@@ -13378,7 +13409,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" ht="115.15" customHeight="1">
       <c r="A67" s="43" t="s">
         <v>31</v>
       </c>
@@ -13411,7 +13442,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" ht="129.6" customHeight="1">
       <c r="A68" s="43" t="s">
         <v>33</v>
       </c>
@@ -13444,7 +13475,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" ht="72" customHeight="1">
       <c r="A69" s="43" t="s">
         <v>42</v>
       </c>
@@ -13477,7 +13508,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" ht="72" customHeight="1">
       <c r="A70" s="43" t="s">
         <v>43</v>
       </c>
@@ -13510,7 +13541,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="43.15" customHeight="1">
       <c r="A71" s="46" t="s">
         <v>855</v>
       </c>
@@ -13553,81 +13584,81 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A72" s="85" t="s">
+    <row r="72" spans="1:17">
+      <c r="A72" s="88" t="s">
         <v>856</v>
       </c>
-      <c r="B72" s="83"/>
-      <c r="C72" s="83"/>
-      <c r="D72" s="83"/>
-      <c r="E72" s="83"/>
-      <c r="F72" s="83"/>
-      <c r="G72" s="83"/>
-      <c r="H72" s="83"/>
-      <c r="I72" s="83"/>
-      <c r="J72" s="83"/>
-      <c r="K72" s="83"/>
-      <c r="L72" s="83"/>
-      <c r="M72" s="83"/>
-      <c r="N72" s="83"/>
-      <c r="O72" s="83"/>
-      <c r="P72" s="83"/>
-      <c r="Q72" s="83"/>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A73" s="83"/>
-      <c r="B73" s="83"/>
-      <c r="C73" s="83"/>
-      <c r="D73" s="83"/>
-      <c r="E73" s="83"/>
-      <c r="F73" s="83"/>
-      <c r="G73" s="83"/>
-      <c r="H73" s="83"/>
-      <c r="I73" s="83"/>
-      <c r="J73" s="83"/>
-      <c r="K73" s="83"/>
-      <c r="L73" s="83"/>
-      <c r="M73" s="83"/>
-      <c r="N73" s="83"/>
-      <c r="O73" s="83"/>
-      <c r="P73" s="83"/>
-      <c r="Q73" s="83"/>
-    </row>
-    <row r="74" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="84" t="s">
+      <c r="B72" s="86"/>
+      <c r="C72" s="86"/>
+      <c r="D72" s="86"/>
+      <c r="E72" s="86"/>
+      <c r="F72" s="86"/>
+      <c r="G72" s="86"/>
+      <c r="H72" s="86"/>
+      <c r="I72" s="86"/>
+      <c r="J72" s="86"/>
+      <c r="K72" s="86"/>
+      <c r="L72" s="86"/>
+      <c r="M72" s="86"/>
+      <c r="N72" s="86"/>
+      <c r="O72" s="86"/>
+      <c r="P72" s="86"/>
+      <c r="Q72" s="86"/>
+    </row>
+    <row r="73" spans="1:17">
+      <c r="A73" s="86"/>
+      <c r="B73" s="86"/>
+      <c r="C73" s="86"/>
+      <c r="D73" s="86"/>
+      <c r="E73" s="86"/>
+      <c r="F73" s="86"/>
+      <c r="G73" s="86"/>
+      <c r="H73" s="86"/>
+      <c r="I73" s="86"/>
+      <c r="J73" s="86"/>
+      <c r="K73" s="86"/>
+      <c r="L73" s="86"/>
+      <c r="M73" s="86"/>
+      <c r="N73" s="86"/>
+      <c r="O73" s="86"/>
+      <c r="P73" s="86"/>
+      <c r="Q73" s="86"/>
+    </row>
+    <row r="74" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A74" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B74" s="82" t="s">
+      <c r="B74" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C74" s="83"/>
-      <c r="D74" s="83"/>
-      <c r="E74" s="82" t="s">
+      <c r="C74" s="86"/>
+      <c r="D74" s="86"/>
+      <c r="E74" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F74" s="83"/>
-      <c r="G74" s="83"/>
-      <c r="H74" s="82" t="s">
+      <c r="F74" s="86"/>
+      <c r="G74" s="86"/>
+      <c r="H74" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I74" s="83"/>
-      <c r="J74" s="83"/>
-      <c r="K74" s="82" t="s">
+      <c r="I74" s="86"/>
+      <c r="J74" s="86"/>
+      <c r="K74" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L74" s="83"/>
-      <c r="M74" s="83"/>
-      <c r="N74" s="83"/>
-      <c r="O74" s="83"/>
-      <c r="P74" s="82" t="s">
+      <c r="L74" s="86"/>
+      <c r="M74" s="86"/>
+      <c r="N74" s="86"/>
+      <c r="O74" s="86"/>
+      <c r="P74" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q74" s="82" t="s">
+      <c r="Q74" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75" s="83"/>
+    <row r="75" spans="1:17">
+      <c r="A75" s="86"/>
       <c r="B75" s="43" t="s">
         <v>27</v>
       </c>
@@ -13670,10 +13701,10 @@
       <c r="O75" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P75" s="83"/>
-      <c r="Q75" s="83"/>
-    </row>
-    <row r="76" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P75" s="86"/>
+      <c r="Q75" s="86"/>
+    </row>
+    <row r="76" spans="1:17" ht="57.6" customHeight="1">
       <c r="A76" s="43" t="s">
         <v>48</v>
       </c>
@@ -13706,7 +13737,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" ht="43.15" customHeight="1">
       <c r="A77" s="43" t="s">
         <v>51</v>
       </c>
@@ -13739,7 +13770,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" ht="72" customHeight="1">
       <c r="A78" s="43" t="s">
         <v>50</v>
       </c>
@@ -13772,7 +13803,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" ht="57.6" customHeight="1">
       <c r="A79" s="43" t="s">
         <v>49</v>
       </c>
@@ -13805,7 +13836,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" ht="28.9" customHeight="1">
       <c r="A80" s="46" t="s">
         <v>857</v>
       </c>
@@ -13848,81 +13879,81 @@
         <v>272</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A81" s="85" t="s">
+    <row r="81" spans="1:17">
+      <c r="A81" s="88" t="s">
         <v>858</v>
       </c>
-      <c r="B81" s="83"/>
-      <c r="C81" s="83"/>
-      <c r="D81" s="83"/>
-      <c r="E81" s="83"/>
-      <c r="F81" s="83"/>
-      <c r="G81" s="83"/>
-      <c r="H81" s="83"/>
-      <c r="I81" s="83"/>
-      <c r="J81" s="83"/>
-      <c r="K81" s="83"/>
-      <c r="L81" s="83"/>
-      <c r="M81" s="83"/>
-      <c r="N81" s="83"/>
-      <c r="O81" s="83"/>
-      <c r="P81" s="83"/>
-      <c r="Q81" s="83"/>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A82" s="83"/>
-      <c r="B82" s="83"/>
-      <c r="C82" s="83"/>
-      <c r="D82" s="83"/>
-      <c r="E82" s="83"/>
-      <c r="F82" s="83"/>
-      <c r="G82" s="83"/>
-      <c r="H82" s="83"/>
-      <c r="I82" s="83"/>
-      <c r="J82" s="83"/>
-      <c r="K82" s="83"/>
-      <c r="L82" s="83"/>
-      <c r="M82" s="83"/>
-      <c r="N82" s="83"/>
-      <c r="O82" s="83"/>
-      <c r="P82" s="83"/>
-      <c r="Q82" s="83"/>
-    </row>
-    <row r="83" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="84" t="s">
+      <c r="B81" s="86"/>
+      <c r="C81" s="86"/>
+      <c r="D81" s="86"/>
+      <c r="E81" s="86"/>
+      <c r="F81" s="86"/>
+      <c r="G81" s="86"/>
+      <c r="H81" s="86"/>
+      <c r="I81" s="86"/>
+      <c r="J81" s="86"/>
+      <c r="K81" s="86"/>
+      <c r="L81" s="86"/>
+      <c r="M81" s="86"/>
+      <c r="N81" s="86"/>
+      <c r="O81" s="86"/>
+      <c r="P81" s="86"/>
+      <c r="Q81" s="86"/>
+    </row>
+    <row r="82" spans="1:17">
+      <c r="A82" s="86"/>
+      <c r="B82" s="86"/>
+      <c r="C82" s="86"/>
+      <c r="D82" s="86"/>
+      <c r="E82" s="86"/>
+      <c r="F82" s="86"/>
+      <c r="G82" s="86"/>
+      <c r="H82" s="86"/>
+      <c r="I82" s="86"/>
+      <c r="J82" s="86"/>
+      <c r="K82" s="86"/>
+      <c r="L82" s="86"/>
+      <c r="M82" s="86"/>
+      <c r="N82" s="86"/>
+      <c r="O82" s="86"/>
+      <c r="P82" s="86"/>
+      <c r="Q82" s="86"/>
+    </row>
+    <row r="83" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A83" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B83" s="82" t="s">
+      <c r="B83" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C83" s="83"/>
-      <c r="D83" s="83"/>
-      <c r="E83" s="82" t="s">
+      <c r="C83" s="86"/>
+      <c r="D83" s="86"/>
+      <c r="E83" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F83" s="83"/>
-      <c r="G83" s="83"/>
-      <c r="H83" s="82" t="s">
+      <c r="F83" s="86"/>
+      <c r="G83" s="86"/>
+      <c r="H83" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I83" s="83"/>
-      <c r="J83" s="83"/>
-      <c r="K83" s="82" t="s">
+      <c r="I83" s="86"/>
+      <c r="J83" s="86"/>
+      <c r="K83" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L83" s="83"/>
-      <c r="M83" s="83"/>
-      <c r="N83" s="83"/>
-      <c r="O83" s="83"/>
-      <c r="P83" s="82" t="s">
+      <c r="L83" s="86"/>
+      <c r="M83" s="86"/>
+      <c r="N83" s="86"/>
+      <c r="O83" s="86"/>
+      <c r="P83" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q83" s="82" t="s">
+      <c r="Q83" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A84" s="83"/>
+    <row r="84" spans="1:17">
+      <c r="A84" s="86"/>
       <c r="B84" s="43" t="s">
         <v>27</v>
       </c>
@@ -13965,10 +13996,10 @@
       <c r="O84" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P84" s="83"/>
-      <c r="Q84" s="83"/>
-    </row>
-    <row r="85" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P84" s="86"/>
+      <c r="Q84" s="86"/>
+    </row>
+    <row r="85" spans="1:17" ht="100.9" customHeight="1">
       <c r="A85" s="43" t="s">
         <v>859</v>
       </c>
@@ -14001,7 +14032,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" ht="100.9" customHeight="1">
       <c r="A86" s="43" t="s">
         <v>860</v>
       </c>
@@ -14034,7 +14065,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" ht="28.9" customHeight="1">
       <c r="A87" s="43" t="s">
         <v>800</v>
       </c>
@@ -14067,7 +14098,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17">
       <c r="A88" s="43" t="s">
         <v>805</v>
       </c>
@@ -14100,7 +14131,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" ht="28.9" customHeight="1">
       <c r="A89" s="43" t="s">
         <v>810</v>
       </c>
@@ -14133,7 +14164,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17">
       <c r="A90" s="43" t="s">
         <v>815</v>
       </c>
@@ -14166,7 +14197,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" ht="28.9" customHeight="1">
       <c r="A91" s="43" t="s">
         <v>861</v>
       </c>
@@ -14199,7 +14230,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" ht="28.9" customHeight="1">
       <c r="A92" s="46" t="s">
         <v>862</v>
       </c>
@@ -14242,81 +14273,81 @@
         <v>30</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A93" s="85" t="s">
+    <row r="93" spans="1:17">
+      <c r="A93" s="88" t="s">
         <v>863</v>
       </c>
-      <c r="B93" s="83"/>
-      <c r="C93" s="83"/>
-      <c r="D93" s="83"/>
-      <c r="E93" s="83"/>
-      <c r="F93" s="83"/>
-      <c r="G93" s="83"/>
-      <c r="H93" s="83"/>
-      <c r="I93" s="83"/>
-      <c r="J93" s="83"/>
-      <c r="K93" s="83"/>
-      <c r="L93" s="83"/>
-      <c r="M93" s="83"/>
-      <c r="N93" s="83"/>
-      <c r="O93" s="83"/>
-      <c r="P93" s="83"/>
-      <c r="Q93" s="83"/>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A94" s="83"/>
-      <c r="B94" s="83"/>
-      <c r="C94" s="83"/>
-      <c r="D94" s="83"/>
-      <c r="E94" s="83"/>
-      <c r="F94" s="83"/>
-      <c r="G94" s="83"/>
-      <c r="H94" s="83"/>
-      <c r="I94" s="83"/>
-      <c r="J94" s="83"/>
-      <c r="K94" s="83"/>
-      <c r="L94" s="83"/>
-      <c r="M94" s="83"/>
-      <c r="N94" s="83"/>
-      <c r="O94" s="83"/>
-      <c r="P94" s="83"/>
-      <c r="Q94" s="83"/>
-    </row>
-    <row r="95" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="84" t="s">
+      <c r="B93" s="86"/>
+      <c r="C93" s="86"/>
+      <c r="D93" s="86"/>
+      <c r="E93" s="86"/>
+      <c r="F93" s="86"/>
+      <c r="G93" s="86"/>
+      <c r="H93" s="86"/>
+      <c r="I93" s="86"/>
+      <c r="J93" s="86"/>
+      <c r="K93" s="86"/>
+      <c r="L93" s="86"/>
+      <c r="M93" s="86"/>
+      <c r="N93" s="86"/>
+      <c r="O93" s="86"/>
+      <c r="P93" s="86"/>
+      <c r="Q93" s="86"/>
+    </row>
+    <row r="94" spans="1:17">
+      <c r="A94" s="86"/>
+      <c r="B94" s="86"/>
+      <c r="C94" s="86"/>
+      <c r="D94" s="86"/>
+      <c r="E94" s="86"/>
+      <c r="F94" s="86"/>
+      <c r="G94" s="86"/>
+      <c r="H94" s="86"/>
+      <c r="I94" s="86"/>
+      <c r="J94" s="86"/>
+      <c r="K94" s="86"/>
+      <c r="L94" s="86"/>
+      <c r="M94" s="86"/>
+      <c r="N94" s="86"/>
+      <c r="O94" s="86"/>
+      <c r="P94" s="86"/>
+      <c r="Q94" s="86"/>
+    </row>
+    <row r="95" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A95" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B95" s="82" t="s">
+      <c r="B95" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C95" s="83"/>
-      <c r="D95" s="83"/>
-      <c r="E95" s="82" t="s">
+      <c r="C95" s="86"/>
+      <c r="D95" s="86"/>
+      <c r="E95" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F95" s="83"/>
-      <c r="G95" s="83"/>
-      <c r="H95" s="82" t="s">
+      <c r="F95" s="86"/>
+      <c r="G95" s="86"/>
+      <c r="H95" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I95" s="83"/>
-      <c r="J95" s="83"/>
-      <c r="K95" s="82" t="s">
+      <c r="I95" s="86"/>
+      <c r="J95" s="86"/>
+      <c r="K95" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L95" s="83"/>
-      <c r="M95" s="83"/>
-      <c r="N95" s="83"/>
-      <c r="O95" s="83"/>
-      <c r="P95" s="82" t="s">
+      <c r="L95" s="86"/>
+      <c r="M95" s="86"/>
+      <c r="N95" s="86"/>
+      <c r="O95" s="86"/>
+      <c r="P95" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q95" s="82" t="s">
+      <c r="Q95" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A96" s="83"/>
+    <row r="96" spans="1:17">
+      <c r="A96" s="86"/>
       <c r="B96" s="43" t="s">
         <v>27</v>
       </c>
@@ -14359,10 +14390,10 @@
       <c r="O96" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P96" s="83"/>
-      <c r="Q96" s="83"/>
-    </row>
-    <row r="97" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P96" s="86"/>
+      <c r="Q96" s="86"/>
+    </row>
+    <row r="97" spans="1:17" ht="57.6" customHeight="1">
       <c r="A97" s="43" t="s">
         <v>864</v>
       </c>
@@ -14395,7 +14426,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" ht="57.6" customHeight="1">
       <c r="A98" s="43" t="s">
         <v>54</v>
       </c>
@@ -14428,7 +14459,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="72" customHeight="1">
       <c r="A99" s="43" t="s">
         <v>55</v>
       </c>
@@ -14461,7 +14492,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" ht="28.9" customHeight="1">
       <c r="A100" s="43" t="s">
         <v>56</v>
       </c>
@@ -14494,7 +14525,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" ht="115.15" customHeight="1">
       <c r="A101" s="43" t="s">
         <v>57</v>
       </c>
@@ -14527,7 +14558,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" ht="72" customHeight="1">
       <c r="A102" s="43" t="s">
         <v>865</v>
       </c>
@@ -14560,7 +14591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" ht="28.9" customHeight="1">
       <c r="A103" s="43" t="s">
         <v>866</v>
       </c>
@@ -14593,7 +14624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" ht="43.15" customHeight="1">
       <c r="A104" s="43" t="s">
         <v>58</v>
       </c>
@@ -14626,7 +14657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" ht="57.6" customHeight="1">
       <c r="A105" s="43" t="s">
         <v>59</v>
       </c>
@@ -14659,7 +14690,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" ht="72" customHeight="1">
       <c r="A106" s="43" t="s">
         <v>60</v>
       </c>
@@ -14692,7 +14723,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" ht="100.9" customHeight="1">
       <c r="A107" s="43" t="s">
         <v>867</v>
       </c>
@@ -14725,7 +14756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" ht="57.6" customHeight="1">
       <c r="A108" s="43" t="s">
         <v>61</v>
       </c>
@@ -14758,7 +14789,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" ht="72" customHeight="1">
       <c r="A109" s="43" t="s">
         <v>868</v>
       </c>
@@ -14791,7 +14822,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" ht="57.6" customHeight="1">
       <c r="A110" s="43" t="s">
         <v>62</v>
       </c>
@@ -14824,7 +14855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" ht="86.45" customHeight="1">
       <c r="A111" s="43" t="s">
         <v>63</v>
       </c>
@@ -14857,7 +14888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" ht="57.6" customHeight="1">
       <c r="A112" s="43" t="s">
         <v>64</v>
       </c>
@@ -14890,7 +14921,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" ht="86.45" customHeight="1">
       <c r="A113" s="43" t="s">
         <v>869</v>
       </c>
@@ -14923,7 +14954,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" ht="57.6" customHeight="1">
       <c r="A114" s="43" t="s">
         <v>870</v>
       </c>
@@ -14956,7 +14987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" ht="86.45" customHeight="1">
       <c r="A115" s="43" t="s">
         <v>871</v>
       </c>
@@ -14989,7 +15020,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" ht="72" customHeight="1">
       <c r="A116" s="43" t="s">
         <v>872</v>
       </c>
@@ -15022,7 +15053,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" ht="72" customHeight="1">
       <c r="A117" s="43" t="s">
         <v>65</v>
       </c>
@@ -15055,7 +15086,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" ht="57.6" customHeight="1">
       <c r="A118" s="43" t="s">
         <v>66</v>
       </c>
@@ -15088,7 +15119,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" ht="72" customHeight="1">
       <c r="A119" s="43" t="s">
         <v>873</v>
       </c>
@@ -15121,7 +15152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" ht="57.6" customHeight="1">
       <c r="A120" s="43" t="s">
         <v>874</v>
       </c>
@@ -15154,7 +15185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" ht="57.6" customHeight="1">
       <c r="A121" s="43" t="s">
         <v>875</v>
       </c>
@@ -15187,7 +15218,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="43.15" customHeight="1">
       <c r="A122" s="43" t="s">
         <v>876</v>
       </c>
@@ -15220,7 +15251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" ht="100.9" customHeight="1">
       <c r="A123" s="43" t="s">
         <v>877</v>
       </c>
@@ -15253,7 +15284,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" ht="100.9" customHeight="1">
       <c r="A124" s="43" t="s">
         <v>878</v>
       </c>
@@ -15286,7 +15317,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" ht="43.15" customHeight="1">
       <c r="A125" s="43" t="s">
         <v>879</v>
       </c>
@@ -15319,7 +15350,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" ht="43.15" customHeight="1">
       <c r="A126" s="46" t="s">
         <v>863</v>
       </c>
@@ -15362,81 +15393,81 @@
         <v>128</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A127" s="85" t="s">
+    <row r="127" spans="1:17">
+      <c r="A127" s="88" t="s">
         <v>557</v>
       </c>
-      <c r="B127" s="83"/>
-      <c r="C127" s="83"/>
-      <c r="D127" s="83"/>
-      <c r="E127" s="83"/>
-      <c r="F127" s="83"/>
-      <c r="G127" s="83"/>
-      <c r="H127" s="83"/>
-      <c r="I127" s="83"/>
-      <c r="J127" s="83"/>
-      <c r="K127" s="83"/>
-      <c r="L127" s="83"/>
-      <c r="M127" s="83"/>
-      <c r="N127" s="83"/>
-      <c r="O127" s="83"/>
-      <c r="P127" s="83"/>
-      <c r="Q127" s="83"/>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A128" s="83"/>
-      <c r="B128" s="83"/>
-      <c r="C128" s="83"/>
-      <c r="D128" s="83"/>
-      <c r="E128" s="83"/>
-      <c r="F128" s="83"/>
-      <c r="G128" s="83"/>
-      <c r="H128" s="83"/>
-      <c r="I128" s="83"/>
-      <c r="J128" s="83"/>
-      <c r="K128" s="83"/>
-      <c r="L128" s="83"/>
-      <c r="M128" s="83"/>
-      <c r="N128" s="83"/>
-      <c r="O128" s="83"/>
-      <c r="P128" s="83"/>
-      <c r="Q128" s="83"/>
-    </row>
-    <row r="129" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="84" t="s">
+      <c r="B127" s="86"/>
+      <c r="C127" s="86"/>
+      <c r="D127" s="86"/>
+      <c r="E127" s="86"/>
+      <c r="F127" s="86"/>
+      <c r="G127" s="86"/>
+      <c r="H127" s="86"/>
+      <c r="I127" s="86"/>
+      <c r="J127" s="86"/>
+      <c r="K127" s="86"/>
+      <c r="L127" s="86"/>
+      <c r="M127" s="86"/>
+      <c r="N127" s="86"/>
+      <c r="O127" s="86"/>
+      <c r="P127" s="86"/>
+      <c r="Q127" s="86"/>
+    </row>
+    <row r="128" spans="1:17">
+      <c r="A128" s="86"/>
+      <c r="B128" s="86"/>
+      <c r="C128" s="86"/>
+      <c r="D128" s="86"/>
+      <c r="E128" s="86"/>
+      <c r="F128" s="86"/>
+      <c r="G128" s="86"/>
+      <c r="H128" s="86"/>
+      <c r="I128" s="86"/>
+      <c r="J128" s="86"/>
+      <c r="K128" s="86"/>
+      <c r="L128" s="86"/>
+      <c r="M128" s="86"/>
+      <c r="N128" s="86"/>
+      <c r="O128" s="86"/>
+      <c r="P128" s="86"/>
+      <c r="Q128" s="86"/>
+    </row>
+    <row r="129" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A129" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B129" s="82" t="s">
+      <c r="B129" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C129" s="83"/>
-      <c r="D129" s="83"/>
-      <c r="E129" s="82" t="s">
+      <c r="C129" s="86"/>
+      <c r="D129" s="86"/>
+      <c r="E129" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F129" s="83"/>
-      <c r="G129" s="83"/>
-      <c r="H129" s="82" t="s">
+      <c r="F129" s="86"/>
+      <c r="G129" s="86"/>
+      <c r="H129" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I129" s="83"/>
-      <c r="J129" s="83"/>
-      <c r="K129" s="82" t="s">
+      <c r="I129" s="86"/>
+      <c r="J129" s="86"/>
+      <c r="K129" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L129" s="83"/>
-      <c r="M129" s="83"/>
-      <c r="N129" s="83"/>
-      <c r="O129" s="83"/>
-      <c r="P129" s="82" t="s">
+      <c r="L129" s="86"/>
+      <c r="M129" s="86"/>
+      <c r="N129" s="86"/>
+      <c r="O129" s="86"/>
+      <c r="P129" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q129" s="82" t="s">
+      <c r="Q129" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A130" s="83"/>
+    <row r="130" spans="1:17">
+      <c r="A130" s="86"/>
       <c r="B130" s="43" t="s">
         <v>27</v>
       </c>
@@ -15479,10 +15510,10 @@
       <c r="O130" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P130" s="83"/>
-      <c r="Q130" s="83"/>
-    </row>
-    <row r="131" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P130" s="86"/>
+      <c r="Q130" s="86"/>
+    </row>
+    <row r="131" spans="1:17" ht="43.15" customHeight="1">
       <c r="A131" s="43" t="s">
         <v>880</v>
       </c>
@@ -15533,7 +15564,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" ht="72" customHeight="1">
       <c r="A132" s="43" t="s">
         <v>881</v>
       </c>
@@ -15584,7 +15615,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" ht="115.15" customHeight="1">
       <c r="A133" s="43" t="s">
         <v>882</v>
       </c>
@@ -15635,7 +15666,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" ht="129.6" customHeight="1">
       <c r="A134" s="43" t="s">
         <v>883</v>
       </c>
@@ -15668,7 +15699,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" ht="129.6" customHeight="1">
       <c r="A135" s="43" t="s">
         <v>38</v>
       </c>
@@ -15701,7 +15732,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="136" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" ht="144" customHeight="1">
       <c r="A136" s="43" t="s">
         <v>884</v>
       </c>
@@ -15734,7 +15765,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="137" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" ht="43.15" customHeight="1">
       <c r="A137" s="46" t="s">
         <v>885</v>
       </c>
@@ -15777,7 +15808,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="138" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" ht="30">
       <c r="A138" s="43" t="s">
         <v>886</v>
       </c>
@@ -15828,7 +15859,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="139" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" ht="57.6" customHeight="1">
       <c r="A139" s="43" t="s">
         <v>887</v>
       </c>
@@ -15861,7 +15892,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" ht="86.45" customHeight="1">
       <c r="A140" s="43" t="s">
         <v>888</v>
       </c>
@@ -15894,7 +15925,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" ht="57.6" customHeight="1">
       <c r="A141" s="46" t="s">
         <v>889</v>
       </c>
@@ -15937,7 +15968,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="142" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" ht="57.6" customHeight="1">
       <c r="A142" s="43" t="s">
         <v>890</v>
       </c>
@@ -15970,7 +16001,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="143" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" ht="72" customHeight="1">
       <c r="A143" s="43" t="s">
         <v>891</v>
       </c>
@@ -16003,7 +16034,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="144" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" ht="43.15" customHeight="1">
       <c r="A144" s="46" t="s">
         <v>892</v>
       </c>
@@ -16046,7 +16077,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="145" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" ht="72" customHeight="1">
       <c r="A145" s="43" t="s">
         <v>893</v>
       </c>
@@ -16079,7 +16110,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" ht="100.9" customHeight="1">
       <c r="A146" s="43" t="s">
         <v>894</v>
       </c>
@@ -16112,7 +16143,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" ht="43.15" customHeight="1">
       <c r="A147" s="46" t="s">
         <v>895</v>
       </c>
@@ -16155,7 +16186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" ht="28.9" customHeight="1">
       <c r="A148" s="43" t="s">
         <v>896</v>
       </c>
@@ -16206,7 +16237,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="149" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" ht="57.6" customHeight="1">
       <c r="A149" s="43" t="s">
         <v>897</v>
       </c>
@@ -16239,7 +16270,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" ht="28.9" customHeight="1">
       <c r="A150" s="43" t="s">
         <v>898</v>
       </c>
@@ -16272,7 +16303,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" ht="43.15" customHeight="1">
       <c r="A151" s="46" t="s">
         <v>899</v>
       </c>
@@ -16315,7 +16346,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" ht="43.15" customHeight="1">
       <c r="A152" s="43" t="s">
         <v>900</v>
       </c>
@@ -16366,7 +16397,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="153" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" ht="28.9" customHeight="1">
       <c r="A153" s="43" t="s">
         <v>750</v>
       </c>
@@ -16417,7 +16448,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" ht="28.9" customHeight="1">
       <c r="A154" s="43" t="s">
         <v>901</v>
       </c>
@@ -16468,7 +16499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" ht="28.9" customHeight="1">
       <c r="A155" s="43" t="s">
         <v>706</v>
       </c>
@@ -16501,7 +16532,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" ht="28.9" customHeight="1">
       <c r="A156" s="43" t="s">
         <v>712</v>
       </c>
@@ -16534,7 +16565,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" ht="28.9" customHeight="1">
       <c r="A157" s="43" t="s">
         <v>902</v>
       </c>
@@ -16567,7 +16598,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" ht="57.6" customHeight="1">
       <c r="A158" s="46" t="s">
         <v>903</v>
       </c>
@@ -16610,81 +16641,81 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A159" s="85" t="s">
+    <row r="159" spans="1:17">
+      <c r="A159" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="B159" s="83"/>
-      <c r="C159" s="83"/>
-      <c r="D159" s="83"/>
-      <c r="E159" s="83"/>
-      <c r="F159" s="83"/>
-      <c r="G159" s="83"/>
-      <c r="H159" s="83"/>
-      <c r="I159" s="83"/>
-      <c r="J159" s="83"/>
-      <c r="K159" s="83"/>
-      <c r="L159" s="83"/>
-      <c r="M159" s="83"/>
-      <c r="N159" s="83"/>
-      <c r="O159" s="83"/>
-      <c r="P159" s="83"/>
-      <c r="Q159" s="83"/>
-    </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A160" s="83"/>
-      <c r="B160" s="83"/>
-      <c r="C160" s="83"/>
-      <c r="D160" s="83"/>
-      <c r="E160" s="83"/>
-      <c r="F160" s="83"/>
-      <c r="G160" s="83"/>
-      <c r="H160" s="83"/>
-      <c r="I160" s="83"/>
-      <c r="J160" s="83"/>
-      <c r="K160" s="83"/>
-      <c r="L160" s="83"/>
-      <c r="M160" s="83"/>
-      <c r="N160" s="83"/>
-      <c r="O160" s="83"/>
-      <c r="P160" s="83"/>
-      <c r="Q160" s="83"/>
-    </row>
-    <row r="161" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="84" t="s">
+      <c r="B159" s="86"/>
+      <c r="C159" s="86"/>
+      <c r="D159" s="86"/>
+      <c r="E159" s="86"/>
+      <c r="F159" s="86"/>
+      <c r="G159" s="86"/>
+      <c r="H159" s="86"/>
+      <c r="I159" s="86"/>
+      <c r="J159" s="86"/>
+      <c r="K159" s="86"/>
+      <c r="L159" s="86"/>
+      <c r="M159" s="86"/>
+      <c r="N159" s="86"/>
+      <c r="O159" s="86"/>
+      <c r="P159" s="86"/>
+      <c r="Q159" s="86"/>
+    </row>
+    <row r="160" spans="1:17">
+      <c r="A160" s="86"/>
+      <c r="B160" s="86"/>
+      <c r="C160" s="86"/>
+      <c r="D160" s="86"/>
+      <c r="E160" s="86"/>
+      <c r="F160" s="86"/>
+      <c r="G160" s="86"/>
+      <c r="H160" s="86"/>
+      <c r="I160" s="86"/>
+      <c r="J160" s="86"/>
+      <c r="K160" s="86"/>
+      <c r="L160" s="86"/>
+      <c r="M160" s="86"/>
+      <c r="N160" s="86"/>
+      <c r="O160" s="86"/>
+      <c r="P160" s="86"/>
+      <c r="Q160" s="86"/>
+    </row>
+    <row r="161" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A161" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B161" s="82" t="s">
+      <c r="B161" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C161" s="83"/>
-      <c r="D161" s="83"/>
-      <c r="E161" s="82" t="s">
+      <c r="C161" s="86"/>
+      <c r="D161" s="86"/>
+      <c r="E161" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F161" s="83"/>
-      <c r="G161" s="83"/>
-      <c r="H161" s="82" t="s">
+      <c r="F161" s="86"/>
+      <c r="G161" s="86"/>
+      <c r="H161" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I161" s="83"/>
-      <c r="J161" s="83"/>
-      <c r="K161" s="82" t="s">
+      <c r="I161" s="86"/>
+      <c r="J161" s="86"/>
+      <c r="K161" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L161" s="83"/>
-      <c r="M161" s="83"/>
-      <c r="N161" s="83"/>
-      <c r="O161" s="83"/>
-      <c r="P161" s="82" t="s">
+      <c r="L161" s="86"/>
+      <c r="M161" s="86"/>
+      <c r="N161" s="86"/>
+      <c r="O161" s="86"/>
+      <c r="P161" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q161" s="82" t="s">
+      <c r="Q161" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A162" s="83"/>
+    <row r="162" spans="1:17">
+      <c r="A162" s="86"/>
       <c r="B162" s="43" t="s">
         <v>27</v>
       </c>
@@ -16727,10 +16758,10 @@
       <c r="O162" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P162" s="83"/>
-      <c r="Q162" s="83"/>
-    </row>
-    <row r="163" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P162" s="86"/>
+      <c r="Q162" s="86"/>
+    </row>
+    <row r="163" spans="1:17" ht="28.9" customHeight="1">
       <c r="A163" s="43" t="s">
         <v>46</v>
       </c>
@@ -16781,81 +16812,81 @@
         <v>13</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A164" s="85" t="s">
+    <row r="164" spans="1:17">
+      <c r="A164" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="B164" s="83"/>
-      <c r="C164" s="83"/>
-      <c r="D164" s="83"/>
-      <c r="E164" s="83"/>
-      <c r="F164" s="83"/>
-      <c r="G164" s="83"/>
-      <c r="H164" s="83"/>
-      <c r="I164" s="83"/>
-      <c r="J164" s="83"/>
-      <c r="K164" s="83"/>
-      <c r="L164" s="83"/>
-      <c r="M164" s="83"/>
-      <c r="N164" s="83"/>
-      <c r="O164" s="83"/>
-      <c r="P164" s="83"/>
-      <c r="Q164" s="83"/>
-    </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A165" s="83"/>
-      <c r="B165" s="83"/>
-      <c r="C165" s="83"/>
-      <c r="D165" s="83"/>
-      <c r="E165" s="83"/>
-      <c r="F165" s="83"/>
-      <c r="G165" s="83"/>
-      <c r="H165" s="83"/>
-      <c r="I165" s="83"/>
-      <c r="J165" s="83"/>
-      <c r="K165" s="83"/>
-      <c r="L165" s="83"/>
-      <c r="M165" s="83"/>
-      <c r="N165" s="83"/>
-      <c r="O165" s="83"/>
-      <c r="P165" s="83"/>
-      <c r="Q165" s="83"/>
-    </row>
-    <row r="166" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="84" t="s">
+      <c r="B164" s="86"/>
+      <c r="C164" s="86"/>
+      <c r="D164" s="86"/>
+      <c r="E164" s="86"/>
+      <c r="F164" s="86"/>
+      <c r="G164" s="86"/>
+      <c r="H164" s="86"/>
+      <c r="I164" s="86"/>
+      <c r="J164" s="86"/>
+      <c r="K164" s="86"/>
+      <c r="L164" s="86"/>
+      <c r="M164" s="86"/>
+      <c r="N164" s="86"/>
+      <c r="O164" s="86"/>
+      <c r="P164" s="86"/>
+      <c r="Q164" s="86"/>
+    </row>
+    <row r="165" spans="1:17">
+      <c r="A165" s="86"/>
+      <c r="B165" s="86"/>
+      <c r="C165" s="86"/>
+      <c r="D165" s="86"/>
+      <c r="E165" s="86"/>
+      <c r="F165" s="86"/>
+      <c r="G165" s="86"/>
+      <c r="H165" s="86"/>
+      <c r="I165" s="86"/>
+      <c r="J165" s="86"/>
+      <c r="K165" s="86"/>
+      <c r="L165" s="86"/>
+      <c r="M165" s="86"/>
+      <c r="N165" s="86"/>
+      <c r="O165" s="86"/>
+      <c r="P165" s="86"/>
+      <c r="Q165" s="86"/>
+    </row>
+    <row r="166" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A166" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B166" s="82" t="s">
+      <c r="B166" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C166" s="83"/>
-      <c r="D166" s="83"/>
-      <c r="E166" s="82" t="s">
+      <c r="C166" s="86"/>
+      <c r="D166" s="86"/>
+      <c r="E166" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F166" s="83"/>
-      <c r="G166" s="83"/>
-      <c r="H166" s="82" t="s">
+      <c r="F166" s="86"/>
+      <c r="G166" s="86"/>
+      <c r="H166" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I166" s="83"/>
-      <c r="J166" s="83"/>
-      <c r="K166" s="82" t="s">
+      <c r="I166" s="86"/>
+      <c r="J166" s="86"/>
+      <c r="K166" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L166" s="83"/>
-      <c r="M166" s="83"/>
-      <c r="N166" s="83"/>
-      <c r="O166" s="83"/>
-      <c r="P166" s="82" t="s">
+      <c r="L166" s="86"/>
+      <c r="M166" s="86"/>
+      <c r="N166" s="86"/>
+      <c r="O166" s="86"/>
+      <c r="P166" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q166" s="82" t="s">
+      <c r="Q166" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A167" s="83"/>
+    <row r="167" spans="1:17">
+      <c r="A167" s="86"/>
       <c r="B167" s="43" t="s">
         <v>27</v>
       </c>
@@ -16898,10 +16929,10 @@
       <c r="O167" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P167" s="83"/>
-      <c r="Q167" s="83"/>
-    </row>
-    <row r="168" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P167" s="86"/>
+      <c r="Q167" s="86"/>
+    </row>
+    <row r="168" spans="1:17" ht="72" customHeight="1">
       <c r="A168" s="43" t="s">
         <v>904</v>
       </c>
@@ -16934,7 +16965,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="169" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" ht="57.6" customHeight="1">
       <c r="A169" s="43" t="s">
         <v>70</v>
       </c>
@@ -16967,7 +16998,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="170" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" ht="72" customHeight="1">
       <c r="A170" s="43" t="s">
         <v>71</v>
       </c>
@@ -17000,7 +17031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" ht="57.6" customHeight="1">
       <c r="A171" s="43" t="s">
         <v>72</v>
       </c>
@@ -17033,7 +17064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" ht="86.45" customHeight="1">
       <c r="A172" s="46" t="s">
         <v>905</v>
       </c>
@@ -17189,184 +17220,184 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Q87"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" s="40"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1">
       <c r="A2" s="41" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1">
       <c r="A3" s="41" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1">
       <c r="A4" s="41" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1">
       <c r="A5" s="41" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1">
       <c r="A6" s="41" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1">
       <c r="A7" s="41" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1">
       <c r="A8" s="41" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1">
       <c r="A9" s="41" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1">
       <c r="A10" s="41" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1">
       <c r="A11" s="41" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" ht="15.6" customHeight="1">
       <c r="A13" s="42" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1">
       <c r="A14" s="40"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1">
       <c r="A15" s="41" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1">
       <c r="A16" s="41" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17">
       <c r="A17" s="41" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17">
       <c r="A18" s="41" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17">
       <c r="A19" s="41" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17">
       <c r="A20" s="41" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17">
       <c r="A22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17">
       <c r="A23" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="85" t="s">
+    <row r="24" spans="1:17">
+      <c r="A24" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="83"/>
-      <c r="C24" s="83"/>
-      <c r="D24" s="83"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="83"/>
-      <c r="J24" s="83"/>
-      <c r="K24" s="83"/>
-      <c r="L24" s="83"/>
-      <c r="M24" s="83"/>
-      <c r="N24" s="83"/>
-      <c r="O24" s="83"/>
-      <c r="P24" s="83"/>
-      <c r="Q24" s="83"/>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="83"/>
-      <c r="B25" s="83"/>
-      <c r="C25" s="83"/>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="83"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="83"/>
-      <c r="J25" s="83"/>
-      <c r="K25" s="83"/>
-      <c r="L25" s="83"/>
-      <c r="M25" s="83"/>
-      <c r="N25" s="83"/>
-      <c r="O25" s="83"/>
-      <c r="P25" s="83"/>
-      <c r="Q25" s="83"/>
-    </row>
-    <row r="26" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="84" t="s">
+      <c r="B24" s="86"/>
+      <c r="C24" s="86"/>
+      <c r="D24" s="86"/>
+      <c r="E24" s="86"/>
+      <c r="F24" s="86"/>
+      <c r="G24" s="86"/>
+      <c r="H24" s="86"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="86"/>
+      <c r="K24" s="86"/>
+      <c r="L24" s="86"/>
+      <c r="M24" s="86"/>
+      <c r="N24" s="86"/>
+      <c r="O24" s="86"/>
+      <c r="P24" s="86"/>
+      <c r="Q24" s="86"/>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" s="86"/>
+      <c r="B25" s="86"/>
+      <c r="C25" s="86"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="86"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="K25" s="86"/>
+      <c r="L25" s="86"/>
+      <c r="M25" s="86"/>
+      <c r="N25" s="86"/>
+      <c r="O25" s="86"/>
+      <c r="P25" s="86"/>
+      <c r="Q25" s="86"/>
+    </row>
+    <row r="26" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A26" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="82" t="s">
+      <c r="B26" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="83"/>
-      <c r="D26" s="83"/>
-      <c r="E26" s="82" t="s">
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="83"/>
-      <c r="G26" s="83"/>
-      <c r="H26" s="82" t="s">
+      <c r="F26" s="86"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I26" s="83"/>
-      <c r="J26" s="83"/>
-      <c r="K26" s="82" t="s">
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L26" s="83"/>
-      <c r="M26" s="83"/>
-      <c r="N26" s="83"/>
-      <c r="O26" s="83"/>
-      <c r="P26" s="82" t="s">
+      <c r="L26" s="86"/>
+      <c r="M26" s="86"/>
+      <c r="N26" s="86"/>
+      <c r="O26" s="86"/>
+      <c r="P26" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q26" s="82" t="s">
+      <c r="Q26" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="83"/>
+    <row r="27" spans="1:17">
+      <c r="A27" s="86"/>
       <c r="B27" s="43" t="s">
         <v>27</v>
       </c>
@@ -17409,10 +17440,10 @@
       <c r="O27" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P27" s="83"/>
-      <c r="Q27" s="83"/>
-    </row>
-    <row r="28" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P27" s="86"/>
+      <c r="Q27" s="86"/>
+    </row>
+    <row r="28" spans="1:17" ht="115.15" customHeight="1">
       <c r="A28" s="43" t="s">
         <v>31</v>
       </c>
@@ -17445,7 +17476,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" ht="144" customHeight="1">
       <c r="A29" s="43" t="s">
         <v>32</v>
       </c>
@@ -17478,7 +17509,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" ht="129.6" customHeight="1">
       <c r="A30" s="43" t="s">
         <v>33</v>
       </c>
@@ -17511,7 +17542,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" ht="28.9" customHeight="1">
       <c r="A31" s="43" t="s">
         <v>34</v>
       </c>
@@ -17544,7 +17575,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" ht="144" customHeight="1">
       <c r="A32" s="43" t="s">
         <v>35</v>
       </c>
@@ -17577,7 +17608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" ht="100.9" customHeight="1">
       <c r="A33" s="43" t="s">
         <v>36</v>
       </c>
@@ -17610,7 +17641,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" ht="43.15" customHeight="1">
       <c r="A34" s="43" t="s">
         <v>37</v>
       </c>
@@ -17643,7 +17674,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" ht="129.6" customHeight="1">
       <c r="A35" s="43" t="s">
         <v>38</v>
       </c>
@@ -17676,7 +17707,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" ht="28.9" customHeight="1">
       <c r="A36" s="43" t="s">
         <v>39</v>
       </c>
@@ -17709,7 +17740,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" ht="43.15" customHeight="1">
       <c r="A37" s="43" t="s">
         <v>40</v>
       </c>
@@ -17742,7 +17773,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" ht="100.9" customHeight="1">
       <c r="A38" s="43" t="s">
         <v>41</v>
       </c>
@@ -17775,7 +17806,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" ht="72" customHeight="1">
       <c r="A39" s="43" t="s">
         <v>42</v>
       </c>
@@ -17808,7 +17839,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" ht="72" customHeight="1">
       <c r="A40" s="43" t="s">
         <v>43</v>
       </c>
@@ -17841,7 +17872,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" ht="115.15" customHeight="1">
       <c r="A41" s="43" t="s">
         <v>44</v>
       </c>
@@ -17874,7 +17905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" ht="28.9" customHeight="1">
       <c r="A42" s="46" t="s">
         <v>45</v>
       </c>
@@ -17917,81 +17948,81 @@
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="85" t="s">
+    <row r="43" spans="1:17">
+      <c r="A43" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="83"/>
-      <c r="C43" s="83"/>
-      <c r="D43" s="83"/>
-      <c r="E43" s="83"/>
-      <c r="F43" s="83"/>
-      <c r="G43" s="83"/>
-      <c r="H43" s="83"/>
-      <c r="I43" s="83"/>
-      <c r="J43" s="83"/>
-      <c r="K43" s="83"/>
-      <c r="L43" s="83"/>
-      <c r="M43" s="83"/>
-      <c r="N43" s="83"/>
-      <c r="O43" s="83"/>
-      <c r="P43" s="83"/>
-      <c r="Q43" s="83"/>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="83"/>
-      <c r="B44" s="83"/>
-      <c r="C44" s="83"/>
-      <c r="D44" s="83"/>
-      <c r="E44" s="83"/>
-      <c r="F44" s="83"/>
-      <c r="G44" s="83"/>
-      <c r="H44" s="83"/>
-      <c r="I44" s="83"/>
-      <c r="J44" s="83"/>
-      <c r="K44" s="83"/>
-      <c r="L44" s="83"/>
-      <c r="M44" s="83"/>
-      <c r="N44" s="83"/>
-      <c r="O44" s="83"/>
-      <c r="P44" s="83"/>
-      <c r="Q44" s="83"/>
-    </row>
-    <row r="45" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="84" t="s">
+      <c r="B43" s="86"/>
+      <c r="C43" s="86"/>
+      <c r="D43" s="86"/>
+      <c r="E43" s="86"/>
+      <c r="F43" s="86"/>
+      <c r="G43" s="86"/>
+      <c r="H43" s="86"/>
+      <c r="I43" s="86"/>
+      <c r="J43" s="86"/>
+      <c r="K43" s="86"/>
+      <c r="L43" s="86"/>
+      <c r="M43" s="86"/>
+      <c r="N43" s="86"/>
+      <c r="O43" s="86"/>
+      <c r="P43" s="86"/>
+      <c r="Q43" s="86"/>
+    </row>
+    <row r="44" spans="1:17">
+      <c r="A44" s="86"/>
+      <c r="B44" s="86"/>
+      <c r="C44" s="86"/>
+      <c r="D44" s="86"/>
+      <c r="E44" s="86"/>
+      <c r="F44" s="86"/>
+      <c r="G44" s="86"/>
+      <c r="H44" s="86"/>
+      <c r="I44" s="86"/>
+      <c r="J44" s="86"/>
+      <c r="K44" s="86"/>
+      <c r="L44" s="86"/>
+      <c r="M44" s="86"/>
+      <c r="N44" s="86"/>
+      <c r="O44" s="86"/>
+      <c r="P44" s="86"/>
+      <c r="Q44" s="86"/>
+    </row>
+    <row r="45" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A45" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="82" t="s">
+      <c r="B45" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="83"/>
-      <c r="D45" s="83"/>
-      <c r="E45" s="82" t="s">
+      <c r="C45" s="86"/>
+      <c r="D45" s="86"/>
+      <c r="E45" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F45" s="83"/>
-      <c r="G45" s="83"/>
-      <c r="H45" s="82" t="s">
+      <c r="F45" s="86"/>
+      <c r="G45" s="86"/>
+      <c r="H45" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I45" s="83"/>
-      <c r="J45" s="83"/>
-      <c r="K45" s="82" t="s">
+      <c r="I45" s="86"/>
+      <c r="J45" s="86"/>
+      <c r="K45" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="83"/>
-      <c r="M45" s="83"/>
-      <c r="N45" s="83"/>
-      <c r="O45" s="83"/>
-      <c r="P45" s="82" t="s">
+      <c r="L45" s="86"/>
+      <c r="M45" s="86"/>
+      <c r="N45" s="86"/>
+      <c r="O45" s="86"/>
+      <c r="P45" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q45" s="82" t="s">
+      <c r="Q45" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" s="83"/>
+    <row r="46" spans="1:17">
+      <c r="A46" s="86"/>
       <c r="B46" s="43" t="s">
         <v>27</v>
       </c>
@@ -18034,10 +18065,10 @@
       <c r="O46" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P46" s="83"/>
-      <c r="Q46" s="83"/>
-    </row>
-    <row r="47" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P46" s="86"/>
+      <c r="Q46" s="86"/>
+    </row>
+    <row r="47" spans="1:17" ht="28.9" customHeight="1">
       <c r="A47" s="43" t="s">
         <v>46</v>
       </c>
@@ -18088,81 +18119,81 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="85" t="s">
+    <row r="48" spans="1:17">
+      <c r="A48" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="83"/>
-      <c r="C48" s="83"/>
-      <c r="D48" s="83"/>
-      <c r="E48" s="83"/>
-      <c r="F48" s="83"/>
-      <c r="G48" s="83"/>
-      <c r="H48" s="83"/>
-      <c r="I48" s="83"/>
-      <c r="J48" s="83"/>
-      <c r="K48" s="83"/>
-      <c r="L48" s="83"/>
-      <c r="M48" s="83"/>
-      <c r="N48" s="83"/>
-      <c r="O48" s="83"/>
-      <c r="P48" s="83"/>
-      <c r="Q48" s="83"/>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="83"/>
-      <c r="B49" s="83"/>
-      <c r="C49" s="83"/>
-      <c r="D49" s="83"/>
-      <c r="E49" s="83"/>
-      <c r="F49" s="83"/>
-      <c r="G49" s="83"/>
-      <c r="H49" s="83"/>
-      <c r="I49" s="83"/>
-      <c r="J49" s="83"/>
-      <c r="K49" s="83"/>
-      <c r="L49" s="83"/>
-      <c r="M49" s="83"/>
-      <c r="N49" s="83"/>
-      <c r="O49" s="83"/>
-      <c r="P49" s="83"/>
-      <c r="Q49" s="83"/>
-    </row>
-    <row r="50" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="84" t="s">
+      <c r="B48" s="86"/>
+      <c r="C48" s="86"/>
+      <c r="D48" s="86"/>
+      <c r="E48" s="86"/>
+      <c r="F48" s="86"/>
+      <c r="G48" s="86"/>
+      <c r="H48" s="86"/>
+      <c r="I48" s="86"/>
+      <c r="J48" s="86"/>
+      <c r="K48" s="86"/>
+      <c r="L48" s="86"/>
+      <c r="M48" s="86"/>
+      <c r="N48" s="86"/>
+      <c r="O48" s="86"/>
+      <c r="P48" s="86"/>
+      <c r="Q48" s="86"/>
+    </row>
+    <row r="49" spans="1:17">
+      <c r="A49" s="86"/>
+      <c r="B49" s="86"/>
+      <c r="C49" s="86"/>
+      <c r="D49" s="86"/>
+      <c r="E49" s="86"/>
+      <c r="F49" s="86"/>
+      <c r="G49" s="86"/>
+      <c r="H49" s="86"/>
+      <c r="I49" s="86"/>
+      <c r="J49" s="86"/>
+      <c r="K49" s="86"/>
+      <c r="L49" s="86"/>
+      <c r="M49" s="86"/>
+      <c r="N49" s="86"/>
+      <c r="O49" s="86"/>
+      <c r="P49" s="86"/>
+      <c r="Q49" s="86"/>
+    </row>
+    <row r="50" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A50" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B50" s="82" t="s">
+      <c r="B50" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C50" s="83"/>
-      <c r="D50" s="83"/>
-      <c r="E50" s="82" t="s">
+      <c r="C50" s="86"/>
+      <c r="D50" s="86"/>
+      <c r="E50" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F50" s="83"/>
-      <c r="G50" s="83"/>
-      <c r="H50" s="82" t="s">
+      <c r="F50" s="86"/>
+      <c r="G50" s="86"/>
+      <c r="H50" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I50" s="83"/>
-      <c r="J50" s="83"/>
-      <c r="K50" s="82" t="s">
+      <c r="I50" s="86"/>
+      <c r="J50" s="86"/>
+      <c r="K50" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="83"/>
-      <c r="M50" s="83"/>
-      <c r="N50" s="83"/>
-      <c r="O50" s="83"/>
-      <c r="P50" s="82" t="s">
+      <c r="L50" s="86"/>
+      <c r="M50" s="86"/>
+      <c r="N50" s="86"/>
+      <c r="O50" s="86"/>
+      <c r="P50" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q50" s="82" t="s">
+      <c r="Q50" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51" s="83"/>
+    <row r="51" spans="1:17">
+      <c r="A51" s="86"/>
       <c r="B51" s="43" t="s">
         <v>27</v>
       </c>
@@ -18205,10 +18236,10 @@
       <c r="O51" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P51" s="83"/>
-      <c r="Q51" s="83"/>
-    </row>
-    <row r="52" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P51" s="86"/>
+      <c r="Q51" s="86"/>
+    </row>
+    <row r="52" spans="1:17" ht="57.6" customHeight="1">
       <c r="A52" s="43" t="s">
         <v>48</v>
       </c>
@@ -18241,7 +18272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" ht="57.6" customHeight="1">
       <c r="A53" s="43" t="s">
         <v>49</v>
       </c>
@@ -18274,7 +18305,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" ht="72" customHeight="1">
       <c r="A54" s="43" t="s">
         <v>50</v>
       </c>
@@ -18307,7 +18338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" ht="43.15" customHeight="1">
       <c r="A55" s="43" t="s">
         <v>51</v>
       </c>
@@ -18340,7 +18371,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" ht="28.9" customHeight="1">
       <c r="A56" s="46" t="s">
         <v>52</v>
       </c>
@@ -18383,81 +18414,81 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57" s="85" t="s">
+    <row r="57" spans="1:17">
+      <c r="A57" s="88" t="s">
         <v>53</v>
       </c>
-      <c r="B57" s="83"/>
-      <c r="C57" s="83"/>
-      <c r="D57" s="83"/>
-      <c r="E57" s="83"/>
-      <c r="F57" s="83"/>
-      <c r="G57" s="83"/>
-      <c r="H57" s="83"/>
-      <c r="I57" s="83"/>
-      <c r="J57" s="83"/>
-      <c r="K57" s="83"/>
-      <c r="L57" s="83"/>
-      <c r="M57" s="83"/>
-      <c r="N57" s="83"/>
-      <c r="O57" s="83"/>
-      <c r="P57" s="83"/>
-      <c r="Q57" s="83"/>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A58" s="83"/>
-      <c r="B58" s="83"/>
-      <c r="C58" s="83"/>
-      <c r="D58" s="83"/>
-      <c r="E58" s="83"/>
-      <c r="F58" s="83"/>
-      <c r="G58" s="83"/>
-      <c r="H58" s="83"/>
-      <c r="I58" s="83"/>
-      <c r="J58" s="83"/>
-      <c r="K58" s="83"/>
-      <c r="L58" s="83"/>
-      <c r="M58" s="83"/>
-      <c r="N58" s="83"/>
-      <c r="O58" s="83"/>
-      <c r="P58" s="83"/>
-      <c r="Q58" s="83"/>
-    </row>
-    <row r="59" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="84" t="s">
+      <c r="B57" s="86"/>
+      <c r="C57" s="86"/>
+      <c r="D57" s="86"/>
+      <c r="E57" s="86"/>
+      <c r="F57" s="86"/>
+      <c r="G57" s="86"/>
+      <c r="H57" s="86"/>
+      <c r="I57" s="86"/>
+      <c r="J57" s="86"/>
+      <c r="K57" s="86"/>
+      <c r="L57" s="86"/>
+      <c r="M57" s="86"/>
+      <c r="N57" s="86"/>
+      <c r="O57" s="86"/>
+      <c r="P57" s="86"/>
+      <c r="Q57" s="86"/>
+    </row>
+    <row r="58" spans="1:17">
+      <c r="A58" s="86"/>
+      <c r="B58" s="86"/>
+      <c r="C58" s="86"/>
+      <c r="D58" s="86"/>
+      <c r="E58" s="86"/>
+      <c r="F58" s="86"/>
+      <c r="G58" s="86"/>
+      <c r="H58" s="86"/>
+      <c r="I58" s="86"/>
+      <c r="J58" s="86"/>
+      <c r="K58" s="86"/>
+      <c r="L58" s="86"/>
+      <c r="M58" s="86"/>
+      <c r="N58" s="86"/>
+      <c r="O58" s="86"/>
+      <c r="P58" s="86"/>
+      <c r="Q58" s="86"/>
+    </row>
+    <row r="59" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A59" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B59" s="82" t="s">
+      <c r="B59" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C59" s="83"/>
-      <c r="D59" s="83"/>
-      <c r="E59" s="82" t="s">
+      <c r="C59" s="86"/>
+      <c r="D59" s="86"/>
+      <c r="E59" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F59" s="83"/>
-      <c r="G59" s="83"/>
-      <c r="H59" s="82" t="s">
+      <c r="F59" s="86"/>
+      <c r="G59" s="86"/>
+      <c r="H59" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I59" s="83"/>
-      <c r="J59" s="83"/>
-      <c r="K59" s="82" t="s">
+      <c r="I59" s="86"/>
+      <c r="J59" s="86"/>
+      <c r="K59" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L59" s="83"/>
-      <c r="M59" s="83"/>
-      <c r="N59" s="83"/>
-      <c r="O59" s="83"/>
-      <c r="P59" s="82" t="s">
+      <c r="L59" s="86"/>
+      <c r="M59" s="86"/>
+      <c r="N59" s="86"/>
+      <c r="O59" s="86"/>
+      <c r="P59" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q59" s="82" t="s">
+      <c r="Q59" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A60" s="83"/>
+    <row r="60" spans="1:17">
+      <c r="A60" s="86"/>
       <c r="B60" s="43" t="s">
         <v>27</v>
       </c>
@@ -18500,10 +18531,10 @@
       <c r="O60" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P60" s="83"/>
-      <c r="Q60" s="83"/>
-    </row>
-    <row r="61" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P60" s="86"/>
+      <c r="Q60" s="86"/>
+    </row>
+    <row r="61" spans="1:17" ht="57.6" customHeight="1">
       <c r="A61" s="43" t="s">
         <v>54</v>
       </c>
@@ -18536,7 +18567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" ht="72" customHeight="1">
       <c r="A62" s="43" t="s">
         <v>55</v>
       </c>
@@ -18569,7 +18600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" ht="28.9" customHeight="1">
       <c r="A63" s="43" t="s">
         <v>56</v>
       </c>
@@ -18602,7 +18633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" ht="115.15" customHeight="1">
       <c r="A64" s="43" t="s">
         <v>57</v>
       </c>
@@ -18635,7 +18666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" ht="43.15" customHeight="1">
       <c r="A65" s="43" t="s">
         <v>58</v>
       </c>
@@ -18668,7 +18699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" ht="57.6" customHeight="1">
       <c r="A66" s="43" t="s">
         <v>59</v>
       </c>
@@ -18701,7 +18732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" ht="72" customHeight="1">
       <c r="A67" s="43" t="s">
         <v>60</v>
       </c>
@@ -18734,7 +18765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" ht="57.6" customHeight="1">
       <c r="A68" s="43" t="s">
         <v>61</v>
       </c>
@@ -18767,7 +18798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" ht="57.6" customHeight="1">
       <c r="A69" s="43" t="s">
         <v>62</v>
       </c>
@@ -18800,7 +18831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" ht="86.45" customHeight="1">
       <c r="A70" s="43" t="s">
         <v>63</v>
       </c>
@@ -18833,7 +18864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="57.6" customHeight="1">
       <c r="A71" s="43" t="s">
         <v>64</v>
       </c>
@@ -18866,7 +18897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" ht="72" customHeight="1">
       <c r="A72" s="43" t="s">
         <v>65</v>
       </c>
@@ -18899,7 +18930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" ht="57.6" customHeight="1">
       <c r="A73" s="43" t="s">
         <v>66</v>
       </c>
@@ -18932,7 +18963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" ht="43.15" customHeight="1">
       <c r="A74" s="46" t="s">
         <v>53</v>
       </c>
@@ -18975,81 +19006,81 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75" s="85" t="s">
+    <row r="75" spans="1:17">
+      <c r="A75" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="B75" s="83"/>
-      <c r="C75" s="83"/>
-      <c r="D75" s="83"/>
-      <c r="E75" s="83"/>
-      <c r="F75" s="83"/>
-      <c r="G75" s="83"/>
-      <c r="H75" s="83"/>
-      <c r="I75" s="83"/>
-      <c r="J75" s="83"/>
-      <c r="K75" s="83"/>
-      <c r="L75" s="83"/>
-      <c r="M75" s="83"/>
-      <c r="N75" s="83"/>
-      <c r="O75" s="83"/>
-      <c r="P75" s="83"/>
-      <c r="Q75" s="83"/>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A76" s="83"/>
-      <c r="B76" s="83"/>
-      <c r="C76" s="83"/>
-      <c r="D76" s="83"/>
-      <c r="E76" s="83"/>
-      <c r="F76" s="83"/>
-      <c r="G76" s="83"/>
-      <c r="H76" s="83"/>
-      <c r="I76" s="83"/>
-      <c r="J76" s="83"/>
-      <c r="K76" s="83"/>
-      <c r="L76" s="83"/>
-      <c r="M76" s="83"/>
-      <c r="N76" s="83"/>
-      <c r="O76" s="83"/>
-      <c r="P76" s="83"/>
-      <c r="Q76" s="83"/>
-    </row>
-    <row r="77" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="84" t="s">
+      <c r="B75" s="86"/>
+      <c r="C75" s="86"/>
+      <c r="D75" s="86"/>
+      <c r="E75" s="86"/>
+      <c r="F75" s="86"/>
+      <c r="G75" s="86"/>
+      <c r="H75" s="86"/>
+      <c r="I75" s="86"/>
+      <c r="J75" s="86"/>
+      <c r="K75" s="86"/>
+      <c r="L75" s="86"/>
+      <c r="M75" s="86"/>
+      <c r="N75" s="86"/>
+      <c r="O75" s="86"/>
+      <c r="P75" s="86"/>
+      <c r="Q75" s="86"/>
+    </row>
+    <row r="76" spans="1:17">
+      <c r="A76" s="86"/>
+      <c r="B76" s="86"/>
+      <c r="C76" s="86"/>
+      <c r="D76" s="86"/>
+      <c r="E76" s="86"/>
+      <c r="F76" s="86"/>
+      <c r="G76" s="86"/>
+      <c r="H76" s="86"/>
+      <c r="I76" s="86"/>
+      <c r="J76" s="86"/>
+      <c r="K76" s="86"/>
+      <c r="L76" s="86"/>
+      <c r="M76" s="86"/>
+      <c r="N76" s="86"/>
+      <c r="O76" s="86"/>
+      <c r="P76" s="86"/>
+      <c r="Q76" s="86"/>
+    </row>
+    <row r="77" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A77" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B77" s="82" t="s">
+      <c r="B77" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C77" s="83"/>
-      <c r="D77" s="83"/>
-      <c r="E77" s="82" t="s">
+      <c r="C77" s="86"/>
+      <c r="D77" s="86"/>
+      <c r="E77" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F77" s="83"/>
-      <c r="G77" s="83"/>
-      <c r="H77" s="82" t="s">
+      <c r="F77" s="86"/>
+      <c r="G77" s="86"/>
+      <c r="H77" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I77" s="83"/>
-      <c r="J77" s="83"/>
-      <c r="K77" s="82" t="s">
+      <c r="I77" s="86"/>
+      <c r="J77" s="86"/>
+      <c r="K77" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L77" s="83"/>
-      <c r="M77" s="83"/>
-      <c r="N77" s="83"/>
-      <c r="O77" s="83"/>
-      <c r="P77" s="82" t="s">
+      <c r="L77" s="86"/>
+      <c r="M77" s="86"/>
+      <c r="N77" s="86"/>
+      <c r="O77" s="86"/>
+      <c r="P77" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q77" s="82" t="s">
+      <c r="Q77" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A78" s="83"/>
+    <row r="78" spans="1:17">
+      <c r="A78" s="86"/>
       <c r="B78" s="43" t="s">
         <v>27</v>
       </c>
@@ -19092,10 +19123,10 @@
       <c r="O78" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P78" s="83"/>
-      <c r="Q78" s="83"/>
-    </row>
-    <row r="79" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P78" s="86"/>
+      <c r="Q78" s="86"/>
+    </row>
+    <row r="79" spans="1:17" ht="28.9" customHeight="1">
       <c r="A79" s="43" t="s">
         <v>68</v>
       </c>
@@ -19146,81 +19177,81 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A80" s="85" t="s">
+    <row r="80" spans="1:17">
+      <c r="A80" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="B80" s="83"/>
-      <c r="C80" s="83"/>
-      <c r="D80" s="83"/>
-      <c r="E80" s="83"/>
-      <c r="F80" s="83"/>
-      <c r="G80" s="83"/>
-      <c r="H80" s="83"/>
-      <c r="I80" s="83"/>
-      <c r="J80" s="83"/>
-      <c r="K80" s="83"/>
-      <c r="L80" s="83"/>
-      <c r="M80" s="83"/>
-      <c r="N80" s="83"/>
-      <c r="O80" s="83"/>
-      <c r="P80" s="83"/>
-      <c r="Q80" s="83"/>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A81" s="83"/>
-      <c r="B81" s="83"/>
-      <c r="C81" s="83"/>
-      <c r="D81" s="83"/>
-      <c r="E81" s="83"/>
-      <c r="F81" s="83"/>
-      <c r="G81" s="83"/>
-      <c r="H81" s="83"/>
-      <c r="I81" s="83"/>
-      <c r="J81" s="83"/>
-      <c r="K81" s="83"/>
-      <c r="L81" s="83"/>
-      <c r="M81" s="83"/>
-      <c r="N81" s="83"/>
-      <c r="O81" s="83"/>
-      <c r="P81" s="83"/>
-      <c r="Q81" s="83"/>
-    </row>
-    <row r="82" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="84" t="s">
+      <c r="B80" s="86"/>
+      <c r="C80" s="86"/>
+      <c r="D80" s="86"/>
+      <c r="E80" s="86"/>
+      <c r="F80" s="86"/>
+      <c r="G80" s="86"/>
+      <c r="H80" s="86"/>
+      <c r="I80" s="86"/>
+      <c r="J80" s="86"/>
+      <c r="K80" s="86"/>
+      <c r="L80" s="86"/>
+      <c r="M80" s="86"/>
+      <c r="N80" s="86"/>
+      <c r="O80" s="86"/>
+      <c r="P80" s="86"/>
+      <c r="Q80" s="86"/>
+    </row>
+    <row r="81" spans="1:17">
+      <c r="A81" s="86"/>
+      <c r="B81" s="86"/>
+      <c r="C81" s="86"/>
+      <c r="D81" s="86"/>
+      <c r="E81" s="86"/>
+      <c r="F81" s="86"/>
+      <c r="G81" s="86"/>
+      <c r="H81" s="86"/>
+      <c r="I81" s="86"/>
+      <c r="J81" s="86"/>
+      <c r="K81" s="86"/>
+      <c r="L81" s="86"/>
+      <c r="M81" s="86"/>
+      <c r="N81" s="86"/>
+      <c r="O81" s="86"/>
+      <c r="P81" s="86"/>
+      <c r="Q81" s="86"/>
+    </row>
+    <row r="82" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A82" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B82" s="82" t="s">
+      <c r="B82" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C82" s="83"/>
-      <c r="D82" s="83"/>
-      <c r="E82" s="82" t="s">
+      <c r="C82" s="86"/>
+      <c r="D82" s="86"/>
+      <c r="E82" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F82" s="83"/>
-      <c r="G82" s="83"/>
-      <c r="H82" s="82" t="s">
+      <c r="F82" s="86"/>
+      <c r="G82" s="86"/>
+      <c r="H82" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I82" s="83"/>
-      <c r="J82" s="83"/>
-      <c r="K82" s="82" t="s">
+      <c r="I82" s="86"/>
+      <c r="J82" s="86"/>
+      <c r="K82" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L82" s="83"/>
-      <c r="M82" s="83"/>
-      <c r="N82" s="83"/>
-      <c r="O82" s="83"/>
-      <c r="P82" s="82" t="s">
+      <c r="L82" s="86"/>
+      <c r="M82" s="86"/>
+      <c r="N82" s="86"/>
+      <c r="O82" s="86"/>
+      <c r="P82" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q82" s="82" t="s">
+      <c r="Q82" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A83" s="83"/>
+    <row r="83" spans="1:17">
+      <c r="A83" s="86"/>
       <c r="B83" s="43" t="s">
         <v>27</v>
       </c>
@@ -19263,10 +19294,10 @@
       <c r="O83" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P83" s="83"/>
-      <c r="Q83" s="83"/>
-    </row>
-    <row r="84" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P83" s="86"/>
+      <c r="Q83" s="86"/>
+    </row>
+    <row r="84" spans="1:17" ht="57.6" customHeight="1">
       <c r="A84" s="43" t="s">
         <v>70</v>
       </c>
@@ -19299,7 +19330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" ht="72" customHeight="1">
       <c r="A85" s="43" t="s">
         <v>71</v>
       </c>
@@ -19332,7 +19363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" ht="57.6" customHeight="1">
       <c r="A86" s="43" t="s">
         <v>72</v>
       </c>
@@ -19365,7 +19396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" ht="72" customHeight="1">
       <c r="A87" s="46" t="s">
         <v>73</v>
       </c>
@@ -19485,7 +19516,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G78"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -19495,18 +19526,18 @@
     <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="87" t="s">
+    <row r="1" spans="1:7" ht="22.15" customHeight="1">
+      <c r="A1" s="90" t="s">
         <v>906</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-    </row>
-    <row r="2" spans="1:7" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+    </row>
+    <row r="2" spans="1:7" ht="37.9" customHeight="1">
       <c r="A2" s="48" t="s">
         <v>907</v>
       </c>
@@ -19529,7 +19560,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="31.9" customHeight="1">
       <c r="A3" s="55" t="s">
         <v>914</v>
       </c>
@@ -19552,7 +19583,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>126</v>
       </c>
@@ -19573,7 +19604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A5" s="49" t="s">
         <v>37</v>
       </c>
@@ -19594,7 +19625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A6" s="49" t="s">
         <v>122</v>
       </c>
@@ -19615,7 +19646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A7" s="49" t="s">
         <v>212</v>
       </c>
@@ -19636,7 +19667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A8" s="49" t="s">
         <v>700</v>
       </c>
@@ -19657,7 +19688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A9" s="49" t="s">
         <v>104</v>
       </c>
@@ -19680,7 +19711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A10" s="49" t="s">
         <v>104</v>
       </c>
@@ -19703,7 +19734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A11" s="49" t="s">
         <v>104</v>
       </c>
@@ -19726,7 +19757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A12" s="49" t="s">
         <v>99</v>
       </c>
@@ -19747,7 +19778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A13" s="49" t="s">
         <v>99</v>
       </c>
@@ -19768,7 +19799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A14" s="49" t="s">
         <v>283</v>
       </c>
@@ -19789,7 +19820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A15" s="49" t="s">
         <v>188</v>
       </c>
@@ -19810,7 +19841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A16" s="49" t="s">
         <v>112</v>
       </c>
@@ -19831,7 +19862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A17" s="49" t="s">
         <v>115</v>
       </c>
@@ -19852,7 +19883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A18" s="49" t="s">
         <v>345</v>
       </c>
@@ -19873,7 +19904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A19" s="49" t="s">
         <v>142</v>
       </c>
@@ -19894,7 +19925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A20" s="49" t="s">
         <v>258</v>
       </c>
@@ -19915,7 +19946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A21" s="49" t="s">
         <v>370</v>
       </c>
@@ -19936,7 +19967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A22" s="49" t="s">
         <v>794</v>
       </c>
@@ -19957,7 +19988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A23" s="49" t="s">
         <v>805</v>
       </c>
@@ -19978,7 +20009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A24" s="49" t="s">
         <v>810</v>
       </c>
@@ -19999,7 +20030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A25" s="49" t="s">
         <v>800</v>
       </c>
@@ -20020,7 +20051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A26" s="49" t="s">
         <v>815</v>
       </c>
@@ -20041,7 +20072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A27" s="49" t="s">
         <v>820</v>
       </c>
@@ -20062,7 +20093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A28" s="51" t="s">
         <v>126</v>
       </c>
@@ -20083,7 +20114,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A29" s="51" t="s">
         <v>283</v>
       </c>
@@ -20104,7 +20135,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A30" s="51" t="s">
         <v>188</v>
       </c>
@@ -20125,7 +20156,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A31" s="51" t="s">
         <v>104</v>
       </c>
@@ -20148,7 +20179,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A32" s="51" t="s">
         <v>104</v>
       </c>
@@ -20169,7 +20200,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A33" s="51" t="s">
         <v>37</v>
       </c>
@@ -20190,7 +20221,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A34" s="51" t="s">
         <v>232</v>
       </c>
@@ -20209,7 +20240,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A35" s="51" t="s">
         <v>122</v>
       </c>
@@ -20230,7 +20261,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A36" s="51" t="s">
         <v>212</v>
       </c>
@@ -20251,7 +20282,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A37" s="51" t="s">
         <v>99</v>
       </c>
@@ -20272,7 +20303,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A38" s="51" t="s">
         <v>99</v>
       </c>
@@ -20293,7 +20324,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A39" s="51" t="s">
         <v>115</v>
       </c>
@@ -20314,7 +20345,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A40" s="51" t="s">
         <v>112</v>
       </c>
@@ -20335,7 +20366,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A41" s="56" t="s">
         <v>345</v>
       </c>
@@ -20356,7 +20387,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A42" s="51" t="s">
         <v>142</v>
       </c>
@@ -20377,7 +20408,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A43" s="51" t="s">
         <v>258</v>
       </c>
@@ -20398,7 +20429,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A44" s="56" t="s">
         <v>370</v>
       </c>
@@ -20419,7 +20450,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A45" s="60" t="s">
         <v>745</v>
       </c>
@@ -20440,7 +20471,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A46" s="53" t="s">
         <v>232</v>
       </c>
@@ -20459,7 +20490,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A47" s="53" t="s">
         <v>88</v>
       </c>
@@ -20478,7 +20509,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A48" s="53" t="s">
         <v>88</v>
       </c>
@@ -20499,7 +20530,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A49" s="53" t="s">
         <v>88</v>
       </c>
@@ -20520,7 +20551,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A50" s="56" t="s">
         <v>740</v>
       </c>
@@ -20541,7 +20572,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A51" s="58" t="s">
         <v>750</v>
       </c>
@@ -20562,7 +20593,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A52" s="53" t="s">
         <v>706</v>
       </c>
@@ -20581,7 +20612,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A53" s="53" t="s">
         <v>712</v>
       </c>
@@ -20600,7 +20631,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A54" s="53" t="s">
         <v>718</v>
       </c>
@@ -20619,7 +20650,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A55" s="56" t="s">
         <v>136</v>
       </c>
@@ -20638,7 +20669,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A56" s="56" t="s">
         <v>136</v>
       </c>
@@ -20657,7 +20688,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A57" s="58" t="s">
         <v>340</v>
       </c>
@@ -20678,7 +20709,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A58" s="58" t="s">
         <v>340</v>
       </c>
@@ -20699,7 +20730,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A59" s="58" t="s">
         <v>169</v>
       </c>
@@ -20720,7 +20751,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A60" s="58" t="s">
         <v>91</v>
       </c>
@@ -20741,7 +20772,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A61" s="58" t="s">
         <v>91</v>
       </c>
@@ -20762,7 +20793,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A62" s="58" t="s">
         <v>194</v>
       </c>
@@ -20783,7 +20814,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A63" s="58" t="s">
         <v>194</v>
       </c>
@@ -20804,7 +20835,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A64" s="58" t="s">
         <v>145</v>
       </c>
@@ -20825,7 +20856,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A65" s="58" t="s">
         <v>145</v>
       </c>
@@ -20846,7 +20877,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A66" s="58" t="s">
         <v>85</v>
       </c>
@@ -20867,7 +20898,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A67" s="58" t="s">
         <v>322</v>
       </c>
@@ -20888,7 +20919,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A68" s="58" t="s">
         <v>322</v>
       </c>
@@ -20909,7 +20940,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A69" s="58" t="s">
         <v>267</v>
       </c>
@@ -20930,7 +20961,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A70" s="58" t="s">
         <v>267</v>
       </c>
@@ -20951,7 +20982,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A71" s="58" t="s">
         <v>429</v>
       </c>
@@ -20972,7 +21003,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A72" s="58" t="s">
         <v>459</v>
       </c>
@@ -20993,7 +21024,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A73" s="58" t="s">
         <v>730</v>
       </c>
@@ -21014,7 +21045,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A74" s="58" t="s">
         <v>735</v>
       </c>
@@ -21035,7 +21066,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A75" s="58" t="s">
         <v>197</v>
       </c>
@@ -21056,7 +21087,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A76" s="58" t="s">
         <v>197</v>
       </c>
@@ -21077,16 +21108,16 @@
         <v>928</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="86" t="s">
+    <row r="78" spans="1:7">
+      <c r="A78" s="89" t="s">
         <v>942</v>
       </c>
-      <c r="B78" s="83"/>
-      <c r="C78" s="83"/>
-      <c r="D78" s="83"/>
-      <c r="E78" s="83"/>
-      <c r="F78" s="83"/>
-      <c r="G78" s="83"/>
+      <c r="B78" s="86"/>
+      <c r="C78" s="86"/>
+      <c r="D78" s="86"/>
+      <c r="E78" s="86"/>
+      <c r="F78" s="86"/>
+      <c r="G78" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="2">
